--- a/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.463</v>
+        <v>0.214</v>
       </c>
       <c r="F2">
-        <v>0.119</v>
+        <v>-0.123</v>
       </c>
       <c r="G2">
-        <v>0.3147140105518801</v>
+        <v>0.3745134043334557</v>
       </c>
       <c r="H2">
-        <v>0.1757181140607989</v>
+        <v>0.2203207246909046</v>
       </c>
       <c r="I2">
-        <v>-0.007390503307930659</v>
+        <v>-0.2897049822499694</v>
       </c>
       <c r="J2">
-        <v>-0.007390503307930659</v>
+        <v>-0.2897049822499694</v>
       </c>
       <c r="K2">
-        <v>-126.5</v>
+        <v>-1776</v>
       </c>
       <c r="L2">
-        <v>-0.02648438154258437</v>
+        <v>-0.4348145427836945</v>
       </c>
       <c r="M2">
-        <v>52.981</v>
+        <v>39.2</v>
       </c>
       <c r="N2">
-        <v>0.02778675197986049</v>
+        <v>0.0158447857720291</v>
       </c>
       <c r="O2">
-        <v>-0.4188221343873518</v>
+        <v>-0.02207207207207207</v>
       </c>
       <c r="P2">
-        <v>52</v>
+        <v>39.2</v>
       </c>
       <c r="Q2">
-        <v>0.02727225048513138</v>
+        <v>0.0158447857720291</v>
       </c>
       <c r="R2">
-        <v>-0.4110671936758893</v>
+        <v>-0.02207207207207207</v>
       </c>
       <c r="S2">
-        <v>0.9810000000000016</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.01851607179932432</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1218.9</v>
+        <v>731.4</v>
       </c>
       <c r="V2">
-        <v>0.6392720406985892</v>
+        <v>0.2956345998383185</v>
       </c>
       <c r="W2">
-        <v>-0.03779278202676865</v>
+        <v>-0.5498452012383901</v>
       </c>
       <c r="X2">
-        <v>0.2719911062700016</v>
+        <v>0.2148096769027702</v>
       </c>
       <c r="Y2">
-        <v>-0.3097838882967702</v>
+        <v>-0.7646548781411603</v>
       </c>
       <c r="Z2">
-        <v>0.8683258494373441</v>
+        <v>0.8520025031289111</v>
       </c>
       <c r="AA2">
-        <v>-0.006417365062628392</v>
+        <v>-0.2468293700458907</v>
       </c>
       <c r="AB2">
-        <v>0.1476085287578102</v>
+        <v>0.1209899475779134</v>
       </c>
       <c r="AC2">
-        <v>-0.1540258938204386</v>
+        <v>-0.367819317623804</v>
       </c>
       <c r="AD2">
-        <v>2782.9</v>
+        <v>3419.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2782.9</v>
+        <v>3419.8</v>
       </c>
       <c r="AG2">
-        <v>1564</v>
+        <v>2688.4</v>
       </c>
       <c r="AH2">
-        <v>0.5934194814056636</v>
+        <v>0.5802368590722454</v>
       </c>
       <c r="AI2">
-        <v>0.4622911060168112</v>
+        <v>0.7180079363413048</v>
       </c>
       <c r="AJ2">
-        <v>0.4506295559973493</v>
+        <v>0.5207655354098869</v>
       </c>
       <c r="AK2">
-        <v>0.3257722510362641</v>
+        <v>0.6668485675306958</v>
       </c>
       <c r="AL2">
-        <v>184.3</v>
+        <v>124.9</v>
       </c>
       <c r="AM2">
-        <v>179.4</v>
+        <v>124.9</v>
       </c>
       <c r="AN2">
-        <v>3.456589243572227</v>
+        <v>6.621103581800581</v>
       </c>
       <c r="AO2">
-        <v>-0.1915355398806294</v>
+        <v>-9.473979183346676</v>
       </c>
       <c r="AP2">
-        <v>1.942615824121227</v>
+        <v>5.205033881897386</v>
       </c>
       <c r="AQ2">
-        <v>-0.1967670011148272</v>
+        <v>-9.473979183346676</v>
       </c>
     </row>
     <row r="3">
@@ -722,121 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.463</v>
+        <v>0.214</v>
       </c>
       <c r="F3">
-        <v>0.119</v>
+        <v>-0.123</v>
       </c>
       <c r="G3">
-        <v>0.3147140105518801</v>
+        <v>0.3745134043334557</v>
       </c>
       <c r="H3">
-        <v>0.1757181140607989</v>
+        <v>0.2203207246909046</v>
       </c>
       <c r="I3">
-        <v>-0.007390503307930659</v>
+        <v>-0.2897049822499694</v>
       </c>
       <c r="J3">
-        <v>-0.007390503307930659</v>
+        <v>-0.2897049822499694</v>
       </c>
       <c r="K3">
-        <v>-126.5</v>
+        <v>-1776</v>
       </c>
       <c r="L3">
-        <v>-0.02648438154258437</v>
+        <v>-0.4348145427836945</v>
       </c>
       <c r="M3">
-        <v>52.981</v>
+        <v>39.2</v>
       </c>
       <c r="N3">
-        <v>0.02778675197986049</v>
+        <v>0.0158447857720291</v>
       </c>
       <c r="O3">
-        <v>-0.4188221343873518</v>
+        <v>-0.02207207207207207</v>
       </c>
       <c r="P3">
-        <v>52</v>
+        <v>39.2</v>
       </c>
       <c r="Q3">
-        <v>0.02727225048513138</v>
+        <v>0.0158447857720291</v>
       </c>
       <c r="R3">
-        <v>-0.4110671936758893</v>
+        <v>-0.02207207207207207</v>
       </c>
       <c r="S3">
-        <v>0.9810000000000016</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.01851607179932432</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>1218.9</v>
+        <v>731.4</v>
       </c>
       <c r="V3">
-        <v>0.6392720406985892</v>
+        <v>0.2956345998383185</v>
       </c>
       <c r="W3">
-        <v>-0.03779278202676865</v>
+        <v>-0.5498452012383901</v>
       </c>
       <c r="X3">
-        <v>0.2719911062700016</v>
+        <v>0.2148096769027702</v>
       </c>
       <c r="Y3">
-        <v>-0.3097838882967702</v>
+        <v>-0.7646548781411603</v>
       </c>
       <c r="Z3">
-        <v>0.8683258494373441</v>
+        <v>0.8520025031289111</v>
       </c>
       <c r="AA3">
-        <v>-0.006417365062628392</v>
+        <v>-0.2468293700458907</v>
       </c>
       <c r="AB3">
-        <v>0.1476085287578102</v>
+        <v>0.1209899475779134</v>
       </c>
       <c r="AC3">
-        <v>-0.1540258938204386</v>
+        <v>-0.367819317623804</v>
       </c>
       <c r="AD3">
-        <v>2782.9</v>
+        <v>3419.8</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2782.9</v>
+        <v>3419.8</v>
       </c>
       <c r="AG3">
-        <v>1564</v>
+        <v>2688.4</v>
       </c>
       <c r="AH3">
-        <v>0.5934194814056636</v>
+        <v>0.5802368590722454</v>
       </c>
       <c r="AI3">
-        <v>0.4622911060168112</v>
+        <v>0.7180079363413048</v>
       </c>
       <c r="AJ3">
-        <v>0.4506295559973493</v>
+        <v>0.5207655354098869</v>
       </c>
       <c r="AK3">
-        <v>0.3257722510362641</v>
+        <v>0.6668485675306958</v>
       </c>
       <c r="AL3">
-        <v>184.3</v>
+        <v>124.9</v>
       </c>
       <c r="AM3">
-        <v>179.4</v>
+        <v>124.9</v>
       </c>
       <c r="AN3">
-        <v>3.456589243572227</v>
+        <v>6.621103581800581</v>
       </c>
       <c r="AO3">
-        <v>-0.1915355398806294</v>
+        <v>-9.473979183346676</v>
       </c>
       <c r="AP3">
-        <v>1.942615824121227</v>
+        <v>5.205033881897386</v>
       </c>
       <c r="AQ3">
-        <v>-0.1967670011148272</v>
+        <v>-9.473979183346676</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="swx_ams" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.214</v>
+        <v>0.149</v>
       </c>
       <c r="F2">
-        <v>-0.123</v>
+        <v>-0.0329</v>
       </c>
       <c r="G2">
-        <v>0.3745134043334557</v>
+        <v>0.2830487361810349</v>
       </c>
       <c r="H2">
-        <v>0.2203207246909046</v>
+        <v>0.1319613847511289</v>
       </c>
       <c r="I2">
-        <v>-0.2897049822499694</v>
+        <v>0.06308714382104115</v>
       </c>
       <c r="J2">
-        <v>-0.2897049822499694</v>
+        <v>0.06308714382104115</v>
       </c>
       <c r="K2">
-        <v>-1776</v>
+        <v>-903.4</v>
       </c>
       <c r="L2">
-        <v>-0.4348145427836945</v>
+        <v>-0.2344423106866663</v>
       </c>
       <c r="M2">
-        <v>39.2</v>
+        <v>33.5</v>
       </c>
       <c r="N2">
-        <v>0.0158447857720291</v>
+        <v>0.05178543824393261</v>
       </c>
       <c r="O2">
-        <v>-0.02207207207207207</v>
+        <v>-0.0370821341598406</v>
       </c>
       <c r="P2">
-        <v>39.2</v>
+        <v>33.5</v>
       </c>
       <c r="Q2">
-        <v>0.0158447857720291</v>
+        <v>0.05178543824393261</v>
       </c>
       <c r="R2">
-        <v>-0.02207207207207207</v>
+        <v>-0.0370821341598406</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>731.4</v>
+        <v>1223.5</v>
       </c>
       <c r="V2">
-        <v>0.2956345998383185</v>
+        <v>1.891327871386613</v>
       </c>
       <c r="W2">
-        <v>-0.5498452012383901</v>
+        <v>-0.6763494796735794</v>
       </c>
       <c r="X2">
-        <v>0.2148096769027702</v>
+        <v>0.4518204657590218</v>
       </c>
       <c r="Y2">
-        <v>-0.7646548781411603</v>
+        <v>-1.128169945432601</v>
       </c>
       <c r="Z2">
-        <v>0.8520025031289111</v>
+        <v>0.9575805770234339</v>
       </c>
       <c r="AA2">
-        <v>-0.2468293700458907</v>
+        <v>0.06041102358291295</v>
       </c>
       <c r="AB2">
-        <v>0.1209899475779134</v>
+        <v>0.1225609199929506</v>
       </c>
       <c r="AC2">
-        <v>-0.367819317623804</v>
+        <v>-0.06214989641003768</v>
       </c>
       <c r="AD2">
-        <v>3419.8</v>
+        <v>3438.5</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3419.8</v>
+        <v>3438.5</v>
       </c>
       <c r="AG2">
-        <v>2688.4</v>
+        <v>2215</v>
       </c>
       <c r="AH2">
-        <v>0.5802368590722454</v>
+        <v>0.8416556518333578</v>
       </c>
       <c r="AI2">
-        <v>0.7180079363413048</v>
+        <v>0.7123324563402457</v>
       </c>
       <c r="AJ2">
-        <v>0.5207655354098869</v>
+        <v>0.7739613543450156</v>
       </c>
       <c r="AK2">
-        <v>0.6668485675306958</v>
+        <v>0.6146631146631146</v>
       </c>
       <c r="AL2">
-        <v>124.9</v>
+        <v>237.6</v>
       </c>
       <c r="AM2">
-        <v>124.9</v>
+        <v>237.6</v>
       </c>
       <c r="AN2">
-        <v>6.621103581800581</v>
+        <v>-9.094154985453583</v>
       </c>
       <c r="AO2">
-        <v>-9.473979183346676</v>
+        <v>1.023148148148148</v>
       </c>
       <c r="AP2">
-        <v>5.205033881897386</v>
+        <v>-5.858238561227188</v>
       </c>
       <c r="AQ2">
-        <v>-9.473979183346676</v>
+        <v>1.023148148148148</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.214</v>
+        <v>0.149</v>
       </c>
       <c r="F3">
-        <v>-0.123</v>
+        <v>-0.0329</v>
       </c>
       <c r="G3">
-        <v>0.3745134043334557</v>
+        <v>0.2830487361810349</v>
       </c>
       <c r="H3">
-        <v>0.2203207246909046</v>
+        <v>0.1319613847511289</v>
       </c>
       <c r="I3">
-        <v>-0.2897049822499694</v>
+        <v>0.06308714382104115</v>
       </c>
       <c r="J3">
-        <v>-0.2897049822499694</v>
+        <v>0.06308714382104115</v>
       </c>
       <c r="K3">
-        <v>-1776</v>
+        <v>-903.4</v>
       </c>
       <c r="L3">
-        <v>-0.4348145427836945</v>
+        <v>-0.2344423106866663</v>
       </c>
       <c r="M3">
-        <v>39.2</v>
+        <v>33.5</v>
       </c>
       <c r="N3">
-        <v>0.0158447857720291</v>
+        <v>0.05178543824393261</v>
       </c>
       <c r="O3">
-        <v>-0.02207207207207207</v>
+        <v>-0.0370821341598406</v>
       </c>
       <c r="P3">
-        <v>39.2</v>
+        <v>33.5</v>
       </c>
       <c r="Q3">
-        <v>0.0158447857720291</v>
+        <v>0.05178543824393261</v>
       </c>
       <c r="R3">
-        <v>-0.02207207207207207</v>
+        <v>-0.0370821341598406</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +772,8834 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>731.4</v>
+        <v>1223.5</v>
       </c>
       <c r="V3">
-        <v>0.2956345998383185</v>
+        <v>1.891327871386613</v>
       </c>
       <c r="W3">
-        <v>-0.5498452012383901</v>
+        <v>-0.6763494796735794</v>
       </c>
       <c r="X3">
-        <v>0.2148096769027702</v>
+        <v>0.4518204657590218</v>
       </c>
       <c r="Y3">
-        <v>-0.7646548781411603</v>
+        <v>-1.128169945432601</v>
       </c>
       <c r="Z3">
-        <v>0.8520025031289111</v>
+        <v>0.9575805770234339</v>
       </c>
       <c r="AA3">
-        <v>-0.2468293700458907</v>
+        <v>0.06041102358291295</v>
       </c>
       <c r="AB3">
-        <v>0.1209899475779134</v>
+        <v>0.1225609199929506</v>
       </c>
       <c r="AC3">
-        <v>-0.367819317623804</v>
+        <v>-0.06214989641003768</v>
       </c>
       <c r="AD3">
-        <v>3419.8</v>
+        <v>3438.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3419.8</v>
+        <v>3438.5</v>
       </c>
       <c r="AG3">
-        <v>2688.4</v>
+        <v>2215</v>
       </c>
       <c r="AH3">
-        <v>0.5802368590722454</v>
+        <v>0.8416556518333578</v>
       </c>
       <c r="AI3">
-        <v>0.7180079363413048</v>
+        <v>0.7123324563402457</v>
       </c>
       <c r="AJ3">
-        <v>0.5207655354098869</v>
+        <v>0.7739613543450156</v>
       </c>
       <c r="AK3">
-        <v>0.6668485675306958</v>
+        <v>0.6146631146631146</v>
       </c>
       <c r="AL3">
-        <v>124.9</v>
+        <v>237.6</v>
       </c>
       <c r="AM3">
-        <v>124.9</v>
+        <v>237.6</v>
       </c>
       <c r="AN3">
-        <v>6.621103581800581</v>
+        <v>-9.094154985453583</v>
       </c>
       <c r="AO3">
-        <v>-9.473979183346676</v>
+        <v>1.023148148148148</v>
       </c>
       <c r="AP3">
-        <v>5.205033881897386</v>
+        <v>-5.858238561227188</v>
       </c>
       <c r="AQ3">
-        <v>-9.473979183346676</v>
+        <v>1.023148148148148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ams-OSRAM AG (SWX:AMS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>SWX:AMS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>1.02314814814815</v>
+      </c>
+      <c r="F2">
+        <v>-0.878774562483797</v>
+      </c>
+      <c r="G2">
+        <v>-9.09415498545358</v>
+      </c>
+      <c r="H2">
+        <v>-0.108050780216874</v>
+      </c>
+      <c r="I2">
+        <v>0.841655651833358</v>
+      </c>
+      <c r="J2">
+        <v>0.01</v>
+      </c>
+      <c r="K2">
+        <v>646.9</v>
+      </c>
+      <c r="L2">
+        <v>3819.84779207943</v>
+      </c>
+      <c r="M2">
+        <v>2861.9</v>
+      </c>
+      <c r="N2">
+        <v>2637.20179207943</v>
+      </c>
+      <c r="O2">
+        <v>3438.5</v>
+      </c>
+      <c r="P2">
+        <v>40.854</v>
+      </c>
+      <c r="Q2">
+        <v>0.122560919992951</v>
+      </c>
+      <c r="R2">
+        <v>0.129101201139639</v>
+      </c>
+      <c r="S2">
+        <v>0.0606158857756839</v>
+      </c>
+      <c r="T2">
+        <v>0.302433125065374</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.451820465759022</v>
+      </c>
+      <c r="X2">
+        <v>0.127350373625238</v>
+      </c>
+      <c r="Y2">
+        <v>8.34387358365694</v>
+      </c>
+      <c r="Z2">
+        <v>1.67589091095922</v>
+      </c>
+      <c r="AA2">
+        <v>3438.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.0797577444416894</v>
+      </c>
+      <c r="AC2">
+        <v>1.023148148148148</v>
+      </c>
+      <c r="AD2">
+        <v>3438.5</v>
+      </c>
+      <c r="AE2">
+        <v>237.6</v>
+      </c>
+      <c r="AF2">
+        <v>-621.2</v>
+      </c>
+      <c r="AG2">
+        <v>-378.1</v>
+      </c>
+      <c r="AH2">
+        <v>0.003957744441689399</v>
+      </c>
+      <c r="AI2">
+        <v>0.0458</v>
+      </c>
+      <c r="AJ2">
+        <v>646.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.0486609081127847</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.24</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>70.29999999999998</v>
+      </c>
+      <c r="AR2">
+        <v>237.6</v>
+      </c>
+      <c r="AS2">
+        <v>3438.5</v>
+      </c>
+      <c r="AT2">
+        <v>1223.5</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>-3438.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1223.5</v>
+      </c>
+      <c r="H2">
+        <v>646.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K2">
+        <v>-621.2</v>
+      </c>
+      <c r="L2">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="O2">
+        <v>-2.152000000000007</v>
+      </c>
+      <c r="P2">
+        <v>-6.81466666666669</v>
+      </c>
+      <c r="Q2">
+        <v>-628.0146666666667</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <v>0.0556577444416894</v>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>-Inf</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Inf</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1291012011396392</v>
+      </c>
+      <c r="C3">
+        <v>3819.84779207943</v>
+      </c>
+      <c r="D3">
+        <v>2637.20179207943</v>
+      </c>
+      <c r="E3">
+        <v>-3397.646</v>
+      </c>
+      <c r="F3">
+        <v>40.854</v>
+      </c>
+      <c r="G3">
+        <v>1223.5</v>
+      </c>
+      <c r="H3">
+        <v>646.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K3">
+        <v>-621.2</v>
+      </c>
+      <c r="L3">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M3">
+        <v>10.20360289142078</v>
+      </c>
+      <c r="N3">
+        <v>-19.17026955808748</v>
+      </c>
+      <c r="O3">
+        <v>-4.600864693940994</v>
+      </c>
+      <c r="P3">
+        <v>-14.56940486414648</v>
+      </c>
+      <c r="Q3">
+        <v>-635.7694048641465</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1273503736252378</v>
+      </c>
+      <c r="T3">
+        <v>1.675890910959223</v>
+      </c>
+      <c r="U3">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V3">
+        <v>-0.2109058949961112</v>
+      </c>
+      <c r="W3">
+        <v>0.3024331250653739</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>-0.8787745624837966</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.131140778584056</v>
+      </c>
+      <c r="C4">
+        <v>3715.966744743517</v>
+      </c>
+      <c r="D4">
+        <v>2574.174744743517</v>
+      </c>
+      <c r="E4">
+        <v>-3356.792</v>
+      </c>
+      <c r="F4">
+        <v>81.708</v>
+      </c>
+      <c r="G4">
+        <v>1223.5</v>
+      </c>
+      <c r="H4">
+        <v>646.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K4">
+        <v>-621.2</v>
+      </c>
+      <c r="L4">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M4">
+        <v>20.40720578284156</v>
+      </c>
+      <c r="N4">
+        <v>-29.37387244950826</v>
+      </c>
+      <c r="O4">
+        <v>-7.049729387881981</v>
+      </c>
+      <c r="P4">
+        <v>-22.32414306162627</v>
+      </c>
+      <c r="Q4">
+        <v>-643.5241430616263</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1281825202948831</v>
+      </c>
+      <c r="T4">
+        <v>1.692991838622072</v>
+      </c>
+      <c r="U4">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V4">
+        <v>-0.1054529474980556</v>
+      </c>
+      <c r="W4">
+        <v>0.2760954347535317</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>-0.4393872812418982</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1331803560284729</v>
+      </c>
+      <c r="C5">
+        <v>3615.027972993953</v>
+      </c>
+      <c r="D5">
+        <v>2514.089972993952</v>
+      </c>
+      <c r="E5">
+        <v>-3315.938</v>
+      </c>
+      <c r="F5">
+        <v>122.562</v>
+      </c>
+      <c r="G5">
+        <v>1223.5</v>
+      </c>
+      <c r="H5">
+        <v>646.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K5">
+        <v>-621.2</v>
+      </c>
+      <c r="L5">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M5">
+        <v>30.61080867426234</v>
+      </c>
+      <c r="N5">
+        <v>-39.57747534092903</v>
+      </c>
+      <c r="O5">
+        <v>-9.498594081822969</v>
+      </c>
+      <c r="P5">
+        <v>-30.07888125910607</v>
+      </c>
+      <c r="Q5">
+        <v>-651.2788812591061</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.12903182462782</v>
+      </c>
+      <c r="T5">
+        <v>1.710445362731578</v>
+      </c>
+      <c r="U5">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V5">
+        <v>-0.07030196499870373</v>
+      </c>
+      <c r="W5">
+        <v>0.2673162046495843</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>-0.2929248541612655</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1352199334728898</v>
+      </c>
+      <c r="C6">
+        <v>3516.830145918664</v>
+      </c>
+      <c r="D6">
+        <v>2456.746145918664</v>
+      </c>
+      <c r="E6">
+        <v>-3275.084</v>
+      </c>
+      <c r="F6">
+        <v>163.416</v>
+      </c>
+      <c r="G6">
+        <v>1223.5</v>
+      </c>
+      <c r="H6">
+        <v>646.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K6">
+        <v>-621.2</v>
+      </c>
+      <c r="L6">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M6">
+        <v>40.81441156568312</v>
+      </c>
+      <c r="N6">
+        <v>-49.78107823234981</v>
+      </c>
+      <c r="O6">
+        <v>-11.94745877576396</v>
+      </c>
+      <c r="P6">
+        <v>-37.83361945658586</v>
+      </c>
+      <c r="Q6">
+        <v>-659.0336194565859</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1298988228010265</v>
+      </c>
+      <c r="T6">
+        <v>1.728262501926698</v>
+      </c>
+      <c r="U6">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V6">
+        <v>-0.05272647374902779</v>
+      </c>
+      <c r="W6">
+        <v>0.2629265895976106</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>-0.2196936406209491</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1372595109173067</v>
+      </c>
+      <c r="C7">
+        <v>3421.189891590186</v>
+      </c>
+      <c r="D7">
+        <v>2401.959891590186</v>
+      </c>
+      <c r="E7">
+        <v>-3234.23</v>
+      </c>
+      <c r="F7">
+        <v>204.27</v>
+      </c>
+      <c r="G7">
+        <v>1223.5</v>
+      </c>
+      <c r="H7">
+        <v>646.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K7">
+        <v>-621.2</v>
+      </c>
+      <c r="L7">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M7">
+        <v>51.0180144571039</v>
+      </c>
+      <c r="N7">
+        <v>-59.98468112377059</v>
+      </c>
+      <c r="O7">
+        <v>-14.39632346970494</v>
+      </c>
+      <c r="P7">
+        <v>-45.58835765406565</v>
+      </c>
+      <c r="Q7">
+        <v>-666.7883576540657</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1307840735673531</v>
+      </c>
+      <c r="T7">
+        <v>1.746454738789085</v>
+      </c>
+      <c r="U7">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V7">
+        <v>-0.04218117899922223</v>
+      </c>
+      <c r="W7">
+        <v>0.2602928205664263</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>-0.1757549124967592</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1392990883617236</v>
+      </c>
+      <c r="C8">
+        <v>3327.939838290409</v>
+      </c>
+      <c r="D8">
+        <v>2349.563838290409</v>
+      </c>
+      <c r="E8">
+        <v>-3193.376</v>
+      </c>
+      <c r="F8">
+        <v>245.124</v>
+      </c>
+      <c r="G8">
+        <v>1223.5</v>
+      </c>
+      <c r="H8">
+        <v>646.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K8">
+        <v>-621.2</v>
+      </c>
+      <c r="L8">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M8">
+        <v>61.22161734852467</v>
+      </c>
+      <c r="N8">
+        <v>-70.18828401519137</v>
+      </c>
+      <c r="O8">
+        <v>-16.84518816364593</v>
+      </c>
+      <c r="P8">
+        <v>-53.34309585154544</v>
+      </c>
+      <c r="Q8">
+        <v>-674.5430958515454</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1316881594563674</v>
+      </c>
+      <c r="T8">
+        <v>1.765034044520883</v>
+      </c>
+      <c r="U8">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V8">
+        <v>-0.03515098249935186</v>
+      </c>
+      <c r="W8">
+        <v>0.2585369745456368</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>-0.1464624270806327</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1413386658061405</v>
+      </c>
+      <c r="C9">
+        <v>3236.926906633162</v>
+      </c>
+      <c r="D9">
+        <v>2299.404906633162</v>
+      </c>
+      <c r="E9">
+        <v>-3152.522</v>
+      </c>
+      <c r="F9">
+        <v>285.978</v>
+      </c>
+      <c r="G9">
+        <v>1223.5</v>
+      </c>
+      <c r="H9">
+        <v>646.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K9">
+        <v>-621.2</v>
+      </c>
+      <c r="L9">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M9">
+        <v>71.42522023994546</v>
+      </c>
+      <c r="N9">
+        <v>-80.39188690661216</v>
+      </c>
+      <c r="O9">
+        <v>-19.29405285758692</v>
+      </c>
+      <c r="P9">
+        <v>-61.09783404902524</v>
+      </c>
+      <c r="Q9">
+        <v>-682.2978340490253</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1326116880526725</v>
+      </c>
+      <c r="T9">
+        <v>1.784012905214656</v>
+      </c>
+      <c r="U9">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V9">
+        <v>-0.03012941357087302</v>
+      </c>
+      <c r="W9">
+        <v>0.2572827988165015</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>-0.125539223211971</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1433782432505574</v>
+      </c>
+      <c r="C10">
+        <v>3148.010815874793</v>
+      </c>
+      <c r="D10">
+        <v>2251.342815874793</v>
+      </c>
+      <c r="E10">
+        <v>-3111.668</v>
+      </c>
+      <c r="F10">
+        <v>326.832</v>
+      </c>
+      <c r="G10">
+        <v>1223.5</v>
+      </c>
+      <c r="H10">
+        <v>646.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K10">
+        <v>-621.2</v>
+      </c>
+      <c r="L10">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M10">
+        <v>81.62882313136623</v>
+      </c>
+      <c r="N10">
+        <v>-90.59548979803293</v>
+      </c>
+      <c r="O10">
+        <v>-21.7429175515279</v>
+      </c>
+      <c r="P10">
+        <v>-68.85257224650502</v>
+      </c>
+      <c r="Q10">
+        <v>-690.0525722465051</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1335552933575928</v>
+      </c>
+      <c r="T10">
+        <v>1.803404349836555</v>
+      </c>
+      <c r="U10">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V10">
+        <v>-0.0263632368745139</v>
+      </c>
+      <c r="W10">
+        <v>0.25634216701965</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>-0.1098468203104745</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1454178206949743</v>
+      </c>
+      <c r="C11">
+        <v>3061.062773715728</v>
+      </c>
+      <c r="D11">
+        <v>2205.248773715728</v>
+      </c>
+      <c r="E11">
+        <v>-3070.814</v>
+      </c>
+      <c r="F11">
+        <v>367.686</v>
+      </c>
+      <c r="G11">
+        <v>1223.5</v>
+      </c>
+      <c r="H11">
+        <v>646.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K11">
+        <v>-621.2</v>
+      </c>
+      <c r="L11">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M11">
+        <v>91.832426022787</v>
+      </c>
+      <c r="N11">
+        <v>-100.7990926894537</v>
+      </c>
+      <c r="O11">
+        <v>-24.19178224546889</v>
+      </c>
+      <c r="P11">
+        <v>-76.60731044398482</v>
+      </c>
+      <c r="Q11">
+        <v>-697.8073104439849</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1345196372406433</v>
+      </c>
+      <c r="T11">
+        <v>1.823221980054539</v>
+      </c>
+      <c r="U11">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V11">
+        <v>-0.02343398833290124</v>
+      </c>
+      <c r="W11">
+        <v>0.2556105645109877</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>-0.09764161805375515</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1474573981393912</v>
+      </c>
+      <c r="C12">
+        <v>2975.964323823048</v>
+      </c>
+      <c r="D12">
+        <v>2161.004323823048</v>
+      </c>
+      <c r="E12">
+        <v>-3029.96</v>
+      </c>
+      <c r="F12">
+        <v>408.54</v>
+      </c>
+      <c r="G12">
+        <v>1223.5</v>
+      </c>
+      <c r="H12">
+        <v>646.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K12">
+        <v>-621.2</v>
+      </c>
+      <c r="L12">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M12">
+        <v>102.0360289142078</v>
+      </c>
+      <c r="N12">
+        <v>-111.0026955808745</v>
+      </c>
+      <c r="O12">
+        <v>-26.64064693940988</v>
+      </c>
+      <c r="P12">
+        <v>-84.36204864146461</v>
+      </c>
+      <c r="Q12">
+        <v>-705.5620486414647</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1355054109877616</v>
+      </c>
+      <c r="T12">
+        <v>1.843480002055145</v>
+      </c>
+      <c r="U12">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V12">
+        <v>-0.02109058949961112</v>
+      </c>
+      <c r="W12">
+        <v>0.2550252825040579</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>-0.08787745624837973</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1494969755838081</v>
+      </c>
+      <c r="C13">
+        <v>2892.60632935896</v>
+      </c>
+      <c r="D13">
+        <v>2118.500329358959</v>
+      </c>
+      <c r="E13">
+        <v>-2989.106</v>
+      </c>
+      <c r="F13">
+        <v>449.394</v>
+      </c>
+      <c r="G13">
+        <v>1223.5</v>
+      </c>
+      <c r="H13">
+        <v>646.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K13">
+        <v>-621.2</v>
+      </c>
+      <c r="L13">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M13">
+        <v>112.2396318056286</v>
+      </c>
+      <c r="N13">
+        <v>-121.2062984722953</v>
+      </c>
+      <c r="O13">
+        <v>-29.08951163335086</v>
+      </c>
+      <c r="P13">
+        <v>-92.11678683894441</v>
+      </c>
+      <c r="Q13">
+        <v>-713.3167868389445</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1365133369539162</v>
+      </c>
+      <c r="T13">
+        <v>1.864193260505203</v>
+      </c>
+      <c r="U13">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V13">
+        <v>-0.01917326318146465</v>
+      </c>
+      <c r="W13">
+        <v>0.2545464154074789</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>-0.07988859658943603</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.151536553028225</v>
+      </c>
+      <c r="C14">
+        <v>2810.888074151047</v>
+      </c>
+      <c r="D14">
+        <v>2077.636074151047</v>
+      </c>
+      <c r="E14">
+        <v>-2948.252</v>
+      </c>
+      <c r="F14">
+        <v>490.248</v>
+      </c>
+      <c r="G14">
+        <v>1223.5</v>
+      </c>
+      <c r="H14">
+        <v>646.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K14">
+        <v>-621.2</v>
+      </c>
+      <c r="L14">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M14">
+        <v>122.4432346970493</v>
+      </c>
+      <c r="N14">
+        <v>-131.409901363716</v>
+      </c>
+      <c r="O14">
+        <v>-31.53837632729185</v>
+      </c>
+      <c r="P14">
+        <v>-99.8715250364242</v>
+      </c>
+      <c r="Q14">
+        <v>-721.0715250364242</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1375441703283925</v>
+      </c>
+      <c r="T14">
+        <v>1.885377274829126</v>
+      </c>
+      <c r="U14">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V14">
+        <v>-0.01757549124967593</v>
+      </c>
+      <c r="W14">
+        <v>0.2541473594936631</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>-0.07323121354031636</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1535761304726419</v>
+      </c>
+      <c r="C15">
+        <v>2730.716465920336</v>
+      </c>
+      <c r="D15">
+        <v>2038.318465920336</v>
+      </c>
+      <c r="E15">
+        <v>-2907.398</v>
+      </c>
+      <c r="F15">
+        <v>531.102</v>
+      </c>
+      <c r="G15">
+        <v>1223.5</v>
+      </c>
+      <c r="H15">
+        <v>646.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K15">
+        <v>-621.2</v>
+      </c>
+      <c r="L15">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M15">
+        <v>132.6468375884701</v>
+      </c>
+      <c r="N15">
+        <v>-141.6135042551368</v>
+      </c>
+      <c r="O15">
+        <v>-33.98724102123284</v>
+      </c>
+      <c r="P15">
+        <v>-107.626263233904</v>
+      </c>
+      <c r="Q15">
+        <v>-728.826263233904</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1385987010218223</v>
+      </c>
+      <c r="T15">
+        <v>1.907048277988081</v>
+      </c>
+      <c r="U15">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V15">
+        <v>-0.01622353038431625</v>
+      </c>
+      <c r="W15">
+        <v>0.2538096967973575</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>-0.06759804326798435</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1556157079170588</v>
+      </c>
+      <c r="C16">
+        <v>2652.005328298736</v>
+      </c>
+      <c r="D16">
+        <v>2000.461328298736</v>
+      </c>
+      <c r="E16">
+        <v>-2866.544</v>
+      </c>
+      <c r="F16">
+        <v>571.956</v>
+      </c>
+      <c r="G16">
+        <v>1223.5</v>
+      </c>
+      <c r="H16">
+        <v>646.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K16">
+        <v>-621.2</v>
+      </c>
+      <c r="L16">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M16">
+        <v>142.8504404798909</v>
+      </c>
+      <c r="N16">
+        <v>-151.8171071465576</v>
+      </c>
+      <c r="O16">
+        <v>-36.43610571517382</v>
+      </c>
+      <c r="P16">
+        <v>-115.3810014313838</v>
+      </c>
+      <c r="Q16">
+        <v>-736.5810014313838</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1396777556848668</v>
+      </c>
+      <c r="T16">
+        <v>1.929223257964687</v>
+      </c>
+      <c r="U16">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V16">
+        <v>-0.01506470678543651</v>
+      </c>
+      <c r="W16">
+        <v>0.2535202716290955</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>-0.06276961160598549</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1576552853614757</v>
+      </c>
+      <c r="C17">
+        <v>2574.67477030292</v>
+      </c>
+      <c r="D17">
+        <v>1963.98477030292</v>
+      </c>
+      <c r="E17">
+        <v>-2825.69</v>
+      </c>
+      <c r="F17">
+        <v>612.8099999999999</v>
+      </c>
+      <c r="G17">
+        <v>1223.5</v>
+      </c>
+      <c r="H17">
+        <v>646.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K17">
+        <v>-621.2</v>
+      </c>
+      <c r="L17">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M17">
+        <v>153.0540433713117</v>
+      </c>
+      <c r="N17">
+        <v>-162.0207100379784</v>
+      </c>
+      <c r="O17">
+        <v>-38.88497040911481</v>
+      </c>
+      <c r="P17">
+        <v>-123.1357396288636</v>
+      </c>
+      <c r="Q17">
+        <v>-744.3357396288636</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1407821998693946</v>
+      </c>
+      <c r="T17">
+        <v>1.951920002176036</v>
+      </c>
+      <c r="U17">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V17">
+        <v>-0.01406039299974074</v>
+      </c>
+      <c r="W17">
+        <v>0.2532694364832684</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>-0.058584970832253</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1596948628058925</v>
+      </c>
+      <c r="C18">
+        <v>2498.650623555259</v>
+      </c>
+      <c r="D18">
+        <v>1928.814623555258</v>
+      </c>
+      <c r="E18">
+        <v>-2784.836</v>
+      </c>
+      <c r="F18">
+        <v>653.664</v>
+      </c>
+      <c r="G18">
+        <v>1223.5</v>
+      </c>
+      <c r="H18">
+        <v>646.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K18">
+        <v>-621.2</v>
+      </c>
+      <c r="L18">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M18">
+        <v>163.2576462627325</v>
+      </c>
+      <c r="N18">
+        <v>-172.2243129293992</v>
+      </c>
+      <c r="O18">
+        <v>-41.3338351030558</v>
+      </c>
+      <c r="P18">
+        <v>-130.8904778263434</v>
+      </c>
+      <c r="Q18">
+        <v>-752.0904778263434</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1419129403440302</v>
+      </c>
+      <c r="T18">
+        <v>1.975157145059084</v>
+      </c>
+      <c r="U18">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V18">
+        <v>-0.01318161843725695</v>
+      </c>
+      <c r="W18">
+        <v>0.2530499557306697</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>-0.05492341015523738</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1617344402503094</v>
+      </c>
+      <c r="C19">
+        <v>2423.863938908909</v>
+      </c>
+      <c r="D19">
+        <v>1894.881938908909</v>
+      </c>
+      <c r="E19">
+        <v>-2743.982</v>
+      </c>
+      <c r="F19">
+        <v>694.518</v>
+      </c>
+      <c r="G19">
+        <v>1223.5</v>
+      </c>
+      <c r="H19">
+        <v>646.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K19">
+        <v>-621.2</v>
+      </c>
+      <c r="L19">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M19">
+        <v>173.4612491541533</v>
+      </c>
+      <c r="N19">
+        <v>-182.4279158208199</v>
+      </c>
+      <c r="O19">
+        <v>-43.78269979699679</v>
+      </c>
+      <c r="P19">
+        <v>-138.6452160238232</v>
+      </c>
+      <c r="Q19">
+        <v>-759.8452160238232</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1430709275770909</v>
+      </c>
+      <c r="T19">
+        <v>1.99895421909594</v>
+      </c>
+      <c r="U19">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V19">
+        <v>-0.0124062291174183</v>
+      </c>
+      <c r="W19">
+        <v>0.2528562962430826</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>-0.05169262132257635</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1637740176947263</v>
+      </c>
+      <c r="C20">
+        <v>2350.250535288087</v>
+      </c>
+      <c r="D20">
+        <v>1862.122535288087</v>
+      </c>
+      <c r="E20">
+        <v>-2703.128</v>
+      </c>
+      <c r="F20">
+        <v>735.372</v>
+      </c>
+      <c r="G20">
+        <v>1223.5</v>
+      </c>
+      <c r="H20">
+        <v>646.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K20">
+        <v>-621.2</v>
+      </c>
+      <c r="L20">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M20">
+        <v>183.664852045574</v>
+      </c>
+      <c r="N20">
+        <v>-192.6315187122407</v>
+      </c>
+      <c r="O20">
+        <v>-46.23156449093777</v>
+      </c>
+      <c r="P20">
+        <v>-146.3999542213029</v>
+      </c>
+      <c r="Q20">
+        <v>-767.5999542213031</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1442571584012017</v>
+      </c>
+      <c r="T20">
+        <v>2.02333170957272</v>
+      </c>
+      <c r="U20">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V20">
+        <v>-0.01171699416645062</v>
+      </c>
+      <c r="W20">
+        <v>0.2526841544763385</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>-0.04882080902687758</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1658135951391432</v>
+      </c>
+      <c r="C21">
+        <v>2277.750594531869</v>
+      </c>
+      <c r="D21">
+        <v>1830.476594531869</v>
+      </c>
+      <c r="E21">
+        <v>-2662.274</v>
+      </c>
+      <c r="F21">
+        <v>776.226</v>
+      </c>
+      <c r="G21">
+        <v>1223.5</v>
+      </c>
+      <c r="H21">
+        <v>646.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K21">
+        <v>-621.2</v>
+      </c>
+      <c r="L21">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M21">
+        <v>193.8684549369948</v>
+      </c>
+      <c r="N21">
+        <v>-202.8351216036615</v>
+      </c>
+      <c r="O21">
+        <v>-48.68042918487875</v>
+      </c>
+      <c r="P21">
+        <v>-154.1546924187827</v>
+      </c>
+      <c r="Q21">
+        <v>-775.3546924187827</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1454726788752906</v>
+      </c>
+      <c r="T21">
+        <v>2.048311113394605</v>
+      </c>
+      <c r="U21">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V21">
+        <v>-0.01110031026295322</v>
+      </c>
+      <c r="W21">
+        <v>0.2525301328955675</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>-0.04625129276230511</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1678531725835601</v>
+      </c>
+      <c r="C22">
+        <v>2206.308296860342</v>
+      </c>
+      <c r="D22">
+        <v>1799.888296860342</v>
+      </c>
+      <c r="E22">
+        <v>-2621.42</v>
+      </c>
+      <c r="F22">
+        <v>817.08</v>
+      </c>
+      <c r="G22">
+        <v>1223.5</v>
+      </c>
+      <c r="H22">
+        <v>646.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K22">
+        <v>-621.2</v>
+      </c>
+      <c r="L22">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M22">
+        <v>204.0720578284156</v>
+      </c>
+      <c r="N22">
+        <v>-213.0387244950823</v>
+      </c>
+      <c r="O22">
+        <v>-51.12929387881974</v>
+      </c>
+      <c r="P22">
+        <v>-161.9094306162625</v>
+      </c>
+      <c r="Q22">
+        <v>-783.1094306162626</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1467185873612318</v>
+      </c>
+      <c r="T22">
+        <v>2.073915002312038</v>
+      </c>
+      <c r="U22">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V22">
+        <v>-0.01054529474980556</v>
+      </c>
+      <c r="W22">
+        <v>0.2523915134728736</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>-0.04393872812418986</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.169892750027977</v>
+      </c>
+      <c r="C23">
+        <v>2135.871492289417</v>
+      </c>
+      <c r="D23">
+        <v>1770.305492289417</v>
+      </c>
+      <c r="E23">
+        <v>-2580.566</v>
+      </c>
+      <c r="F23">
+        <v>857.934</v>
+      </c>
+      <c r="G23">
+        <v>1223.5</v>
+      </c>
+      <c r="H23">
+        <v>646.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K23">
+        <v>-621.2</v>
+      </c>
+      <c r="L23">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M23">
+        <v>214.2756607198364</v>
+      </c>
+      <c r="N23">
+        <v>-223.2423273865031</v>
+      </c>
+      <c r="O23">
+        <v>-53.57815857276074</v>
+      </c>
+      <c r="P23">
+        <v>-169.6641688137423</v>
+      </c>
+      <c r="Q23">
+        <v>-790.8641688137424</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1479960378341587</v>
+      </c>
+      <c r="T23">
+        <v>2.100167090948899</v>
+      </c>
+      <c r="U23">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V23">
+        <v>-0.01004313785695768</v>
+      </c>
+      <c r="W23">
+        <v>0.2522660958999601</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>-0.04184640773732373</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1719323274723939</v>
+      </c>
+      <c r="C24">
+        <v>2066.391403925265</v>
+      </c>
+      <c r="D24">
+        <v>1741.679403925265</v>
+      </c>
+      <c r="E24">
+        <v>-2539.712</v>
+      </c>
+      <c r="F24">
+        <v>898.788</v>
+      </c>
+      <c r="G24">
+        <v>1223.5</v>
+      </c>
+      <c r="H24">
+        <v>646.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K24">
+        <v>-621.2</v>
+      </c>
+      <c r="L24">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M24">
+        <v>224.4792636112572</v>
+      </c>
+      <c r="N24">
+        <v>-233.4459302779238</v>
+      </c>
+      <c r="O24">
+        <v>-56.02702326670173</v>
+      </c>
+      <c r="P24">
+        <v>-177.4189070112221</v>
+      </c>
+      <c r="Q24">
+        <v>-798.6189070112222</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1493062434474172</v>
+      </c>
+      <c r="T24">
+        <v>2.127092310063629</v>
+      </c>
+      <c r="U24">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V24">
+        <v>-0.009586631590732326</v>
+      </c>
+      <c r="W24">
+        <v>0.2521520799245842</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>-0.03994429829471802</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1739719049168108</v>
+      </c>
+      <c r="C25">
+        <v>1997.822359587296</v>
+      </c>
+      <c r="D25">
+        <v>1713.964359587296</v>
+      </c>
+      <c r="E25">
+        <v>-2498.858</v>
+      </c>
+      <c r="F25">
+        <v>939.6420000000001</v>
+      </c>
+      <c r="G25">
+        <v>1223.5</v>
+      </c>
+      <c r="H25">
+        <v>646.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K25">
+        <v>-621.2</v>
+      </c>
+      <c r="L25">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M25">
+        <v>234.6828665026779</v>
+      </c>
+      <c r="N25">
+        <v>-243.6495331693446</v>
+      </c>
+      <c r="O25">
+        <v>-58.47588796064271</v>
+      </c>
+      <c r="P25">
+        <v>-185.1736452087019</v>
+      </c>
+      <c r="Q25">
+        <v>-806.373645208702</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1506504803753057</v>
+      </c>
+      <c r="T25">
+        <v>2.154716885519</v>
+      </c>
+      <c r="U25">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V25">
+        <v>-0.009169821521570051</v>
+      </c>
+      <c r="W25">
+        <v>0.2520479783818496</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>-0.03820758967320859</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1760114823612277</v>
+      </c>
+      <c r="C26">
+        <v>1930.121548653596</v>
+      </c>
+      <c r="D26">
+        <v>1687.117548653596</v>
+      </c>
+      <c r="E26">
+        <v>-2458.004</v>
+      </c>
+      <c r="F26">
+        <v>980.496</v>
+      </c>
+      <c r="G26">
+        <v>1223.5</v>
+      </c>
+      <c r="H26">
+        <v>646.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K26">
+        <v>-621.2</v>
+      </c>
+      <c r="L26">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M26">
+        <v>244.8864693940987</v>
+      </c>
+      <c r="N26">
+        <v>-253.8531360607654</v>
+      </c>
+      <c r="O26">
+        <v>-60.92475265458369</v>
+      </c>
+      <c r="P26">
+        <v>-192.9283834061817</v>
+      </c>
+      <c r="Q26">
+        <v>-814.1283834061817</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1520300919591913</v>
+      </c>
+      <c r="T26">
+        <v>2.183068423486356</v>
+      </c>
+      <c r="U26">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V26">
+        <v>-0.008787745624837966</v>
+      </c>
+      <c r="W26">
+        <v>0.2519525519676762</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>-0.03661560677015818</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1780510598056446</v>
+      </c>
+      <c r="C27">
+        <v>1863.24880140597</v>
+      </c>
+      <c r="D27">
+        <v>1661.098801405969</v>
+      </c>
+      <c r="E27">
+        <v>-2417.15</v>
+      </c>
+      <c r="F27">
+        <v>1021.35</v>
+      </c>
+      <c r="G27">
+        <v>1223.5</v>
+      </c>
+      <c r="H27">
+        <v>646.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K27">
+        <v>-621.2</v>
+      </c>
+      <c r="L27">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M27">
+        <v>255.0900722855195</v>
+      </c>
+      <c r="N27">
+        <v>-264.0567389521862</v>
+      </c>
+      <c r="O27">
+        <v>-63.37361734852468</v>
+      </c>
+      <c r="P27">
+        <v>-200.6831216036615</v>
+      </c>
+      <c r="Q27">
+        <v>-821.8831216036615</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1534464931853139</v>
+      </c>
+      <c r="T27">
+        <v>2.212176002466174</v>
+      </c>
+      <c r="U27">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V27">
+        <v>-0.008436235799844446</v>
+      </c>
+      <c r="W27">
+        <v>0.2518647596666368</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>-0.03515098249935167</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1800906372500615</v>
+      </c>
+      <c r="C28">
+        <v>1797.166388482536</v>
+      </c>
+      <c r="D28">
+        <v>1635.870388482536</v>
+      </c>
+      <c r="E28">
+        <v>-2376.296</v>
+      </c>
+      <c r="F28">
+        <v>1062.204</v>
+      </c>
+      <c r="G28">
+        <v>1223.5</v>
+      </c>
+      <c r="H28">
+        <v>646.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K28">
+        <v>-621.2</v>
+      </c>
+      <c r="L28">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M28">
+        <v>265.2936751769403</v>
+      </c>
+      <c r="N28">
+        <v>-274.260341843607</v>
+      </c>
+      <c r="O28">
+        <v>-65.82248204246567</v>
+      </c>
+      <c r="P28">
+        <v>-208.4378598011413</v>
+      </c>
+      <c r="Q28">
+        <v>-829.6378598011413</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1549011755256559</v>
+      </c>
+      <c r="T28">
+        <v>2.242070272769771</v>
+      </c>
+      <c r="U28">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V28">
+        <v>-0.008111765192158123</v>
+      </c>
+      <c r="W28">
+        <v>0.2517837206195234</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>-0.03379902163399207</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1821302146944784</v>
+      </c>
+      <c r="C29">
+        <v>1731.838838332148</v>
+      </c>
+      <c r="D29">
+        <v>1611.396838332148</v>
+      </c>
+      <c r="E29">
+        <v>-2335.442</v>
+      </c>
+      <c r="F29">
+        <v>1103.058</v>
+      </c>
+      <c r="G29">
+        <v>1223.5</v>
+      </c>
+      <c r="H29">
+        <v>646.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K29">
+        <v>-621.2</v>
+      </c>
+      <c r="L29">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M29">
+        <v>275.497278068361</v>
+      </c>
+      <c r="N29">
+        <v>-284.4639447350277</v>
+      </c>
+      <c r="O29">
+        <v>-68.27134673640666</v>
+      </c>
+      <c r="P29">
+        <v>-216.1925979986211</v>
+      </c>
+      <c r="Q29">
+        <v>-837.3925979986211</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1563957121766923</v>
+      </c>
+      <c r="T29">
+        <v>2.272783564177576</v>
+      </c>
+      <c r="U29">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V29">
+        <v>-0.007811329444300414</v>
+      </c>
+      <c r="W29">
+        <v>0.2517086844647889</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>-0.03254720601791838</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1841697921388953</v>
+      </c>
+      <c r="C30">
+        <v>1667.232770813192</v>
+      </c>
+      <c r="D30">
+        <v>1587.644770813192</v>
+      </c>
+      <c r="E30">
+        <v>-2294.588</v>
+      </c>
+      <c r="F30">
+        <v>1143.912</v>
+      </c>
+      <c r="G30">
+        <v>1223.5</v>
+      </c>
+      <c r="H30">
+        <v>646.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K30">
+        <v>-621.2</v>
+      </c>
+      <c r="L30">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M30">
+        <v>285.7008809597818</v>
+      </c>
+      <c r="N30">
+        <v>-294.6675476264485</v>
+      </c>
+      <c r="O30">
+        <v>-70.72021143034765</v>
+      </c>
+      <c r="P30">
+        <v>-223.9473361961009</v>
+      </c>
+      <c r="Q30">
+        <v>-845.1473361961009</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1579317637347019</v>
+      </c>
+      <c r="T30">
+        <v>2.304350002568931</v>
+      </c>
+      <c r="U30">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V30">
+        <v>-0.007532353392718255</v>
+      </c>
+      <c r="W30">
+        <v>0.2516390080353925</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>-0.03138480580299263</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1862093695833121</v>
+      </c>
+      <c r="C31">
+        <v>1603.31674529519</v>
+      </c>
+      <c r="D31">
+        <v>1564.58274529519</v>
+      </c>
+      <c r="E31">
+        <v>-2253.734</v>
+      </c>
+      <c r="F31">
+        <v>1184.766</v>
+      </c>
+      <c r="G31">
+        <v>1223.5</v>
+      </c>
+      <c r="H31">
+        <v>646.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K31">
+        <v>-621.2</v>
+      </c>
+      <c r="L31">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M31">
+        <v>295.9044838512025</v>
+      </c>
+      <c r="N31">
+        <v>-304.8711505178692</v>
+      </c>
+      <c r="O31">
+        <v>-73.16907612428861</v>
+      </c>
+      <c r="P31">
+        <v>-231.7020743935806</v>
+      </c>
+      <c r="Q31">
+        <v>-852.9020743935807</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1595110843506836</v>
+      </c>
+      <c r="T31">
+        <v>2.33680563640793</v>
+      </c>
+      <c r="U31">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V31">
+        <v>-0.007272617068831421</v>
+      </c>
+      <c r="W31">
+        <v>0.2515741368769889</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>-0.03030257112013102</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.188248947027729</v>
+      </c>
+      <c r="C32">
+        <v>1540.061121809642</v>
+      </c>
+      <c r="D32">
+        <v>1542.181121809642</v>
+      </c>
+      <c r="E32">
+        <v>-2212.88</v>
+      </c>
+      <c r="F32">
+        <v>1225.62</v>
+      </c>
+      <c r="G32">
+        <v>1223.5</v>
+      </c>
+      <c r="H32">
+        <v>646.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K32">
+        <v>-621.2</v>
+      </c>
+      <c r="L32">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M32">
+        <v>306.1080867426234</v>
+      </c>
+      <c r="N32">
+        <v>-315.0747534092901</v>
+      </c>
+      <c r="O32">
+        <v>-75.61794081822961</v>
+      </c>
+      <c r="P32">
+        <v>-239.4568125910604</v>
+      </c>
+      <c r="Q32">
+        <v>-860.6568125910605</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1611355284128363</v>
+      </c>
+      <c r="T32">
+        <v>2.370188574070901</v>
+      </c>
+      <c r="U32">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V32">
+        <v>-0.007030196499870372</v>
+      </c>
+      <c r="W32">
+        <v>0.2515135904624789</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>-0.0292924854161265</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1902885244721459</v>
+      </c>
+      <c r="C33">
+        <v>1477.437933960714</v>
+      </c>
+      <c r="D33">
+        <v>1520.411933960714</v>
+      </c>
+      <c r="E33">
+        <v>-2172.026</v>
+      </c>
+      <c r="F33">
+        <v>1266.474</v>
+      </c>
+      <c r="G33">
+        <v>1223.5</v>
+      </c>
+      <c r="H33">
+        <v>646.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K33">
+        <v>-621.2</v>
+      </c>
+      <c r="L33">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M33">
+        <v>316.3116896340441</v>
+      </c>
+      <c r="N33">
+        <v>-325.2783563007108</v>
+      </c>
+      <c r="O33">
+        <v>-78.06680551217059</v>
+      </c>
+      <c r="P33">
+        <v>-247.2115507885402</v>
+      </c>
+      <c r="Q33">
+        <v>-868.4115507885402</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1628070578101238</v>
+      </c>
+      <c r="T33">
+        <v>2.404539133115406</v>
+      </c>
+      <c r="U33">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V33">
+        <v>-0.00680341596761649</v>
+      </c>
+      <c r="W33">
+        <v>0.2514569502682599</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>-0.02834756653173542</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1923281019165629</v>
+      </c>
+      <c r="C34">
+        <v>1415.420772449932</v>
+      </c>
+      <c r="D34">
+        <v>1499.248772449932</v>
+      </c>
+      <c r="E34">
+        <v>-2131.172</v>
+      </c>
+      <c r="F34">
+        <v>1307.328</v>
+      </c>
+      <c r="G34">
+        <v>1223.5</v>
+      </c>
+      <c r="H34">
+        <v>646.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K34">
+        <v>-621.2</v>
+      </c>
+      <c r="L34">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M34">
+        <v>326.5152925254649</v>
+      </c>
+      <c r="N34">
+        <v>-335.4819591921316</v>
+      </c>
+      <c r="O34">
+        <v>-80.51567020611159</v>
+      </c>
+      <c r="P34">
+        <v>-254.96628898602</v>
+      </c>
+      <c r="Q34">
+        <v>-876.16628898602</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1645277498367432</v>
+      </c>
+      <c r="T34">
+        <v>2.439900002720045</v>
+      </c>
+      <c r="U34">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V34">
+        <v>-0.006590809218628474</v>
+      </c>
+      <c r="W34">
+        <v>0.2514038500861795</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>-0.02746170507761869</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1943676793609798</v>
+      </c>
+      <c r="C35">
+        <v>1353.984678194903</v>
+      </c>
+      <c r="D35">
+        <v>1478.666678194903</v>
+      </c>
+      <c r="E35">
+        <v>-2090.318</v>
+      </c>
+      <c r="F35">
+        <v>1348.182</v>
+      </c>
+      <c r="G35">
+        <v>1223.5</v>
+      </c>
+      <c r="H35">
+        <v>646.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K35">
+        <v>-621.2</v>
+      </c>
+      <c r="L35">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M35">
+        <v>336.7188954168857</v>
+      </c>
+      <c r="N35">
+        <v>-345.6855620835524</v>
+      </c>
+      <c r="O35">
+        <v>-82.96453490005258</v>
+      </c>
+      <c r="P35">
+        <v>-262.7210271834999</v>
+      </c>
+      <c r="Q35">
+        <v>-883.9210271835</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1662998058044558</v>
+      </c>
+      <c r="T35">
+        <v>2.47631642067109</v>
+      </c>
+      <c r="U35">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V35">
+        <v>-0.006391087727154883</v>
+      </c>
+      <c r="W35">
+        <v>0.2513539680969526</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>-0.02662953219647868</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1964072568053966</v>
+      </c>
+      <c r="C36">
+        <v>1293.106044132588</v>
+      </c>
+      <c r="D36">
+        <v>1458.642044132588</v>
+      </c>
+      <c r="E36">
+        <v>-2049.464</v>
+      </c>
+      <c r="F36">
+        <v>1389.036</v>
+      </c>
+      <c r="G36">
+        <v>1223.5</v>
+      </c>
+      <c r="H36">
+        <v>646.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K36">
+        <v>-621.2</v>
+      </c>
+      <c r="L36">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M36">
+        <v>346.9224983083065</v>
+      </c>
+      <c r="N36">
+        <v>-355.8891649749732</v>
+      </c>
+      <c r="O36">
+        <v>-85.41339959399356</v>
+      </c>
+      <c r="P36">
+        <v>-270.4757653809796</v>
+      </c>
+      <c r="Q36">
+        <v>-891.6757653809797</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1681255604378567</v>
+      </c>
+      <c r="T36">
+        <v>2.513836366438834</v>
+      </c>
+      <c r="U36">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V36">
+        <v>-0.006203114558709152</v>
+      </c>
+      <c r="W36">
+        <v>0.251307020342386</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>-0.02584631066128806</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1984468342498135</v>
+      </c>
+      <c r="C37">
+        <v>1232.762524894854</v>
+      </c>
+      <c r="D37">
+        <v>1439.152524894854</v>
+      </c>
+      <c r="E37">
+        <v>-2008.61</v>
+      </c>
+      <c r="F37">
+        <v>1429.89</v>
+      </c>
+      <c r="G37">
+        <v>1223.5</v>
+      </c>
+      <c r="H37">
+        <v>646.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K37">
+        <v>-621.2</v>
+      </c>
+      <c r="L37">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M37">
+        <v>357.1261011997273</v>
+      </c>
+      <c r="N37">
+        <v>-366.092767866394</v>
+      </c>
+      <c r="O37">
+        <v>-87.86226428793456</v>
+      </c>
+      <c r="P37">
+        <v>-278.2305035784594</v>
+      </c>
+      <c r="Q37">
+        <v>-899.4305035784595</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1700074921369006</v>
+      </c>
+      <c r="T37">
+        <v>2.552510772076355</v>
+      </c>
+      <c r="U37">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V37">
+        <v>-0.006025882714174604</v>
+      </c>
+      <c r="W37">
+        <v>0.2512627553166518</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>-0.02510784464239424</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.2004864116942305</v>
+      </c>
+      <c r="C38">
+        <v>1172.932953629723</v>
+      </c>
+      <c r="D38">
+        <v>1420.176953629723</v>
+      </c>
+      <c r="E38">
+        <v>-1967.756</v>
+      </c>
+      <c r="F38">
+        <v>1470.744</v>
+      </c>
+      <c r="G38">
+        <v>1223.5</v>
+      </c>
+      <c r="H38">
+        <v>646.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K38">
+        <v>-621.2</v>
+      </c>
+      <c r="L38">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M38">
+        <v>367.329704091148</v>
+      </c>
+      <c r="N38">
+        <v>-376.2963707578147</v>
+      </c>
+      <c r="O38">
+        <v>-90.31112898187553</v>
+      </c>
+      <c r="P38">
+        <v>-285.9852417759392</v>
+      </c>
+      <c r="Q38">
+        <v>-907.1852417759392</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1719482342015397</v>
+      </c>
+      <c r="T38">
+        <v>2.592393752890048</v>
+      </c>
+      <c r="U38">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V38">
+        <v>-0.005858497083225311</v>
+      </c>
+      <c r="W38">
+        <v>0.251220949459014</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>-0.02441040451343879</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.2025259891386473</v>
+      </c>
+      <c r="C39">
+        <v>1113.597265317382</v>
+      </c>
+      <c r="D39">
+        <v>1401.695265317382</v>
+      </c>
+      <c r="E39">
+        <v>-1926.902</v>
+      </c>
+      <c r="F39">
+        <v>1511.598</v>
+      </c>
+      <c r="G39">
+        <v>1223.5</v>
+      </c>
+      <c r="H39">
+        <v>646.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K39">
+        <v>-621.2</v>
+      </c>
+      <c r="L39">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M39">
+        <v>377.5333069825688</v>
+      </c>
+      <c r="N39">
+        <v>-386.4999736492355</v>
+      </c>
+      <c r="O39">
+        <v>-92.75999367581652</v>
+      </c>
+      <c r="P39">
+        <v>-293.739979973419</v>
+      </c>
+      <c r="Q39">
+        <v>-914.939979973419</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1739505871253737</v>
+      </c>
+      <c r="T39">
+        <v>2.633542860078779</v>
+      </c>
+      <c r="U39">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V39">
+        <v>-0.005700159324219221</v>
+      </c>
+      <c r="W39">
+        <v>0.2511814033774646</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>-0.02375066385091351</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.2045655665830642</v>
+      </c>
+      <c r="C40">
+        <v>1054.736425996895</v>
+      </c>
+      <c r="D40">
+        <v>1383.688425996895</v>
+      </c>
+      <c r="E40">
+        <v>-1886.048</v>
+      </c>
+      <c r="F40">
+        <v>1552.452</v>
+      </c>
+      <c r="G40">
+        <v>1223.5</v>
+      </c>
+      <c r="H40">
+        <v>646.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K40">
+        <v>-621.2</v>
+      </c>
+      <c r="L40">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M40">
+        <v>387.7369098739896</v>
+      </c>
+      <c r="N40">
+        <v>-396.7035765406563</v>
+      </c>
+      <c r="O40">
+        <v>-95.20885836975751</v>
+      </c>
+      <c r="P40">
+        <v>-301.4947181708988</v>
+      </c>
+      <c r="Q40">
+        <v>-922.6947181708988</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1760175320790087</v>
+      </c>
+      <c r="T40">
+        <v>2.676019357821985</v>
+      </c>
+      <c r="U40">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V40">
+        <v>-0.00555015513147661</v>
+      </c>
+      <c r="W40">
+        <v>0.2511439386686285</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>-0.02312564638115244</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.2066051440274811</v>
+      </c>
+      <c r="C41">
+        <v>996.3323673788591</v>
+      </c>
+      <c r="D41">
+        <v>1366.138367378859</v>
+      </c>
+      <c r="E41">
+        <v>-1845.194</v>
+      </c>
+      <c r="F41">
+        <v>1593.306</v>
+      </c>
+      <c r="G41">
+        <v>1223.5</v>
+      </c>
+      <c r="H41">
+        <v>646.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K41">
+        <v>-621.2</v>
+      </c>
+      <c r="L41">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M41">
+        <v>397.9405127654104</v>
+      </c>
+      <c r="N41">
+        <v>-406.9071794320771</v>
+      </c>
+      <c r="O41">
+        <v>-97.6577230636985</v>
+      </c>
+      <c r="P41">
+        <v>-309.2494563683786</v>
+      </c>
+      <c r="Q41">
+        <v>-930.4494563683786</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1781522457196482</v>
+      </c>
+      <c r="T41">
+        <v>2.719888527622345</v>
+      </c>
+      <c r="U41">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V41">
+        <v>-0.005407843461438748</v>
+      </c>
+      <c r="W41">
+        <v>0.2511083952269121</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>-0.02253268108932804</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.208644721471898</v>
+      </c>
+      <c r="C42">
+        <v>938.3679263717847</v>
+      </c>
+      <c r="D42">
+        <v>1349.027926371785</v>
+      </c>
+      <c r="E42">
+        <v>-1804.34</v>
+      </c>
+      <c r="F42">
+        <v>1634.16</v>
+      </c>
+      <c r="G42">
+        <v>1223.5</v>
+      </c>
+      <c r="H42">
+        <v>646.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K42">
+        <v>-621.2</v>
+      </c>
+      <c r="L42">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M42">
+        <v>408.1441156568312</v>
+      </c>
+      <c r="N42">
+        <v>-417.1107823234979</v>
+      </c>
+      <c r="O42">
+        <v>-100.1065877576395</v>
+      </c>
+      <c r="P42">
+        <v>-317.0041945658584</v>
+      </c>
+      <c r="Q42">
+        <v>-938.2041945658584</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1803581164816423</v>
+      </c>
+      <c r="T42">
+        <v>2.765220003082717</v>
+      </c>
+      <c r="U42">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V42">
+        <v>-0.005272647374902779</v>
+      </c>
+      <c r="W42">
+        <v>0.2510746289572815</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>-0.02196936406209482</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.2106842989163149</v>
+      </c>
+      <c r="C43">
+        <v>880.8267890967377</v>
+      </c>
+      <c r="D43">
+        <v>1332.340789096738</v>
+      </c>
+      <c r="E43">
+        <v>-1763.486</v>
+      </c>
+      <c r="F43">
+        <v>1675.014</v>
+      </c>
+      <c r="G43">
+        <v>1223.5</v>
+      </c>
+      <c r="H43">
+        <v>646.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K43">
+        <v>-621.2</v>
+      </c>
+      <c r="L43">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M43">
+        <v>418.347718548252</v>
+      </c>
+      <c r="N43">
+        <v>-427.3143852149187</v>
+      </c>
+      <c r="O43">
+        <v>-102.5554524515805</v>
+      </c>
+      <c r="P43">
+        <v>-324.7589327633382</v>
+      </c>
+      <c r="Q43">
+        <v>-945.9589327633382</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1826387625237041</v>
+      </c>
+      <c r="T43">
+        <v>2.812088138728187</v>
+      </c>
+      <c r="U43">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V43">
+        <v>-0.005144046219417346</v>
+      </c>
+      <c r="W43">
+        <v>0.2510425098227549</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>-0.02143352591423886</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.2127238763607318</v>
+      </c>
+      <c r="C44">
+        <v>823.6934390063657</v>
+      </c>
+      <c r="D44">
+        <v>1316.061439006366</v>
+      </c>
+      <c r="E44">
+        <v>-1722.632</v>
+      </c>
+      <c r="F44">
+        <v>1715.868</v>
+      </c>
+      <c r="G44">
+        <v>1223.5</v>
+      </c>
+      <c r="H44">
+        <v>646.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K44">
+        <v>-621.2</v>
+      </c>
+      <c r="L44">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M44">
+        <v>428.5513214396727</v>
+      </c>
+      <c r="N44">
+        <v>-437.5179881063394</v>
+      </c>
+      <c r="O44">
+        <v>-105.0043171455215</v>
+      </c>
+      <c r="P44">
+        <v>-332.513670960818</v>
+      </c>
+      <c r="Q44">
+        <v>-953.713670960818</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1849980515327334</v>
+      </c>
+      <c r="T44">
+        <v>2.860572416982121</v>
+      </c>
+      <c r="U44">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V44">
+        <v>-0.005021568928478838</v>
+      </c>
+      <c r="W44">
+        <v>0.2510119201708248</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>-0.02092320386866175</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.2147634538051487</v>
+      </c>
+      <c r="C45">
+        <v>766.9531087614853</v>
+      </c>
+      <c r="D45">
+        <v>1300.175108761485</v>
+      </c>
+      <c r="E45">
+        <v>-1681.778</v>
+      </c>
+      <c r="F45">
+        <v>1756.722</v>
+      </c>
+      <c r="G45">
+        <v>1223.5</v>
+      </c>
+      <c r="H45">
+        <v>646.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K45">
+        <v>-621.2</v>
+      </c>
+      <c r="L45">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M45">
+        <v>438.7549243310935</v>
+      </c>
+      <c r="N45">
+        <v>-447.7215909977602</v>
+      </c>
+      <c r="O45">
+        <v>-107.4531818394624</v>
+      </c>
+      <c r="P45">
+        <v>-340.2684091582977</v>
+      </c>
+      <c r="Q45">
+        <v>-961.4684091582978</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1874401226122551</v>
+      </c>
+      <c r="T45">
+        <v>2.910757897981808</v>
+      </c>
+      <c r="U45">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V45">
+        <v>-0.004904788255723515</v>
+      </c>
+      <c r="W45">
+        <v>0.250982753293403</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>-0.02043661773218131</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.2168030312495656</v>
+      </c>
+      <c r="C46">
+        <v>710.5917355515207</v>
+      </c>
+      <c r="D46">
+        <v>1284.667735551521</v>
+      </c>
+      <c r="E46">
+        <v>-1640.924</v>
+      </c>
+      <c r="F46">
+        <v>1797.576</v>
+      </c>
+      <c r="G46">
+        <v>1223.5</v>
+      </c>
+      <c r="H46">
+        <v>646.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K46">
+        <v>-621.2</v>
+      </c>
+      <c r="L46">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M46">
+        <v>448.9585272225143</v>
+      </c>
+      <c r="N46">
+        <v>-457.925193889181</v>
+      </c>
+      <c r="O46">
+        <v>-109.9020465334034</v>
+      </c>
+      <c r="P46">
+        <v>-348.0231473557776</v>
+      </c>
+      <c r="Q46">
+        <v>-969.2231473557777</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1899694105160454</v>
+      </c>
+      <c r="T46">
+        <v>2.962735717588626</v>
+      </c>
+      <c r="U46">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V46">
+        <v>-0.004793315795366163</v>
+      </c>
+      <c r="W46">
+        <v>0.2509549121831368</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>-0.01997214914735901</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.2188426086939825</v>
+      </c>
+      <c r="C47">
+        <v>654.5959195746552</v>
+      </c>
+      <c r="D47">
+        <v>1269.525919574655</v>
+      </c>
+      <c r="E47">
+        <v>-1600.07</v>
+      </c>
+      <c r="F47">
+        <v>1838.43</v>
+      </c>
+      <c r="G47">
+        <v>1223.5</v>
+      </c>
+      <c r="H47">
+        <v>646.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K47">
+        <v>-621.2</v>
+      </c>
+      <c r="L47">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M47">
+        <v>459.1621301139351</v>
+      </c>
+      <c r="N47">
+        <v>-468.1287967806018</v>
+      </c>
+      <c r="O47">
+        <v>-112.3509112273444</v>
+      </c>
+      <c r="P47">
+        <v>-355.7778855532574</v>
+      </c>
+      <c r="Q47">
+        <v>-976.9778855532575</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.192590672525428</v>
+      </c>
+      <c r="T47">
+        <v>3.016603639726601</v>
+      </c>
+      <c r="U47">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V47">
+        <v>-0.004686797666580249</v>
+      </c>
+      <c r="W47">
+        <v>0.2509283084555491</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>-0.01952832361075107</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.2208821861383994</v>
+      </c>
+      <c r="C48">
+        <v>598.9528854200312</v>
+      </c>
+      <c r="D48">
+        <v>1254.736885420032</v>
+      </c>
+      <c r="E48">
+        <v>-1559.216</v>
+      </c>
+      <c r="F48">
+        <v>1879.284</v>
+      </c>
+      <c r="G48">
+        <v>1223.5</v>
+      </c>
+      <c r="H48">
+        <v>646.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K48">
+        <v>-621.2</v>
+      </c>
+      <c r="L48">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M48">
+        <v>469.3657330053559</v>
+      </c>
+      <c r="N48">
+        <v>-478.3323996720226</v>
+      </c>
+      <c r="O48">
+        <v>-114.7997759212854</v>
+      </c>
+      <c r="P48">
+        <v>-363.5326237507372</v>
+      </c>
+      <c r="Q48">
+        <v>-984.7326237507373</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1953090183129359</v>
+      </c>
+      <c r="T48">
+        <v>3.072466670091908</v>
+      </c>
+      <c r="U48">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V48">
+        <v>-0.004584910760785025</v>
+      </c>
+      <c r="W48">
+        <v>0.2509028614117695</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>-0.01910379483660418</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.2229217635828163</v>
+      </c>
+      <c r="C49">
+        <v>543.6504461180814</v>
+      </c>
+      <c r="D49">
+        <v>1240.288446118082</v>
+      </c>
+      <c r="E49">
+        <v>-1518.362</v>
+      </c>
+      <c r="F49">
+        <v>1920.138</v>
+      </c>
+      <c r="G49">
+        <v>1223.5</v>
+      </c>
+      <c r="H49">
+        <v>646.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K49">
+        <v>-621.2</v>
+      </c>
+      <c r="L49">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M49">
+        <v>479.5693358967766</v>
+      </c>
+      <c r="N49">
+        <v>-488.5360025634433</v>
+      </c>
+      <c r="O49">
+        <v>-117.2486406152264</v>
+      </c>
+      <c r="P49">
+        <v>-371.2873619482169</v>
+      </c>
+      <c r="Q49">
+        <v>-992.487361948217</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1981299431867649</v>
+      </c>
+      <c r="T49">
+        <v>3.130437739338925</v>
+      </c>
+      <c r="U49">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V49">
+        <v>-0.004487359468002366</v>
+      </c>
+      <c r="W49">
+        <v>0.2508784972209168</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>-0.01869733111667649</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.2249613410272331</v>
+      </c>
+      <c r="C50">
+        <v>488.6769696463755</v>
+      </c>
+      <c r="D50">
+        <v>1226.168969646376</v>
+      </c>
+      <c r="E50">
+        <v>-1477.508</v>
+      </c>
+      <c r="F50">
+        <v>1960.992</v>
+      </c>
+      <c r="G50">
+        <v>1223.5</v>
+      </c>
+      <c r="H50">
+        <v>646.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K50">
+        <v>-621.2</v>
+      </c>
+      <c r="L50">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M50">
+        <v>489.7729387881974</v>
+      </c>
+      <c r="N50">
+        <v>-498.7396054548641</v>
+      </c>
+      <c r="O50">
+        <v>-119.6975053091674</v>
+      </c>
+      <c r="P50">
+        <v>-379.0421001456967</v>
+      </c>
+      <c r="Q50">
+        <v>-1000.242100145697</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2010593651711258</v>
+      </c>
+      <c r="T50">
+        <v>3.190638465095443</v>
+      </c>
+      <c r="U50">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V50">
+        <v>-0.004393872812418983</v>
+      </c>
+      <c r="W50">
+        <v>0.2508551482046828</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>-0.0183078033850792</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.22700091847165</v>
+      </c>
+      <c r="C51">
+        <v>434.0213476975005</v>
+      </c>
+      <c r="D51">
+        <v>1212.3673476975</v>
+      </c>
+      <c r="E51">
+        <v>-1436.654</v>
+      </c>
+      <c r="F51">
+        <v>2001.846</v>
+      </c>
+      <c r="G51">
+        <v>1223.5</v>
+      </c>
+      <c r="H51">
+        <v>646.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K51">
+        <v>-621.2</v>
+      </c>
+      <c r="L51">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M51">
+        <v>499.9765416796182</v>
+      </c>
+      <c r="N51">
+        <v>-508.9432083462849</v>
+      </c>
+      <c r="O51">
+        <v>-122.1463700031084</v>
+      </c>
+      <c r="P51">
+        <v>-386.7968383431765</v>
+      </c>
+      <c r="Q51">
+        <v>-1007.996838343177</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.204103666448991</v>
+      </c>
+      <c r="T51">
+        <v>3.253200003626726</v>
+      </c>
+      <c r="U51">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V51">
+        <v>-0.004304201938696147</v>
+      </c>
+      <c r="W51">
+        <v>0.2508327522095197</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>-0.01793417474456738</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.229040495916067</v>
+      </c>
+      <c r="C52">
+        <v>379.6729665327391</v>
+      </c>
+      <c r="D52">
+        <v>1198.872966532739</v>
+      </c>
+      <c r="E52">
+        <v>-1395.8</v>
+      </c>
+      <c r="F52">
+        <v>2042.7</v>
+      </c>
+      <c r="G52">
+        <v>1223.5</v>
+      </c>
+      <c r="H52">
+        <v>646.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K52">
+        <v>-621.2</v>
+      </c>
+      <c r="L52">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M52">
+        <v>510.180144571039</v>
+      </c>
+      <c r="N52">
+        <v>-519.1468112377056</v>
+      </c>
+      <c r="O52">
+        <v>-124.5952346970493</v>
+      </c>
+      <c r="P52">
+        <v>-394.5515765406562</v>
+      </c>
+      <c r="Q52">
+        <v>-1015.751576540656</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.2072697397779708</v>
+      </c>
+      <c r="T52">
+        <v>3.318264003699261</v>
+      </c>
+      <c r="U52">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V52">
+        <v>-0.004218117899922223</v>
+      </c>
+      <c r="W52">
+        <v>0.2508112520541631</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>-0.01757549124967572</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2310800733604839</v>
+      </c>
+      <c r="C53">
+        <v>325.6216797608149</v>
+      </c>
+      <c r="D53">
+        <v>1185.675679760815</v>
+      </c>
+      <c r="E53">
+        <v>-1354.946</v>
+      </c>
+      <c r="F53">
+        <v>2083.554</v>
+      </c>
+      <c r="G53">
+        <v>1223.5</v>
+      </c>
+      <c r="H53">
+        <v>646.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K53">
+        <v>-621.2</v>
+      </c>
+      <c r="L53">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M53">
+        <v>520.3837474624597</v>
+      </c>
+      <c r="N53">
+        <v>-529.3504141291264</v>
+      </c>
+      <c r="O53">
+        <v>-127.0440993909903</v>
+      </c>
+      <c r="P53">
+        <v>-402.3063147381361</v>
+      </c>
+      <c r="Q53">
+        <v>-1023.506314738136</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.2105650405897661</v>
+      </c>
+      <c r="T53">
+        <v>3.385983677244144</v>
+      </c>
+      <c r="U53">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V53">
+        <v>-0.004135409705806102</v>
+      </c>
+      <c r="W53">
+        <v>0.2507905950421538</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>-0.01723087377419219</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2331196508049007</v>
+      </c>
+      <c r="C54">
+        <v>271.8577828949892</v>
+      </c>
+      <c r="D54">
+        <v>1172.765782894989</v>
+      </c>
+      <c r="E54">
+        <v>-1314.092</v>
+      </c>
+      <c r="F54">
+        <v>2124.408</v>
+      </c>
+      <c r="G54">
+        <v>1223.5</v>
+      </c>
+      <c r="H54">
+        <v>646.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K54">
+        <v>-621.2</v>
+      </c>
+      <c r="L54">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M54">
+        <v>530.5873503538805</v>
+      </c>
+      <c r="N54">
+        <v>-539.5540170205472</v>
+      </c>
+      <c r="O54">
+        <v>-129.4929640849313</v>
+      </c>
+      <c r="P54">
+        <v>-410.0610529356159</v>
+      </c>
+      <c r="Q54">
+        <v>-1031.261052935616</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2139976456020529</v>
+      </c>
+      <c r="T54">
+        <v>3.456525003853396</v>
+      </c>
+      <c r="U54">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V54">
+        <v>-0.004055882596079061</v>
+      </c>
+      <c r="W54">
+        <v>0.2507707325306064</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>-0.01689951081699603</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2351592282493177</v>
+      </c>
+      <c r="C55">
+        <v>218.3719895544118</v>
+      </c>
+      <c r="D55">
+        <v>1160.133989554412</v>
+      </c>
+      <c r="E55">
+        <v>-1273.238</v>
+      </c>
+      <c r="F55">
+        <v>2165.262</v>
+      </c>
+      <c r="G55">
+        <v>1223.5</v>
+      </c>
+      <c r="H55">
+        <v>646.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K55">
+        <v>-621.2</v>
+      </c>
+      <c r="L55">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M55">
+        <v>540.7909532453014</v>
+      </c>
+      <c r="N55">
+        <v>-549.757619911968</v>
+      </c>
+      <c r="O55">
+        <v>-131.9418287788723</v>
+      </c>
+      <c r="P55">
+        <v>-417.8157911330957</v>
+      </c>
+      <c r="Q55">
+        <v>-1039.015791133096</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2175763189127349</v>
+      </c>
+      <c r="T55">
+        <v>3.530068089041767</v>
+      </c>
+      <c r="U55">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V55">
+        <v>-0.003979356509360587</v>
+      </c>
+      <c r="W55">
+        <v>0.2507516195477967</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>-0.01658065212233573</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2371988056937346</v>
+      </c>
+      <c r="C56">
+        <v>165.1554091870985</v>
+      </c>
+      <c r="D56">
+        <v>1147.771409187098</v>
+      </c>
+      <c r="E56">
+        <v>-1232.384</v>
+      </c>
+      <c r="F56">
+        <v>2206.116</v>
+      </c>
+      <c r="G56">
+        <v>1223.5</v>
+      </c>
+      <c r="H56">
+        <v>646.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K56">
+        <v>-621.2</v>
+      </c>
+      <c r="L56">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M56">
+        <v>550.9945561367221</v>
+      </c>
+      <c r="N56">
+        <v>-559.9612228033888</v>
+      </c>
+      <c r="O56">
+        <v>-134.3906934728133</v>
+      </c>
+      <c r="P56">
+        <v>-425.5705293305755</v>
+      </c>
+      <c r="Q56">
+        <v>-1046.770529330576</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2213105867151857</v>
+      </c>
+      <c r="T56">
+        <v>3.60680869967311</v>
+      </c>
+      <c r="U56">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V56">
+        <v>-0.003905664722150207</v>
+      </c>
+      <c r="W56">
+        <v>0.2507332144532392</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>-0.01627360300895919</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2392383831381514</v>
+      </c>
+      <c r="C57">
+        <v>112.1995262022065</v>
+      </c>
+      <c r="D57">
+        <v>1135.669526202207</v>
+      </c>
+      <c r="E57">
+        <v>-1191.53</v>
+      </c>
+      <c r="F57">
+        <v>2246.97</v>
+      </c>
+      <c r="G57">
+        <v>1223.5</v>
+      </c>
+      <c r="H57">
+        <v>646.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K57">
+        <v>-621.2</v>
+      </c>
+      <c r="L57">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M57">
+        <v>561.1981590281429</v>
+      </c>
+      <c r="N57">
+        <v>-570.1648256948096</v>
+      </c>
+      <c r="O57">
+        <v>-136.8395581667543</v>
+      </c>
+      <c r="P57">
+        <v>-433.3252675280553</v>
+      </c>
+      <c r="Q57">
+        <v>-1054.525267528055</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2252108219755231</v>
+      </c>
+      <c r="T57">
+        <v>3.68696000411029</v>
+      </c>
+      <c r="U57">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V57">
+        <v>-0.003834652636292931</v>
+      </c>
+      <c r="W57">
+        <v>0.2507154786348473</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>-0.01597771931788716</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2412779605825683</v>
+      </c>
+      <c r="C58">
+        <v>59.49618040869382</v>
+      </c>
+      <c r="D58">
+        <v>1123.820180408694</v>
+      </c>
+      <c r="E58">
+        <v>-1150.676</v>
+      </c>
+      <c r="F58">
+        <v>2287.824</v>
+      </c>
+      <c r="G58">
+        <v>1223.5</v>
+      </c>
+      <c r="H58">
+        <v>646.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K58">
+        <v>-621.2</v>
+      </c>
+      <c r="L58">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M58">
+        <v>571.4017619195637</v>
+      </c>
+      <c r="N58">
+        <v>-580.3684285862304</v>
+      </c>
+      <c r="O58">
+        <v>-139.2884228606953</v>
+      </c>
+      <c r="P58">
+        <v>-441.0800057255351</v>
+      </c>
+      <c r="Q58">
+        <v>-1062.280005725535</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.229288340656785</v>
+      </c>
+      <c r="T58">
+        <v>3.770754549658251</v>
+      </c>
+      <c r="U58">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V58">
+        <v>-0.003766176696359127</v>
+      </c>
+      <c r="W58">
+        <v>0.2506983762385409</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>-0.01569240290149643</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2433175380269852</v>
+      </c>
+      <c r="C59">
+        <v>7.037548665920895</v>
+      </c>
+      <c r="D59">
+        <v>1112.215548665921</v>
+      </c>
+      <c r="E59">
+        <v>-1109.822</v>
+      </c>
+      <c r="F59">
+        <v>2328.678</v>
+      </c>
+      <c r="G59">
+        <v>1223.5</v>
+      </c>
+      <c r="H59">
+        <v>646.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K59">
+        <v>-621.2</v>
+      </c>
+      <c r="L59">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M59">
+        <v>581.6053648109845</v>
+      </c>
+      <c r="N59">
+        <v>-590.5720314776512</v>
+      </c>
+      <c r="O59">
+        <v>-141.7372875546363</v>
+      </c>
+      <c r="P59">
+        <v>-448.8347439230149</v>
+      </c>
+      <c r="Q59">
+        <v>-1070.034743923015</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2335555113697335</v>
+      </c>
+      <c r="T59">
+        <v>3.858446515929374</v>
+      </c>
+      <c r="U59">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V59">
+        <v>-0.003700103420984406</v>
+      </c>
+      <c r="W59">
+        <v>0.2506818739263155</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>-0.01541709758743504</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2453571154714021</v>
+      </c>
+      <c r="C60">
+        <v>-45.18387234049123</v>
+      </c>
+      <c r="D60">
+        <v>1100.848127659509</v>
+      </c>
+      <c r="E60">
+        <v>-1068.968</v>
+      </c>
+      <c r="F60">
+        <v>2369.532</v>
+      </c>
+      <c r="G60">
+        <v>1223.5</v>
+      </c>
+      <c r="H60">
+        <v>646.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K60">
+        <v>-621.2</v>
+      </c>
+      <c r="L60">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M60">
+        <v>591.8089677024051</v>
+      </c>
+      <c r="N60">
+        <v>-600.7756343690718</v>
+      </c>
+      <c r="O60">
+        <v>-144.1861522485772</v>
+      </c>
+      <c r="P60">
+        <v>-456.5894821204946</v>
+      </c>
+      <c r="Q60">
+        <v>-1077.789482120495</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2380258806880605</v>
+      </c>
+      <c r="T60">
+        <v>3.950314290118167</v>
+      </c>
+      <c r="U60">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V60">
+        <v>-0.00363630853441571</v>
+      </c>
+      <c r="W60">
+        <v>0.2506659406593392</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>-0.01515128556006551</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.247396692915819</v>
+      </c>
+      <c r="C61">
+        <v>-97.1752822772728</v>
+      </c>
+      <c r="D61">
+        <v>1089.710717722727</v>
+      </c>
+      <c r="E61">
+        <v>-1028.114</v>
+      </c>
+      <c r="F61">
+        <v>2410.386</v>
+      </c>
+      <c r="G61">
+        <v>1223.5</v>
+      </c>
+      <c r="H61">
+        <v>646.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K61">
+        <v>-621.2</v>
+      </c>
+      <c r="L61">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M61">
+        <v>602.012570593826</v>
+      </c>
+      <c r="N61">
+        <v>-610.9792372604927</v>
+      </c>
+      <c r="O61">
+        <v>-146.6350169425182</v>
+      </c>
+      <c r="P61">
+        <v>-464.3442203179745</v>
+      </c>
+      <c r="Q61">
+        <v>-1085.544220317975</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2427143168024034</v>
+      </c>
+      <c r="T61">
+        <v>4.04666341914544</v>
+      </c>
+      <c r="U61">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V61">
+        <v>-0.003574676186374766</v>
+      </c>
+      <c r="W61">
+        <v>0.2506505475031078</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>-0.0148944841098948</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2494362703602359</v>
+      </c>
+      <c r="C62">
+        <v>-148.9435923698456</v>
+      </c>
+      <c r="D62">
+        <v>1078.796407630154</v>
+      </c>
+      <c r="E62">
+        <v>-987.2600000000002</v>
+      </c>
+      <c r="F62">
+        <v>2451.24</v>
+      </c>
+      <c r="G62">
+        <v>1223.5</v>
+      </c>
+      <c r="H62">
+        <v>646.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K62">
+        <v>-621.2</v>
+      </c>
+      <c r="L62">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M62">
+        <v>612.2161734852467</v>
+      </c>
+      <c r="N62">
+        <v>-621.1828401519134</v>
+      </c>
+      <c r="O62">
+        <v>-149.0838816364592</v>
+      </c>
+      <c r="P62">
+        <v>-472.0989585154542</v>
+      </c>
+      <c r="Q62">
+        <v>-1093.298958515454</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2476371747224635</v>
+      </c>
+      <c r="T62">
+        <v>4.147830004624076</v>
+      </c>
+      <c r="U62">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V62">
+        <v>-0.003515098249935186</v>
+      </c>
+      <c r="W62">
+        <v>0.2506356674520842</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>-0.01464624270806336</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2514758478046528</v>
+      </c>
+      <c r="C63">
+        <v>-200.4954397039196</v>
+      </c>
+      <c r="D63">
+        <v>1068.09856029608</v>
+      </c>
+      <c r="E63">
+        <v>-946.4059999999999</v>
+      </c>
+      <c r="F63">
+        <v>2492.094</v>
+      </c>
+      <c r="G63">
+        <v>1223.5</v>
+      </c>
+      <c r="H63">
+        <v>646.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K63">
+        <v>-621.2</v>
+      </c>
+      <c r="L63">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M63">
+        <v>622.4197763766675</v>
+      </c>
+      <c r="N63">
+        <v>-631.3864430433342</v>
+      </c>
+      <c r="O63">
+        <v>-151.5327463304002</v>
+      </c>
+      <c r="P63">
+        <v>-479.853696712934</v>
+      </c>
+      <c r="Q63">
+        <v>-1101.053696712934</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2528124868948344</v>
+      </c>
+      <c r="T63">
+        <v>4.254184620127258</v>
+      </c>
+      <c r="U63">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V63">
+        <v>-0.003457473688460839</v>
+      </c>
+      <c r="W63">
+        <v>0.2506212752715859</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>-0.01440614036858689</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2535154252490697</v>
+      </c>
+      <c r="C64">
+        <v>-251.8372006845102</v>
+      </c>
+      <c r="D64">
+        <v>1057.61079931549</v>
+      </c>
+      <c r="E64">
+        <v>-905.5520000000001</v>
+      </c>
+      <c r="F64">
+        <v>2532.948</v>
+      </c>
+      <c r="G64">
+        <v>1223.5</v>
+      </c>
+      <c r="H64">
+        <v>646.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K64">
+        <v>-621.2</v>
+      </c>
+      <c r="L64">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M64">
+        <v>632.6233792680882</v>
+      </c>
+      <c r="N64">
+        <v>-641.5900459347549</v>
+      </c>
+      <c r="O64">
+        <v>-153.9816110243412</v>
+      </c>
+      <c r="P64">
+        <v>-487.6084349104137</v>
+      </c>
+      <c r="Q64">
+        <v>-1108.808434910414</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2582601839183826</v>
+      </c>
+      <c r="T64">
+        <v>4.366136846972711</v>
+      </c>
+      <c r="U64">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V64">
+        <v>-0.003401707983808245</v>
+      </c>
+      <c r="W64">
+        <v>0.2506073473549746</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>-0.01417378326586771</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2555550026934865</v>
+      </c>
+      <c r="C65">
+        <v>-302.9750037097365</v>
+      </c>
+      <c r="D65">
+        <v>1047.326996290264</v>
+      </c>
+      <c r="E65">
+        <v>-864.6979999999999</v>
+      </c>
+      <c r="F65">
+        <v>2573.802</v>
+      </c>
+      <c r="G65">
+        <v>1223.5</v>
+      </c>
+      <c r="H65">
+        <v>646.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K65">
+        <v>-621.2</v>
+      </c>
+      <c r="L65">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M65">
+        <v>642.8269821595092</v>
+      </c>
+      <c r="N65">
+        <v>-651.7936488261759</v>
+      </c>
+      <c r="O65">
+        <v>-156.4304757182822</v>
+      </c>
+      <c r="P65">
+        <v>-495.3631731078937</v>
+      </c>
+      <c r="Q65">
+        <v>-1116.563173107894</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2640023510513119</v>
+      </c>
+      <c r="T65">
+        <v>4.484140545539542</v>
+      </c>
+      <c r="U65">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V65">
+        <v>-0.003347712618985891</v>
+      </c>
+      <c r="W65">
+        <v>0.2505938615944463</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>-0.01394880257910791</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2575945801379035</v>
+      </c>
+      <c r="C66">
+        <v>-353.9147411123258</v>
+      </c>
+      <c r="D66">
+        <v>1037.241258887674</v>
+      </c>
+      <c r="E66">
+        <v>-823.8440000000001</v>
+      </c>
+      <c r="F66">
+        <v>2614.656</v>
+      </c>
+      <c r="G66">
+        <v>1223.5</v>
+      </c>
+      <c r="H66">
+        <v>646.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K66">
+        <v>-621.2</v>
+      </c>
+      <c r="L66">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M66">
+        <v>653.0305850509299</v>
+      </c>
+      <c r="N66">
+        <v>-661.9972517175966</v>
+      </c>
+      <c r="O66">
+        <v>-158.8793404122232</v>
+      </c>
+      <c r="P66">
+        <v>-503.1179113053734</v>
+      </c>
+      <c r="Q66">
+        <v>-1124.317911305373</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2700635274694039</v>
+      </c>
+      <c r="T66">
+        <v>4.608700005137862</v>
+      </c>
+      <c r="U66">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V66">
+        <v>-0.003295404609314237</v>
+      </c>
+      <c r="W66">
+        <v>0.2505807972639345</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>-0.01373085253880935</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2596341575823204</v>
+      </c>
+      <c r="C67">
+        <v>-404.6620804177246</v>
+      </c>
+      <c r="D67">
+        <v>1027.347919582276</v>
+      </c>
+      <c r="E67">
+        <v>-782.9899999999998</v>
+      </c>
+      <c r="F67">
+        <v>2655.51</v>
+      </c>
+      <c r="G67">
+        <v>1223.5</v>
+      </c>
+      <c r="H67">
+        <v>646.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K67">
+        <v>-621.2</v>
+      </c>
+      <c r="L67">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M67">
+        <v>663.2341879423507</v>
+      </c>
+      <c r="N67">
+        <v>-672.2008546090174</v>
+      </c>
+      <c r="O67">
+        <v>-161.3282051061642</v>
+      </c>
+      <c r="P67">
+        <v>-510.8726495028532</v>
+      </c>
+      <c r="Q67">
+        <v>-1132.072649502853</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2764710568256726</v>
+      </c>
+      <c r="T67">
+        <v>4.740377148141802</v>
+      </c>
+      <c r="U67">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V67">
+        <v>-0.003244706076863249</v>
+      </c>
+      <c r="W67">
+        <v>0.250568134912823</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>-0.01351960865359692</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2616737350267372</v>
+      </c>
+      <c r="C68">
+        <v>-455.222474964004</v>
+      </c>
+      <c r="D68">
+        <v>1017.641525035996</v>
+      </c>
+      <c r="E68">
+        <v>-742.136</v>
+      </c>
+      <c r="F68">
+        <v>2696.364</v>
+      </c>
+      <c r="G68">
+        <v>1223.5</v>
+      </c>
+      <c r="H68">
+        <v>646.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K68">
+        <v>-621.2</v>
+      </c>
+      <c r="L68">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M68">
+        <v>673.4377908337715</v>
+      </c>
+      <c r="N68">
+        <v>-682.4044575004382</v>
+      </c>
+      <c r="O68">
+        <v>-163.7770698001052</v>
+      </c>
+      <c r="P68">
+        <v>-518.627387700333</v>
+      </c>
+      <c r="Q68">
+        <v>-1139.827387700333</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2832554996734865</v>
+      </c>
+      <c r="T68">
+        <v>4.87980000544009</v>
+      </c>
+      <c r="U68">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V68">
+        <v>-0.003195543863577442</v>
+      </c>
+      <c r="W68">
+        <v>0.250555856269321</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>-0.01331476609823934</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2637133124711541</v>
+      </c>
+      <c r="C69">
+        <v>-505.6011739253868</v>
+      </c>
+      <c r="D69">
+        <v>1008.116826074614</v>
+      </c>
+      <c r="E69">
+        <v>-701.2819999999997</v>
+      </c>
+      <c r="F69">
+        <v>2737.218</v>
+      </c>
+      <c r="G69">
+        <v>1223.5</v>
+      </c>
+      <c r="H69">
+        <v>646.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K69">
+        <v>-621.2</v>
+      </c>
+      <c r="L69">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M69">
+        <v>683.6413937251923</v>
+      </c>
+      <c r="N69">
+        <v>-692.608060391859</v>
+      </c>
+      <c r="O69">
+        <v>-166.2259344940462</v>
+      </c>
+      <c r="P69">
+        <v>-526.3821258978128</v>
+      </c>
+      <c r="Q69">
+        <v>-1147.582125897813</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2904511208757133</v>
+      </c>
+      <c r="T69">
+        <v>5.027672732877668</v>
+      </c>
+      <c r="U69">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V69">
+        <v>-0.003147849179046435</v>
+      </c>
+      <c r="W69">
+        <v>0.2505439441524906</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>-0.01311603824602692</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2657528899155711</v>
+      </c>
+      <c r="C70">
+        <v>-555.8032317780853</v>
+      </c>
+      <c r="D70">
+        <v>998.7687682219148</v>
+      </c>
+      <c r="E70">
+        <v>-660.4279999999999</v>
+      </c>
+      <c r="F70">
+        <v>2778.072</v>
+      </c>
+      <c r="G70">
+        <v>1223.5</v>
+      </c>
+      <c r="H70">
+        <v>646.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K70">
+        <v>-621.2</v>
+      </c>
+      <c r="L70">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M70">
+        <v>693.844996616613</v>
+      </c>
+      <c r="N70">
+        <v>-702.8116632832797</v>
+      </c>
+      <c r="O70">
+        <v>-168.6747991879871</v>
+      </c>
+      <c r="P70">
+        <v>-534.1368640952926</v>
+      </c>
+      <c r="Q70">
+        <v>-1155.336864095293</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2980964684030795</v>
+      </c>
+      <c r="T70">
+        <v>5.184787505780096</v>
+      </c>
+      <c r="U70">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V70">
+        <v>-0.003101557279354576</v>
+      </c>
+      <c r="W70">
+        <v>0.2505323823920377</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>-0.01292315533064414</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.267792467359988</v>
+      </c>
+      <c r="C71">
+        <v>-605.8335172443399</v>
+      </c>
+      <c r="D71">
+        <v>989.5924827556605</v>
+      </c>
+      <c r="E71">
+        <v>-619.5739999999996</v>
+      </c>
+      <c r="F71">
+        <v>2818.926</v>
+      </c>
+      <c r="G71">
+        <v>1223.5</v>
+      </c>
+      <c r="H71">
+        <v>646.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K71">
+        <v>-621.2</v>
+      </c>
+      <c r="L71">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M71">
+        <v>704.0485995080338</v>
+      </c>
+      <c r="N71">
+        <v>-713.0152661747005</v>
+      </c>
+      <c r="O71">
+        <v>-171.1236638819281</v>
+      </c>
+      <c r="P71">
+        <v>-541.8916022927724</v>
+      </c>
+      <c r="Q71">
+        <v>-1163.091602292772</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.3062350641580175</v>
+      </c>
+      <c r="T71">
+        <v>5.35203871564397</v>
+      </c>
+      <c r="U71">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V71">
+        <v>-0.003056607173856684</v>
+      </c>
+      <c r="W71">
+        <v>0.2505211557550762</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>-0.01273586322440279</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2698320448044049</v>
+      </c>
+      <c r="C72">
+        <v>-655.6967217478973</v>
+      </c>
+      <c r="D72">
+        <v>980.5832782521031</v>
+      </c>
+      <c r="E72">
+        <v>-578.7199999999998</v>
+      </c>
+      <c r="F72">
+        <v>2859.78</v>
+      </c>
+      <c r="G72">
+        <v>1223.5</v>
+      </c>
+      <c r="H72">
+        <v>646.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K72">
+        <v>-621.2</v>
+      </c>
+      <c r="L72">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M72">
+        <v>714.2522023994546</v>
+      </c>
+      <c r="N72">
+        <v>-723.2188690661213</v>
+      </c>
+      <c r="O72">
+        <v>-173.5725285758691</v>
+      </c>
+      <c r="P72">
+        <v>-549.6463404902522</v>
+      </c>
+      <c r="Q72">
+        <v>-1170.846340490252</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.3149162329632847</v>
+      </c>
+      <c r="T72">
+        <v>5.530440006165436</v>
+      </c>
+      <c r="U72">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V72">
+        <v>-0.003012941357087302</v>
+      </c>
+      <c r="W72">
+        <v>0.2505102498791706</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>-0.01255392232119701</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2718716222488217</v>
+      </c>
+      <c r="C73">
+        <v>-705.3973674117833</v>
+      </c>
+      <c r="D73">
+        <v>971.7366325882167</v>
+      </c>
+      <c r="E73">
+        <v>-537.866</v>
+      </c>
+      <c r="F73">
+        <v>2900.634</v>
+      </c>
+      <c r="G73">
+        <v>1223.5</v>
+      </c>
+      <c r="H73">
+        <v>646.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K73">
+        <v>-621.2</v>
+      </c>
+      <c r="L73">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M73">
+        <v>724.4558052908753</v>
+      </c>
+      <c r="N73">
+        <v>-733.422471957542</v>
+      </c>
+      <c r="O73">
+        <v>-176.0213932698101</v>
+      </c>
+      <c r="P73">
+        <v>-557.4010786877319</v>
+      </c>
+      <c r="Q73">
+        <v>-1178.601078687732</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3241961030654669</v>
+      </c>
+      <c r="T73">
+        <v>5.721144833964242</v>
+      </c>
+      <c r="U73">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V73">
+        <v>-0.00297050556332551</v>
+      </c>
+      <c r="W73">
+        <v>0.2504996512110371</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>-0.01237710651385626</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2739111996932386</v>
+      </c>
+      <c r="C74">
+        <v>-754.9398146270264</v>
+      </c>
+      <c r="D74">
+        <v>963.0481853729734</v>
+      </c>
+      <c r="E74">
+        <v>-497.0120000000002</v>
+      </c>
+      <c r="F74">
+        <v>2941.488</v>
+      </c>
+      <c r="G74">
+        <v>1223.5</v>
+      </c>
+      <c r="H74">
+        <v>646.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K74">
+        <v>-621.2</v>
+      </c>
+      <c r="L74">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M74">
+        <v>734.659408182296</v>
+      </c>
+      <c r="N74">
+        <v>-743.6260748489627</v>
+      </c>
+      <c r="O74">
+        <v>-178.470257963751</v>
+      </c>
+      <c r="P74">
+        <v>-565.1558168852117</v>
+      </c>
+      <c r="Q74">
+        <v>-1186.355816885212</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3341388210320907</v>
+      </c>
+      <c r="T74">
+        <v>5.925471435177251</v>
+      </c>
+      <c r="U74">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V74">
+        <v>-0.002929248541612656</v>
+      </c>
+      <c r="W74">
+        <v>0.2504893469503517</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>-0.01220520225671939</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2759507771376555</v>
+      </c>
+      <c r="C75">
+        <v>-804.3282692189332</v>
+      </c>
+      <c r="D75">
+        <v>954.5137307810668</v>
+      </c>
+      <c r="E75">
+        <v>-456.1579999999999</v>
+      </c>
+      <c r="F75">
+        <v>2982.342</v>
+      </c>
+      <c r="G75">
+        <v>1223.5</v>
+      </c>
+      <c r="H75">
+        <v>646.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K75">
+        <v>-621.2</v>
+      </c>
+      <c r="L75">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M75">
+        <v>744.863011073717</v>
+      </c>
+      <c r="N75">
+        <v>-753.8296777403837</v>
+      </c>
+      <c r="O75">
+        <v>-180.9191226576921</v>
+      </c>
+      <c r="P75">
+        <v>-572.9105550826916</v>
+      </c>
+      <c r="Q75">
+        <v>-1194.110555082692</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3448180366258718</v>
+      </c>
+      <c r="T75">
+        <v>6.144933340183815</v>
+      </c>
+      <c r="U75">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V75">
+        <v>-0.002889121849261796</v>
+      </c>
+      <c r="W75">
+        <v>0.2504793249981782</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>-0.01203800770525754</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2779903545820724</v>
+      </c>
+      <c r="C76">
+        <v>-853.5667892356728</v>
+      </c>
+      <c r="D76">
+        <v>946.1292107643271</v>
+      </c>
+      <c r="E76">
+        <v>-415.3040000000001</v>
+      </c>
+      <c r="F76">
+        <v>3023.196</v>
+      </c>
+      <c r="G76">
+        <v>1223.5</v>
+      </c>
+      <c r="H76">
+        <v>646.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K76">
+        <v>-621.2</v>
+      </c>
+      <c r="L76">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M76">
+        <v>755.0666139651377</v>
+      </c>
+      <c r="N76">
+        <v>-764.0332806318044</v>
+      </c>
+      <c r="O76">
+        <v>-183.367987351633</v>
+      </c>
+      <c r="P76">
+        <v>-580.6652932801713</v>
+      </c>
+      <c r="Q76">
+        <v>-1201.865293280171</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3563187303422515</v>
+      </c>
+      <c r="T76">
+        <v>6.381276930190886</v>
+      </c>
+      <c r="U76">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V76">
+        <v>-0.00285007966210961</v>
+      </c>
+      <c r="W76">
+        <v>0.250469573909577</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>-0.01187533192545676</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2800299320264893</v>
+      </c>
+      <c r="C77">
+        <v>-902.6592913821905</v>
+      </c>
+      <c r="D77">
+        <v>937.8907086178097</v>
+      </c>
+      <c r="E77">
+        <v>-374.4499999999998</v>
+      </c>
+      <c r="F77">
+        <v>3064.05</v>
+      </c>
+      <c r="G77">
+        <v>1223.5</v>
+      </c>
+      <c r="H77">
+        <v>646.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K77">
+        <v>-621.2</v>
+      </c>
+      <c r="L77">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M77">
+        <v>765.2702168565585</v>
+      </c>
+      <c r="N77">
+        <v>-774.2368835232252</v>
+      </c>
+      <c r="O77">
+        <v>-185.816852045574</v>
+      </c>
+      <c r="P77">
+        <v>-588.4200314776512</v>
+      </c>
+      <c r="Q77">
+        <v>-1209.620031477651</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3687394795559416</v>
+      </c>
+      <c r="T77">
+        <v>6.636528007398521</v>
+      </c>
+      <c r="U77">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V77">
+        <v>-0.002812078599948149</v>
+      </c>
+      <c r="W77">
+        <v>0.2504600828500052</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>-0.01171699416645056</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2820695094709062</v>
+      </c>
+      <c r="C78">
+        <v>-951.6095571208748</v>
+      </c>
+      <c r="D78">
+        <v>929.7944428791251</v>
+      </c>
+      <c r="E78">
+        <v>-333.596</v>
+      </c>
+      <c r="F78">
+        <v>3104.904</v>
+      </c>
+      <c r="G78">
+        <v>1223.5</v>
+      </c>
+      <c r="H78">
+        <v>646.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K78">
+        <v>-621.2</v>
+      </c>
+      <c r="L78">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M78">
+        <v>775.4738197479792</v>
+      </c>
+      <c r="N78">
+        <v>-784.4404864146459</v>
+      </c>
+      <c r="O78">
+        <v>-188.265716739515</v>
+      </c>
+      <c r="P78">
+        <v>-596.1747696751308</v>
+      </c>
+      <c r="Q78">
+        <v>-1217.374769675131</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3821952912041058</v>
+      </c>
+      <c r="T78">
+        <v>6.913050007706793</v>
+      </c>
+      <c r="U78">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V78">
+        <v>-0.002775077565738305</v>
+      </c>
+      <c r="W78">
+        <v>0.250450841555159</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>-0.01156282319057622</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2841090869153231</v>
+      </c>
+      <c r="C79">
+        <v>-1000.421238458953</v>
+      </c>
+      <c r="D79">
+        <v>921.8367615410473</v>
+      </c>
+      <c r="E79">
+        <v>-292.7419999999997</v>
+      </c>
+      <c r="F79">
+        <v>3145.758</v>
+      </c>
+      <c r="G79">
+        <v>1223.5</v>
+      </c>
+      <c r="H79">
+        <v>646.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K79">
+        <v>-621.2</v>
+      </c>
+      <c r="L79">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M79">
+        <v>785.6774226394001</v>
+      </c>
+      <c r="N79">
+        <v>-794.6440893060668</v>
+      </c>
+      <c r="O79">
+        <v>-190.714581433456</v>
+      </c>
+      <c r="P79">
+        <v>-603.9295078726108</v>
+      </c>
+      <c r="Q79">
+        <v>-1225.129507872611</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3968211734303714</v>
+      </c>
+      <c r="T79">
+        <v>7.21361739934622</v>
+      </c>
+      <c r="U79">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V79">
+        <v>-0.002739037597352093</v>
+      </c>
+      <c r="W79">
+        <v>0.2504418402939451</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>-0.01141265665563362</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.28614866435974</v>
+      </c>
+      <c r="C80">
+        <v>-1049.097863441214</v>
+      </c>
+      <c r="D80">
+        <v>914.0141365587866</v>
+      </c>
+      <c r="E80">
+        <v>-251.8879999999999</v>
+      </c>
+      <c r="F80">
+        <v>3186.612</v>
+      </c>
+      <c r="G80">
+        <v>1223.5</v>
+      </c>
+      <c r="H80">
+        <v>646.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K80">
+        <v>-621.2</v>
+      </c>
+      <c r="L80">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M80">
+        <v>795.8810255308208</v>
+      </c>
+      <c r="N80">
+        <v>-804.8476921974875</v>
+      </c>
+      <c r="O80">
+        <v>-193.163446127397</v>
+      </c>
+      <c r="P80">
+        <v>-611.6842460700905</v>
+      </c>
+      <c r="Q80">
+        <v>-1232.884246070091</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.4127766813135701</v>
+      </c>
+      <c r="T80">
+        <v>7.541509099316504</v>
+      </c>
+      <c r="U80">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V80">
+        <v>-0.002703921730719374</v>
+      </c>
+      <c r="W80">
+        <v>0.2504330698343007</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>-0.01126634054466402</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2881882418041569</v>
+      </c>
+      <c r="C81">
+        <v>-1097.642841365422</v>
+      </c>
+      <c r="D81">
+        <v>906.3231586345782</v>
+      </c>
+      <c r="E81">
+        <v>-211.0339999999997</v>
+      </c>
+      <c r="F81">
+        <v>3227.466</v>
+      </c>
+      <c r="G81">
+        <v>1223.5</v>
+      </c>
+      <c r="H81">
+        <v>646.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K81">
+        <v>-621.2</v>
+      </c>
+      <c r="L81">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M81">
+        <v>806.0846284222416</v>
+      </c>
+      <c r="N81">
+        <v>-815.0512950889083</v>
+      </c>
+      <c r="O81">
+        <v>-195.612310821338</v>
+      </c>
+      <c r="P81">
+        <v>-619.4389842675703</v>
+      </c>
+      <c r="Q81">
+        <v>-1240.63898426757</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.430251761376121</v>
+      </c>
+      <c r="T81">
+        <v>7.900628580236337</v>
+      </c>
+      <c r="U81">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V81">
+        <v>-0.002669694873368495</v>
+      </c>
+      <c r="W81">
+        <v>0.2504245214116095</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>-0.01112372863903532</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2902278192485738</v>
+      </c>
+      <c r="C82">
+        <v>-1146.05946773662</v>
+      </c>
+      <c r="D82">
+        <v>898.76053226338</v>
+      </c>
+      <c r="E82">
+        <v>-170.1799999999998</v>
+      </c>
+      <c r="F82">
+        <v>3268.32</v>
+      </c>
+      <c r="G82">
+        <v>1223.5</v>
+      </c>
+      <c r="H82">
+        <v>646.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K82">
+        <v>-621.2</v>
+      </c>
+      <c r="L82">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M82">
+        <v>816.2882313136623</v>
+      </c>
+      <c r="N82">
+        <v>-825.254897980329</v>
+      </c>
+      <c r="O82">
+        <v>-198.061175515279</v>
+      </c>
+      <c r="P82">
+        <v>-627.1937224650501</v>
+      </c>
+      <c r="Q82">
+        <v>-1248.39372246505</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4494743494449271</v>
+      </c>
+      <c r="T82">
+        <v>8.295660009248154</v>
+      </c>
+      <c r="U82">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V82">
+        <v>-0.00263632368745139</v>
+      </c>
+      <c r="W82">
+        <v>0.2504161866994855</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>-0.01098468203104752</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2922673966929907</v>
+      </c>
+      <c r="C83">
+        <v>-1194.350928975438</v>
+      </c>
+      <c r="D83">
+        <v>891.323071024562</v>
+      </c>
+      <c r="E83">
+        <v>-129.3259999999996</v>
+      </c>
+      <c r="F83">
+        <v>3309.174</v>
+      </c>
+      <c r="G83">
+        <v>1223.5</v>
+      </c>
+      <c r="H83">
+        <v>646.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K83">
+        <v>-621.2</v>
+      </c>
+      <c r="L83">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M83">
+        <v>826.4918342050833</v>
+      </c>
+      <c r="N83">
+        <v>-835.4585008717499</v>
+      </c>
+      <c r="O83">
+        <v>-200.51004020922</v>
+      </c>
+      <c r="P83">
+        <v>-634.94846066253</v>
+      </c>
+      <c r="Q83">
+        <v>-1256.14846066253</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4707203678367654</v>
+      </c>
+      <c r="T83">
+        <v>8.732273693945425</v>
+      </c>
+      <c r="U83">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V83">
+        <v>-0.002603776481433471</v>
+      </c>
+      <c r="W83">
+        <v>0.2504080577827226</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>-0.01084906867263946</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2943069741374076</v>
+      </c>
+      <c r="C84">
+        <v>-1242.52030689455</v>
+      </c>
+      <c r="D84">
+        <v>884.0076931054499</v>
+      </c>
+      <c r="E84">
+        <v>-88.47199999999975</v>
+      </c>
+      <c r="F84">
+        <v>3350.028</v>
+      </c>
+      <c r="G84">
+        <v>1223.5</v>
+      </c>
+      <c r="H84">
+        <v>646.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K84">
+        <v>-621.2</v>
+      </c>
+      <c r="L84">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M84">
+        <v>836.695437096504</v>
+      </c>
+      <c r="N84">
+        <v>-845.6621037631706</v>
+      </c>
+      <c r="O84">
+        <v>-202.9589049031609</v>
+      </c>
+      <c r="P84">
+        <v>-642.7031988600097</v>
+      </c>
+      <c r="Q84">
+        <v>-1263.90319886001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4943270549388079</v>
+      </c>
+      <c r="T84">
+        <v>9.217400010275727</v>
+      </c>
+      <c r="U84">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V84">
+        <v>-0.002572023109708673</v>
+      </c>
+      <c r="W84">
+        <v>0.2504001271322222</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>-0.01071676295711943</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2963465515818245</v>
+      </c>
+      <c r="C85">
+        <v>-1290.570582956486</v>
+      </c>
+      <c r="D85">
+        <v>876.8114170435141</v>
+      </c>
+      <c r="E85">
+        <v>-47.61799999999948</v>
+      </c>
+      <c r="F85">
+        <v>3390.882000000001</v>
+      </c>
+      <c r="G85">
+        <v>1223.5</v>
+      </c>
+      <c r="H85">
+        <v>646.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K85">
+        <v>-621.2</v>
+      </c>
+      <c r="L85">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M85">
+        <v>846.8990399879248</v>
+      </c>
+      <c r="N85">
+        <v>-855.8657066545915</v>
+      </c>
+      <c r="O85">
+        <v>-205.4077695971019</v>
+      </c>
+      <c r="P85">
+        <v>-650.4579370574895</v>
+      </c>
+      <c r="Q85">
+        <v>-1271.65793705749</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.5207109993469731</v>
+      </c>
+      <c r="T85">
+        <v>9.759600010880183</v>
+      </c>
+      <c r="U85">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V85">
+        <v>-0.002541034879471219</v>
+      </c>
+      <c r="W85">
+        <v>0.2503923875817338</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>-0.01058764533112999</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2983861290262413</v>
+      </c>
+      <c r="C86">
+        <v>-1338.504642325159</v>
+      </c>
+      <c r="D86">
+        <v>869.731357674841</v>
+      </c>
+      <c r="E86">
+        <v>-6.764000000000124</v>
+      </c>
+      <c r="F86">
+        <v>3431.736</v>
+      </c>
+      <c r="G86">
+        <v>1223.5</v>
+      </c>
+      <c r="H86">
+        <v>646.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K86">
+        <v>-621.2</v>
+      </c>
+      <c r="L86">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M86">
+        <v>857.1026428793455</v>
+      </c>
+      <c r="N86">
+        <v>-866.0693095460122</v>
+      </c>
+      <c r="O86">
+        <v>-207.8566342910429</v>
+      </c>
+      <c r="P86">
+        <v>-658.2126752549692</v>
+      </c>
+      <c r="Q86">
+        <v>-1279.412675254969</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5503929368061585</v>
+      </c>
+      <c r="T86">
+        <v>10.36957501156019</v>
+      </c>
+      <c r="U86">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V86">
+        <v>-0.002510784464239419</v>
+      </c>
+      <c r="W86">
+        <v>0.2503848323062571</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>-0.01046160193433088</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.3004257064706582</v>
+      </c>
+      <c r="C87">
+        <v>-1386.325277722674</v>
+      </c>
+      <c r="D87">
+        <v>862.7647222773262</v>
+      </c>
+      <c r="E87">
+        <v>34.09000000000015</v>
+      </c>
+      <c r="F87">
+        <v>3472.59</v>
+      </c>
+      <c r="G87">
+        <v>1223.5</v>
+      </c>
+      <c r="H87">
+        <v>646.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K87">
+        <v>-621.2</v>
+      </c>
+      <c r="L87">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M87">
+        <v>867.3062457707663</v>
+      </c>
+      <c r="N87">
+        <v>-876.272912437433</v>
+      </c>
+      <c r="O87">
+        <v>-210.3054989849839</v>
+      </c>
+      <c r="P87">
+        <v>-665.9674134524491</v>
+      </c>
+      <c r="Q87">
+        <v>-1287.167413452449</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5840324659265692</v>
+      </c>
+      <c r="T87">
+        <v>11.06088001233087</v>
+      </c>
+      <c r="U87">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V87">
+        <v>-0.002481245823483661</v>
+      </c>
+      <c r="W87">
+        <v>0.250377454801968</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>-0.01033852426451531</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.3024652839150752</v>
+      </c>
+      <c r="C88">
+        <v>-1434.035193102246</v>
+      </c>
+      <c r="D88">
+        <v>855.9088068977544</v>
+      </c>
+      <c r="E88">
+        <v>74.94399999999996</v>
+      </c>
+      <c r="F88">
+        <v>3513.444</v>
+      </c>
+      <c r="G88">
+        <v>1223.5</v>
+      </c>
+      <c r="H88">
+        <v>646.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K88">
+        <v>-621.2</v>
+      </c>
+      <c r="L88">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M88">
+        <v>877.509848662187</v>
+      </c>
+      <c r="N88">
+        <v>-886.4765153288537</v>
+      </c>
+      <c r="O88">
+        <v>-212.7543636789249</v>
+      </c>
+      <c r="P88">
+        <v>-673.7221516499288</v>
+      </c>
+      <c r="Q88">
+        <v>-1294.922151649929</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.6224776420641814</v>
+      </c>
+      <c r="T88">
+        <v>11.8509428703545</v>
+      </c>
+      <c r="U88">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V88">
+        <v>-0.002452394127861758</v>
+      </c>
+      <c r="W88">
+        <v>0.2503702488675462</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>-0.01021830886609076</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.304504861359492</v>
+      </c>
+      <c r="C89">
+        <v>-1481.637007147381</v>
+      </c>
+      <c r="D89">
+        <v>849.160992852619</v>
+      </c>
+      <c r="E89">
+        <v>115.7980000000002</v>
+      </c>
+      <c r="F89">
+        <v>3554.298</v>
+      </c>
+      <c r="G89">
+        <v>1223.5</v>
+      </c>
+      <c r="H89">
+        <v>646.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K89">
+        <v>-621.2</v>
+      </c>
+      <c r="L89">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M89">
+        <v>887.7134515536078</v>
+      </c>
+      <c r="N89">
+        <v>-896.6801182202745</v>
+      </c>
+      <c r="O89">
+        <v>-215.2032283728659</v>
+      </c>
+      <c r="P89">
+        <v>-681.4768898474086</v>
+      </c>
+      <c r="Q89">
+        <v>-1302.676889847409</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.666837460684503</v>
+      </c>
+      <c r="T89">
+        <v>12.76255386038177</v>
+      </c>
+      <c r="U89">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V89">
+        <v>-0.002424205689610473</v>
+      </c>
+      <c r="W89">
+        <v>0.2503632085867892</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>-0.0101008570400436</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.3065444388039089</v>
+      </c>
+      <c r="C90">
+        <v>-1529.133256606835</v>
+      </c>
+      <c r="D90">
+        <v>842.5187433931651</v>
+      </c>
+      <c r="E90">
+        <v>156.652</v>
+      </c>
+      <c r="F90">
+        <v>3595.152</v>
+      </c>
+      <c r="G90">
+        <v>1223.5</v>
+      </c>
+      <c r="H90">
+        <v>646.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K90">
+        <v>-621.2</v>
+      </c>
+      <c r="L90">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M90">
+        <v>897.9170544450286</v>
+      </c>
+      <c r="N90">
+        <v>-906.8837211116953</v>
+      </c>
+      <c r="O90">
+        <v>-217.6520930668069</v>
+      </c>
+      <c r="P90">
+        <v>-689.2316280448885</v>
+      </c>
+      <c r="Q90">
+        <v>-1310.431628044888</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.7185905824082116</v>
+      </c>
+      <c r="T90">
+        <v>13.82610001541359</v>
+      </c>
+      <c r="U90">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V90">
+        <v>-0.002396657897683081</v>
+      </c>
+      <c r="W90">
+        <v>0.2503563283124131</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>-0.009986074573679504</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.3085840162483258</v>
+      </c>
+      <c r="C91">
+        <v>-1576.526399474259</v>
+      </c>
+      <c r="D91">
+        <v>835.9796005257414</v>
+      </c>
+      <c r="E91">
+        <v>197.5060000000003</v>
+      </c>
+      <c r="F91">
+        <v>3636.006</v>
+      </c>
+      <c r="G91">
+        <v>1223.5</v>
+      </c>
+      <c r="H91">
+        <v>646.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K91">
+        <v>-621.2</v>
+      </c>
+      <c r="L91">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M91">
+        <v>908.1206573364494</v>
+      </c>
+      <c r="N91">
+        <v>-917.0873240031161</v>
+      </c>
+      <c r="O91">
+        <v>-220.1009577607479</v>
+      </c>
+      <c r="P91">
+        <v>-696.9863662423683</v>
+      </c>
+      <c r="Q91">
+        <v>-1318.186366242368</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.77975336262714</v>
+      </c>
+      <c r="T91">
+        <v>15.083018198633</v>
+      </c>
+      <c r="U91">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V91">
+        <v>-0.002369729157259676</v>
+      </c>
+      <c r="W91">
+        <v>0.2503496026509443</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>-0.009873871488581987</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.3106235936927427</v>
+      </c>
+      <c r="C92">
+        <v>-1623.81881802092</v>
+      </c>
+      <c r="D92">
+        <v>829.54118197908</v>
+      </c>
+      <c r="E92">
+        <v>238.3600000000001</v>
+      </c>
+      <c r="F92">
+        <v>3676.86</v>
+      </c>
+      <c r="G92">
+        <v>1223.5</v>
+      </c>
+      <c r="H92">
+        <v>646.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K92">
+        <v>-621.2</v>
+      </c>
+      <c r="L92">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M92">
+        <v>918.3242602278701</v>
+      </c>
+      <c r="N92">
+        <v>-927.2909268945368</v>
+      </c>
+      <c r="O92">
+        <v>-222.5498224546888</v>
+      </c>
+      <c r="P92">
+        <v>-704.741104439848</v>
+      </c>
+      <c r="Q92">
+        <v>-1325.941104439848</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8531486988898541</v>
+      </c>
+      <c r="T92">
+        <v>16.59132001849631</v>
+      </c>
+      <c r="U92">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V92">
+        <v>-0.002343398833290124</v>
+      </c>
+      <c r="W92">
+        <v>0.2503430264486192</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>-0.009764161805375426</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.3126631711371596</v>
+      </c>
+      <c r="C93">
+        <v>-1671.012821689354</v>
+      </c>
+      <c r="D93">
+        <v>823.2011783106461</v>
+      </c>
+      <c r="E93">
+        <v>279.2140000000004</v>
+      </c>
+      <c r="F93">
+        <v>3717.714</v>
+      </c>
+      <c r="G93">
+        <v>1223.5</v>
+      </c>
+      <c r="H93">
+        <v>646.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K93">
+        <v>-621.2</v>
+      </c>
+      <c r="L93">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M93">
+        <v>928.5278631192911</v>
+      </c>
+      <c r="N93">
+        <v>-937.4945297859578</v>
+      </c>
+      <c r="O93">
+        <v>-224.9986871486298</v>
+      </c>
+      <c r="P93">
+        <v>-712.4958426373279</v>
+      </c>
+      <c r="Q93">
+        <v>-1333.695842637328</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9428541098776159</v>
+      </c>
+      <c r="T93">
+        <v>18.43480002055146</v>
+      </c>
+      <c r="U93">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V93">
+        <v>-0.002317647197759463</v>
+      </c>
+      <c r="W93">
+        <v>0.2503365947782134</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>-0.009656863323997733</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.3147027485815765</v>
+      </c>
+      <c r="C94">
+        <v>-1718.110649855322</v>
+      </c>
+      <c r="D94">
+        <v>816.9573501446783</v>
+      </c>
+      <c r="E94">
+        <v>320.0680000000002</v>
+      </c>
+      <c r="F94">
+        <v>3758.568</v>
+      </c>
+      <c r="G94">
+        <v>1223.5</v>
+      </c>
+      <c r="H94">
+        <v>646.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K94">
+        <v>-621.2</v>
+      </c>
+      <c r="L94">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M94">
+        <v>938.7314660107118</v>
+      </c>
+      <c r="N94">
+        <v>-947.6981326773785</v>
+      </c>
+      <c r="O94">
+        <v>-227.4475518425708</v>
+      </c>
+      <c r="P94">
+        <v>-720.2505808348076</v>
+      </c>
+      <c r="Q94">
+        <v>-1341.450580834808</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.054985873612318</v>
+      </c>
+      <c r="T94">
+        <v>20.73915002312039</v>
+      </c>
+      <c r="U94">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V94">
+        <v>-0.002292455380392513</v>
+      </c>
+      <c r="W94">
+        <v>0.2503303029267295</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>-0.009551897418302202</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3167423260259934</v>
+      </c>
+      <c r="C95">
+        <v>-1765.114474465028</v>
+      </c>
+      <c r="D95">
+        <v>810.8075255349722</v>
+      </c>
+      <c r="E95">
+        <v>360.9220000000005</v>
+      </c>
+      <c r="F95">
+        <v>3799.422</v>
+      </c>
+      <c r="G95">
+        <v>1223.5</v>
+      </c>
+      <c r="H95">
+        <v>646.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K95">
+        <v>-621.2</v>
+      </c>
+      <c r="L95">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M95">
+        <v>948.9350689021326</v>
+      </c>
+      <c r="N95">
+        <v>-957.9017355687993</v>
+      </c>
+      <c r="O95">
+        <v>-229.8964165365118</v>
+      </c>
+      <c r="P95">
+        <v>-728.0053190322874</v>
+      </c>
+      <c r="Q95">
+        <v>-1349.205319032287</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.199155284128364</v>
+      </c>
+      <c r="T95">
+        <v>23.70188574070902</v>
+      </c>
+      <c r="U95">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V95">
+        <v>-0.00226780532253883</v>
+      </c>
+      <c r="W95">
+        <v>0.2503241463838796</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>-0.009449188843911882</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3187819034704103</v>
+      </c>
+      <c r="C96">
+        <v>-1812.026402554111</v>
+      </c>
+      <c r="D96">
+        <v>804.7495974458898</v>
+      </c>
+      <c r="E96">
+        <v>401.7760000000003</v>
+      </c>
+      <c r="F96">
+        <v>3840.276</v>
+      </c>
+      <c r="G96">
+        <v>1223.5</v>
+      </c>
+      <c r="H96">
+        <v>646.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K96">
+        <v>-621.2</v>
+      </c>
+      <c r="L96">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M96">
+        <v>959.1386717935533</v>
+      </c>
+      <c r="N96">
+        <v>-968.10533846022</v>
+      </c>
+      <c r="O96">
+        <v>-232.3452812304528</v>
+      </c>
+      <c r="P96">
+        <v>-735.7600572297672</v>
+      </c>
+      <c r="Q96">
+        <v>-1356.960057229767</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.391381164816424</v>
+      </c>
+      <c r="T96">
+        <v>27.6522000308272</v>
+      </c>
+      <c r="U96">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V96">
+        <v>-0.002243679734001183</v>
+      </c>
+      <c r="W96">
+        <v>0.2503181208313031</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>-0.009348665558338354</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3208214809148272</v>
+      </c>
+      <c r="C97">
+        <v>-1858.848478654546</v>
+      </c>
+      <c r="D97">
+        <v>798.7815213454541</v>
+      </c>
+      <c r="E97">
+        <v>442.6300000000006</v>
+      </c>
+      <c r="F97">
+        <v>3881.130000000001</v>
+      </c>
+      <c r="G97">
+        <v>1223.5</v>
+      </c>
+      <c r="H97">
+        <v>646.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K97">
+        <v>-621.2</v>
+      </c>
+      <c r="L97">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M97">
+        <v>969.3422746849742</v>
+      </c>
+      <c r="N97">
+        <v>-978.3089413516409</v>
+      </c>
+      <c r="O97">
+        <v>-234.7941459243938</v>
+      </c>
+      <c r="P97">
+        <v>-743.5147954272471</v>
+      </c>
+      <c r="Q97">
+        <v>-1364.714795427247</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.660497397779711</v>
+      </c>
+      <c r="T97">
+        <v>33.18264003699266</v>
+      </c>
+      <c r="U97">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V97">
+        <v>-0.002220062052590644</v>
+      </c>
+      <c r="W97">
+        <v>0.2503122221324651</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>-0.009250258552460977</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3228610583592441</v>
+      </c>
+      <c r="C98">
+        <v>-1905.582687095246</v>
+      </c>
+      <c r="D98">
+        <v>792.9013129047541</v>
+      </c>
+      <c r="E98">
+        <v>483.4839999999999</v>
+      </c>
+      <c r="F98">
+        <v>3921.984</v>
+      </c>
+      <c r="G98">
+        <v>1223.5</v>
+      </c>
+      <c r="H98">
+        <v>646.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K98">
+        <v>-621.2</v>
+      </c>
+      <c r="L98">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M98">
+        <v>979.5458775763948</v>
+      </c>
+      <c r="N98">
+        <v>-988.5125442430615</v>
+      </c>
+      <c r="O98">
+        <v>-237.2430106183348</v>
+      </c>
+      <c r="P98">
+        <v>-751.2695336247267</v>
+      </c>
+      <c r="Q98">
+        <v>-1372.469533624727</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>2.064171747224633</v>
+      </c>
+      <c r="T98">
+        <v>41.47830004624073</v>
+      </c>
+      <c r="U98">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V98">
+        <v>-0.002196936406209491</v>
+      </c>
+      <c r="W98">
+        <v>0.2503064463231862</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>-0.00915390169253949</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3249006358036609</v>
+      </c>
+      <c r="C99">
+        <v>-1952.230954201777</v>
+      </c>
+      <c r="D99">
+        <v>787.1070457982232</v>
+      </c>
+      <c r="E99">
+        <v>524.3380000000002</v>
+      </c>
+      <c r="F99">
+        <v>3962.838</v>
+      </c>
+      <c r="G99">
+        <v>1223.5</v>
+      </c>
+      <c r="H99">
+        <v>646.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K99">
+        <v>-621.2</v>
+      </c>
+      <c r="L99">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M99">
+        <v>989.7494804678156</v>
+      </c>
+      <c r="N99">
+        <v>-998.7161471344823</v>
+      </c>
+      <c r="O99">
+        <v>-239.6918753122758</v>
+      </c>
+      <c r="P99">
+        <v>-759.0242718222065</v>
+      </c>
+      <c r="Q99">
+        <v>-1380.224271822206</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.736962329632844</v>
+      </c>
+      <c r="T99">
+        <v>55.30440006165429</v>
+      </c>
+      <c r="U99">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V99">
+        <v>-0.002174287577279497</v>
+      </c>
+      <c r="W99">
+        <v>0.2503007896027583</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>-0.009059531571997903</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3269402132480779</v>
+      </c>
+      <c r="C100">
+        <v>-1998.795150400337</v>
+      </c>
+      <c r="D100">
+        <v>781.3968495996628</v>
+      </c>
+      <c r="E100">
+        <v>565.192</v>
+      </c>
+      <c r="F100">
+        <v>4003.692</v>
+      </c>
+      <c r="G100">
+        <v>1223.5</v>
+      </c>
+      <c r="H100">
+        <v>646.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K100">
+        <v>-621.2</v>
+      </c>
+      <c r="L100">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M100">
+        <v>999.9530833592364</v>
+      </c>
+      <c r="N100">
+        <v>-1008.919750025903</v>
+      </c>
+      <c r="O100">
+        <v>-242.1407400062167</v>
+      </c>
+      <c r="P100">
+        <v>-766.7790100196864</v>
+      </c>
+      <c r="Q100">
+        <v>-1387.979010019686</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>4.082543494449267</v>
+      </c>
+      <c r="T100">
+        <v>82.95660009248145</v>
+      </c>
+      <c r="U100">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V100">
+        <v>-0.002152100969348073</v>
+      </c>
+      <c r="W100">
+        <v>0.2502952483256046</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>-0.008967087372283578</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3289797906924948</v>
+      </c>
+      <c r="C101">
+        <v>-2045.277092230807</v>
+      </c>
+      <c r="D101">
+        <v>775.7689077691929</v>
+      </c>
+      <c r="E101">
+        <v>606.0460000000003</v>
+      </c>
+      <c r="F101">
+        <v>4044.546</v>
+      </c>
+      <c r="G101">
+        <v>1223.5</v>
+      </c>
+      <c r="H101">
+        <v>646.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>-630.1666666666667</v>
+      </c>
+      <c r="K101">
+        <v>-621.2</v>
+      </c>
+      <c r="L101">
+        <v>-8.966666666666697</v>
+      </c>
+      <c r="M101">
+        <v>1010.156686250657</v>
+      </c>
+      <c r="N101">
+        <v>-1019.123352917324</v>
+      </c>
+      <c r="O101">
+        <v>-244.5896047001577</v>
+      </c>
+      <c r="P101">
+        <v>-774.5337482171662</v>
+      </c>
+      <c r="Q101">
+        <v>-1395.733748217166</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>8.119286988898534</v>
+      </c>
+      <c r="T101">
+        <v>165.9132001849629</v>
+      </c>
+      <c r="U101">
+        <v>0.2497577444416894</v>
+      </c>
+      <c r="V101">
+        <v>-0.002130362575718294</v>
+      </c>
+      <c r="W101">
+        <v>0.2502898189934438</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>-0.008876510732159559</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
@@ -647,10 +647,10 @@
         <v>-0.6763494796735794</v>
       </c>
       <c r="X2">
-        <v>0.4518204657590218</v>
+        <v>0.4516096528014012</v>
       </c>
       <c r="Y2">
-        <v>-1.128169945432601</v>
+        <v>-1.12795913247498</v>
       </c>
       <c r="Z2">
         <v>0.9575805770234339</v>
@@ -659,10 +659,10 @@
         <v>0.06041102358291295</v>
       </c>
       <c r="AB2">
-        <v>0.1225609199929506</v>
+        <v>0.1225275389525911</v>
       </c>
       <c r="AC2">
-        <v>-0.06214989641003768</v>
+        <v>-0.06211651536967816</v>
       </c>
       <c r="AD2">
         <v>3438.5</v>
@@ -781,10 +781,10 @@
         <v>-0.6763494796735794</v>
       </c>
       <c r="X3">
-        <v>0.4518204657590218</v>
+        <v>0.4516096528014012</v>
       </c>
       <c r="Y3">
-        <v>-1.128169945432601</v>
+        <v>-1.12795913247498</v>
       </c>
       <c r="Z3">
         <v>0.9575805770234339</v>
@@ -793,10 +793,10 @@
         <v>0.06041102358291295</v>
       </c>
       <c r="AB3">
-        <v>0.1225609199929506</v>
+        <v>0.1225275389525911</v>
       </c>
       <c r="AC3">
-        <v>-0.06214989641003768</v>
+        <v>-0.06211651536967816</v>
       </c>
       <c r="AD3">
         <v>3438.5</v>
@@ -1133,7 +1133,7 @@
         <v>1.02314814814815</v>
       </c>
       <c r="F2">
-        <v>-0.878774562483797</v>
+        <v>-0.915427166324817</v>
       </c>
       <c r="G2">
         <v>-9.09415498545358</v>
@@ -1151,13 +1151,13 @@
         <v>646.9</v>
       </c>
       <c r="L2">
-        <v>3819.84779207943</v>
+        <v>3822.97472452272</v>
       </c>
       <c r="M2">
         <v>2861.9</v>
       </c>
       <c r="N2">
-        <v>2637.20179207943</v>
+        <v>2640.32872452272</v>
       </c>
       <c r="O2">
         <v>3438.5</v>
@@ -1166,16 +1166,16 @@
         <v>40.854</v>
       </c>
       <c r="Q2">
-        <v>0.122560919992951</v>
+        <v>0.122527538952591</v>
       </c>
       <c r="R2">
-        <v>0.129101201139639</v>
+        <v>0.128966365494173</v>
       </c>
       <c r="S2">
         <v>0.0606158857756839</v>
       </c>
       <c r="T2">
-        <v>0.302433125065374</v>
+        <v>0.292433125065374</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,16 +1188,16 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.451820465759022</v>
+        <v>0.451609652801401</v>
       </c>
       <c r="X2">
-        <v>0.127350373625238</v>
+        <v>0.127315186104565</v>
       </c>
       <c r="Y2">
         <v>8.34387358365694</v>
       </c>
       <c r="Z2">
-        <v>1.67589091095922</v>
+        <v>1.67603802252978</v>
       </c>
       <c r="AA2">
         <v>3438.5</v>
@@ -1230,7 +1230,7 @@
         <v>646.9</v>
       </c>
       <c r="AK2">
-        <v>0.0486609081127847</v>
+        <v>0.04863564251455781</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.0556577444416894</v>
+        <v>0.0542577444416894</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -1489,13 +1489,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.1291012011396392</v>
+        <v>0.1289663654941731</v>
       </c>
       <c r="C3">
-        <v>3819.84779207943</v>
+        <v>3822.974724522722</v>
       </c>
       <c r="D3">
-        <v>2637.20179207943</v>
+        <v>2640.328724522722</v>
       </c>
       <c r="E3">
         <v>-3397.646</v>
@@ -1522,37 +1522,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M3">
-        <v>10.20360289142078</v>
+        <v>9.795062891420779</v>
       </c>
       <c r="N3">
-        <v>-19.17026955808748</v>
+        <v>-18.76172955808747</v>
       </c>
       <c r="O3">
-        <v>-4.600864693940994</v>
+        <v>-4.502815093940994</v>
       </c>
       <c r="P3">
-        <v>-14.56940486414648</v>
+        <v>-14.25891446414648</v>
       </c>
       <c r="Q3">
-        <v>-635.7694048641465</v>
+        <v>-635.4589144641466</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.1273503736252378</v>
+        <v>0.127315186104565</v>
       </c>
       <c r="T3">
-        <v>1.675890910959223</v>
+        <v>1.676038022529784</v>
       </c>
       <c r="U3">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V3">
-        <v>-0.2109058949961112</v>
+        <v>-0.2197025199179562</v>
       </c>
       <c r="W3">
-        <v>0.3024331250653739</v>
+        <v>0.2924331250653739</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1560,7 +1560,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-0.8787745624837966</v>
+        <v>-0.9154271663248172</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1571,13 +1571,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.131140778584056</v>
+        <v>0.13090594293859</v>
       </c>
       <c r="C4">
-        <v>3715.966744743517</v>
+        <v>3721.947229428196</v>
       </c>
       <c r="D4">
-        <v>2574.174744743517</v>
+        <v>2580.155229428196</v>
       </c>
       <c r="E4">
         <v>-3356.792</v>
@@ -1604,37 +1604,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M4">
-        <v>20.40720578284156</v>
+        <v>19.59012578284156</v>
       </c>
       <c r="N4">
-        <v>-29.37387244950826</v>
+        <v>-28.55679244950825</v>
       </c>
       <c r="O4">
-        <v>-7.049729387881981</v>
+        <v>-6.853630187881981</v>
       </c>
       <c r="P4">
-        <v>-22.32414306162627</v>
+        <v>-21.70316226162628</v>
       </c>
       <c r="Q4">
-        <v>-643.5241430616263</v>
+        <v>-642.9031622616263</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.1281825202948831</v>
+        <v>0.1281469737178769</v>
       </c>
       <c r="T4">
-        <v>1.692991838622072</v>
+        <v>1.693140451331109</v>
       </c>
       <c r="U4">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V4">
-        <v>-0.1054529474980556</v>
+        <v>-0.1098512599589781</v>
       </c>
       <c r="W4">
-        <v>0.2760954347535317</v>
+        <v>0.2660954347535316</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1642,7 +1642,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-0.4393872812418982</v>
+        <v>-0.4577135831624088</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1653,13 +1653,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.1331803560284729</v>
+        <v>0.1328455203830068</v>
       </c>
       <c r="C5">
-        <v>3615.027972993953</v>
+        <v>3623.601346283912</v>
       </c>
       <c r="D5">
-        <v>2514.089972993952</v>
+        <v>2522.663346283912</v>
       </c>
       <c r="E5">
         <v>-3315.938</v>
@@ -1686,37 +1686,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M5">
-        <v>30.61080867426234</v>
+        <v>29.38518867426233</v>
       </c>
       <c r="N5">
-        <v>-39.57747534092903</v>
+        <v>-38.35185534092903</v>
       </c>
       <c r="O5">
-        <v>-9.498594081822969</v>
+        <v>-9.204445281822968</v>
       </c>
       <c r="P5">
-        <v>-30.07888125910607</v>
+        <v>-29.14741005910606</v>
       </c>
       <c r="Q5">
-        <v>-651.2788812591061</v>
+        <v>-650.3474100591061</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.12903182462782</v>
+        <v>0.128995911591257</v>
       </c>
       <c r="T5">
-        <v>1.710445362731578</v>
+        <v>1.710595507530398</v>
       </c>
       <c r="U5">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V5">
-        <v>-0.07030196499870373</v>
+        <v>-0.0732341733059854</v>
       </c>
       <c r="W5">
-        <v>0.2673162046495843</v>
+        <v>0.2573162046495842</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-0.2929248541612655</v>
+        <v>-0.3051423887749394</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.1352199334728898</v>
+        <v>0.1347850978274237</v>
       </c>
       <c r="C6">
-        <v>3516.830145918664</v>
+        <v>3527.76172458129</v>
       </c>
       <c r="D6">
-        <v>2456.746145918664</v>
+        <v>2467.67772458129</v>
       </c>
       <c r="E6">
         <v>-3275.084</v>
@@ -1768,37 +1768,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M6">
-        <v>40.81441156568312</v>
+        <v>39.18025156568311</v>
       </c>
       <c r="N6">
-        <v>-49.78107823234981</v>
+        <v>-48.14691823234981</v>
       </c>
       <c r="O6">
-        <v>-11.94745877576396</v>
+        <v>-11.55526037576395</v>
       </c>
       <c r="P6">
-        <v>-37.83361945658586</v>
+        <v>-36.59165785658585</v>
       </c>
       <c r="Q6">
-        <v>-659.0336194565859</v>
+        <v>-657.7916578565859</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.1298988228010265</v>
+        <v>0.1298625356703326</v>
       </c>
       <c r="T6">
-        <v>1.728262501926698</v>
+        <v>1.72841421073384</v>
       </c>
       <c r="U6">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V6">
-        <v>-0.05272647374902779</v>
+        <v>-0.05492562997948905</v>
       </c>
       <c r="W6">
-        <v>0.2629265895976106</v>
+        <v>0.2529265895976106</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-0.2196936406209491</v>
+        <v>-0.2288567915812043</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1817,13 +1817,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.1372595109173067</v>
+        <v>0.1367246752718407</v>
       </c>
       <c r="C7">
-        <v>3421.189891590186</v>
+        <v>3434.267975906046</v>
       </c>
       <c r="D7">
-        <v>2401.959891590186</v>
+        <v>2415.037975906046</v>
       </c>
       <c r="E7">
         <v>-3234.23</v>
@@ -1850,37 +1850,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M7">
-        <v>51.0180144571039</v>
+        <v>48.9753144571039</v>
       </c>
       <c r="N7">
-        <v>-59.98468112377059</v>
+        <v>-57.9419811237706</v>
       </c>
       <c r="O7">
-        <v>-14.39632346970494</v>
+        <v>-13.90607546970494</v>
       </c>
       <c r="P7">
-        <v>-45.58835765406565</v>
+        <v>-44.03590565406565</v>
       </c>
       <c r="Q7">
-        <v>-666.7883576540657</v>
+        <v>-665.2359056540657</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.1307840735673531</v>
+        <v>0.1307474044668624</v>
       </c>
       <c r="T7">
-        <v>1.746454738789085</v>
+        <v>1.746608044531038</v>
       </c>
       <c r="U7">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V7">
-        <v>-0.04218117899922223</v>
+        <v>-0.04394050398359124</v>
       </c>
       <c r="W7">
-        <v>0.2602928205664263</v>
+        <v>0.2502928205664263</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-0.1757549124967592</v>
+        <v>-0.1830854332649634</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1899,13 +1899,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.1392990883617236</v>
+        <v>0.1386642527162575</v>
       </c>
       <c r="C8">
-        <v>3327.939838290409</v>
+        <v>3342.973111434871</v>
       </c>
       <c r="D8">
-        <v>2349.563838290409</v>
+        <v>2364.597111434871</v>
       </c>
       <c r="E8">
         <v>-3193.376</v>
@@ -1932,37 +1932,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M8">
-        <v>61.22161734852467</v>
+        <v>58.77037734852467</v>
       </c>
       <c r="N8">
-        <v>-70.18828401519137</v>
+        <v>-67.73704401519137</v>
       </c>
       <c r="O8">
-        <v>-16.84518816364593</v>
+        <v>-16.25689056364593</v>
       </c>
       <c r="P8">
-        <v>-53.34309585154544</v>
+        <v>-51.48015345154545</v>
       </c>
       <c r="Q8">
-        <v>-674.5430958515454</v>
+        <v>-672.6801534515455</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.1316881594563674</v>
+        <v>0.1316511002590631</v>
       </c>
       <c r="T8">
-        <v>1.765034044520883</v>
+        <v>1.765188981174986</v>
       </c>
       <c r="U8">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V8">
-        <v>-0.03515098249935186</v>
+        <v>-0.0366170866529927</v>
       </c>
       <c r="W8">
-        <v>0.2585369745456368</v>
+        <v>0.2485369745456368</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-0.1464624270806327</v>
+        <v>-0.1525711943874697</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1981,13 +1981,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.1413386658061405</v>
+        <v>0.1406038301606744</v>
       </c>
       <c r="C9">
-        <v>3236.926906633162</v>
+        <v>3253.742171234254</v>
       </c>
       <c r="D9">
-        <v>2299.404906633162</v>
+        <v>2316.220171234254</v>
       </c>
       <c r="E9">
         <v>-3152.522</v>
@@ -2014,37 +2014,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M9">
-        <v>71.42522023994546</v>
+        <v>68.56544023994546</v>
       </c>
       <c r="N9">
-        <v>-80.39188690661216</v>
+        <v>-77.53210690661216</v>
       </c>
       <c r="O9">
-        <v>-19.29405285758692</v>
+        <v>-18.60770565758692</v>
       </c>
       <c r="P9">
-        <v>-61.09783404902524</v>
+        <v>-58.92440124902524</v>
       </c>
       <c r="Q9">
-        <v>-682.2978340490253</v>
+        <v>-680.1244012490253</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.1326116880526725</v>
+        <v>0.1325742303693756</v>
       </c>
       <c r="T9">
-        <v>1.784012905214656</v>
+        <v>1.784169507854287</v>
       </c>
       <c r="U9">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V9">
-        <v>-0.03012941357087302</v>
+        <v>-0.03138607427399374</v>
       </c>
       <c r="W9">
-        <v>0.2572827988165015</v>
+        <v>0.2472827988165015</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.125539223211971</v>
+        <v>-0.130775309474974</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2063,13 +2063,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.1433782432505574</v>
+        <v>0.1425434076050913</v>
       </c>
       <c r="C10">
-        <v>3148.010815874793</v>
+        <v>3166.451018443774</v>
       </c>
       <c r="D10">
-        <v>2251.342815874793</v>
+        <v>2269.783018443773</v>
       </c>
       <c r="E10">
         <v>-3111.668</v>
@@ -2096,37 +2096,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M10">
-        <v>81.62882313136623</v>
+        <v>78.36050313136623</v>
       </c>
       <c r="N10">
-        <v>-90.59548979803293</v>
+        <v>-87.32716979803293</v>
       </c>
       <c r="O10">
-        <v>-21.7429175515279</v>
+        <v>-20.9585207515279</v>
       </c>
       <c r="P10">
-        <v>-68.85257224650502</v>
+        <v>-66.36864904650503</v>
       </c>
       <c r="Q10">
-        <v>-690.0525722465051</v>
+        <v>-687.568649046505</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.1335552933575928</v>
+        <v>0.1335174285255645</v>
       </c>
       <c r="T10">
-        <v>1.803404349836555</v>
+        <v>1.80356265467879</v>
       </c>
       <c r="U10">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V10">
-        <v>-0.0263632368745139</v>
+        <v>-0.02746281498974452</v>
       </c>
       <c r="W10">
-        <v>0.25634216701965</v>
+        <v>0.2463421670196499</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.1098468203104745</v>
+        <v>-0.1144283957906023</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2145,13 +2145,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.1454178206949743</v>
+        <v>0.1444829850495082</v>
       </c>
       <c r="C11">
-        <v>3061.062773715728</v>
+        <v>3080.985275658678</v>
       </c>
       <c r="D11">
-        <v>2205.248773715728</v>
+        <v>2225.171275658678</v>
       </c>
       <c r="E11">
         <v>-3070.814</v>
@@ -2178,37 +2178,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M11">
-        <v>91.832426022787</v>
+        <v>88.155566022787</v>
       </c>
       <c r="N11">
-        <v>-100.7990926894537</v>
+        <v>-97.1222326894537</v>
       </c>
       <c r="O11">
-        <v>-24.19178224546889</v>
+        <v>-23.30933584546889</v>
       </c>
       <c r="P11">
-        <v>-76.60731044398482</v>
+        <v>-73.81289684398482</v>
       </c>
       <c r="Q11">
-        <v>-697.8073104439849</v>
+        <v>-695.0128968439849</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.1345196372406433</v>
+        <v>0.1344813563115597</v>
       </c>
       <c r="T11">
-        <v>1.823221980054539</v>
+        <v>1.823382024510425</v>
       </c>
       <c r="U11">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V11">
-        <v>-0.02343398833290124</v>
+        <v>-0.02441139110199514</v>
       </c>
       <c r="W11">
-        <v>0.2556105645109877</v>
+        <v>0.2456105645109877</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.09764161805375515</v>
+        <v>-0.1017141295916464</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2227,13 +2227,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.1474573981393912</v>
+        <v>0.1464225624939251</v>
       </c>
       <c r="C12">
-        <v>2975.964323823048</v>
+        <v>2997.239384324739</v>
       </c>
       <c r="D12">
-        <v>2161.004323823048</v>
+        <v>2182.279384324739</v>
       </c>
       <c r="E12">
         <v>-3029.96</v>
@@ -2260,37 +2260,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M12">
-        <v>102.0360289142078</v>
+        <v>97.9506289142078</v>
       </c>
       <c r="N12">
-        <v>-111.0026955808745</v>
+        <v>-106.9172955808745</v>
       </c>
       <c r="O12">
-        <v>-26.64064693940988</v>
+        <v>-25.66015093940988</v>
       </c>
       <c r="P12">
-        <v>-84.36204864146461</v>
+        <v>-81.25714464146462</v>
       </c>
       <c r="Q12">
-        <v>-705.5620486414647</v>
+        <v>-702.4571446414647</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.1355054109877616</v>
+        <v>0.1354667047150215</v>
       </c>
       <c r="T12">
-        <v>1.843480002055145</v>
+        <v>1.843641824782763</v>
       </c>
       <c r="U12">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V12">
-        <v>-0.02109058949961112</v>
+        <v>-0.02197025199179562</v>
       </c>
       <c r="W12">
-        <v>0.2550252825040579</v>
+        <v>0.2450252825040579</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.08787745624837973</v>
+        <v>-0.09154271663248181</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2309,13 +2309,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.1494969755838081</v>
+        <v>0.148362139938342</v>
       </c>
       <c r="C13">
-        <v>2892.60632935896</v>
+        <v>2915.115770861166</v>
       </c>
       <c r="D13">
-        <v>2118.500329358959</v>
+        <v>2141.009770861166</v>
       </c>
       <c r="E13">
         <v>-2989.106</v>
@@ -2342,37 +2342,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M13">
-        <v>112.2396318056286</v>
+        <v>107.7456918056286</v>
       </c>
       <c r="N13">
-        <v>-121.2062984722953</v>
+        <v>-116.7123584722953</v>
       </c>
       <c r="O13">
-        <v>-29.08951163335086</v>
+        <v>-28.01096603335086</v>
       </c>
       <c r="P13">
-        <v>-92.11678683894441</v>
+        <v>-88.7013924389444</v>
       </c>
       <c r="Q13">
-        <v>-713.3167868389445</v>
+        <v>-709.9013924389444</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.1365133369539162</v>
+        <v>0.1364741957792352</v>
       </c>
       <c r="T13">
-        <v>1.864193260505203</v>
+        <v>1.864356901465715</v>
       </c>
       <c r="U13">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V13">
-        <v>-0.01917326318146465</v>
+        <v>-0.01997295635617783</v>
       </c>
       <c r="W13">
-        <v>0.2545464154074789</v>
+        <v>0.2445464154074789</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.07988859658943603</v>
+        <v>-0.08322065148407432</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2391,13 +2391,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.151536553028225</v>
+        <v>0.1503017173827589</v>
       </c>
       <c r="C14">
-        <v>2810.888074151047</v>
+        <v>2834.524105645306</v>
       </c>
       <c r="D14">
-        <v>2077.636074151047</v>
+        <v>2101.272105645306</v>
       </c>
       <c r="E14">
         <v>-2948.252</v>
@@ -2424,37 +2424,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M14">
-        <v>122.4432346970493</v>
+        <v>117.5407546970493</v>
       </c>
       <c r="N14">
-        <v>-131.409901363716</v>
+        <v>-126.507421363716</v>
       </c>
       <c r="O14">
-        <v>-31.53837632729185</v>
+        <v>-30.36178112729185</v>
       </c>
       <c r="P14">
-        <v>-99.8715250364242</v>
+        <v>-96.14564023642419</v>
       </c>
       <c r="Q14">
-        <v>-721.0715250364242</v>
+        <v>-717.3456402364243</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.1375441703283925</v>
+        <v>0.1375045843676356</v>
       </c>
       <c r="T14">
-        <v>1.885377274829126</v>
+        <v>1.885542775346008</v>
       </c>
       <c r="U14">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V14">
-        <v>-0.01757549124967593</v>
+        <v>-0.01830854332649635</v>
       </c>
       <c r="W14">
-        <v>0.2541473594936631</v>
+        <v>0.2441473594936631</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.07323121354031636</v>
+        <v>-0.07628559719373484</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2473,13 +2473,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.1535761304726419</v>
+        <v>0.1522412948271758</v>
       </c>
       <c r="C15">
-        <v>2730.716465920336</v>
+        <v>2755.380643014197</v>
       </c>
       <c r="D15">
-        <v>2038.318465920336</v>
+        <v>2062.982643014197</v>
       </c>
       <c r="E15">
         <v>-2907.398</v>
@@ -2506,37 +2506,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M15">
-        <v>132.6468375884701</v>
+        <v>127.3358175884701</v>
       </c>
       <c r="N15">
-        <v>-141.6135042551368</v>
+        <v>-136.3024842551368</v>
       </c>
       <c r="O15">
-        <v>-33.98724102123284</v>
+        <v>-32.71259622123284</v>
       </c>
       <c r="P15">
-        <v>-107.626263233904</v>
+        <v>-103.589888033904</v>
       </c>
       <c r="Q15">
-        <v>-728.826263233904</v>
+        <v>-724.789888033904</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.1385987010218223</v>
+        <v>0.1385586600500222</v>
       </c>
       <c r="T15">
-        <v>1.907048277988081</v>
+        <v>1.907215680809755</v>
       </c>
       <c r="U15">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V15">
-        <v>-0.01622353038431625</v>
+        <v>-0.01690019383984278</v>
       </c>
       <c r="W15">
-        <v>0.2538096967973575</v>
+        <v>0.2438096967973574</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.06759804326798435</v>
+        <v>-0.0704174743326782</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2555,13 +2555,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.1556157079170588</v>
+        <v>0.1541808722715927</v>
       </c>
       <c r="C16">
-        <v>2652.005328298736</v>
+        <v>2677.607632133873</v>
       </c>
       <c r="D16">
-        <v>2000.461328298736</v>
+        <v>2026.063632133873</v>
       </c>
       <c r="E16">
         <v>-2866.544</v>
@@ -2588,37 +2588,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M16">
-        <v>142.8504404798909</v>
+        <v>137.1308804798909</v>
       </c>
       <c r="N16">
-        <v>-151.8171071465576</v>
+        <v>-146.0975471465576</v>
       </c>
       <c r="O16">
-        <v>-36.43610571517382</v>
+        <v>-35.06341131517382</v>
       </c>
       <c r="P16">
-        <v>-115.3810014313838</v>
+        <v>-111.0341358313838</v>
       </c>
       <c r="Q16">
-        <v>-736.5810014313838</v>
+        <v>-732.2341358313838</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.1396777556848668</v>
+        <v>0.1396372491203713</v>
       </c>
       <c r="T16">
-        <v>1.929223257964687</v>
+        <v>1.929392607330799</v>
       </c>
       <c r="U16">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V16">
-        <v>-0.01506470678543651</v>
+        <v>-0.01569303713699687</v>
       </c>
       <c r="W16">
-        <v>0.2535202716290955</v>
+        <v>0.2435202716290954</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.06276961160598549</v>
+        <v>-0.06538765473748698</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2637,13 +2637,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.1576552853614757</v>
+        <v>0.1561204497160096</v>
       </c>
       <c r="C17">
-        <v>2574.67477030292</v>
+        <v>2601.13279001479</v>
       </c>
       <c r="D17">
-        <v>1963.98477030292</v>
+        <v>1990.44279001479</v>
       </c>
       <c r="E17">
         <v>-2825.69</v>
@@ -2670,37 +2670,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M17">
-        <v>153.0540433713117</v>
+        <v>146.9259433713117</v>
       </c>
       <c r="N17">
-        <v>-162.0207100379784</v>
+        <v>-155.8926100379784</v>
       </c>
       <c r="O17">
-        <v>-38.88497040911481</v>
+        <v>-37.4142264091148</v>
       </c>
       <c r="P17">
-        <v>-123.1357396288636</v>
+        <v>-118.4783836288636</v>
       </c>
       <c r="Q17">
-        <v>-744.3357396288636</v>
+        <v>-739.6783836288636</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.1407821998693946</v>
+        <v>0.1407412167570816</v>
       </c>
       <c r="T17">
-        <v>1.951920002176036</v>
+        <v>1.952091343887631</v>
       </c>
       <c r="U17">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V17">
-        <v>-0.01406039299974074</v>
+        <v>-0.01464683466119708</v>
       </c>
       <c r="W17">
-        <v>0.2532694364832684</v>
+        <v>0.2432694364832683</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2708,7 +2708,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.058584970832253</v>
+        <v>-0.06102847775498788</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2719,13 +2719,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.1596948628058925</v>
+        <v>0.1580600271604265</v>
       </c>
       <c r="C18">
-        <v>2498.650623555259</v>
+        <v>2525.888829157238</v>
       </c>
       <c r="D18">
-        <v>1928.814623555258</v>
+        <v>1956.052829157237</v>
       </c>
       <c r="E18">
         <v>-2784.836</v>
@@ -2752,37 +2752,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M18">
-        <v>163.2576462627325</v>
+        <v>156.7210062627325</v>
       </c>
       <c r="N18">
-        <v>-172.2243129293992</v>
+        <v>-165.6876729293992</v>
       </c>
       <c r="O18">
-        <v>-41.3338351030558</v>
+        <v>-39.7650415030558</v>
       </c>
       <c r="P18">
-        <v>-130.8904778263434</v>
+        <v>-125.9226314263434</v>
       </c>
       <c r="Q18">
-        <v>-752.0904778263434</v>
+        <v>-747.1226314263434</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.1419129403440302</v>
+        <v>0.141871469337523</v>
       </c>
       <c r="T18">
-        <v>1.975157145059084</v>
+        <v>1.97533052655296</v>
       </c>
       <c r="U18">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V18">
-        <v>-0.01318161843725695</v>
+        <v>-0.01373140749487226</v>
       </c>
       <c r="W18">
-        <v>0.2530499557306697</v>
+        <v>0.2430499557306697</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2790,7 +2790,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.05492341015523738</v>
+        <v>-0.05721419789530113</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2801,13 +2801,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.1617344402503094</v>
+        <v>0.1599996046048434</v>
       </c>
       <c r="C19">
-        <v>2423.863938908909</v>
+        <v>2451.813033331857</v>
       </c>
       <c r="D19">
-        <v>1894.881938908909</v>
+        <v>1922.831033331857</v>
       </c>
       <c r="E19">
         <v>-2743.982</v>
@@ -2834,37 +2834,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M19">
-        <v>173.4612491541533</v>
+        <v>166.5160691541533</v>
       </c>
       <c r="N19">
-        <v>-182.4279158208199</v>
+        <v>-175.48273582082</v>
       </c>
       <c r="O19">
-        <v>-43.78269979699679</v>
+        <v>-42.11585659699679</v>
       </c>
       <c r="P19">
-        <v>-138.6452160238232</v>
+        <v>-133.3668792238232</v>
       </c>
       <c r="Q19">
-        <v>-759.8452160238232</v>
+        <v>-754.5668792238232</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.1430709275770909</v>
+        <v>0.1430289569199028</v>
       </c>
       <c r="T19">
-        <v>1.99895421909594</v>
+        <v>1.999129689523478</v>
       </c>
       <c r="U19">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V19">
-        <v>-0.0124062291174183</v>
+        <v>-0.01292367764223271</v>
       </c>
       <c r="W19">
-        <v>0.2528562962430826</v>
+        <v>0.2428562962430826</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2872,7 +2872,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.05169262132257635</v>
+        <v>-0.0538486568426364</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2883,13 +2883,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.1637740176947263</v>
+        <v>0.1619391820492603</v>
       </c>
       <c r="C20">
-        <v>2350.250535288087</v>
+        <v>2378.846875868122</v>
       </c>
       <c r="D20">
-        <v>1862.122535288087</v>
+        <v>1890.718875868121</v>
       </c>
       <c r="E20">
         <v>-2703.128</v>
@@ -2916,37 +2916,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M20">
-        <v>183.664852045574</v>
+        <v>176.311132045574</v>
       </c>
       <c r="N20">
-        <v>-192.6315187122407</v>
+        <v>-185.2777987122407</v>
       </c>
       <c r="O20">
-        <v>-46.23156449093777</v>
+        <v>-44.46667169093777</v>
       </c>
       <c r="P20">
-        <v>-146.3999542213029</v>
+        <v>-140.8111270213029</v>
       </c>
       <c r="Q20">
-        <v>-767.5999542213031</v>
+        <v>-762.011127021303</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.1442571584012017</v>
+        <v>0.1442146759067309</v>
       </c>
       <c r="T20">
-        <v>2.02333170957272</v>
+        <v>2.02350931988352</v>
       </c>
       <c r="U20">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V20">
-        <v>-0.01171699416645062</v>
+        <v>-0.01220569555099757</v>
       </c>
       <c r="W20">
-        <v>0.2526841544763385</v>
+        <v>0.2426841544763385</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.04882080902687758</v>
+        <v>-0.0508570647958233</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2965,13 +2965,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.1658135951391432</v>
+        <v>0.1638787594936772</v>
       </c>
       <c r="C21">
-        <v>2277.750594531869</v>
+        <v>2306.935675563071</v>
       </c>
       <c r="D21">
-        <v>1830.476594531869</v>
+        <v>1859.661675563071</v>
       </c>
       <c r="E21">
         <v>-2662.274</v>
@@ -2998,37 +2998,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M21">
-        <v>193.8684549369948</v>
+        <v>186.1061949369948</v>
       </c>
       <c r="N21">
-        <v>-202.8351216036615</v>
+        <v>-195.0728616036615</v>
       </c>
       <c r="O21">
-        <v>-48.68042918487875</v>
+        <v>-46.81748678487876</v>
       </c>
       <c r="P21">
-        <v>-154.1546924187827</v>
+        <v>-148.2553748187827</v>
       </c>
       <c r="Q21">
-        <v>-775.3546924187827</v>
+        <v>-769.4553748187827</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.1454726788752906</v>
+        <v>0.1454296719055794</v>
       </c>
       <c r="T21">
-        <v>2.048311113394605</v>
+        <v>2.048490916425292</v>
       </c>
       <c r="U21">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V21">
-        <v>-0.01110031026295322</v>
+        <v>-0.01156329052199769</v>
       </c>
       <c r="W21">
-        <v>0.2525301328955675</v>
+        <v>0.2425301328955675</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.04625129276230511</v>
+        <v>-0.04818037717499046</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3047,13 +3047,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.1678531725835601</v>
+        <v>0.1658183369380941</v>
       </c>
       <c r="C22">
-        <v>2206.308296860342</v>
+        <v>2236.028285954538</v>
       </c>
       <c r="D22">
-        <v>1799.888296860342</v>
+        <v>1829.608285954538</v>
       </c>
       <c r="E22">
         <v>-2621.42</v>
@@ -3080,37 +3080,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M22">
-        <v>204.0720578284156</v>
+        <v>195.9012578284156</v>
       </c>
       <c r="N22">
-        <v>-213.0387244950823</v>
+        <v>-204.8679244950823</v>
       </c>
       <c r="O22">
-        <v>-51.12929387881974</v>
+        <v>-49.16830187881975</v>
       </c>
       <c r="P22">
-        <v>-161.9094306162625</v>
+        <v>-155.6996226162626</v>
       </c>
       <c r="Q22">
-        <v>-783.1094306162626</v>
+        <v>-776.8996226162626</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.1467185873612318</v>
+        <v>0.1466750428043992</v>
       </c>
       <c r="T22">
-        <v>2.073915002312038</v>
+        <v>2.074097052880608</v>
       </c>
       <c r="U22">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V22">
-        <v>-0.01054529474980556</v>
+        <v>-0.01098512599589781</v>
       </c>
       <c r="W22">
-        <v>0.2523915134728736</v>
+        <v>0.2423915134728736</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.04393872812418986</v>
+        <v>-0.04577135831624091</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3129,13 +3129,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.169892750027977</v>
+        <v>0.1677579143825109</v>
       </c>
       <c r="C23">
-        <v>2135.871492289417</v>
+        <v>2166.076814244539</v>
       </c>
       <c r="D23">
-        <v>1770.305492289417</v>
+        <v>1800.510814244538</v>
       </c>
       <c r="E23">
         <v>-2580.566</v>
@@ -3162,37 +3162,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M23">
-        <v>214.2756607198364</v>
+        <v>205.6963207198363</v>
       </c>
       <c r="N23">
-        <v>-223.2423273865031</v>
+        <v>-214.662987386503</v>
       </c>
       <c r="O23">
-        <v>-53.57815857276074</v>
+        <v>-51.51911697276073</v>
       </c>
       <c r="P23">
-        <v>-169.6641688137423</v>
+        <v>-163.1438704137423</v>
       </c>
       <c r="Q23">
-        <v>-790.8641688137424</v>
+        <v>-784.3438704137424</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.1479960378341587</v>
+        <v>0.1479519420804042</v>
       </c>
       <c r="T23">
-        <v>2.100167090948899</v>
+        <v>2.100351445955046</v>
       </c>
       <c r="U23">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V23">
-        <v>-0.01004313785695768</v>
+        <v>-0.01046202475799791</v>
       </c>
       <c r="W23">
-        <v>0.2522660958999601</v>
+        <v>0.2422660958999601</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.04184640773732373</v>
+        <v>-0.04359176982499124</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3211,13 +3211,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.1719323274723939</v>
+        <v>0.1696974918269278</v>
       </c>
       <c r="C24">
-        <v>2066.391403925265</v>
+        <v>2097.036366623664</v>
       </c>
       <c r="D24">
-        <v>1741.679403925265</v>
+        <v>1772.324366623664</v>
       </c>
       <c r="E24">
         <v>-2539.712</v>
@@ -3244,37 +3244,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M24">
-        <v>224.4792636112572</v>
+        <v>215.4913836112571</v>
       </c>
       <c r="N24">
-        <v>-233.4459302779238</v>
+        <v>-224.4580502779238</v>
       </c>
       <c r="O24">
-        <v>-56.02702326670173</v>
+        <v>-53.86993206670171</v>
       </c>
       <c r="P24">
-        <v>-177.4189070112221</v>
+        <v>-170.5881182112221</v>
       </c>
       <c r="Q24">
-        <v>-798.6189070112222</v>
+        <v>-791.7881182112221</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.1493062434474172</v>
+        <v>0.1492615823634863</v>
       </c>
       <c r="T24">
-        <v>2.127092310063629</v>
+        <v>2.127279028595496</v>
       </c>
       <c r="U24">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V24">
-        <v>-0.009586631590732326</v>
+        <v>-0.009986478178088917</v>
       </c>
       <c r="W24">
-        <v>0.2521520799245842</v>
+        <v>0.2421520799245842</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3282,7 +3282,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.03994429829471802</v>
+        <v>-0.04161032574203727</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3293,13 +3293,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.1739719049168108</v>
+        <v>0.1716370692713447</v>
       </c>
       <c r="C25">
-        <v>1997.822359587296</v>
+        <v>2028.864817147991</v>
       </c>
       <c r="D25">
-        <v>1713.964359587296</v>
+        <v>1745.006817147991</v>
       </c>
       <c r="E25">
         <v>-2498.858</v>
@@ -3326,37 +3326,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M25">
-        <v>234.6828665026779</v>
+        <v>225.2864465026779</v>
       </c>
       <c r="N25">
-        <v>-243.6495331693446</v>
+        <v>-234.2531131693446</v>
       </c>
       <c r="O25">
-        <v>-58.47588796064271</v>
+        <v>-56.22074716064271</v>
       </c>
       <c r="P25">
-        <v>-185.1736452087019</v>
+        <v>-178.0323660087019</v>
       </c>
       <c r="Q25">
-        <v>-806.373645208702</v>
+        <v>-799.232366008702</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.1506504803753057</v>
+        <v>0.1506052392772978</v>
       </c>
       <c r="T25">
-        <v>2.154716885519</v>
+        <v>2.154906028966866</v>
       </c>
       <c r="U25">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V25">
-        <v>-0.009169821521570051</v>
+        <v>-0.009552283474693748</v>
       </c>
       <c r="W25">
-        <v>0.2520479783818496</v>
+        <v>0.2420479783818496</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.03820758967320859</v>
+        <v>-0.03980118114455733</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3375,13 +3375,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.1760114823612277</v>
+        <v>0.1735766467157616</v>
       </c>
       <c r="C26">
-        <v>1930.121548653596</v>
+        <v>1961.52259766589</v>
       </c>
       <c r="D26">
-        <v>1687.117548653596</v>
+        <v>1718.51859766589</v>
       </c>
       <c r="E26">
         <v>-2458.004</v>
@@ -3408,37 +3408,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M26">
-        <v>244.8864693940987</v>
+        <v>235.0815093940987</v>
       </c>
       <c r="N26">
-        <v>-253.8531360607654</v>
+        <v>-244.0481760607654</v>
       </c>
       <c r="O26">
-        <v>-60.92475265458369</v>
+        <v>-58.57156225458369</v>
       </c>
       <c r="P26">
-        <v>-192.9283834061817</v>
+        <v>-185.4766138061817</v>
       </c>
       <c r="Q26">
-        <v>-814.1283834061817</v>
+        <v>-806.6766138061818</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.1520300919591913</v>
+        <v>0.1519842555835781</v>
       </c>
       <c r="T26">
-        <v>2.183068423486356</v>
+        <v>2.183260055663798</v>
       </c>
       <c r="U26">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V26">
-        <v>-0.008787745624837966</v>
+        <v>-0.009154271663248175</v>
       </c>
       <c r="W26">
-        <v>0.2519525519676762</v>
+        <v>0.2419525519676763</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3446,7 +3446,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.03661560677015818</v>
+        <v>-0.03814279859686742</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3457,13 +3457,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.1780510598056446</v>
+        <v>0.1755162241601785</v>
       </c>
       <c r="C27">
-        <v>1863.24880140597</v>
+        <v>1894.972506591517</v>
       </c>
       <c r="D27">
-        <v>1661.098801405969</v>
+        <v>1692.822506591517</v>
       </c>
       <c r="E27">
         <v>-2417.15</v>
@@ -3490,37 +3490,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M27">
-        <v>255.0900722855195</v>
+        <v>244.8765722855195</v>
       </c>
       <c r="N27">
-        <v>-264.0567389521862</v>
+        <v>-253.8432389521862</v>
       </c>
       <c r="O27">
-        <v>-63.37361734852468</v>
+        <v>-60.92237734852468</v>
       </c>
       <c r="P27">
-        <v>-200.6831216036615</v>
+        <v>-192.9208616036615</v>
       </c>
       <c r="Q27">
-        <v>-821.8831216036615</v>
+        <v>-814.1208616036615</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.1534464931853139</v>
+        <v>0.1534000456580258</v>
       </c>
       <c r="T27">
-        <v>2.212176002466174</v>
+        <v>2.212370189739315</v>
       </c>
       <c r="U27">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V27">
-        <v>-0.008436235799844446</v>
+        <v>-0.008788100796718249</v>
       </c>
       <c r="W27">
-        <v>0.2518647596666368</v>
+        <v>0.2418647596666368</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.03515098249935167</v>
+        <v>-0.03661708665299268</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3539,13 +3539,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.1800906372500615</v>
+        <v>0.1774558016045954</v>
       </c>
       <c r="C28">
-        <v>1797.166388482536</v>
+        <v>1829.179534581402</v>
       </c>
       <c r="D28">
-        <v>1635.870388482536</v>
+        <v>1667.883534581402</v>
       </c>
       <c r="E28">
         <v>-2376.296</v>
@@ -3572,37 +3572,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M28">
-        <v>265.2936751769403</v>
+        <v>254.6716351769402</v>
       </c>
       <c r="N28">
-        <v>-274.260341843607</v>
+        <v>-263.6383018436069</v>
       </c>
       <c r="O28">
-        <v>-65.82248204246567</v>
+        <v>-63.27319244246566</v>
       </c>
       <c r="P28">
-        <v>-208.4378598011413</v>
+        <v>-200.3651094011413</v>
       </c>
       <c r="Q28">
-        <v>-829.6378598011413</v>
+        <v>-821.5651094011413</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.1549011755256559</v>
+        <v>0.1548541003290802</v>
       </c>
       <c r="T28">
-        <v>2.242070272769771</v>
+        <v>2.242267084195252</v>
       </c>
       <c r="U28">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V28">
-        <v>-0.008111765192158123</v>
+        <v>-0.008450096919921391</v>
       </c>
       <c r="W28">
-        <v>0.2517837206195234</v>
+        <v>0.2417837206195234</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3610,7 +3610,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.03379902163399207</v>
+        <v>-0.03520873716633921</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3621,13 +3621,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.1821302146944784</v>
+        <v>0.1793953790490123</v>
       </c>
       <c r="C29">
-        <v>1731.838838332148</v>
+        <v>1764.110705396318</v>
       </c>
       <c r="D29">
-        <v>1611.396838332148</v>
+        <v>1643.668705396318</v>
       </c>
       <c r="E29">
         <v>-2335.442</v>
@@ -3654,37 +3654,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M29">
-        <v>275.497278068361</v>
+        <v>264.466698068361</v>
       </c>
       <c r="N29">
-        <v>-284.4639447350277</v>
+        <v>-273.4333647350277</v>
       </c>
       <c r="O29">
-        <v>-68.27134673640666</v>
+        <v>-65.62400753640665</v>
       </c>
       <c r="P29">
-        <v>-216.1925979986211</v>
+        <v>-207.8093571986211</v>
       </c>
       <c r="Q29">
-        <v>-837.3925979986211</v>
+        <v>-829.0093571986212</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.1563957121766923</v>
+        <v>0.15634799211441</v>
       </c>
       <c r="T29">
-        <v>2.272783564177576</v>
+        <v>2.272983071649981</v>
       </c>
       <c r="U29">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V29">
-        <v>-0.007811329444300414</v>
+        <v>-0.008137130367331711</v>
       </c>
       <c r="W29">
-        <v>0.2517086844647889</v>
+        <v>0.2417086844647888</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.03254720601791838</v>
+        <v>-0.03390470986388205</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3703,13 +3703,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.1841697921388953</v>
+        <v>0.1813349564934292</v>
       </c>
       <c r="C30">
-        <v>1667.232770813192</v>
+        <v>1699.734930427252</v>
       </c>
       <c r="D30">
-        <v>1587.644770813192</v>
+        <v>1620.146930427252</v>
       </c>
       <c r="E30">
         <v>-2294.588</v>
@@ -3736,37 +3736,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M30">
-        <v>285.7008809597818</v>
+        <v>274.2617609597818</v>
       </c>
       <c r="N30">
-        <v>-294.6675476264485</v>
+        <v>-283.2284276264485</v>
       </c>
       <c r="O30">
-        <v>-70.72021143034765</v>
+        <v>-67.97482263034765</v>
       </c>
       <c r="P30">
-        <v>-223.9473361961009</v>
+        <v>-215.2536049961009</v>
       </c>
       <c r="Q30">
-        <v>-845.1473361961009</v>
+        <v>-836.4536049961009</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.1579317637347019</v>
+        <v>0.1578833808937768</v>
       </c>
       <c r="T30">
-        <v>2.304350002568931</v>
+        <v>2.304552280978454</v>
       </c>
       <c r="U30">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V30">
-        <v>-0.007532353392718255</v>
+        <v>-0.007846518568498434</v>
       </c>
       <c r="W30">
-        <v>0.2516390080353925</v>
+        <v>0.2416390080353924</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.03138480580299263</v>
+        <v>-0.03269382736874338</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.1862093695833121</v>
+        <v>0.1832745339378461</v>
       </c>
       <c r="C31">
-        <v>1603.31674529519</v>
+        <v>1636.022875536019</v>
       </c>
       <c r="D31">
-        <v>1564.58274529519</v>
+        <v>1597.288875536019</v>
       </c>
       <c r="E31">
         <v>-2253.734</v>
@@ -3818,37 +3818,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M31">
-        <v>295.9044838512025</v>
+        <v>284.0568238512025</v>
       </c>
       <c r="N31">
-        <v>-304.8711505178692</v>
+        <v>-293.0234905178692</v>
       </c>
       <c r="O31">
-        <v>-73.16907612428861</v>
+        <v>-70.32563772428861</v>
       </c>
       <c r="P31">
-        <v>-231.7020743935806</v>
+        <v>-222.6978527935806</v>
       </c>
       <c r="Q31">
-        <v>-852.9020743935807</v>
+        <v>-843.8978527935807</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.1595110843506836</v>
+        <v>0.1594620200612948</v>
       </c>
       <c r="T31">
-        <v>2.33680563640793</v>
+        <v>2.337010763809136</v>
       </c>
       <c r="U31">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V31">
-        <v>-0.007272617068831421</v>
+        <v>-0.007575948962688146</v>
       </c>
       <c r="W31">
-        <v>0.2515741368769889</v>
+        <v>0.2415741368769889</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.03030257112013102</v>
+        <v>-0.03156645401120062</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3867,13 +3867,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.188248947027729</v>
+        <v>0.185214111382263</v>
       </c>
       <c r="C32">
-        <v>1540.061121809642</v>
+        <v>1572.946839011231</v>
       </c>
       <c r="D32">
-        <v>1542.181121809642</v>
+        <v>1575.06683901123</v>
       </c>
       <c r="E32">
         <v>-2212.88</v>
@@ -3900,37 +3900,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M32">
-        <v>306.1080867426234</v>
+        <v>293.8518867426233</v>
       </c>
       <c r="N32">
-        <v>-315.0747534092901</v>
+        <v>-302.81855340929</v>
       </c>
       <c r="O32">
-        <v>-75.61794081822961</v>
+        <v>-72.67645281822961</v>
       </c>
       <c r="P32">
-        <v>-239.4568125910604</v>
+        <v>-230.1421005910604</v>
       </c>
       <c r="Q32">
-        <v>-860.6568125910605</v>
+        <v>-851.3421005910604</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.1611355284128363</v>
+        <v>0.1610857632050276</v>
       </c>
       <c r="T32">
-        <v>2.370188574070901</v>
+        <v>2.370396631863552</v>
       </c>
       <c r="U32">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V32">
-        <v>-0.007030196499870372</v>
+        <v>-0.00732341733059854</v>
       </c>
       <c r="W32">
-        <v>0.2515135904624789</v>
+        <v>0.2415135904624789</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3938,7 +3938,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.0292924854161265</v>
+        <v>-0.03051423887749394</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3949,13 +3949,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.1902885244721459</v>
+        <v>0.1871536888266799</v>
       </c>
       <c r="C33">
-        <v>1477.437933960714</v>
+        <v>1510.480639571985</v>
       </c>
       <c r="D33">
-        <v>1520.411933960714</v>
+        <v>1553.454639571985</v>
       </c>
       <c r="E33">
         <v>-2172.026</v>
@@ -3982,37 +3982,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M33">
-        <v>316.3116896340441</v>
+        <v>303.6469496340441</v>
       </c>
       <c r="N33">
-        <v>-325.2783563007108</v>
+        <v>-312.6136163007108</v>
       </c>
       <c r="O33">
-        <v>-78.06680551217059</v>
+        <v>-75.02726791217059</v>
       </c>
       <c r="P33">
-        <v>-247.2115507885402</v>
+        <v>-237.5863483885402</v>
       </c>
       <c r="Q33">
-        <v>-868.4115507885402</v>
+        <v>-858.7863483885403</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.1628070578101238</v>
+        <v>0.1627565713674193</v>
       </c>
       <c r="T33">
-        <v>2.404539133115406</v>
+        <v>2.404750206238386</v>
       </c>
       <c r="U33">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V33">
-        <v>-0.00680341596761649</v>
+        <v>-0.007087178061869555</v>
       </c>
       <c r="W33">
-        <v>0.2514569502682599</v>
+        <v>0.2414569502682599</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.02834756653173542</v>
+        <v>-0.02952990859112314</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4031,13 +4031,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.1923281019165629</v>
+        <v>0.1890932662710968</v>
       </c>
       <c r="C34">
-        <v>1415.420772449932</v>
+        <v>1448.599513467272</v>
       </c>
       <c r="D34">
-        <v>1499.248772449932</v>
+        <v>1532.427513467271</v>
       </c>
       <c r="E34">
         <v>-2131.172</v>
@@ -4064,37 +4064,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M34">
-        <v>326.5152925254649</v>
+        <v>313.4420125254649</v>
       </c>
       <c r="N34">
-        <v>-335.4819591921316</v>
+        <v>-322.4086791921316</v>
       </c>
       <c r="O34">
-        <v>-80.51567020611159</v>
+        <v>-77.37808300611158</v>
       </c>
       <c r="P34">
-        <v>-254.96628898602</v>
+        <v>-245.03059618602</v>
       </c>
       <c r="Q34">
-        <v>-876.16628898602</v>
+        <v>-866.2305961860201</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.1645277498367432</v>
+        <v>0.164476520946352</v>
       </c>
       <c r="T34">
-        <v>2.439900002720045</v>
+        <v>2.440114179859539</v>
       </c>
       <c r="U34">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V34">
-        <v>-0.006590809218628474</v>
+        <v>-0.006865703747436131</v>
       </c>
       <c r="W34">
-        <v>0.2514038500861795</v>
+        <v>0.2414038500861796</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.02746170507761869</v>
+        <v>-0.02860709894765057</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4113,13 +4113,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.1943676793609798</v>
+        <v>0.1910328437155137</v>
       </c>
       <c r="C35">
-        <v>1353.984678194903</v>
+        <v>1387.280019820758</v>
       </c>
       <c r="D35">
-        <v>1478.666678194903</v>
+        <v>1511.962019820758</v>
       </c>
       <c r="E35">
         <v>-2090.318</v>
@@ -4146,37 +4146,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M35">
-        <v>336.7188954168857</v>
+        <v>323.2370754168857</v>
       </c>
       <c r="N35">
-        <v>-345.6855620835524</v>
+        <v>-332.2037420835524</v>
       </c>
       <c r="O35">
-        <v>-82.96453490005258</v>
+        <v>-79.72889810005258</v>
       </c>
       <c r="P35">
-        <v>-262.7210271834999</v>
+        <v>-252.4748439834999</v>
       </c>
       <c r="Q35">
-        <v>-883.9210271835</v>
+        <v>-873.6748439834998</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.1662998058044558</v>
+        <v>0.1662478123037602</v>
       </c>
       <c r="T35">
-        <v>2.47631642067109</v>
+        <v>2.476533794484309</v>
       </c>
       <c r="U35">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V35">
-        <v>-0.006391087727154883</v>
+        <v>-0.006657652118725945</v>
       </c>
       <c r="W35">
-        <v>0.2513539680969526</v>
+        <v>0.2413539680969526</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.02662953219647868</v>
+        <v>-0.02774021716135811</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4195,13 +4195,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.1964072568053966</v>
+        <v>0.1929724211599306</v>
       </c>
       <c r="C36">
-        <v>1293.106044132588</v>
+        <v>1326.499953460318</v>
       </c>
       <c r="D36">
-        <v>1458.642044132588</v>
+        <v>1492.035953460318</v>
       </c>
       <c r="E36">
         <v>-2049.464</v>
@@ -4228,37 +4228,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M36">
-        <v>346.9224983083065</v>
+        <v>333.0321383083065</v>
       </c>
       <c r="N36">
-        <v>-355.8891649749732</v>
+        <v>-341.9988049749732</v>
       </c>
       <c r="O36">
-        <v>-85.41339959399356</v>
+        <v>-82.07971319399357</v>
       </c>
       <c r="P36">
-        <v>-270.4757653809796</v>
+        <v>-259.9190917809797</v>
       </c>
       <c r="Q36">
-        <v>-891.6757653809797</v>
+        <v>-881.1190917809797</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1681255604378567</v>
+        <v>0.1680727791568475</v>
       </c>
       <c r="T36">
-        <v>2.513836366438834</v>
+        <v>2.514057033794677</v>
       </c>
       <c r="U36">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V36">
-        <v>-0.006203114558709152</v>
+        <v>-0.006461838821116357</v>
       </c>
       <c r="W36">
-        <v>0.251307020342386</v>
+        <v>0.241307020342386</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.02584631066128806</v>
+        <v>-0.02692432842131809</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4277,13 +4277,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.1984468342498135</v>
+        <v>0.1949119986043474</v>
       </c>
       <c r="C37">
-        <v>1232.762524894854</v>
+        <v>1266.238264550793</v>
       </c>
       <c r="D37">
-        <v>1439.152524894854</v>
+        <v>1472.628264550793</v>
       </c>
       <c r="E37">
         <v>-2008.61</v>
@@ -4310,37 +4310,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M37">
-        <v>357.1261011997273</v>
+        <v>342.8272011997273</v>
       </c>
       <c r="N37">
-        <v>-366.092767866394</v>
+        <v>-351.793867866394</v>
       </c>
       <c r="O37">
-        <v>-87.86226428793456</v>
+        <v>-84.43052828793455</v>
       </c>
       <c r="P37">
-        <v>-278.2305035784594</v>
+        <v>-267.3633395784594</v>
       </c>
       <c r="Q37">
-        <v>-899.4305035784595</v>
+        <v>-888.5633395784595</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1700074921369006</v>
+        <v>0.1699538988361836</v>
       </c>
       <c r="T37">
-        <v>2.552510772076355</v>
+        <v>2.552734834314595</v>
       </c>
       <c r="U37">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V37">
-        <v>-0.006025882714174604</v>
+        <v>-0.006277214854798749</v>
       </c>
       <c r="W37">
-        <v>0.2512627553166518</v>
+        <v>0.2412627553166518</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4348,7 +4348,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.02510784464239424</v>
+        <v>-0.02615506189499484</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4359,13 +4359,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.2004864116942305</v>
+        <v>0.1968515760487644</v>
       </c>
       <c r="C38">
-        <v>1172.932953629723</v>
+        <v>1206.47498441848</v>
       </c>
       <c r="D38">
-        <v>1420.176953629723</v>
+        <v>1453.71898441848</v>
       </c>
       <c r="E38">
         <v>-1967.756</v>
@@ -4392,37 +4392,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M38">
-        <v>367.329704091148</v>
+        <v>352.622264091148</v>
       </c>
       <c r="N38">
-        <v>-376.2963707578147</v>
+        <v>-361.5889307578147</v>
       </c>
       <c r="O38">
-        <v>-90.31112898187553</v>
+        <v>-86.78134338187553</v>
       </c>
       <c r="P38">
-        <v>-285.9852417759392</v>
+        <v>-274.8075873759392</v>
       </c>
       <c r="Q38">
-        <v>-907.1852417759392</v>
+        <v>-896.0075873759392</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1719482342015397</v>
+        <v>0.171893803505499</v>
       </c>
       <c r="T38">
-        <v>2.592393752890048</v>
+        <v>2.59262131610076</v>
       </c>
       <c r="U38">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V38">
-        <v>-0.005858497083225311</v>
+        <v>-0.006102847775498784</v>
       </c>
       <c r="W38">
-        <v>0.251220949459014</v>
+        <v>0.241220949459014</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.02441040451343879</v>
+        <v>-0.02542853239791154</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4441,13 +4441,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.2025259891386473</v>
+        <v>0.1987911534931813</v>
       </c>
       <c r="C39">
-        <v>1113.597265317382</v>
+        <v>1147.191157017875</v>
       </c>
       <c r="D39">
-        <v>1401.695265317382</v>
+        <v>1435.289157017875</v>
       </c>
       <c r="E39">
         <v>-1926.902</v>
@@ -4474,37 +4474,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M39">
-        <v>377.5333069825688</v>
+        <v>362.4173269825688</v>
       </c>
       <c r="N39">
-        <v>-386.4999736492355</v>
+        <v>-371.3839936492355</v>
       </c>
       <c r="O39">
-        <v>-92.75999367581652</v>
+        <v>-89.13215847581651</v>
       </c>
       <c r="P39">
-        <v>-293.739979973419</v>
+        <v>-282.251835173419</v>
       </c>
       <c r="Q39">
-        <v>-914.939979973419</v>
+        <v>-903.451835173419</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1739505871253737</v>
+        <v>0.1738952924500307</v>
       </c>
       <c r="T39">
-        <v>2.633542860078779</v>
+        <v>2.633774035403947</v>
       </c>
       <c r="U39">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V39">
-        <v>-0.005700159324219221</v>
+        <v>-0.005937905943728545</v>
       </c>
       <c r="W39">
-        <v>0.2511814033774646</v>
+        <v>0.2411814033774647</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4512,7 +4512,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.02375066385091351</v>
+        <v>-0.02474127476553556</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4523,13 +4523,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.2045655665830642</v>
+        <v>0.2007307309375982</v>
       </c>
       <c r="C40">
-        <v>1054.736425996895</v>
+        <v>1088.368775546227</v>
       </c>
       <c r="D40">
-        <v>1383.688425996895</v>
+        <v>1417.320775546227</v>
       </c>
       <c r="E40">
         <v>-1886.048</v>
@@ -4556,37 +4556,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M40">
-        <v>387.7369098739896</v>
+        <v>372.2123898739896</v>
       </c>
       <c r="N40">
-        <v>-396.7035765406563</v>
+        <v>-381.1790565406563</v>
       </c>
       <c r="O40">
-        <v>-95.20885836975751</v>
+        <v>-91.4829735697575</v>
       </c>
       <c r="P40">
-        <v>-301.4947181708988</v>
+        <v>-289.6960829708988</v>
       </c>
       <c r="Q40">
-        <v>-922.6947181708988</v>
+        <v>-910.8960829708988</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1760175320790087</v>
+        <v>0.1759613455540635</v>
       </c>
       <c r="T40">
-        <v>2.676019357821985</v>
+        <v>2.67625426178143</v>
       </c>
       <c r="U40">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V40">
-        <v>-0.00555015513147661</v>
+        <v>-0.005781645260998847</v>
       </c>
       <c r="W40">
-        <v>0.2511439386686285</v>
+        <v>0.2411439386686285</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.02312564638115244</v>
+        <v>-0.02409018858749512</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4605,13 +4605,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.2066051440274811</v>
+        <v>0.2026703083820151</v>
       </c>
       <c r="C41">
-        <v>996.3323673788591</v>
+        <v>1029.99072376035</v>
       </c>
       <c r="D41">
-        <v>1366.138367378859</v>
+        <v>1399.79672376035</v>
       </c>
       <c r="E41">
         <v>-1845.194</v>
@@ -4638,37 +4638,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M41">
-        <v>397.9405127654104</v>
+        <v>382.0074527654104</v>
       </c>
       <c r="N41">
-        <v>-406.9071794320771</v>
+        <v>-390.9741194320771</v>
       </c>
       <c r="O41">
-        <v>-97.6577230636985</v>
+        <v>-93.8337886636985</v>
       </c>
       <c r="P41">
-        <v>-309.2494563683786</v>
+        <v>-297.1403307683786</v>
       </c>
       <c r="Q41">
-        <v>-930.4494563683786</v>
+        <v>-918.3403307683786</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1781522457196482</v>
+        <v>0.1780951381041301</v>
       </c>
       <c r="T41">
-        <v>2.719888527622345</v>
+        <v>2.720127282466372</v>
       </c>
       <c r="U41">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V41">
-        <v>-0.005407843461438748</v>
+        <v>-0.005633397946614261</v>
       </c>
       <c r="W41">
-        <v>0.2511083952269121</v>
+        <v>0.2411083952269121</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.02253268108932804</v>
+        <v>-0.02347249144422614</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4687,13 +4687,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.208644721471898</v>
+        <v>0.2046098858264319</v>
       </c>
       <c r="C42">
-        <v>938.3679263717847</v>
+        <v>972.0407215936996</v>
       </c>
       <c r="D42">
-        <v>1349.027926371785</v>
+        <v>1382.7007215937</v>
       </c>
       <c r="E42">
         <v>-1804.34</v>
@@ -4720,37 +4720,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M42">
-        <v>408.1441156568312</v>
+        <v>391.8025156568312</v>
       </c>
       <c r="N42">
-        <v>-417.1107823234979</v>
+        <v>-400.7691823234979</v>
       </c>
       <c r="O42">
-        <v>-100.1065877576395</v>
+        <v>-96.18460375763949</v>
       </c>
       <c r="P42">
-        <v>-317.0041945658584</v>
+        <v>-304.5845785658584</v>
       </c>
       <c r="Q42">
-        <v>-938.2041945658584</v>
+        <v>-925.7845785658585</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1803581164816423</v>
+        <v>0.1803000570725322</v>
       </c>
       <c r="T42">
-        <v>2.765220003082717</v>
+        <v>2.765462737174144</v>
       </c>
       <c r="U42">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V42">
-        <v>-0.005272647374902779</v>
+        <v>-0.005492562997948904</v>
       </c>
       <c r="W42">
-        <v>0.2510746289572815</v>
+        <v>0.2410746289572815</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.02196936406209482</v>
+        <v>-0.02288567915812045</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4769,13 +4769,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.2106842989163149</v>
+        <v>0.2065494632708488</v>
       </c>
       <c r="C43">
-        <v>880.8267890967377</v>
+        <v>914.5032747104997</v>
       </c>
       <c r="D43">
-        <v>1332.340789096738</v>
+        <v>1366.0172747105</v>
       </c>
       <c r="E43">
         <v>-1763.486</v>
@@ -4802,37 +4802,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M43">
-        <v>418.347718548252</v>
+        <v>401.597578548252</v>
       </c>
       <c r="N43">
-        <v>-427.3143852149187</v>
+        <v>-410.5642452149187</v>
       </c>
       <c r="O43">
-        <v>-102.5554524515805</v>
+        <v>-98.53541885158049</v>
       </c>
       <c r="P43">
-        <v>-324.7589327633382</v>
+        <v>-312.0288263633382</v>
       </c>
       <c r="Q43">
-        <v>-945.9589327633382</v>
+        <v>-933.2288263633383</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1826387625237041</v>
+        <v>0.1825797190568124</v>
       </c>
       <c r="T43">
-        <v>2.812088138728187</v>
+        <v>2.812334986956757</v>
       </c>
       <c r="U43">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V43">
-        <v>-0.005144046219417346</v>
+        <v>-0.005358598046779419</v>
       </c>
       <c r="W43">
-        <v>0.2510425098227549</v>
+        <v>0.2410425098227549</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.02143352591423886</v>
+        <v>-0.02232749186158101</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4851,13 +4851,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.2127238763607318</v>
+        <v>0.2084890407152657</v>
       </c>
       <c r="C44">
-        <v>823.6934390063657</v>
+        <v>857.3636276683651</v>
       </c>
       <c r="D44">
-        <v>1316.061439006366</v>
+        <v>1349.731627668365</v>
       </c>
       <c r="E44">
         <v>-1722.632</v>
@@ -4884,37 +4884,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M44">
-        <v>428.5513214396727</v>
+        <v>411.3926414396727</v>
       </c>
       <c r="N44">
-        <v>-437.5179881063394</v>
+        <v>-420.3593081063394</v>
       </c>
       <c r="O44">
-        <v>-105.0043171455215</v>
+        <v>-100.8862339455214</v>
       </c>
       <c r="P44">
-        <v>-332.513670960818</v>
+        <v>-319.4730741608179</v>
       </c>
       <c r="Q44">
-        <v>-953.713670960818</v>
+        <v>-940.673074160818</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1849980515327334</v>
+        <v>0.1849379900750333</v>
       </c>
       <c r="T44">
-        <v>2.860572416982121</v>
+        <v>2.860823521214632</v>
       </c>
       <c r="U44">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V44">
-        <v>-0.005021568928478838</v>
+        <v>-0.005231012378998957</v>
       </c>
       <c r="W44">
-        <v>0.2510119201708248</v>
+        <v>0.2410119201708247</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4922,7 +4922,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.02092320386866175</v>
+        <v>-0.02179588491249573</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4933,13 +4933,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.2147634538051487</v>
+        <v>0.2104286181596826</v>
       </c>
       <c r="C45">
-        <v>766.9531087614853</v>
+        <v>800.6077203918155</v>
       </c>
       <c r="D45">
-        <v>1300.175108761485</v>
+        <v>1333.829720391816</v>
       </c>
       <c r="E45">
         <v>-1681.778</v>
@@ -4966,37 +4966,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M45">
-        <v>438.7549243310935</v>
+        <v>421.1877043310935</v>
       </c>
       <c r="N45">
-        <v>-447.7215909977602</v>
+        <v>-430.1543709977602</v>
       </c>
       <c r="O45">
-        <v>-107.4531818394624</v>
+        <v>-103.2370490394624</v>
       </c>
       <c r="P45">
-        <v>-340.2684091582977</v>
+        <v>-326.9173219582977</v>
       </c>
       <c r="Q45">
-        <v>-961.4684091582978</v>
+        <v>-948.1173219582978</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1874401226122551</v>
+        <v>0.1873790074447708</v>
       </c>
       <c r="T45">
-        <v>2.910757897981808</v>
+        <v>2.911013407551731</v>
       </c>
       <c r="U45">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V45">
-        <v>-0.004904788255723515</v>
+        <v>-0.005109360928324562</v>
       </c>
       <c r="W45">
-        <v>0.250982753293403</v>
+        <v>0.240982753293403</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.02043661773218131</v>
+        <v>-0.02128900386801891</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5015,13 +5015,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.2168030312495656</v>
+        <v>0.2123681956040995</v>
       </c>
       <c r="C46">
-        <v>710.5917355515207</v>
+        <v>744.2221476868212</v>
       </c>
       <c r="D46">
-        <v>1284.667735551521</v>
+        <v>1318.298147686821</v>
       </c>
       <c r="E46">
         <v>-1640.924</v>
@@ -5048,37 +5048,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M46">
-        <v>448.9585272225143</v>
+        <v>430.9827672225143</v>
       </c>
       <c r="N46">
-        <v>-457.925193889181</v>
+        <v>-439.949433889181</v>
       </c>
       <c r="O46">
-        <v>-109.9020465334034</v>
+        <v>-105.5878641334034</v>
       </c>
       <c r="P46">
-        <v>-348.0231473557776</v>
+        <v>-334.3615697557775</v>
       </c>
       <c r="Q46">
-        <v>-969.2231473557777</v>
+        <v>-955.5615697557776</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1899694105160454</v>
+        <v>0.1899072040062845</v>
       </c>
       <c r="T46">
-        <v>2.962735717588626</v>
+        <v>2.96299578982944</v>
       </c>
       <c r="U46">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V46">
-        <v>-0.004793315795366163</v>
+        <v>-0.004993239089044458</v>
       </c>
       <c r="W46">
-        <v>0.2509549121831368</v>
+        <v>0.2409549121831367</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.01997214914735901</v>
+        <v>-0.02080516287101863</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5097,13 +5097,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.2188426086939825</v>
+        <v>0.2143077730485164</v>
       </c>
       <c r="C47">
-        <v>654.5959195746552</v>
+        <v>688.1941215513395</v>
       </c>
       <c r="D47">
-        <v>1269.525919574655</v>
+        <v>1303.12412155134</v>
       </c>
       <c r="E47">
         <v>-1600.07</v>
@@ -5130,37 +5130,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M47">
-        <v>459.1621301139351</v>
+        <v>440.7778301139351</v>
       </c>
       <c r="N47">
-        <v>-468.1287967806018</v>
+        <v>-449.7444967806018</v>
       </c>
       <c r="O47">
-        <v>-112.3509112273444</v>
+        <v>-107.9386792273444</v>
       </c>
       <c r="P47">
-        <v>-355.7778855532574</v>
+        <v>-341.8058175532573</v>
       </c>
       <c r="Q47">
-        <v>-976.9778855532575</v>
+        <v>-963.0058175532574</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.192590672525428</v>
+        <v>0.192527334988217</v>
       </c>
       <c r="T47">
-        <v>3.016603639726601</v>
+        <v>3.016868440553612</v>
       </c>
       <c r="U47">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V47">
-        <v>-0.004686797666580249</v>
+        <v>-0.004882278220399026</v>
       </c>
       <c r="W47">
-        <v>0.2509283084555491</v>
+        <v>0.2409283084555491</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.01952832361075107</v>
+        <v>-0.02034282591832937</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5179,13 +5179,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.2208821861383994</v>
+        <v>0.2162473504929333</v>
       </c>
       <c r="C48">
-        <v>598.9528854200312</v>
+        <v>632.511436059151</v>
       </c>
       <c r="D48">
-        <v>1254.736885420032</v>
+        <v>1288.295436059151</v>
       </c>
       <c r="E48">
         <v>-1559.216</v>
@@ -5212,37 +5212,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M48">
-        <v>469.3657330053559</v>
+        <v>450.5728930053559</v>
       </c>
       <c r="N48">
-        <v>-478.3323996720226</v>
+        <v>-459.5395596720226</v>
       </c>
       <c r="O48">
-        <v>-114.7997759212854</v>
+        <v>-110.2894943212854</v>
       </c>
       <c r="P48">
-        <v>-363.5326237507372</v>
+        <v>-349.2500653507371</v>
       </c>
       <c r="Q48">
-        <v>-984.7326237507373</v>
+        <v>-970.4500653507372</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1953090183129359</v>
+        <v>0.1952445078583691</v>
       </c>
       <c r="T48">
-        <v>3.072466670091908</v>
+        <v>3.072736374637938</v>
       </c>
       <c r="U48">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V48">
-        <v>-0.004584910760785025</v>
+        <v>-0.004776141737346874</v>
       </c>
       <c r="W48">
-        <v>0.2509028614117695</v>
+        <v>0.2409028614117695</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5250,7 +5250,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.01910379483660418</v>
+        <v>-0.01990059057227866</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5261,13 +5261,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.2229217635828163</v>
+        <v>0.2181869279373502</v>
       </c>
       <c r="C49">
-        <v>543.6504461180814</v>
+        <v>577.1624346142987</v>
       </c>
       <c r="D49">
-        <v>1240.288446118082</v>
+        <v>1273.800434614299</v>
       </c>
       <c r="E49">
         <v>-1518.362</v>
@@ -5294,37 +5294,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M49">
-        <v>479.5693358967766</v>
+        <v>460.3679558967767</v>
       </c>
       <c r="N49">
-        <v>-488.5360025634433</v>
+        <v>-469.3346225634434</v>
       </c>
       <c r="O49">
-        <v>-117.2486406152264</v>
+        <v>-112.6403094152264</v>
       </c>
       <c r="P49">
-        <v>-371.2873619482169</v>
+        <v>-356.694313148217</v>
       </c>
       <c r="Q49">
-        <v>-992.487361948217</v>
+        <v>-977.894313148217</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1981299431867649</v>
+        <v>0.1980642155538101</v>
       </c>
       <c r="T49">
-        <v>3.130437739338925</v>
+        <v>3.130712532649975</v>
       </c>
       <c r="U49">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V49">
-        <v>-0.004487359468002366</v>
+        <v>-0.004674521700382046</v>
       </c>
       <c r="W49">
-        <v>0.2508784972209168</v>
+        <v>0.2408784972209167</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.01869733111667649</v>
+        <v>-0.01947717375159197</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5343,13 +5343,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.2249613410272331</v>
+        <v>0.2201265053817671</v>
       </c>
       <c r="C50">
-        <v>488.6769696463755</v>
+        <v>522.1359793915215</v>
       </c>
       <c r="D50">
-        <v>1226.168969646376</v>
+        <v>1259.627979391521</v>
       </c>
       <c r="E50">
         <v>-1477.508</v>
@@ -5376,37 +5376,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M50">
-        <v>489.7729387881974</v>
+        <v>470.1630187881973</v>
       </c>
       <c r="N50">
-        <v>-498.7396054548641</v>
+        <v>-479.129685454864</v>
       </c>
       <c r="O50">
-        <v>-119.6975053091674</v>
+        <v>-114.9911245091674</v>
       </c>
       <c r="P50">
-        <v>-379.0421001456967</v>
+        <v>-364.1385609456967</v>
       </c>
       <c r="Q50">
-        <v>-1000.242100145697</v>
+        <v>-985.3385609456967</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.2010593651711258</v>
+        <v>0.2009923735452295</v>
       </c>
       <c r="T50">
-        <v>3.190638465095443</v>
+        <v>3.190918542893244</v>
       </c>
       <c r="U50">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V50">
-        <v>-0.004393872812418983</v>
+        <v>-0.004577135831624088</v>
       </c>
       <c r="W50">
-        <v>0.2508551482046828</v>
+        <v>0.2408551482046828</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5414,7 +5414,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.0183078033850792</v>
+        <v>-0.01907139929843371</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5425,13 +5425,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.22700091847165</v>
+        <v>0.222066082826184</v>
       </c>
       <c r="C51">
-        <v>434.0213476975005</v>
+        <v>467.4214227942925</v>
       </c>
       <c r="D51">
-        <v>1212.3673476975</v>
+        <v>1245.767422794293</v>
       </c>
       <c r="E51">
         <v>-1436.654</v>
@@ -5458,37 +5458,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M51">
-        <v>499.9765416796182</v>
+        <v>479.9580816796181</v>
       </c>
       <c r="N51">
-        <v>-508.9432083462849</v>
+        <v>-488.9247483462848</v>
       </c>
       <c r="O51">
-        <v>-122.1463700031084</v>
+        <v>-117.3419396031084</v>
       </c>
       <c r="P51">
-        <v>-386.7968383431765</v>
+        <v>-371.5828087431765</v>
       </c>
       <c r="Q51">
-        <v>-1007.996838343177</v>
+        <v>-992.7828087431765</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.204103666448991</v>
+        <v>0.2040353612618026</v>
       </c>
       <c r="T51">
-        <v>3.253200003626726</v>
+        <v>3.253485573146052</v>
       </c>
       <c r="U51">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V51">
-        <v>-0.004304201938696147</v>
+        <v>-0.00448372489628482</v>
       </c>
       <c r="W51">
-        <v>0.2508327522095197</v>
+        <v>0.2408327522095197</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5496,7 +5496,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.01793417474456738</v>
+        <v>-0.01868218706785352</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5507,13 +5507,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.229040495916067</v>
+        <v>0.2240056602706009</v>
       </c>
       <c r="C52">
-        <v>379.6729665327391</v>
+        <v>413.0085807767484</v>
       </c>
       <c r="D52">
-        <v>1198.872966532739</v>
+        <v>1232.208580776748</v>
       </c>
       <c r="E52">
         <v>-1395.8</v>
@@ -5540,37 +5540,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M52">
-        <v>510.180144571039</v>
+        <v>489.7531445710389</v>
       </c>
       <c r="N52">
-        <v>-519.1468112377056</v>
+        <v>-498.7198112377056</v>
       </c>
       <c r="O52">
-        <v>-124.5952346970493</v>
+        <v>-119.6927546970494</v>
       </c>
       <c r="P52">
-        <v>-394.5515765406562</v>
+        <v>-379.0270565406563</v>
       </c>
       <c r="Q52">
-        <v>-1015.751576540656</v>
+        <v>-1000.227056540656</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.2072697397779708</v>
+        <v>0.2072000684870386</v>
       </c>
       <c r="T52">
-        <v>3.318264003699261</v>
+        <v>3.318555284608973</v>
       </c>
       <c r="U52">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V52">
-        <v>-0.004218117899922223</v>
+        <v>-0.004394050398359124</v>
       </c>
       <c r="W52">
-        <v>0.2508112520541631</v>
+        <v>0.2408112520541631</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.01757549124967572</v>
+        <v>-0.01830854332649645</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5589,13 +5589,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.2310800733604839</v>
+        <v>0.2259452377150178</v>
       </c>
       <c r="C53">
-        <v>325.6216797608149</v>
+        <v>358.8877078890378</v>
       </c>
       <c r="D53">
-        <v>1185.675679760815</v>
+        <v>1218.941707889038</v>
       </c>
       <c r="E53">
         <v>-1354.946</v>
@@ -5622,37 +5622,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M53">
-        <v>520.3837474624597</v>
+        <v>499.5482074624597</v>
       </c>
       <c r="N53">
-        <v>-529.3504141291264</v>
+        <v>-508.5148741291264</v>
       </c>
       <c r="O53">
-        <v>-127.0440993909903</v>
+        <v>-122.0435697909903</v>
       </c>
       <c r="P53">
-        <v>-402.3063147381361</v>
+        <v>-386.4713043381361</v>
       </c>
       <c r="Q53">
-        <v>-1023.506314738136</v>
+        <v>-1007.671304338136</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.2105650405897661</v>
+        <v>0.2104939474357538</v>
       </c>
       <c r="T53">
-        <v>3.385983677244144</v>
+        <v>3.386280902662218</v>
       </c>
       <c r="U53">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V53">
-        <v>-0.004135409705806102</v>
+        <v>-0.004307892547410905</v>
       </c>
       <c r="W53">
-        <v>0.2507905950421538</v>
+        <v>0.2407905950421538</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.01723087377419219</v>
+        <v>-0.0179495522808788</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5671,13 +5671,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.2331196508049007</v>
+        <v>0.2278848151594347</v>
       </c>
       <c r="C54">
-        <v>271.8577828949892</v>
+        <v>305.0494739175756</v>
       </c>
       <c r="D54">
-        <v>1172.765782894989</v>
+        <v>1205.957473917575</v>
       </c>
       <c r="E54">
         <v>-1314.092</v>
@@ -5704,37 +5704,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M54">
-        <v>530.5873503538805</v>
+        <v>509.3432703538805</v>
       </c>
       <c r="N54">
-        <v>-539.5540170205472</v>
+        <v>-518.3099370205472</v>
       </c>
       <c r="O54">
-        <v>-129.4929640849313</v>
+        <v>-124.3943848849313</v>
       </c>
       <c r="P54">
-        <v>-410.0610529356159</v>
+        <v>-393.9155521356159</v>
       </c>
       <c r="Q54">
-        <v>-1031.261052935616</v>
+        <v>-1015.115552135616</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.2139976456020529</v>
+        <v>0.2139250713406653</v>
       </c>
       <c r="T54">
-        <v>3.456525003853396</v>
+        <v>3.456828421467681</v>
       </c>
       <c r="U54">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V54">
-        <v>-0.004055882596079061</v>
+        <v>-0.004225048459960696</v>
       </c>
       <c r="W54">
-        <v>0.2507707325306064</v>
+        <v>0.2407707325306064</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.01689951081699603</v>
+        <v>-0.01760436858316949</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5753,13 +5753,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.2351592282493177</v>
+        <v>0.2298243926038516</v>
       </c>
       <c r="C55">
-        <v>218.3719895544118</v>
+        <v>251.4849420025384</v>
       </c>
       <c r="D55">
-        <v>1160.133989554412</v>
+        <v>1193.246942002539</v>
       </c>
       <c r="E55">
         <v>-1273.238</v>
@@ -5786,37 +5786,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M55">
-        <v>540.7909532453014</v>
+        <v>519.1383332453013</v>
       </c>
       <c r="N55">
-        <v>-549.757619911968</v>
+        <v>-528.104999911968</v>
       </c>
       <c r="O55">
-        <v>-131.9418287788723</v>
+        <v>-126.7451999788723</v>
       </c>
       <c r="P55">
-        <v>-417.8157911330957</v>
+        <v>-401.3597999330957</v>
       </c>
       <c r="Q55">
-        <v>-1039.015791133096</v>
+        <v>-1022.559799933096</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.2175763189127349</v>
+        <v>0.2175022005181262</v>
       </c>
       <c r="T55">
-        <v>3.530068089041767</v>
+        <v>3.530377962349971</v>
       </c>
       <c r="U55">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V55">
-        <v>-0.003979356509360587</v>
+        <v>-0.004145330564489739</v>
       </c>
       <c r="W55">
-        <v>0.2507516195477967</v>
+        <v>0.2407516195477967</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5824,7 +5824,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.01658065212233573</v>
+        <v>-0.01727221068537399</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5835,13 +5835,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.2371988056937346</v>
+        <v>0.2317639700482685</v>
       </c>
       <c r="C56">
-        <v>165.1554091870985</v>
+        <v>198.1855481247526</v>
       </c>
       <c r="D56">
-        <v>1147.771409187098</v>
+        <v>1180.801548124753</v>
       </c>
       <c r="E56">
         <v>-1232.384</v>
@@ -5868,37 +5868,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M56">
-        <v>550.9945561367221</v>
+        <v>528.9333961367221</v>
       </c>
       <c r="N56">
-        <v>-559.9612228033888</v>
+        <v>-537.9000628033888</v>
       </c>
       <c r="O56">
-        <v>-134.3906934728133</v>
+        <v>-129.0960150728133</v>
       </c>
       <c r="P56">
-        <v>-425.5705293305755</v>
+        <v>-408.8040477305755</v>
       </c>
       <c r="Q56">
-        <v>-1046.770529330576</v>
+        <v>-1030.004047730576</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.2213105867151857</v>
+        <v>0.221234857051129</v>
       </c>
       <c r="T56">
-        <v>3.60680869967311</v>
+        <v>3.607125309357579</v>
       </c>
       <c r="U56">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V56">
-        <v>-0.003905664722150207</v>
+        <v>-0.004068565183665856</v>
       </c>
       <c r="W56">
-        <v>0.2507332144532392</v>
+        <v>0.2407332144532391</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.01627360300895919</v>
+        <v>-0.01695235493194103</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5917,13 +5917,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.2392383831381514</v>
+        <v>0.2337035474926853</v>
       </c>
       <c r="C57">
-        <v>112.1995262022065</v>
+        <v>145.1430818630151</v>
       </c>
       <c r="D57">
-        <v>1135.669526202207</v>
+        <v>1168.613081863015</v>
       </c>
       <c r="E57">
         <v>-1191.53</v>
@@ -5950,37 +5950,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M57">
-        <v>561.1981590281429</v>
+        <v>538.7284590281429</v>
       </c>
       <c r="N57">
-        <v>-570.1648256948096</v>
+        <v>-547.6951256948096</v>
       </c>
       <c r="O57">
-        <v>-136.8395581667543</v>
+        <v>-131.4468301667543</v>
       </c>
       <c r="P57">
-        <v>-433.3252675280553</v>
+        <v>-416.2482955280553</v>
       </c>
       <c r="Q57">
-        <v>-1054.525267528055</v>
+        <v>-1037.448295528055</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.2252108219755231</v>
+        <v>0.225133409430043</v>
       </c>
       <c r="T57">
-        <v>3.68696000411029</v>
+        <v>3.687283649565526</v>
       </c>
       <c r="U57">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V57">
-        <v>-0.003834652636292931</v>
+        <v>-0.003994591271235567</v>
       </c>
       <c r="W57">
-        <v>0.2507154786348473</v>
+        <v>0.2407154786348473</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.01597771931788716</v>
+        <v>-0.01664413029681477</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5999,13 +5999,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2412779605825683</v>
+        <v>0.2356431249371023</v>
       </c>
       <c r="C58">
-        <v>59.49618040869382</v>
+        <v>92.34966833101089</v>
       </c>
       <c r="D58">
-        <v>1123.820180408694</v>
+        <v>1156.673668331011</v>
       </c>
       <c r="E58">
         <v>-1150.676</v>
@@ -6032,37 +6032,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M58">
-        <v>571.4017619195637</v>
+        <v>548.5235219195637</v>
       </c>
       <c r="N58">
-        <v>-580.3684285862304</v>
+        <v>-557.4901885862304</v>
       </c>
       <c r="O58">
-        <v>-139.2884228606953</v>
+        <v>-133.7976452606953</v>
       </c>
       <c r="P58">
-        <v>-441.0800057255351</v>
+        <v>-423.6925433255351</v>
       </c>
       <c r="Q58">
-        <v>-1062.280005725535</v>
+        <v>-1044.892543325535</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.229288340656785</v>
+        <v>0.2292091687352713</v>
       </c>
       <c r="T58">
-        <v>3.770754549658251</v>
+        <v>3.771085550692016</v>
       </c>
       <c r="U58">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V58">
-        <v>-0.003766176696359127</v>
+        <v>-0.003923259284249217</v>
       </c>
       <c r="W58">
-        <v>0.2506983762385409</v>
+        <v>0.2406983762385409</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.01569240290149643</v>
+        <v>-0.01634691368437169</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6081,13 +6081,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2433175380269852</v>
+        <v>0.2375827023815192</v>
       </c>
       <c r="C59">
-        <v>7.037548665920895</v>
+        <v>39.7977512102957</v>
       </c>
       <c r="D59">
-        <v>1112.215548665921</v>
+        <v>1144.975751210296</v>
       </c>
       <c r="E59">
         <v>-1109.822</v>
@@ -6114,37 +6114,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M59">
-        <v>581.6053648109845</v>
+        <v>558.3185848109845</v>
       </c>
       <c r="N59">
-        <v>-590.5720314776512</v>
+        <v>-567.2852514776512</v>
       </c>
       <c r="O59">
-        <v>-141.7372875546363</v>
+        <v>-136.1484603546363</v>
       </c>
       <c r="P59">
-        <v>-448.8347439230149</v>
+        <v>-431.1367911230149</v>
       </c>
       <c r="Q59">
-        <v>-1070.034743923015</v>
+        <v>-1052.336791123015</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.2335555113697335</v>
+        <v>0.2334744982407427</v>
       </c>
       <c r="T59">
-        <v>3.858446515929374</v>
+        <v>3.858785214661598</v>
       </c>
       <c r="U59">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V59">
-        <v>-0.003700103420984406</v>
+        <v>-0.003854430173999231</v>
       </c>
       <c r="W59">
-        <v>0.2506818739263155</v>
+        <v>0.2406818739263155</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.01541709758743504</v>
+        <v>-0.01606012572499682</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6163,13 +6163,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.2453571154714021</v>
+        <v>0.239522279825936</v>
       </c>
       <c r="C60">
-        <v>-45.18387234049123</v>
+        <v>-12.51992319745523</v>
       </c>
       <c r="D60">
-        <v>1100.848127659509</v>
+        <v>1133.512076802545</v>
       </c>
       <c r="E60">
         <v>-1068.968</v>
@@ -6196,37 +6196,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M60">
-        <v>591.8089677024051</v>
+        <v>568.113647702405</v>
       </c>
       <c r="N60">
-        <v>-600.7756343690718</v>
+        <v>-577.0803143690717</v>
       </c>
       <c r="O60">
-        <v>-144.1861522485772</v>
+        <v>-138.4992754485772</v>
       </c>
       <c r="P60">
-        <v>-456.5894821204946</v>
+        <v>-438.5810389204945</v>
       </c>
       <c r="Q60">
-        <v>-1077.789482120495</v>
+        <v>-1059.781038920495</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.2380258806880605</v>
+        <v>0.237942938675046</v>
       </c>
       <c r="T60">
-        <v>3.950314290118167</v>
+        <v>3.95066105310592</v>
       </c>
       <c r="U60">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V60">
-        <v>-0.00363630853441571</v>
+        <v>-0.003787974481344073</v>
       </c>
       <c r="W60">
-        <v>0.2506659406593392</v>
+        <v>0.2406659406593391</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.01515128556006551</v>
+        <v>-0.0157832270056002</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6245,13 +6245,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.247396692915819</v>
+        <v>0.2414618572703529</v>
       </c>
       <c r="C61">
-        <v>-97.1752822772728</v>
+        <v>-64.61032096967165</v>
       </c>
       <c r="D61">
-        <v>1089.710717722727</v>
+        <v>1122.275679030328</v>
       </c>
       <c r="E61">
         <v>-1028.114</v>
@@ -6278,37 +6278,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M61">
-        <v>602.012570593826</v>
+        <v>577.908710593826</v>
       </c>
       <c r="N61">
-        <v>-610.9792372604927</v>
+        <v>-586.8753772604927</v>
       </c>
       <c r="O61">
-        <v>-146.6350169425182</v>
+        <v>-140.8500905425182</v>
       </c>
       <c r="P61">
-        <v>-464.3442203179745</v>
+        <v>-446.0252867179744</v>
       </c>
       <c r="Q61">
-        <v>-1085.544220317975</v>
+        <v>-1067.225286717975</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.2427143168024034</v>
+        <v>0.2426293518134618</v>
       </c>
       <c r="T61">
-        <v>4.04666341914544</v>
+        <v>4.047018639767041</v>
       </c>
       <c r="U61">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V61">
-        <v>-0.003574676186374766</v>
+        <v>-0.003723771524033156</v>
       </c>
       <c r="W61">
-        <v>0.2506505475031078</v>
+        <v>0.2406505475031078</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6316,7 +6316,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.0148944841098948</v>
+        <v>-0.01551571468347146</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6327,13 +6327,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.2494362703602359</v>
+        <v>0.2434014347147698</v>
       </c>
       <c r="C62">
-        <v>-148.9435923698456</v>
+        <v>-116.4801346787517</v>
       </c>
       <c r="D62">
-        <v>1078.796407630154</v>
+        <v>1111.259865321248</v>
       </c>
       <c r="E62">
         <v>-987.2600000000002</v>
@@ -6360,37 +6360,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M62">
-        <v>612.2161734852467</v>
+        <v>587.7037734852466</v>
       </c>
       <c r="N62">
-        <v>-621.1828401519134</v>
+        <v>-596.6704401519133</v>
       </c>
       <c r="O62">
-        <v>-149.0838816364592</v>
+        <v>-143.2009056364592</v>
       </c>
       <c r="P62">
-        <v>-472.0989585154542</v>
+        <v>-453.4695345154541</v>
       </c>
       <c r="Q62">
-        <v>-1093.298958515454</v>
+        <v>-1074.669534515454</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.2476371747224635</v>
+        <v>0.2475500856087983</v>
       </c>
       <c r="T62">
-        <v>4.147830004624076</v>
+        <v>4.148194105761216</v>
       </c>
       <c r="U62">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V62">
-        <v>-0.003515098249935186</v>
+        <v>-0.00366170866529927</v>
       </c>
       <c r="W62">
-        <v>0.2506356674520842</v>
+        <v>0.2406356674520841</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6398,7 +6398,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.01464624270806336</v>
+        <v>-0.01525711943874697</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6409,13 +6409,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.2514758478046528</v>
+        <v>0.2453410121591867</v>
       </c>
       <c r="C63">
-        <v>-200.4954397039196</v>
+        <v>-168.1357966846726</v>
       </c>
       <c r="D63">
-        <v>1068.09856029608</v>
+        <v>1100.458203315327</v>
       </c>
       <c r="E63">
         <v>-946.4059999999999</v>
@@ -6442,37 +6442,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M63">
-        <v>622.4197763766675</v>
+        <v>597.4988363766676</v>
       </c>
       <c r="N63">
-        <v>-631.3864430433342</v>
+        <v>-606.4655030433343</v>
       </c>
       <c r="O63">
-        <v>-151.5327463304002</v>
+        <v>-145.5517207304002</v>
       </c>
       <c r="P63">
-        <v>-479.853696712934</v>
+        <v>-460.913782312934</v>
       </c>
       <c r="Q63">
-        <v>-1101.053696712934</v>
+        <v>-1082.113782312934</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.2528124868948344</v>
+        <v>0.2527231647269726</v>
       </c>
       <c r="T63">
-        <v>4.254184620127258</v>
+        <v>4.254558057190992</v>
       </c>
       <c r="U63">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V63">
-        <v>-0.003457473688460839</v>
+        <v>-0.003601680654392724</v>
       </c>
       <c r="W63">
-        <v>0.2506212752715859</v>
+        <v>0.2406212752715859</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.01440614036858689</v>
+        <v>-0.01500700272663624</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6491,13 +6491,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.2535154252490697</v>
+        <v>0.2472805896036036</v>
       </c>
       <c r="C64">
-        <v>-251.8372006845102</v>
+        <v>-219.5834916598228</v>
       </c>
       <c r="D64">
-        <v>1057.61079931549</v>
+        <v>1089.864508340177</v>
       </c>
       <c r="E64">
         <v>-905.5520000000001</v>
@@ -6524,37 +6524,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M64">
-        <v>632.6233792680882</v>
+        <v>607.2938992680882</v>
       </c>
       <c r="N64">
-        <v>-641.5900459347549</v>
+        <v>-616.2605659347549</v>
       </c>
       <c r="O64">
-        <v>-153.9816110243412</v>
+        <v>-147.9025358243412</v>
       </c>
       <c r="P64">
-        <v>-487.6084349104137</v>
+        <v>-468.3580301104138</v>
       </c>
       <c r="Q64">
-        <v>-1108.808434910414</v>
+        <v>-1089.558030110414</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.2582601839183826</v>
+        <v>0.2581685111671561</v>
       </c>
       <c r="T64">
-        <v>4.366136846972711</v>
+        <v>4.366520111327596</v>
       </c>
       <c r="U64">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V64">
-        <v>-0.003401707983808245</v>
+        <v>-0.003543589030934778</v>
       </c>
       <c r="W64">
-        <v>0.2506073473549746</v>
+        <v>0.2406073473549746</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.01417378326586771</v>
+        <v>-0.01476495429556168</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6573,13 +6573,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.2555550026934865</v>
+        <v>0.2492201670480205</v>
       </c>
       <c r="C65">
-        <v>-302.9750037097365</v>
+        <v>-270.8291683973021</v>
       </c>
       <c r="D65">
-        <v>1047.326996290264</v>
+        <v>1079.472831602698</v>
       </c>
       <c r="E65">
         <v>-864.6979999999999</v>
@@ -6606,37 +6606,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M65">
-        <v>642.8269821595092</v>
+        <v>617.0889621595092</v>
       </c>
       <c r="N65">
-        <v>-651.7936488261759</v>
+        <v>-626.0556288261758</v>
       </c>
       <c r="O65">
-        <v>-156.4304757182822</v>
+        <v>-150.2533509182822</v>
       </c>
       <c r="P65">
-        <v>-495.3631731078937</v>
+        <v>-475.8022779078937</v>
       </c>
       <c r="Q65">
-        <v>-1116.563173107894</v>
+        <v>-1097.002277907894</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.2640023510513119</v>
+        <v>0.2639082006581603</v>
       </c>
       <c r="T65">
-        <v>4.484140545539542</v>
+        <v>4.484534168390504</v>
       </c>
       <c r="U65">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V65">
-        <v>-0.003347712618985891</v>
+        <v>-0.003487341585999304</v>
       </c>
       <c r="W65">
-        <v>0.2505938615944463</v>
+        <v>0.2405938615944463</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.01394880257910791</v>
+        <v>-0.01453058994166367</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6655,13 +6655,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.2575945801379035</v>
+        <v>0.2511597444924374</v>
       </c>
       <c r="C66">
-        <v>-353.9147411123258</v>
+        <v>-321.8785509500622</v>
       </c>
       <c r="D66">
-        <v>1037.241258887674</v>
+        <v>1069.277449049938</v>
       </c>
       <c r="E66">
         <v>-823.8440000000001</v>
@@ -6688,37 +6688,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M66">
-        <v>653.0305850509299</v>
+        <v>626.8840250509298</v>
       </c>
       <c r="N66">
-        <v>-661.9972517175966</v>
+        <v>-635.8506917175965</v>
       </c>
       <c r="O66">
-        <v>-158.8793404122232</v>
+        <v>-152.6041660122232</v>
       </c>
       <c r="P66">
-        <v>-503.1179113053734</v>
+        <v>-483.2465257053734</v>
       </c>
       <c r="Q66">
-        <v>-1124.317911305373</v>
+        <v>-1104.446525705373</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.2700635274694039</v>
+        <v>0.2699667617875537</v>
       </c>
       <c r="T66">
-        <v>4.608700005137862</v>
+        <v>4.609104561956907</v>
       </c>
       <c r="U66">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V66">
-        <v>-0.003295404609314237</v>
+        <v>-0.003432851873718066</v>
       </c>
       <c r="W66">
-        <v>0.2505807972639345</v>
+        <v>0.2405807972639345</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6726,7 +6726,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.01373085253880935</v>
+        <v>-0.01430354947382528</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6737,13 +6737,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.2596341575823204</v>
+        <v>0.2530993219368543</v>
       </c>
       <c r="C67">
-        <v>-404.6620804177246</v>
+        <v>-372.7371491447093</v>
       </c>
       <c r="D67">
-        <v>1027.347919582276</v>
+        <v>1059.272850855291</v>
       </c>
       <c r="E67">
         <v>-782.9899999999998</v>
@@ -6770,37 +6770,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M67">
-        <v>663.2341879423507</v>
+        <v>636.6790879423506</v>
       </c>
       <c r="N67">
-        <v>-672.2008546090174</v>
+        <v>-645.6457546090173</v>
       </c>
       <c r="O67">
-        <v>-161.3282051061642</v>
+        <v>-154.9549811061642</v>
       </c>
       <c r="P67">
-        <v>-510.8726495028532</v>
+        <v>-490.6907735028532</v>
       </c>
       <c r="Q67">
-        <v>-1132.072649502853</v>
+        <v>-1111.890773502853</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.2764710568256726</v>
+        <v>0.2763715264100552</v>
       </c>
       <c r="T67">
-        <v>4.740377148141802</v>
+        <v>4.740793263727105</v>
       </c>
       <c r="U67">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V67">
-        <v>-0.003244706076863249</v>
+        <v>-0.003380038767968557</v>
       </c>
       <c r="W67">
-        <v>0.250568134912823</v>
+        <v>0.240568134912823</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.01351960865359692</v>
+        <v>-0.0140834948665356</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6819,13 +6819,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.2616737350267372</v>
+        <v>0.2550388993812712</v>
       </c>
       <c r="C68">
-        <v>-455.222474964004</v>
+        <v>-423.4102685105504</v>
       </c>
       <c r="D68">
-        <v>1017.641525035996</v>
+        <v>1049.45373148945</v>
       </c>
       <c r="E68">
         <v>-742.136</v>
@@ -6852,37 +6852,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M68">
-        <v>673.4377908337715</v>
+        <v>646.4741508337714</v>
       </c>
       <c r="N68">
-        <v>-682.4044575004382</v>
+        <v>-655.4408175004381</v>
       </c>
       <c r="O68">
-        <v>-163.7770698001052</v>
+        <v>-157.3057962001051</v>
       </c>
       <c r="P68">
-        <v>-518.627387700333</v>
+        <v>-498.135021300333</v>
       </c>
       <c r="Q68">
-        <v>-1139.827387700333</v>
+        <v>-1119.335021300333</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.2832554996734865</v>
+        <v>0.2831530418927039</v>
       </c>
       <c r="T68">
-        <v>4.87980000544009</v>
+        <v>4.880228359719078</v>
       </c>
       <c r="U68">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V68">
-        <v>-0.003195543863577442</v>
+        <v>-0.003328826059362972</v>
       </c>
       <c r="W68">
-        <v>0.250555856269321</v>
+        <v>0.240555856269321</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.01331476609823934</v>
+        <v>-0.01387010858067894</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6901,13 +6901,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.2637133124711541</v>
+        <v>0.2569784768256881</v>
       </c>
       <c r="C69">
-        <v>-505.6011739253868</v>
+        <v>-473.9030196614854</v>
       </c>
       <c r="D69">
-        <v>1008.116826074614</v>
+        <v>1039.814980338515</v>
       </c>
       <c r="E69">
         <v>-701.2819999999997</v>
@@ -6934,37 +6934,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M69">
-        <v>683.6413937251923</v>
+        <v>656.2692137251922</v>
       </c>
       <c r="N69">
-        <v>-692.608060391859</v>
+        <v>-665.2358803918589</v>
       </c>
       <c r="O69">
-        <v>-166.2259344940462</v>
+        <v>-159.6566112940461</v>
       </c>
       <c r="P69">
-        <v>-526.3821258978128</v>
+        <v>-505.5792690978128</v>
       </c>
       <c r="Q69">
-        <v>-1147.582125897813</v>
+        <v>-1126.779269097813</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.2904511208757133</v>
+        <v>0.290345558313695</v>
       </c>
       <c r="T69">
-        <v>5.027672732877668</v>
+        <v>5.028114067589355</v>
       </c>
       <c r="U69">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V69">
-        <v>-0.003147849179046435</v>
+        <v>-0.003279142088327704</v>
       </c>
       <c r="W69">
-        <v>0.2505439441524906</v>
+        <v>0.2405439441524907</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6972,7 +6972,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.01311603824602692</v>
+        <v>-0.01366309203469873</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6983,13 +6983,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.2657528899155711</v>
+        <v>0.258918054270105</v>
       </c>
       <c r="C70">
-        <v>-555.8032317780853</v>
+        <v>-524.2203271655749</v>
       </c>
       <c r="D70">
-        <v>998.7687682219148</v>
+        <v>1030.351672834425</v>
       </c>
       <c r="E70">
         <v>-660.4279999999999</v>
@@ -7016,37 +7016,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M70">
-        <v>693.844996616613</v>
+        <v>666.064276616613</v>
       </c>
       <c r="N70">
-        <v>-702.8116632832797</v>
+        <v>-675.0309432832797</v>
       </c>
       <c r="O70">
-        <v>-168.6747991879871</v>
+        <v>-162.0074263879871</v>
       </c>
       <c r="P70">
-        <v>-534.1368640952926</v>
+        <v>-513.0235168952926</v>
       </c>
       <c r="Q70">
-        <v>-1155.336864095293</v>
+        <v>-1134.223516895293</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.2980964684030795</v>
+        <v>0.297987607010998</v>
       </c>
       <c r="T70">
-        <v>5.184787505780096</v>
+        <v>5.185242632201522</v>
       </c>
       <c r="U70">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V70">
-        <v>-0.003101557279354576</v>
+        <v>-0.003230919410558179</v>
       </c>
       <c r="W70">
-        <v>0.2505323823920377</v>
+        <v>0.2405323823920377</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.01292315533064414</v>
+        <v>-0.01346216421065916</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7065,13 +7065,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.267792467359988</v>
+        <v>0.2608576317145219</v>
       </c>
       <c r="C71">
-        <v>-605.8335172443399</v>
+        <v>-574.366937934672</v>
       </c>
       <c r="D71">
-        <v>989.5924827556605</v>
+        <v>1021.059062065328</v>
       </c>
       <c r="E71">
         <v>-619.5739999999996</v>
@@ -7098,37 +7098,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M71">
-        <v>704.0485995080338</v>
+        <v>675.8593395080338</v>
       </c>
       <c r="N71">
-        <v>-713.0152661747005</v>
+        <v>-684.8260061747005</v>
       </c>
       <c r="O71">
-        <v>-171.1236638819281</v>
+        <v>-164.3582414819281</v>
       </c>
       <c r="P71">
-        <v>-541.8916022927724</v>
+        <v>-520.4677646927723</v>
       </c>
       <c r="Q71">
-        <v>-1163.091602292772</v>
+        <v>-1141.667764692772</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.3062350641580175</v>
+        <v>0.3061226911081269</v>
       </c>
       <c r="T71">
-        <v>5.35203871564397</v>
+        <v>5.352508523562861</v>
       </c>
       <c r="U71">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V71">
-        <v>-0.003056607173856684</v>
+        <v>-0.003184094491564582</v>
       </c>
       <c r="W71">
-        <v>0.2505211557550762</v>
+        <v>0.2405211557550762</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7136,7 +7136,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.01273586322440279</v>
+        <v>-0.01326706038151904</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7147,13 +7147,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2698320448044049</v>
+        <v>0.2627972091589388</v>
       </c>
       <c r="C72">
-        <v>-655.6967217478973</v>
+        <v>-624.3474291641</v>
       </c>
       <c r="D72">
-        <v>980.5832782521031</v>
+        <v>1011.9325708359</v>
       </c>
       <c r="E72">
         <v>-578.7199999999998</v>
@@ -7180,37 +7180,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M72">
-        <v>714.2522023994546</v>
+        <v>685.6544023994545</v>
       </c>
       <c r="N72">
-        <v>-723.2188690661213</v>
+        <v>-694.6210690661212</v>
       </c>
       <c r="O72">
-        <v>-173.5725285758691</v>
+        <v>-166.7090565758691</v>
       </c>
       <c r="P72">
-        <v>-549.6463404902522</v>
+        <v>-527.9120124902521</v>
       </c>
       <c r="Q72">
-        <v>-1170.846340490252</v>
+        <v>-1149.112012490252</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.3149162329632847</v>
+        <v>0.3148001141450645</v>
       </c>
       <c r="T72">
-        <v>5.530440006165436</v>
+        <v>5.530925474348289</v>
       </c>
       <c r="U72">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V72">
-        <v>-0.003012941357087302</v>
+        <v>-0.003138607427399374</v>
       </c>
       <c r="W72">
-        <v>0.2505102498791706</v>
+        <v>0.2405102498791706</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.01255392232119701</v>
+        <v>-0.01307753094749731</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7229,13 +7229,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.2718716222488217</v>
+        <v>0.2647367866033556</v>
       </c>
       <c r="C73">
-        <v>-705.3973674117833</v>
+        <v>-674.1662158503132</v>
       </c>
       <c r="D73">
-        <v>971.7366325882167</v>
+        <v>1002.967784149687</v>
       </c>
       <c r="E73">
         <v>-537.866</v>
@@ -7262,37 +7262,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M73">
-        <v>724.4558052908753</v>
+        <v>695.4494652908753</v>
       </c>
       <c r="N73">
-        <v>-733.422471957542</v>
+        <v>-704.416131957542</v>
       </c>
       <c r="O73">
-        <v>-176.0213932698101</v>
+        <v>-169.0598716698101</v>
       </c>
       <c r="P73">
-        <v>-557.4010786877319</v>
+        <v>-535.356260287732</v>
       </c>
       <c r="Q73">
-        <v>-1178.601078687732</v>
+        <v>-1156.556260287732</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.3241961030654669</v>
+        <v>0.3240759801500666</v>
       </c>
       <c r="T73">
-        <v>5.721144833964242</v>
+        <v>5.721647042429264</v>
       </c>
       <c r="U73">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V73">
-        <v>-0.00297050556332551</v>
+        <v>-0.003094401688985299</v>
       </c>
       <c r="W73">
-        <v>0.2504996512110371</v>
+        <v>0.2404996512110371</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.01237710651385626</v>
+        <v>-0.01289334037077206</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7311,13 +7311,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.2739111996932386</v>
+        <v>0.2666763640477726</v>
       </c>
       <c r="C74">
-        <v>-754.9398146270264</v>
+        <v>-723.827557912467</v>
       </c>
       <c r="D74">
-        <v>963.0481853729734</v>
+        <v>994.1604420875331</v>
       </c>
       <c r="E74">
         <v>-497.0120000000002</v>
@@ -7344,37 +7344,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M74">
-        <v>734.659408182296</v>
+        <v>705.244528182296</v>
       </c>
       <c r="N74">
-        <v>-743.6260748489627</v>
+        <v>-714.2111948489627</v>
       </c>
       <c r="O74">
-        <v>-178.470257963751</v>
+        <v>-171.410686763751</v>
       </c>
       <c r="P74">
-        <v>-565.1558168852117</v>
+        <v>-542.8005080852116</v>
       </c>
       <c r="Q74">
-        <v>-1186.355816885212</v>
+        <v>-1164.000508085212</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.3341388210320907</v>
+        <v>0.334014408012569</v>
       </c>
       <c r="T74">
-        <v>5.925471435177251</v>
+        <v>5.925991579658881</v>
       </c>
       <c r="U74">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V74">
-        <v>-0.002929248541612656</v>
+        <v>-0.003051423887749392</v>
       </c>
       <c r="W74">
-        <v>0.2504893469503517</v>
+        <v>0.2404893469503517</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.01220520225671939</v>
+        <v>-0.01271426619895588</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7393,13 +7393,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.2759507771376555</v>
+        <v>0.2686159414921894</v>
       </c>
       <c r="C75">
-        <v>-804.3282692189332</v>
+        <v>-773.3355669420321</v>
       </c>
       <c r="D75">
-        <v>954.5137307810668</v>
+        <v>985.5064330579678</v>
       </c>
       <c r="E75">
         <v>-456.1579999999999</v>
@@ -7426,37 +7426,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M75">
-        <v>744.863011073717</v>
+        <v>715.0395910737169</v>
       </c>
       <c r="N75">
-        <v>-753.8296777403837</v>
+        <v>-724.0062577403836</v>
       </c>
       <c r="O75">
-        <v>-180.9191226576921</v>
+        <v>-173.7615018576921</v>
       </c>
       <c r="P75">
-        <v>-572.9105550826916</v>
+        <v>-550.2447558826916</v>
       </c>
       <c r="Q75">
-        <v>-1194.110555082692</v>
+        <v>-1171.444755882692</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.3448180366258718</v>
+        <v>0.3446890157167382</v>
       </c>
       <c r="T75">
-        <v>6.144933340183815</v>
+        <v>6.145472749275876</v>
       </c>
       <c r="U75">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V75">
-        <v>-0.002889121849261796</v>
+        <v>-0.003009623560519948</v>
       </c>
       <c r="W75">
-        <v>0.2504793249981782</v>
+        <v>0.2404793249981782</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.01203800770525754</v>
+        <v>-0.01254009816883306</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7475,13 +7475,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.2779903545820724</v>
+        <v>0.2705555189366063</v>
       </c>
       <c r="C76">
-        <v>-853.5667892356728</v>
+        <v>-822.6942126029298</v>
       </c>
       <c r="D76">
-        <v>946.1292107643271</v>
+        <v>977.0017873970703</v>
       </c>
       <c r="E76">
         <v>-415.3040000000001</v>
@@ -7508,37 +7508,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M76">
-        <v>755.0666139651377</v>
+        <v>724.8346539651376</v>
       </c>
       <c r="N76">
-        <v>-764.0332806318044</v>
+        <v>-733.8013206318043</v>
       </c>
       <c r="O76">
-        <v>-183.367987351633</v>
+        <v>-176.112316951633</v>
       </c>
       <c r="P76">
-        <v>-580.6652932801713</v>
+        <v>-557.6890036801713</v>
       </c>
       <c r="Q76">
-        <v>-1201.865293280171</v>
+        <v>-1178.889003680171</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.3563187303422515</v>
+        <v>0.3561847470904589</v>
       </c>
       <c r="T76">
-        <v>6.381276930190886</v>
+        <v>6.381837085786486</v>
       </c>
       <c r="U76">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V76">
-        <v>-0.00285007966210961</v>
+        <v>-0.002968952971864273</v>
       </c>
       <c r="W76">
-        <v>0.250469573909577</v>
+        <v>0.240469573909577</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7546,7 +7546,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.01187533192545676</v>
+        <v>-0.01237063738276789</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7557,13 +7557,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.2800299320264893</v>
+        <v>0.2724950963810232</v>
       </c>
       <c r="C77">
-        <v>-902.6592913821905</v>
+        <v>-871.9073287031088</v>
       </c>
       <c r="D77">
-        <v>937.8907086178097</v>
+        <v>968.6426712968912</v>
       </c>
       <c r="E77">
         <v>-374.4499999999998</v>
@@ -7590,37 +7590,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M77">
-        <v>765.2702168565585</v>
+        <v>734.6297168565585</v>
       </c>
       <c r="N77">
-        <v>-774.2368835232252</v>
+        <v>-743.5963835232252</v>
       </c>
       <c r="O77">
-        <v>-185.816852045574</v>
+        <v>-178.463132045574</v>
       </c>
       <c r="P77">
-        <v>-588.4200314776512</v>
+        <v>-565.1332514776511</v>
       </c>
       <c r="Q77">
-        <v>-1209.620031477651</v>
+        <v>-1186.333251477651</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.3687394795559416</v>
+        <v>0.3686001369740773</v>
       </c>
       <c r="T77">
-        <v>6.636528007398521</v>
+        <v>6.637110569217947</v>
       </c>
       <c r="U77">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V77">
-        <v>-0.002812078599948149</v>
+        <v>-0.002929366932239416</v>
       </c>
       <c r="W77">
-        <v>0.2504600828500052</v>
+        <v>0.2404600828500052</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7628,7 +7628,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.01171699416645056</v>
+        <v>-0.01220569555099749</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7639,13 +7639,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.2820695094709062</v>
+        <v>0.2744346738254401</v>
       </c>
       <c r="C78">
-        <v>-951.6095571208748</v>
+        <v>-920.9786189570864</v>
       </c>
       <c r="D78">
-        <v>929.7944428791251</v>
+        <v>960.4253810429135</v>
       </c>
       <c r="E78">
         <v>-333.596</v>
@@ -7672,37 +7672,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M78">
-        <v>775.4738197479792</v>
+        <v>744.4247797479792</v>
       </c>
       <c r="N78">
-        <v>-784.4404864146459</v>
+        <v>-753.3914464146459</v>
       </c>
       <c r="O78">
-        <v>-188.265716739515</v>
+        <v>-180.813947139515</v>
       </c>
       <c r="P78">
-        <v>-596.1747696751308</v>
+        <v>-572.5774992751309</v>
       </c>
       <c r="Q78">
-        <v>-1217.374769675131</v>
+        <v>-1193.777499275131</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.3821952912041058</v>
+        <v>0.3820501426813305</v>
       </c>
       <c r="T78">
-        <v>6.913050007706793</v>
+        <v>6.913656842935361</v>
       </c>
       <c r="U78">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V78">
-        <v>-0.002775077565738305</v>
+        <v>-0.002890822630499423</v>
       </c>
       <c r="W78">
-        <v>0.250450841555159</v>
+        <v>0.2404508415551589</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7710,7 +7710,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.01156282319057622</v>
+        <v>-0.01204509429374756</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7721,13 +7721,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.2841090869153231</v>
+        <v>0.276374251269857</v>
       </c>
       <c r="C79">
-        <v>-1000.421238458953</v>
+        <v>-969.9116624576391</v>
       </c>
       <c r="D79">
-        <v>921.8367615410473</v>
+        <v>952.3463375423613</v>
       </c>
       <c r="E79">
         <v>-292.7419999999997</v>
@@ -7754,37 +7754,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M79">
-        <v>785.6774226394001</v>
+        <v>754.2198426394</v>
       </c>
       <c r="N79">
-        <v>-794.6440893060668</v>
+        <v>-763.1865093060667</v>
       </c>
       <c r="O79">
-        <v>-190.714581433456</v>
+        <v>-183.164762233456</v>
       </c>
       <c r="P79">
-        <v>-603.9295078726108</v>
+        <v>-580.0217470726107</v>
       </c>
       <c r="Q79">
-        <v>-1225.129507872611</v>
+        <v>-1201.221747072611</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.3968211734303714</v>
+        <v>0.3966697141022579</v>
       </c>
       <c r="T79">
-        <v>7.21361739934622</v>
+        <v>7.214250618715159</v>
       </c>
       <c r="U79">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V79">
-        <v>-0.002739037597352093</v>
+        <v>-0.002853279479453976</v>
       </c>
       <c r="W79">
-        <v>0.2504418402939451</v>
+        <v>0.2404418402939451</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7792,7 +7792,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.01141265665563362</v>
+        <v>-0.01188866449772497</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7803,13 +7803,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.28614866435974</v>
+        <v>0.2783138287142739</v>
       </c>
       <c r="C80">
-        <v>-1049.097863441214</v>
+        <v>-1018.709918873631</v>
       </c>
       <c r="D80">
-        <v>914.0141365587866</v>
+        <v>944.4020811263694</v>
       </c>
       <c r="E80">
         <v>-251.8879999999999</v>
@@ -7836,37 +7836,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M80">
-        <v>795.8810255308208</v>
+        <v>764.0149055308208</v>
       </c>
       <c r="N80">
-        <v>-804.8476921974875</v>
+        <v>-772.9815721974875</v>
       </c>
       <c r="O80">
-        <v>-193.163446127397</v>
+        <v>-185.515577327397</v>
       </c>
       <c r="P80">
-        <v>-611.6842460700905</v>
+        <v>-587.4659948700905</v>
       </c>
       <c r="Q80">
-        <v>-1232.884246070091</v>
+        <v>-1208.665994870091</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.4127766813135701</v>
+        <v>0.4126183374705425</v>
       </c>
       <c r="T80">
-        <v>7.541509099316504</v>
+        <v>7.542171101384032</v>
       </c>
       <c r="U80">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V80">
-        <v>-0.002703921730719374</v>
+        <v>-0.00281669897330713</v>
       </c>
       <c r="W80">
-        <v>0.2504330698343007</v>
+        <v>0.2404330698343007</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7874,7 +7874,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.01126634054466402</v>
+        <v>-0.01173624572211307</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7885,13 +7885,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.2881882418041569</v>
+        <v>0.2802534061586908</v>
       </c>
       <c r="C81">
-        <v>-1097.642841365422</v>
+        <v>-1067.376733389848</v>
       </c>
       <c r="D81">
-        <v>906.3231586345782</v>
+        <v>936.5892666101528</v>
       </c>
       <c r="E81">
         <v>-211.0339999999997</v>
@@ -7918,37 +7918,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M81">
-        <v>806.0846284222416</v>
+        <v>773.8099684222416</v>
       </c>
       <c r="N81">
-        <v>-815.0512950889083</v>
+        <v>-782.7766350889083</v>
       </c>
       <c r="O81">
-        <v>-195.612310821338</v>
+        <v>-187.866392421338</v>
       </c>
       <c r="P81">
-        <v>-619.4389842675703</v>
+        <v>-594.9102426675703</v>
       </c>
       <c r="Q81">
-        <v>-1240.63898426757</v>
+        <v>-1216.11024266757</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.430251761376121</v>
+        <v>0.4300858773500922</v>
       </c>
       <c r="T81">
-        <v>7.900628580236337</v>
+        <v>7.901322106211844</v>
       </c>
       <c r="U81">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V81">
-        <v>-0.002669694873368495</v>
+        <v>-0.002781044555923496</v>
       </c>
       <c r="W81">
-        <v>0.2504245214116095</v>
+        <v>0.2404245214116095</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7956,7 +7956,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.01112372863903532</v>
+        <v>-0.01158768564968127</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7967,13 +7967,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.2902278192485738</v>
+        <v>0.2821929836031077</v>
       </c>
       <c r="C82">
-        <v>-1146.05946773662</v>
+        <v>-1115.915341403637</v>
       </c>
       <c r="D82">
-        <v>898.76053226338</v>
+        <v>928.9046585963631</v>
       </c>
       <c r="E82">
         <v>-170.1799999999998</v>
@@ -8000,37 +8000,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M82">
-        <v>816.2882313136623</v>
+        <v>783.6050313136624</v>
       </c>
       <c r="N82">
-        <v>-825.254897980329</v>
+        <v>-792.5716979803291</v>
       </c>
       <c r="O82">
-        <v>-198.061175515279</v>
+        <v>-190.217207515279</v>
       </c>
       <c r="P82">
-        <v>-627.1937224650501</v>
+        <v>-602.35449046505</v>
       </c>
       <c r="Q82">
-        <v>-1248.39372246505</v>
+        <v>-1223.55449046505</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.4494743494449271</v>
+        <v>0.4493001712175967</v>
       </c>
       <c r="T82">
-        <v>8.295660009248154</v>
+        <v>8.296388211522435</v>
       </c>
       <c r="U82">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V82">
-        <v>-0.00263632368745139</v>
+        <v>-0.002746281498974452</v>
       </c>
       <c r="W82">
-        <v>0.2504161866994855</v>
+        <v>0.2404161866994855</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8038,7 +8038,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.01098468203104752</v>
+        <v>-0.01144283957906023</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8049,13 +8049,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2922673966929907</v>
+        <v>0.2841325610475246</v>
       </c>
       <c r="C83">
-        <v>-1194.350928975438</v>
+        <v>-1164.328872992223</v>
       </c>
       <c r="D83">
-        <v>891.323071024562</v>
+        <v>921.3451270077776</v>
       </c>
       <c r="E83">
         <v>-129.3259999999996</v>
@@ -8082,37 +8082,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M83">
-        <v>826.4918342050833</v>
+        <v>793.4000942050832</v>
       </c>
       <c r="N83">
-        <v>-835.4585008717499</v>
+        <v>-802.3667608717499</v>
       </c>
       <c r="O83">
-        <v>-200.51004020922</v>
+        <v>-192.56802260922</v>
       </c>
       <c r="P83">
-        <v>-634.94846066253</v>
+        <v>-609.7987382625299</v>
       </c>
       <c r="Q83">
-        <v>-1256.14846066253</v>
+        <v>-1230.99873826253</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.4707203678367654</v>
+        <v>0.4705370223343124</v>
       </c>
       <c r="T83">
-        <v>8.732273693945425</v>
+        <v>8.733040222655196</v>
       </c>
       <c r="U83">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V83">
-        <v>-0.002603776481433471</v>
+        <v>-0.00271237678911057</v>
       </c>
       <c r="W83">
-        <v>0.2504080577827226</v>
+        <v>0.2404080577827226</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8120,7 +8120,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.01084906867263946</v>
+        <v>-0.01130156995462728</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8131,13 +8131,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2943069741374076</v>
+        <v>0.2860721384919415</v>
       </c>
       <c r="C84">
-        <v>-1242.52030689455</v>
+        <v>-1212.620357163645</v>
       </c>
       <c r="D84">
-        <v>884.0076931054499</v>
+        <v>913.9076428363552</v>
       </c>
       <c r="E84">
         <v>-88.47199999999975</v>
@@ -8164,37 +8164,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M84">
-        <v>836.695437096504</v>
+        <v>803.195157096504</v>
       </c>
       <c r="N84">
-        <v>-845.6621037631706</v>
+        <v>-812.1618237631707</v>
       </c>
       <c r="O84">
-        <v>-202.9589049031609</v>
+        <v>-194.918837703161</v>
       </c>
       <c r="P84">
-        <v>-642.7031988600097</v>
+        <v>-617.2429860600097</v>
       </c>
       <c r="Q84">
-        <v>-1263.90319886001</v>
+        <v>-1238.44298606001</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.4943270549388079</v>
+        <v>0.4941335235751075</v>
       </c>
       <c r="T84">
-        <v>9.217400010275727</v>
+        <v>9.218209123913818</v>
       </c>
       <c r="U84">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V84">
-        <v>-0.002572023109708673</v>
+        <v>-0.002679299023389709</v>
       </c>
       <c r="W84">
-        <v>0.2504001271322222</v>
+        <v>0.2404001271322221</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.01071676295711943</v>
+        <v>-0.0111637459307905</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8213,13 +8213,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2963465515818245</v>
+        <v>0.2880117159363583</v>
       </c>
       <c r="C85">
-        <v>-1290.570582956486</v>
+        <v>-1260.79272590346</v>
       </c>
       <c r="D85">
-        <v>876.8114170435141</v>
+        <v>906.5892740965401</v>
       </c>
       <c r="E85">
         <v>-47.61799999999948</v>
@@ -8246,37 +8246,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M85">
-        <v>846.8990399879248</v>
+        <v>812.9902199879248</v>
       </c>
       <c r="N85">
-        <v>-855.8657066545915</v>
+        <v>-821.9568866545915</v>
       </c>
       <c r="O85">
-        <v>-205.4077695971019</v>
+        <v>-197.2696527971019</v>
       </c>
       <c r="P85">
-        <v>-650.4579370574895</v>
+        <v>-624.6872338574896</v>
       </c>
       <c r="Q85">
-        <v>-1271.65793705749</v>
+        <v>-1245.88723385749</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.5207109993469731</v>
+        <v>0.5205060837854079</v>
       </c>
       <c r="T85">
-        <v>9.759600010880183</v>
+        <v>9.760456719438158</v>
       </c>
       <c r="U85">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V85">
-        <v>-0.002541034879471219</v>
+        <v>-0.002647018312264532</v>
       </c>
       <c r="W85">
-        <v>0.2503923875817338</v>
+        <v>0.2403923875817338</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.01058764533112999</v>
+        <v>-0.01102924296776897</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8295,13 +8295,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.2983861290262413</v>
+        <v>0.2899512933807752</v>
       </c>
       <c r="C86">
-        <v>-1338.504642325159</v>
+        <v>-1308.848818028549</v>
       </c>
       <c r="D86">
-        <v>869.731357674841</v>
+        <v>899.3871819714512</v>
       </c>
       <c r="E86">
         <v>-6.764000000000124</v>
@@ -8328,37 +8328,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M86">
-        <v>857.1026428793455</v>
+        <v>822.7852828793453</v>
       </c>
       <c r="N86">
-        <v>-866.0693095460122</v>
+        <v>-831.751949546012</v>
       </c>
       <c r="O86">
-        <v>-207.8566342910429</v>
+        <v>-199.6204678910429</v>
       </c>
       <c r="P86">
-        <v>-658.2126752549692</v>
+        <v>-632.1314816549691</v>
       </c>
       <c r="Q86">
-        <v>-1279.412675254969</v>
+        <v>-1253.331481654969</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.5503929368061585</v>
+        <v>0.5501752140219958</v>
       </c>
       <c r="T86">
-        <v>10.36957501156019</v>
+        <v>10.37048526440304</v>
       </c>
       <c r="U86">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V86">
-        <v>-0.002510784464239419</v>
+        <v>-0.002615506189499479</v>
       </c>
       <c r="W86">
-        <v>0.2503848323062571</v>
+        <v>0.2403848323062571</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.01046160193433088</v>
+        <v>-0.01089794245624787</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8377,13 +8377,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.3004257064706582</v>
+        <v>0.2918908708251922</v>
       </c>
       <c r="C87">
-        <v>-1386.325277722674</v>
+        <v>-1356.791382858687</v>
       </c>
       <c r="D87">
-        <v>862.7647222773262</v>
+        <v>892.298617141313</v>
       </c>
       <c r="E87">
         <v>34.09000000000015</v>
@@ -8410,37 +8410,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M87">
-        <v>867.3062457707663</v>
+        <v>832.5803457707663</v>
       </c>
       <c r="N87">
-        <v>-876.272912437433</v>
+        <v>-841.547012437433</v>
       </c>
       <c r="O87">
-        <v>-210.3054989849839</v>
+        <v>-201.9712829849839</v>
       </c>
       <c r="P87">
-        <v>-665.9674134524491</v>
+        <v>-639.5757294524491</v>
       </c>
       <c r="Q87">
-        <v>-1287.167413452449</v>
+        <v>-1260.775729452449</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.5840324659265692</v>
+        <v>0.5838002282901288</v>
       </c>
       <c r="T87">
-        <v>11.06088001233087</v>
+        <v>11.06185094869658</v>
       </c>
       <c r="U87">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V87">
-        <v>-0.002481245823483661</v>
+        <v>-0.002584735528446543</v>
       </c>
       <c r="W87">
-        <v>0.250377454801968</v>
+        <v>0.240377454801968</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8448,7 +8448,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.01033852426451531</v>
+        <v>-0.01076973136852732</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8459,13 +8459,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.3024652839150752</v>
+        <v>0.2938304482696091</v>
       </c>
       <c r="C88">
-        <v>-1434.035193102246</v>
+        <v>-1404.623083715843</v>
       </c>
       <c r="D88">
-        <v>855.9088068977544</v>
+        <v>885.3209162841569</v>
       </c>
       <c r="E88">
         <v>74.94399999999996</v>
@@ -8492,37 +8492,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M88">
-        <v>877.509848662187</v>
+        <v>842.3754086621869</v>
       </c>
       <c r="N88">
-        <v>-886.4765153288537</v>
+        <v>-851.3420753288536</v>
       </c>
       <c r="O88">
-        <v>-212.7543636789249</v>
+        <v>-204.3220980789249</v>
       </c>
       <c r="P88">
-        <v>-673.7221516499288</v>
+        <v>-647.0199772499288</v>
       </c>
       <c r="Q88">
-        <v>-1294.922151649929</v>
+        <v>-1268.219977249929</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.6224776420641814</v>
+        <v>0.622228816025138</v>
       </c>
       <c r="T88">
-        <v>11.8509428703545</v>
+        <v>11.85198315931776</v>
       </c>
       <c r="U88">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V88">
-        <v>-0.002452394127861758</v>
+        <v>-0.002554680464162281</v>
       </c>
       <c r="W88">
-        <v>0.2503702488675462</v>
+        <v>0.2403702488675462</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8530,7 +8530,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.01021830886609076</v>
+        <v>-0.01064450193400956</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8541,13 +8541,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.304504861359492</v>
+        <v>0.2957700257140259</v>
       </c>
       <c r="C89">
-        <v>-1481.637007147381</v>
+        <v>-1452.346501260568</v>
       </c>
       <c r="D89">
-        <v>849.160992852619</v>
+        <v>878.4514987394321</v>
       </c>
       <c r="E89">
         <v>115.7980000000002</v>
@@ -8574,37 +8574,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M89">
-        <v>887.7134515536078</v>
+        <v>852.1704715536079</v>
       </c>
       <c r="N89">
-        <v>-896.6801182202745</v>
+        <v>-861.1371382202746</v>
       </c>
       <c r="O89">
-        <v>-215.2032283728659</v>
+        <v>-206.6729131728659</v>
       </c>
       <c r="P89">
-        <v>-681.4768898474086</v>
+        <v>-654.4642250474087</v>
       </c>
       <c r="Q89">
-        <v>-1302.676889847409</v>
+        <v>-1275.664225047409</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.666837460684503</v>
+        <v>0.6665694941809178</v>
       </c>
       <c r="T89">
-        <v>12.76255386038177</v>
+        <v>12.76367417157297</v>
       </c>
       <c r="U89">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V89">
-        <v>-0.002424205689610473</v>
+        <v>-0.002525316320896048</v>
       </c>
       <c r="W89">
-        <v>0.2503632085867892</v>
+        <v>0.2403632085867892</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8612,7 +8612,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.0101008570400436</v>
+        <v>-0.0105221513370668</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8623,13 +8623,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.3065444388039089</v>
+        <v>0.2977096031584429</v>
       </c>
       <c r="C90">
-        <v>-1529.133256606835</v>
+        <v>-1499.964136674251</v>
       </c>
       <c r="D90">
-        <v>842.5187433931651</v>
+        <v>871.6878633257493</v>
       </c>
       <c r="E90">
         <v>156.652</v>
@@ -8656,37 +8656,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M90">
-        <v>897.9170544450286</v>
+        <v>861.9655344450285</v>
       </c>
       <c r="N90">
-        <v>-906.8837211116953</v>
+        <v>-870.9322011116952</v>
       </c>
       <c r="O90">
-        <v>-217.6520930668069</v>
+        <v>-209.0237282668068</v>
       </c>
       <c r="P90">
-        <v>-689.2316280448885</v>
+        <v>-661.9084728448884</v>
       </c>
       <c r="Q90">
-        <v>-1310.431628044888</v>
+        <v>-1283.108472844888</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.7185905824082116</v>
+        <v>0.718300285362661</v>
       </c>
       <c r="T90">
-        <v>13.82610001541359</v>
+        <v>13.82731368587072</v>
       </c>
       <c r="U90">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V90">
-        <v>-0.002396657897683081</v>
+        <v>-0.002496619544522229</v>
       </c>
       <c r="W90">
-        <v>0.2503563283124131</v>
+        <v>0.2403563283124131</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8694,7 +8694,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.009986074573679504</v>
+        <v>-0.01040258143550932</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8705,13 +8705,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.3085840162483258</v>
+        <v>0.2996491806028597</v>
       </c>
       <c r="C91">
-        <v>-1576.526399474259</v>
+        <v>-1547.478414695489</v>
       </c>
       <c r="D91">
-        <v>835.9796005257414</v>
+        <v>865.0275853045111</v>
       </c>
       <c r="E91">
         <v>197.5060000000003</v>
@@ -8738,37 +8738,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M91">
-        <v>908.1206573364494</v>
+        <v>871.7605973364493</v>
       </c>
       <c r="N91">
-        <v>-917.0873240031161</v>
+        <v>-880.727264003116</v>
       </c>
       <c r="O91">
-        <v>-220.1009577607479</v>
+        <v>-211.3745433607479</v>
       </c>
       <c r="P91">
-        <v>-696.9863662423683</v>
+        <v>-669.3527206423682</v>
       </c>
       <c r="Q91">
-        <v>-1318.186366242368</v>
+        <v>-1290.552720642368</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.77975336262714</v>
+        <v>0.7794366749410848</v>
       </c>
       <c r="T91">
-        <v>15.083018198633</v>
+        <v>15.08434220276806</v>
       </c>
       <c r="U91">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V91">
-        <v>-0.002369729157259676</v>
+        <v>-0.002468567639527598</v>
       </c>
       <c r="W91">
-        <v>0.2503496026509443</v>
+        <v>0.2403496026509443</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8776,7 +8776,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.009873871488581987</v>
+        <v>-0.01028569849803174</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8787,13 +8787,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.3106235936927427</v>
+        <v>0.3015887580472766</v>
       </c>
       <c r="C92">
-        <v>-1623.81881802092</v>
+        <v>-1594.891686518314</v>
       </c>
       <c r="D92">
-        <v>829.54118197908</v>
+        <v>858.4683134816858</v>
       </c>
       <c r="E92">
         <v>238.3600000000001</v>
@@ -8820,37 +8820,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M92">
-        <v>918.3242602278701</v>
+        <v>881.5556602278701</v>
       </c>
       <c r="N92">
-        <v>-927.2909268945368</v>
+        <v>-890.5223268945368</v>
       </c>
       <c r="O92">
-        <v>-222.5498224546888</v>
+        <v>-213.7253584546888</v>
       </c>
       <c r="P92">
-        <v>-704.741104439848</v>
+        <v>-676.796968439848</v>
       </c>
       <c r="Q92">
-        <v>-1325.941104439848</v>
+        <v>-1297.996968439848</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.8531486988898541</v>
+        <v>0.8528003424351934</v>
       </c>
       <c r="T92">
-        <v>16.59132001849631</v>
+        <v>16.59277642304487</v>
       </c>
       <c r="U92">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V92">
-        <v>-0.002343398833290124</v>
+        <v>-0.002441139110199513</v>
       </c>
       <c r="W92">
-        <v>0.2503430264486192</v>
+        <v>0.2403430264486192</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8858,7 +8858,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.009764161805375426</v>
+        <v>-0.01017141295916457</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8869,13 +8869,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.3126631711371596</v>
+        <v>0.3035283354916935</v>
       </c>
       <c r="C93">
-        <v>-1671.012821689354</v>
+        <v>-1642.206232559553</v>
       </c>
       <c r="D93">
-        <v>823.2011783106461</v>
+        <v>852.0077674404479</v>
       </c>
       <c r="E93">
         <v>279.2140000000004</v>
@@ -8902,37 +8902,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M93">
-        <v>928.5278631192911</v>
+        <v>891.3507231192909</v>
       </c>
       <c r="N93">
-        <v>-937.4945297859578</v>
+        <v>-900.3173897859576</v>
       </c>
       <c r="O93">
-        <v>-224.9986871486298</v>
+        <v>-216.0761735486298</v>
       </c>
       <c r="P93">
-        <v>-712.4958426373279</v>
+        <v>-684.2412162373278</v>
       </c>
       <c r="Q93">
-        <v>-1333.695842637328</v>
+        <v>-1305.441216237328</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.9428541098776159</v>
+        <v>0.9424670471502149</v>
       </c>
       <c r="T93">
-        <v>18.43480002055146</v>
+        <v>18.43641824782763</v>
       </c>
       <c r="U93">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V93">
-        <v>-0.002317647197759463</v>
+        <v>-0.002414313405691826</v>
       </c>
       <c r="W93">
-        <v>0.2503365947782134</v>
+        <v>0.2403365947782134</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8940,7 +8940,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.009656863323997733</v>
+        <v>-0.01005963919038266</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8951,13 +8951,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.3147027485815765</v>
+        <v>0.3054679129361104</v>
       </c>
       <c r="C94">
-        <v>-1718.110649855322</v>
+        <v>-1689.424265102156</v>
       </c>
       <c r="D94">
-        <v>816.9573501446783</v>
+        <v>845.6437348978437</v>
       </c>
       <c r="E94">
         <v>320.0680000000002</v>
@@ -8984,37 +8984,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M94">
-        <v>938.7314660107118</v>
+        <v>901.1457860107117</v>
       </c>
       <c r="N94">
-        <v>-947.6981326773785</v>
+        <v>-910.1124526773784</v>
       </c>
       <c r="O94">
-        <v>-227.4475518425708</v>
+        <v>-218.4269886425708</v>
       </c>
       <c r="P94">
-        <v>-720.2505808348076</v>
+        <v>-691.6854640348076</v>
       </c>
       <c r="Q94">
-        <v>-1341.450580834808</v>
+        <v>-1312.885464034808</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>1.054985873612318</v>
+        <v>1.054550428043992</v>
       </c>
       <c r="T94">
-        <v>20.73915002312039</v>
+        <v>20.74097052880609</v>
       </c>
       <c r="U94">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V94">
-        <v>-0.002292455380392513</v>
+        <v>-0.002388070868673437</v>
       </c>
       <c r="W94">
-        <v>0.2503303029267295</v>
+        <v>0.2403303029267294</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9022,7 +9022,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.009551897418302202</v>
+        <v>-0.009950295286139221</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9033,13 +9033,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.3167423260259934</v>
+        <v>0.3074074903805273</v>
       </c>
       <c r="C95">
-        <v>-1765.114474465028</v>
+        <v>-1736.547930820958</v>
       </c>
       <c r="D95">
-        <v>810.8075255349722</v>
+        <v>839.3740691790426</v>
       </c>
       <c r="E95">
         <v>360.9220000000005</v>
@@ -9066,37 +9066,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M95">
-        <v>948.9350689021326</v>
+        <v>910.9408489021325</v>
       </c>
       <c r="N95">
-        <v>-957.9017355687993</v>
+        <v>-919.9075155687992</v>
       </c>
       <c r="O95">
-        <v>-229.8964165365118</v>
+        <v>-220.7778037365118</v>
       </c>
       <c r="P95">
-        <v>-728.0053190322874</v>
+        <v>-699.1297118322874</v>
       </c>
       <c r="Q95">
-        <v>-1349.205319032287</v>
+        <v>-1320.329711832288</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>1.199155284128364</v>
+        <v>1.198657632050277</v>
       </c>
       <c r="T95">
-        <v>23.70188574070902</v>
+        <v>23.70396631863554</v>
       </c>
       <c r="U95">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V95">
-        <v>-0.00226780532253883</v>
+        <v>-0.002362392687289851</v>
       </c>
       <c r="W95">
-        <v>0.2503241463838796</v>
+        <v>0.2403241463838795</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9104,7 +9104,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.009449188843911882</v>
+        <v>-0.009843302863707715</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9115,13 +9115,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3187819034704103</v>
+        <v>0.3093470678249443</v>
       </c>
       <c r="C96">
-        <v>-1812.026402554111</v>
+        <v>-1783.579313196881</v>
       </c>
       <c r="D96">
-        <v>804.7495974458898</v>
+        <v>833.1966868031191</v>
       </c>
       <c r="E96">
         <v>401.7760000000003</v>
@@ -9148,37 +9148,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M96">
-        <v>959.1386717935533</v>
+        <v>920.7359117935533</v>
       </c>
       <c r="N96">
-        <v>-968.10533846022</v>
+        <v>-929.70257846022</v>
       </c>
       <c r="O96">
-        <v>-232.3452812304528</v>
+        <v>-223.1286188304528</v>
       </c>
       <c r="P96">
-        <v>-735.7600572297672</v>
+        <v>-706.5739596297672</v>
       </c>
       <c r="Q96">
-        <v>-1356.960057229767</v>
+        <v>-1327.773959629767</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>1.391381164816424</v>
+        <v>1.390800570725323</v>
       </c>
       <c r="T96">
-        <v>27.6522000308272</v>
+        <v>27.65462737174147</v>
       </c>
       <c r="U96">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V96">
-        <v>-0.002243679734001183</v>
+        <v>-0.002337260850191023</v>
       </c>
       <c r="W96">
-        <v>0.2503181208313031</v>
+        <v>0.2403181208313031</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9186,7 +9186,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.009348665558338354</v>
+        <v>-0.009738586875795985</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9197,13 +9197,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3208214809148272</v>
+        <v>0.3112866452693611</v>
       </c>
       <c r="C97">
-        <v>-1858.848478654546</v>
+        <v>-1830.520434825341</v>
       </c>
       <c r="D97">
-        <v>798.7815213454541</v>
+        <v>827.10956517466</v>
       </c>
       <c r="E97">
         <v>442.6300000000006</v>
@@ -9230,37 +9230,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M97">
-        <v>969.3422746849742</v>
+        <v>930.5309746849741</v>
       </c>
       <c r="N97">
-        <v>-978.3089413516409</v>
+        <v>-939.4976413516408</v>
       </c>
       <c r="O97">
-        <v>-234.7941459243938</v>
+        <v>-225.4794339243938</v>
       </c>
       <c r="P97">
-        <v>-743.5147954272471</v>
+        <v>-714.018207427247</v>
       </c>
       <c r="Q97">
-        <v>-1364.714795427247</v>
+        <v>-1335.218207427247</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>1.660497397779711</v>
+        <v>1.659800684870389</v>
       </c>
       <c r="T97">
-        <v>33.18264003699266</v>
+        <v>33.18555284608978</v>
       </c>
       <c r="U97">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V97">
-        <v>-0.002220062052590644</v>
+        <v>-0.002312658104399538</v>
       </c>
       <c r="W97">
-        <v>0.2503122221324651</v>
+        <v>0.240312222132465</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9268,7 +9268,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.009250258552460977</v>
+        <v>-0.009636075434998004</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9279,13 +9279,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.3228610583592441</v>
+        <v>0.313226222713778</v>
       </c>
       <c r="C98">
-        <v>-1905.582687095246</v>
+        <v>-1877.373259624175</v>
       </c>
       <c r="D98">
-        <v>792.9013129047541</v>
+        <v>821.1107403758249</v>
       </c>
       <c r="E98">
         <v>483.4839999999999</v>
@@ -9312,37 +9312,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M98">
-        <v>979.5458775763948</v>
+        <v>940.3260375763947</v>
       </c>
       <c r="N98">
-        <v>-988.5125442430615</v>
+        <v>-949.2927042430614</v>
       </c>
       <c r="O98">
-        <v>-237.2430106183348</v>
+        <v>-227.8302490183347</v>
       </c>
       <c r="P98">
-        <v>-751.2695336247267</v>
+        <v>-721.4624552247267</v>
       </c>
       <c r="Q98">
-        <v>-1372.469533624727</v>
+        <v>-1342.662455224727</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>2.064171747224633</v>
+        <v>2.063300856087981</v>
       </c>
       <c r="T98">
-        <v>41.47830004624073</v>
+        <v>41.48194105761213</v>
       </c>
       <c r="U98">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V98">
-        <v>-0.002196936406209491</v>
+        <v>-0.002288567915812044</v>
       </c>
       <c r="W98">
-        <v>0.2503064463231862</v>
+        <v>0.2403064463231861</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.00915390169253949</v>
+        <v>-0.009535699649216856</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9361,13 +9361,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.3249006358036609</v>
+        <v>0.3151658001581949</v>
       </c>
       <c r="C99">
-        <v>-1952.230954201777</v>
+        <v>-1924.139694946202</v>
       </c>
       <c r="D99">
-        <v>787.1070457982232</v>
+        <v>815.1983050537978</v>
       </c>
       <c r="E99">
         <v>524.3380000000002</v>
@@ -9394,37 +9394,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M99">
-        <v>989.7494804678156</v>
+        <v>950.1211004678156</v>
       </c>
       <c r="N99">
-        <v>-998.7161471344823</v>
+        <v>-959.0877671344823</v>
       </c>
       <c r="O99">
-        <v>-239.6918753122758</v>
+        <v>-230.1810641122757</v>
       </c>
       <c r="P99">
-        <v>-759.0242718222065</v>
+        <v>-728.9067030222066</v>
       </c>
       <c r="Q99">
-        <v>-1380.224271822206</v>
+        <v>-1350.106703022207</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>2.736962329632844</v>
+        <v>2.735801141450642</v>
       </c>
       <c r="T99">
-        <v>55.30440006165429</v>
+        <v>55.30925474348284</v>
       </c>
       <c r="U99">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V99">
-        <v>-0.002174287577279497</v>
+        <v>-0.002264974432143878</v>
       </c>
       <c r="W99">
-        <v>0.2503007896027583</v>
+        <v>0.2403007896027583</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9432,7 +9432,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.009059531571997903</v>
+        <v>-0.009437393467266242</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9443,13 +9443,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.3269402132480779</v>
+        <v>0.3171053776026118</v>
       </c>
       <c r="C100">
-        <v>-1998.795150400337</v>
+        <v>-1970.821593601146</v>
       </c>
       <c r="D100">
-        <v>781.3968495996628</v>
+        <v>809.370406398854</v>
       </c>
       <c r="E100">
         <v>565.192</v>
@@ -9476,37 +9476,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M100">
-        <v>999.9530833592364</v>
+        <v>959.9161633592363</v>
       </c>
       <c r="N100">
-        <v>-1008.919750025903</v>
+        <v>-968.882830025903</v>
       </c>
       <c r="O100">
-        <v>-242.1407400062167</v>
+        <v>-232.5318792062167</v>
       </c>
       <c r="P100">
-        <v>-766.7790100196864</v>
+        <v>-736.3509508196863</v>
       </c>
       <c r="Q100">
-        <v>-1387.979010019686</v>
+        <v>-1357.550950819686</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>4.082543494449267</v>
+        <v>4.080801712175963</v>
       </c>
       <c r="T100">
-        <v>82.95660009248145</v>
+        <v>82.96388211522427</v>
       </c>
       <c r="U100">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V100">
-        <v>-0.002152100969348073</v>
+        <v>-0.00224186244814241</v>
       </c>
       <c r="W100">
-        <v>0.2502952483256046</v>
+        <v>0.2402952483256046</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9514,7 +9514,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.008967087372283578</v>
+        <v>-0.009341093533926648</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9525,13 +9525,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.3289797906924948</v>
+        <v>0.3190449550470287</v>
       </c>
       <c r="C101">
-        <v>-2045.277092230807</v>
+        <v>-2017.420755791458</v>
       </c>
       <c r="D101">
-        <v>775.7689077691929</v>
+        <v>803.6252442085419</v>
       </c>
       <c r="E101">
         <v>606.0460000000003</v>
@@ -9558,37 +9558,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M101">
-        <v>1010.156686250657</v>
+        <v>969.7112262506572</v>
       </c>
       <c r="N101">
-        <v>-1019.123352917324</v>
+        <v>-978.6778929173239</v>
       </c>
       <c r="O101">
-        <v>-244.5896047001577</v>
+        <v>-234.8826943001577</v>
       </c>
       <c r="P101">
-        <v>-774.5337482171662</v>
+        <v>-743.7951986171662</v>
       </c>
       <c r="Q101">
-        <v>-1395.733748217166</v>
+        <v>-1364.995198617166</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>8.119286988898534</v>
+        <v>8.115803424351927</v>
       </c>
       <c r="T101">
-        <v>165.9132001849629</v>
+        <v>165.9277642304486</v>
       </c>
       <c r="U101">
-        <v>0.2497577444416894</v>
+        <v>0.2397577444416894</v>
       </c>
       <c r="V101">
-        <v>-0.002130362575718294</v>
+        <v>-0.002219217372908648</v>
       </c>
       <c r="W101">
-        <v>0.2502898189934438</v>
+        <v>0.2402898189934438</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9596,7 +9596,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>-0.008876510732159559</v>
+        <v>-0.009246739053786035</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/austria/austria_semiconductor.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,13 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
+      </c>
+      <c r="B2">
+        <v>0.1289663654941731</v>
+      </c>
+      <c r="C2">
+        <v>3822.974724522722</v>
+      </c>
+      <c r="D2">
+        <v>2640.328724522722</v>
       </c>
       <c r="E2">
-        <v>-3438.5</v>
+        <v>-3397.646</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>40.854</v>
       </c>
       <c r="G2">
         <v>1223.5</v>
@@ -1442,43 +1451,45 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>9.795062891420779</v>
       </c>
       <c r="N2">
-        <v>-8.966666666666697</v>
+        <v>-18.76172955808747</v>
       </c>
       <c r="O2">
-        <v>-2.152000000000007</v>
+        <v>-4.502815093940994</v>
       </c>
       <c r="P2">
-        <v>-6.81466666666669</v>
+        <v>-14.25891446414648</v>
       </c>
       <c r="Q2">
-        <v>-628.0146666666667</v>
+        <v>-635.4589144641466</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S2">
+        <v>0.127315186104565</v>
+      </c>
+      <c r="T2">
+        <v>1.676038022529784</v>
       </c>
       <c r="U2">
-        <v>0.0542577444416894</v>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-Inf</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>Inf</t>
-        </is>
+        <v>0.2397577444416894</v>
+      </c>
+      <c r="V2">
+        <v>-0.2197025199179562</v>
+      </c>
+      <c r="W2">
+        <v>0.2924331250653739</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>-0.9154271663248172</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1486,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1289663654941731</v>
+        <v>0.13090594293859</v>
       </c>
       <c r="C3">
-        <v>3822.974724522722</v>
+        <v>3721.947229428196</v>
       </c>
       <c r="D3">
-        <v>2640.328724522722</v>
+        <v>2580.155229428196</v>
       </c>
       <c r="E3">
-        <v>-3397.646</v>
+        <v>-3356.792</v>
       </c>
       <c r="F3">
-        <v>40.854</v>
+        <v>81.708</v>
       </c>
       <c r="G3">
         <v>1223.5</v>
@@ -1522,37 +1533,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M3">
-        <v>9.795062891420779</v>
+        <v>19.59012578284156</v>
       </c>
       <c r="N3">
-        <v>-18.76172955808747</v>
+        <v>-28.55679244950825</v>
       </c>
       <c r="O3">
-        <v>-4.502815093940994</v>
+        <v>-6.853630187881981</v>
       </c>
       <c r="P3">
-        <v>-14.25891446414648</v>
+        <v>-21.70316226162628</v>
       </c>
       <c r="Q3">
-        <v>-635.4589144641466</v>
+        <v>-642.9031622616263</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.127315186104565</v>
+        <v>0.1281469737178769</v>
       </c>
       <c r="T3">
-        <v>1.676038022529784</v>
+        <v>1.693140451331109</v>
       </c>
       <c r="U3">
         <v>0.2397577444416894</v>
       </c>
       <c r="V3">
-        <v>-0.2197025199179562</v>
+        <v>-0.1098512599589781</v>
       </c>
       <c r="W3">
-        <v>0.2924331250653739</v>
+        <v>0.2660954347535316</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1560,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>-0.9154271663248172</v>
+        <v>-0.4577135831624088</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1568,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.13090594293859</v>
+        <v>0.1328455203830068</v>
       </c>
       <c r="C4">
-        <v>3721.947229428196</v>
+        <v>3623.601346283912</v>
       </c>
       <c r="D4">
-        <v>2580.155229428196</v>
+        <v>2522.663346283912</v>
       </c>
       <c r="E4">
-        <v>-3356.792</v>
+        <v>-3315.938</v>
       </c>
       <c r="F4">
-        <v>81.708</v>
+        <v>122.562</v>
       </c>
       <c r="G4">
         <v>1223.5</v>
@@ -1604,37 +1615,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M4">
-        <v>19.59012578284156</v>
+        <v>29.38518867426233</v>
       </c>
       <c r="N4">
-        <v>-28.55679244950825</v>
+        <v>-38.35185534092903</v>
       </c>
       <c r="O4">
-        <v>-6.853630187881981</v>
+        <v>-9.204445281822968</v>
       </c>
       <c r="P4">
-        <v>-21.70316226162628</v>
+        <v>-29.14741005910606</v>
       </c>
       <c r="Q4">
-        <v>-642.9031622616263</v>
+        <v>-650.3474100591061</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1281469737178769</v>
+        <v>0.128995911591257</v>
       </c>
       <c r="T4">
-        <v>1.693140451331109</v>
+        <v>1.710595507530398</v>
       </c>
       <c r="U4">
         <v>0.2397577444416894</v>
       </c>
       <c r="V4">
-        <v>-0.1098512599589781</v>
+        <v>-0.0732341733059854</v>
       </c>
       <c r="W4">
-        <v>0.2660954347535316</v>
+        <v>0.2573162046495842</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1642,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>-0.4577135831624088</v>
+        <v>-0.3051423887749394</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1650,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1328455203830068</v>
+        <v>0.1347850978274237</v>
       </c>
       <c r="C5">
-        <v>3623.601346283912</v>
+        <v>3527.76172458129</v>
       </c>
       <c r="D5">
-        <v>2522.663346283912</v>
+        <v>2467.67772458129</v>
       </c>
       <c r="E5">
-        <v>-3315.938</v>
+        <v>-3275.084</v>
       </c>
       <c r="F5">
-        <v>122.562</v>
+        <v>163.416</v>
       </c>
       <c r="G5">
         <v>1223.5</v>
@@ -1686,37 +1697,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M5">
-        <v>29.38518867426233</v>
+        <v>39.18025156568311</v>
       </c>
       <c r="N5">
-        <v>-38.35185534092903</v>
+        <v>-48.14691823234981</v>
       </c>
       <c r="O5">
-        <v>-9.204445281822968</v>
+        <v>-11.55526037576395</v>
       </c>
       <c r="P5">
-        <v>-29.14741005910606</v>
+        <v>-36.59165785658585</v>
       </c>
       <c r="Q5">
-        <v>-650.3474100591061</v>
+        <v>-657.7916578565859</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.128995911591257</v>
+        <v>0.1298625356703326</v>
       </c>
       <c r="T5">
-        <v>1.710595507530398</v>
+        <v>1.72841421073384</v>
       </c>
       <c r="U5">
         <v>0.2397577444416894</v>
       </c>
       <c r="V5">
-        <v>-0.0732341733059854</v>
+        <v>-0.05492562997948905</v>
       </c>
       <c r="W5">
-        <v>0.2573162046495842</v>
+        <v>0.2529265895976106</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1724,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>-0.3051423887749394</v>
+        <v>-0.2288567915812043</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1732,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1347850978274237</v>
+        <v>0.1367246752718407</v>
       </c>
       <c r="C6">
-        <v>3527.76172458129</v>
+        <v>3434.267975906046</v>
       </c>
       <c r="D6">
-        <v>2467.67772458129</v>
+        <v>2415.037975906046</v>
       </c>
       <c r="E6">
-        <v>-3275.084</v>
+        <v>-3234.23</v>
       </c>
       <c r="F6">
-        <v>163.416</v>
+        <v>204.27</v>
       </c>
       <c r="G6">
         <v>1223.5</v>
@@ -1768,37 +1779,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M6">
-        <v>39.18025156568311</v>
+        <v>48.9753144571039</v>
       </c>
       <c r="N6">
-        <v>-48.14691823234981</v>
+        <v>-57.9419811237706</v>
       </c>
       <c r="O6">
-        <v>-11.55526037576395</v>
+        <v>-13.90607546970494</v>
       </c>
       <c r="P6">
-        <v>-36.59165785658585</v>
+        <v>-44.03590565406565</v>
       </c>
       <c r="Q6">
-        <v>-657.7916578565859</v>
+        <v>-665.2359056540657</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1298625356703326</v>
+        <v>0.1307474044668624</v>
       </c>
       <c r="T6">
-        <v>1.72841421073384</v>
+        <v>1.746608044531038</v>
       </c>
       <c r="U6">
         <v>0.2397577444416894</v>
       </c>
       <c r="V6">
-        <v>-0.05492562997948905</v>
+        <v>-0.04394050398359124</v>
       </c>
       <c r="W6">
-        <v>0.2529265895976106</v>
+        <v>0.2502928205664263</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1806,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>-0.2288567915812043</v>
+        <v>-0.1830854332649634</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1814,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1367246752718407</v>
+        <v>0.1386642527162575</v>
       </c>
       <c r="C7">
-        <v>3434.267975906046</v>
+        <v>3342.973111434871</v>
       </c>
       <c r="D7">
-        <v>2415.037975906046</v>
+        <v>2364.597111434871</v>
       </c>
       <c r="E7">
-        <v>-3234.23</v>
+        <v>-3193.376</v>
       </c>
       <c r="F7">
-        <v>204.27</v>
+        <v>245.124</v>
       </c>
       <c r="G7">
         <v>1223.5</v>
@@ -1850,37 +1861,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M7">
-        <v>48.9753144571039</v>
+        <v>58.77037734852468</v>
       </c>
       <c r="N7">
-        <v>-57.9419811237706</v>
+        <v>-67.73704401519137</v>
       </c>
       <c r="O7">
-        <v>-13.90607546970494</v>
+        <v>-16.25689056364593</v>
       </c>
       <c r="P7">
-        <v>-44.03590565406565</v>
+        <v>-51.48015345154545</v>
       </c>
       <c r="Q7">
-        <v>-665.2359056540657</v>
+        <v>-672.6801534515455</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1307474044668624</v>
+        <v>0.1316511002590631</v>
       </c>
       <c r="T7">
-        <v>1.746608044531038</v>
+        <v>1.765188981174986</v>
       </c>
       <c r="U7">
         <v>0.2397577444416894</v>
       </c>
       <c r="V7">
-        <v>-0.04394050398359124</v>
+        <v>-0.03661708665299269</v>
       </c>
       <c r="W7">
-        <v>0.2502928205664263</v>
+        <v>0.2485369745456368</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1888,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>-0.1830854332649634</v>
+        <v>-0.1525711943874695</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1896,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1386642527162575</v>
+        <v>0.1406038301606744</v>
       </c>
       <c r="C8">
-        <v>3342.973111434871</v>
+        <v>3253.742171234254</v>
       </c>
       <c r="D8">
-        <v>2364.597111434871</v>
+        <v>2316.220171234254</v>
       </c>
       <c r="E8">
-        <v>-3193.376</v>
+        <v>-3152.522</v>
       </c>
       <c r="F8">
-        <v>245.124</v>
+        <v>285.978</v>
       </c>
       <c r="G8">
         <v>1223.5</v>
@@ -1932,37 +1943,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M8">
-        <v>58.77037734852467</v>
+        <v>68.56544023994545</v>
       </c>
       <c r="N8">
-        <v>-67.73704401519137</v>
+        <v>-77.53210690661214</v>
       </c>
       <c r="O8">
-        <v>-16.25689056364593</v>
+        <v>-18.60770565758691</v>
       </c>
       <c r="P8">
-        <v>-51.48015345154545</v>
+        <v>-58.92440124902523</v>
       </c>
       <c r="Q8">
-        <v>-672.6801534515455</v>
+        <v>-680.1244012490253</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1316511002590631</v>
+        <v>0.1325742303693756</v>
       </c>
       <c r="T8">
-        <v>1.765188981174986</v>
+        <v>1.784169507854287</v>
       </c>
       <c r="U8">
         <v>0.2397577444416894</v>
       </c>
       <c r="V8">
-        <v>-0.0366170866529927</v>
+        <v>-0.03138607427399374</v>
       </c>
       <c r="W8">
-        <v>0.2485369745456368</v>
+        <v>0.2472827988165015</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1970,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>-0.1525711943874697</v>
+        <v>-0.130775309474974</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1978,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1406038301606744</v>
+        <v>0.1425434076050913</v>
       </c>
       <c r="C9">
-        <v>3253.742171234254</v>
+        <v>3166.451018443774</v>
       </c>
       <c r="D9">
-        <v>2316.220171234254</v>
+        <v>2269.783018443773</v>
       </c>
       <c r="E9">
-        <v>-3152.522</v>
+        <v>-3111.668</v>
       </c>
       <c r="F9">
-        <v>285.978</v>
+        <v>326.832</v>
       </c>
       <c r="G9">
         <v>1223.5</v>
@@ -2014,37 +2025,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M9">
-        <v>68.56544023994546</v>
+        <v>78.36050313136623</v>
       </c>
       <c r="N9">
-        <v>-77.53210690661216</v>
+        <v>-87.32716979803293</v>
       </c>
       <c r="O9">
-        <v>-18.60770565758692</v>
+        <v>-20.9585207515279</v>
       </c>
       <c r="P9">
-        <v>-58.92440124902524</v>
+        <v>-66.36864904650503</v>
       </c>
       <c r="Q9">
-        <v>-680.1244012490253</v>
+        <v>-687.568649046505</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1325742303693756</v>
+        <v>0.1335174285255645</v>
       </c>
       <c r="T9">
-        <v>1.784169507854287</v>
+        <v>1.80356265467879</v>
       </c>
       <c r="U9">
         <v>0.2397577444416894</v>
       </c>
       <c r="V9">
-        <v>-0.03138607427399374</v>
+        <v>-0.02746281498974452</v>
       </c>
       <c r="W9">
-        <v>0.2472827988165015</v>
+        <v>0.2463421670196499</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2052,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>-0.130775309474974</v>
+        <v>-0.1144283957906023</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2060,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1425434076050913</v>
+        <v>0.1444829850495082</v>
       </c>
       <c r="C10">
-        <v>3166.451018443774</v>
+        <v>3080.985275658678</v>
       </c>
       <c r="D10">
-        <v>2269.783018443773</v>
+        <v>2225.171275658678</v>
       </c>
       <c r="E10">
-        <v>-3111.668</v>
+        <v>-3070.814</v>
       </c>
       <c r="F10">
-        <v>326.832</v>
+        <v>367.686</v>
       </c>
       <c r="G10">
         <v>1223.5</v>
@@ -2096,37 +2107,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M10">
-        <v>78.36050313136623</v>
+        <v>88.155566022787</v>
       </c>
       <c r="N10">
-        <v>-87.32716979803293</v>
+        <v>-97.1222326894537</v>
       </c>
       <c r="O10">
-        <v>-20.9585207515279</v>
+        <v>-23.30933584546889</v>
       </c>
       <c r="P10">
-        <v>-66.36864904650503</v>
+        <v>-73.81289684398482</v>
       </c>
       <c r="Q10">
-        <v>-687.568649046505</v>
+        <v>-695.0128968439849</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1335174285255645</v>
+        <v>0.1344813563115597</v>
       </c>
       <c r="T10">
-        <v>1.80356265467879</v>
+        <v>1.823382024510425</v>
       </c>
       <c r="U10">
         <v>0.2397577444416894</v>
       </c>
       <c r="V10">
-        <v>-0.02746281498974452</v>
+        <v>-0.02441139110199514</v>
       </c>
       <c r="W10">
-        <v>0.2463421670196499</v>
+        <v>0.2456105645109877</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2134,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>-0.1144283957906023</v>
+        <v>-0.1017141295916464</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2142,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1444829850495082</v>
+        <v>0.1464225624939251</v>
       </c>
       <c r="C11">
-        <v>3080.985275658678</v>
+        <v>2997.239384324739</v>
       </c>
       <c r="D11">
-        <v>2225.171275658678</v>
+        <v>2182.279384324739</v>
       </c>
       <c r="E11">
-        <v>-3070.814</v>
+        <v>-3029.96</v>
       </c>
       <c r="F11">
-        <v>367.686</v>
+        <v>408.54</v>
       </c>
       <c r="G11">
         <v>1223.5</v>
@@ -2178,37 +2189,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M11">
-        <v>88.155566022787</v>
+        <v>97.95062891420778</v>
       </c>
       <c r="N11">
-        <v>-97.1222326894537</v>
+        <v>-106.9172955808745</v>
       </c>
       <c r="O11">
-        <v>-23.30933584546889</v>
+        <v>-25.66015093940987</v>
       </c>
       <c r="P11">
-        <v>-73.81289684398482</v>
+        <v>-81.25714464146461</v>
       </c>
       <c r="Q11">
-        <v>-695.0128968439849</v>
+        <v>-702.4571446414647</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1344813563115597</v>
+        <v>0.1354667047150215</v>
       </c>
       <c r="T11">
-        <v>1.823382024510425</v>
+        <v>1.843641824782763</v>
       </c>
       <c r="U11">
         <v>0.2397577444416894</v>
       </c>
       <c r="V11">
-        <v>-0.02441139110199514</v>
+        <v>-0.02197025199179562</v>
       </c>
       <c r="W11">
-        <v>0.2456105645109877</v>
+        <v>0.2450252825040579</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2216,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>-0.1017141295916464</v>
+        <v>-0.09154271663248181</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2224,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1464225624939251</v>
+        <v>0.148362139938342</v>
       </c>
       <c r="C12">
-        <v>2997.239384324739</v>
+        <v>2915.115770861166</v>
       </c>
       <c r="D12">
-        <v>2182.279384324739</v>
+        <v>2141.009770861166</v>
       </c>
       <c r="E12">
-        <v>-3029.96</v>
+        <v>-2989.106</v>
       </c>
       <c r="F12">
-        <v>408.54</v>
+        <v>449.394</v>
       </c>
       <c r="G12">
         <v>1223.5</v>
@@ -2260,37 +2271,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M12">
-        <v>97.9506289142078</v>
+        <v>107.7456918056286</v>
       </c>
       <c r="N12">
-        <v>-106.9172955808745</v>
+        <v>-116.7123584722953</v>
       </c>
       <c r="O12">
-        <v>-25.66015093940988</v>
+        <v>-28.01096603335086</v>
       </c>
       <c r="P12">
-        <v>-81.25714464146462</v>
+        <v>-88.7013924389444</v>
       </c>
       <c r="Q12">
-        <v>-702.4571446414647</v>
+        <v>-709.9013924389444</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1354667047150215</v>
+        <v>0.1364741957792352</v>
       </c>
       <c r="T12">
-        <v>1.843641824782763</v>
+        <v>1.864356901465715</v>
       </c>
       <c r="U12">
         <v>0.2397577444416894</v>
       </c>
       <c r="V12">
-        <v>-0.02197025199179562</v>
+        <v>-0.01997295635617783</v>
       </c>
       <c r="W12">
-        <v>0.2450252825040579</v>
+        <v>0.2445464154074789</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2298,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>-0.09154271663248181</v>
+        <v>-0.08322065148407432</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2306,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.148362139938342</v>
+        <v>0.1503017173827589</v>
       </c>
       <c r="C13">
-        <v>2915.115770861166</v>
+        <v>2834.524105645306</v>
       </c>
       <c r="D13">
-        <v>2141.009770861166</v>
+        <v>2101.272105645306</v>
       </c>
       <c r="E13">
-        <v>-2989.106</v>
+        <v>-2948.252</v>
       </c>
       <c r="F13">
-        <v>449.394</v>
+        <v>490.248</v>
       </c>
       <c r="G13">
         <v>1223.5</v>
@@ -2342,37 +2353,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M13">
-        <v>107.7456918056286</v>
+        <v>117.5407546970493</v>
       </c>
       <c r="N13">
-        <v>-116.7123584722953</v>
+        <v>-126.507421363716</v>
       </c>
       <c r="O13">
-        <v>-28.01096603335086</v>
+        <v>-30.36178112729185</v>
       </c>
       <c r="P13">
-        <v>-88.7013924389444</v>
+        <v>-96.14564023642419</v>
       </c>
       <c r="Q13">
-        <v>-709.9013924389444</v>
+        <v>-717.3456402364243</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1364741957792352</v>
+        <v>0.1375045843676356</v>
       </c>
       <c r="T13">
-        <v>1.864356901465715</v>
+        <v>1.885542775346008</v>
       </c>
       <c r="U13">
         <v>0.2397577444416894</v>
       </c>
       <c r="V13">
-        <v>-0.01997295635617783</v>
+        <v>-0.01830854332649635</v>
       </c>
       <c r="W13">
-        <v>0.2445464154074789</v>
+        <v>0.2441473594936631</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2380,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>-0.08322065148407432</v>
+        <v>-0.07628559719373484</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2388,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1503017173827589</v>
+        <v>0.1522412948271758</v>
       </c>
       <c r="C14">
-        <v>2834.524105645306</v>
+        <v>2755.380643014197</v>
       </c>
       <c r="D14">
-        <v>2101.272105645306</v>
+        <v>2062.982643014197</v>
       </c>
       <c r="E14">
-        <v>-2948.252</v>
+        <v>-2907.398</v>
       </c>
       <c r="F14">
-        <v>490.248</v>
+        <v>531.102</v>
       </c>
       <c r="G14">
         <v>1223.5</v>
@@ -2424,37 +2435,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M14">
-        <v>117.5407546970493</v>
+        <v>127.3358175884701</v>
       </c>
       <c r="N14">
-        <v>-126.507421363716</v>
+        <v>-136.3024842551368</v>
       </c>
       <c r="O14">
-        <v>-30.36178112729185</v>
+        <v>-32.71259622123284</v>
       </c>
       <c r="P14">
-        <v>-96.14564023642419</v>
+        <v>-103.589888033904</v>
       </c>
       <c r="Q14">
-        <v>-717.3456402364243</v>
+        <v>-724.789888033904</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1375045843676356</v>
+        <v>0.1385586600500222</v>
       </c>
       <c r="T14">
-        <v>1.885542775346008</v>
+        <v>1.907215680809755</v>
       </c>
       <c r="U14">
         <v>0.2397577444416894</v>
       </c>
       <c r="V14">
-        <v>-0.01830854332649635</v>
+        <v>-0.01690019383984278</v>
       </c>
       <c r="W14">
-        <v>0.2441473594936631</v>
+        <v>0.2438096967973574</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2462,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>-0.07628559719373484</v>
+        <v>-0.0704174743326782</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2470,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1522412948271758</v>
+        <v>0.1541808722715927</v>
       </c>
       <c r="C15">
-        <v>2755.380643014197</v>
+        <v>2677.607632133873</v>
       </c>
       <c r="D15">
-        <v>2062.982643014197</v>
+        <v>2026.063632133873</v>
       </c>
       <c r="E15">
-        <v>-2907.398</v>
+        <v>-2866.544</v>
       </c>
       <c r="F15">
-        <v>531.102</v>
+        <v>571.956</v>
       </c>
       <c r="G15">
         <v>1223.5</v>
@@ -2506,37 +2517,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M15">
-        <v>127.3358175884701</v>
+        <v>137.1308804798909</v>
       </c>
       <c r="N15">
-        <v>-136.3024842551368</v>
+        <v>-146.0975471465576</v>
       </c>
       <c r="O15">
-        <v>-32.71259622123284</v>
+        <v>-35.06341131517382</v>
       </c>
       <c r="P15">
-        <v>-103.589888033904</v>
+        <v>-111.0341358313838</v>
       </c>
       <c r="Q15">
-        <v>-724.789888033904</v>
+        <v>-732.2341358313838</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1385586600500222</v>
+        <v>0.1396372491203713</v>
       </c>
       <c r="T15">
-        <v>1.907215680809755</v>
+        <v>1.929392607330799</v>
       </c>
       <c r="U15">
         <v>0.2397577444416894</v>
       </c>
       <c r="V15">
-        <v>-0.01690019383984278</v>
+        <v>-0.01569303713699687</v>
       </c>
       <c r="W15">
-        <v>0.2438096967973574</v>
+        <v>0.2435202716290954</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2544,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>-0.0704174743326782</v>
+        <v>-0.06538765473748698</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2552,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1541808722715927</v>
+        <v>0.1561204497160096</v>
       </c>
       <c r="C16">
-        <v>2677.607632133873</v>
+        <v>2601.13279001479</v>
       </c>
       <c r="D16">
-        <v>2026.063632133873</v>
+        <v>1990.44279001479</v>
       </c>
       <c r="E16">
-        <v>-2866.544</v>
+        <v>-2825.69</v>
       </c>
       <c r="F16">
-        <v>571.956</v>
+        <v>612.8100000000001</v>
       </c>
       <c r="G16">
         <v>1223.5</v>
@@ -2588,37 +2599,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M16">
-        <v>137.1308804798909</v>
+        <v>146.9259433713117</v>
       </c>
       <c r="N16">
-        <v>-146.0975471465576</v>
+        <v>-155.8926100379784</v>
       </c>
       <c r="O16">
-        <v>-35.06341131517382</v>
+        <v>-37.41422640911481</v>
       </c>
       <c r="P16">
-        <v>-111.0341358313838</v>
+        <v>-118.4783836288636</v>
       </c>
       <c r="Q16">
-        <v>-732.2341358313838</v>
+        <v>-739.6783836288637</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1396372491203713</v>
+        <v>0.1407412167570816</v>
       </c>
       <c r="T16">
-        <v>1.929392607330799</v>
+        <v>1.952091343887631</v>
       </c>
       <c r="U16">
         <v>0.2397577444416894</v>
       </c>
       <c r="V16">
-        <v>-0.01569303713699687</v>
+        <v>-0.01464683466119708</v>
       </c>
       <c r="W16">
-        <v>0.2435202716290954</v>
+        <v>0.2432694364832683</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2626,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>-0.06538765473748698</v>
+        <v>-0.06102847775498788</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2634,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1561204497160096</v>
+        <v>0.1580600271604265</v>
       </c>
       <c r="C17">
-        <v>2601.13279001479</v>
+        <v>2525.888829157238</v>
       </c>
       <c r="D17">
-        <v>1990.44279001479</v>
+        <v>1956.052829157237</v>
       </c>
       <c r="E17">
-        <v>-2825.69</v>
+        <v>-2784.836</v>
       </c>
       <c r="F17">
-        <v>612.8099999999999</v>
+        <v>653.664</v>
       </c>
       <c r="G17">
         <v>1223.5</v>
@@ -2670,37 +2681,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M17">
-        <v>146.9259433713117</v>
+        <v>156.7210062627325</v>
       </c>
       <c r="N17">
-        <v>-155.8926100379784</v>
+        <v>-165.6876729293992</v>
       </c>
       <c r="O17">
-        <v>-37.4142264091148</v>
+        <v>-39.7650415030558</v>
       </c>
       <c r="P17">
-        <v>-118.4783836288636</v>
+        <v>-125.9226314263434</v>
       </c>
       <c r="Q17">
-        <v>-739.6783836288636</v>
+        <v>-747.1226314263434</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1407412167570816</v>
+        <v>0.141871469337523</v>
       </c>
       <c r="T17">
-        <v>1.952091343887631</v>
+        <v>1.97533052655296</v>
       </c>
       <c r="U17">
         <v>0.2397577444416894</v>
       </c>
       <c r="V17">
-        <v>-0.01464683466119708</v>
+        <v>-0.01373140749487226</v>
       </c>
       <c r="W17">
-        <v>0.2432694364832683</v>
+        <v>0.2430499557306697</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2708,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>-0.06102847775498788</v>
+        <v>-0.05721419789530113</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2716,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1580600271604265</v>
+        <v>0.1599996046048434</v>
       </c>
       <c r="C18">
-        <v>2525.888829157238</v>
+        <v>2451.813033331857</v>
       </c>
       <c r="D18">
-        <v>1956.052829157237</v>
+        <v>1922.831033331857</v>
       </c>
       <c r="E18">
-        <v>-2784.836</v>
+        <v>-2743.982</v>
       </c>
       <c r="F18">
-        <v>653.664</v>
+        <v>694.518</v>
       </c>
       <c r="G18">
         <v>1223.5</v>
@@ -2752,37 +2763,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M18">
-        <v>156.7210062627325</v>
+        <v>166.5160691541533</v>
       </c>
       <c r="N18">
-        <v>-165.6876729293992</v>
+        <v>-175.48273582082</v>
       </c>
       <c r="O18">
-        <v>-39.7650415030558</v>
+        <v>-42.11585659699679</v>
       </c>
       <c r="P18">
-        <v>-125.9226314263434</v>
+        <v>-133.3668792238232</v>
       </c>
       <c r="Q18">
-        <v>-747.1226314263434</v>
+        <v>-754.5668792238232</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.141871469337523</v>
+        <v>0.1430289569199028</v>
       </c>
       <c r="T18">
-        <v>1.97533052655296</v>
+        <v>1.999129689523478</v>
       </c>
       <c r="U18">
         <v>0.2397577444416894</v>
       </c>
       <c r="V18">
-        <v>-0.01373140749487226</v>
+        <v>-0.01292367764223271</v>
       </c>
       <c r="W18">
-        <v>0.2430499557306697</v>
+        <v>0.2428562962430826</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2790,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>-0.05721419789530113</v>
+        <v>-0.0538486568426364</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2798,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1599996046048434</v>
+        <v>0.1619391820492603</v>
       </c>
       <c r="C19">
-        <v>2451.813033331857</v>
+        <v>2378.846875868121</v>
       </c>
       <c r="D19">
-        <v>1922.831033331857</v>
+        <v>1890.718875868121</v>
       </c>
       <c r="E19">
-        <v>-2743.982</v>
+        <v>-2703.128</v>
       </c>
       <c r="F19">
-        <v>694.518</v>
+        <v>735.3720000000001</v>
       </c>
       <c r="G19">
         <v>1223.5</v>
@@ -2834,37 +2845,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M19">
-        <v>166.5160691541533</v>
+        <v>176.311132045574</v>
       </c>
       <c r="N19">
-        <v>-175.48273582082</v>
+        <v>-185.2777987122407</v>
       </c>
       <c r="O19">
-        <v>-42.11585659699679</v>
+        <v>-44.46667169093777</v>
       </c>
       <c r="P19">
-        <v>-133.3668792238232</v>
+        <v>-140.811127021303</v>
       </c>
       <c r="Q19">
-        <v>-754.5668792238232</v>
+        <v>-762.011127021303</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1430289569199028</v>
+        <v>0.1442146759067309</v>
       </c>
       <c r="T19">
-        <v>1.999129689523478</v>
+        <v>2.02350931988352</v>
       </c>
       <c r="U19">
         <v>0.2397577444416894</v>
       </c>
       <c r="V19">
-        <v>-0.01292367764223271</v>
+        <v>-0.01220569555099757</v>
       </c>
       <c r="W19">
-        <v>0.2428562962430826</v>
+        <v>0.2426841544763385</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2872,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>-0.0538486568426364</v>
+        <v>-0.05085706479582308</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2880,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1619391820492603</v>
+        <v>0.1638787594936772</v>
       </c>
       <c r="C20">
-        <v>2378.846875868122</v>
+        <v>2306.935675563071</v>
       </c>
       <c r="D20">
-        <v>1890.718875868121</v>
+        <v>1859.661675563071</v>
       </c>
       <c r="E20">
-        <v>-2703.128</v>
+        <v>-2662.274</v>
       </c>
       <c r="F20">
-        <v>735.372</v>
+        <v>776.226</v>
       </c>
       <c r="G20">
         <v>1223.5</v>
@@ -2916,37 +2927,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M20">
-        <v>176.311132045574</v>
+        <v>186.1061949369948</v>
       </c>
       <c r="N20">
-        <v>-185.2777987122407</v>
+        <v>-195.0728616036615</v>
       </c>
       <c r="O20">
-        <v>-44.46667169093777</v>
+        <v>-46.81748678487876</v>
       </c>
       <c r="P20">
-        <v>-140.8111270213029</v>
+        <v>-148.2553748187827</v>
       </c>
       <c r="Q20">
-        <v>-762.011127021303</v>
+        <v>-769.4553748187827</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1442146759067309</v>
+        <v>0.1454296719055794</v>
       </c>
       <c r="T20">
-        <v>2.02350931988352</v>
+        <v>2.048490916425292</v>
       </c>
       <c r="U20">
         <v>0.2397577444416894</v>
       </c>
       <c r="V20">
-        <v>-0.01220569555099757</v>
+        <v>-0.01156329052199769</v>
       </c>
       <c r="W20">
-        <v>0.2426841544763385</v>
+        <v>0.2425301328955675</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2954,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>-0.0508570647958233</v>
+        <v>-0.04818037717499046</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2962,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1638787594936772</v>
+        <v>0.1658183369380941</v>
       </c>
       <c r="C21">
-        <v>2306.935675563071</v>
+        <v>2236.028285954538</v>
       </c>
       <c r="D21">
-        <v>1859.661675563071</v>
+        <v>1829.608285954538</v>
       </c>
       <c r="E21">
-        <v>-2662.274</v>
+        <v>-2621.42</v>
       </c>
       <c r="F21">
-        <v>776.226</v>
+        <v>817.08</v>
       </c>
       <c r="G21">
         <v>1223.5</v>
@@ -2998,37 +3009,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M21">
-        <v>186.1061949369948</v>
+        <v>195.9012578284156</v>
       </c>
       <c r="N21">
-        <v>-195.0728616036615</v>
+        <v>-204.8679244950823</v>
       </c>
       <c r="O21">
-        <v>-46.81748678487876</v>
+        <v>-49.16830187881975</v>
       </c>
       <c r="P21">
-        <v>-148.2553748187827</v>
+        <v>-155.6996226162626</v>
       </c>
       <c r="Q21">
-        <v>-769.4553748187827</v>
+        <v>-776.8996226162626</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1454296719055794</v>
+        <v>0.1466750428043992</v>
       </c>
       <c r="T21">
-        <v>2.048490916425292</v>
+        <v>2.074097052880608</v>
       </c>
       <c r="U21">
         <v>0.2397577444416894</v>
       </c>
       <c r="V21">
-        <v>-0.01156329052199769</v>
+        <v>-0.01098512599589781</v>
       </c>
       <c r="W21">
-        <v>0.2425301328955675</v>
+        <v>0.2423915134728736</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3036,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>-0.04818037717499046</v>
+        <v>-0.04577135831624091</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3044,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1658183369380941</v>
+        <v>0.1677579143825109</v>
       </c>
       <c r="C22">
-        <v>2236.028285954538</v>
+        <v>2166.076814244538</v>
       </c>
       <c r="D22">
-        <v>1829.608285954538</v>
+        <v>1800.510814244538</v>
       </c>
       <c r="E22">
-        <v>-2621.42</v>
+        <v>-2580.566</v>
       </c>
       <c r="F22">
-        <v>817.08</v>
+        <v>857.9340000000001</v>
       </c>
       <c r="G22">
         <v>1223.5</v>
@@ -3080,37 +3091,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M22">
-        <v>195.9012578284156</v>
+        <v>205.6963207198364</v>
       </c>
       <c r="N22">
-        <v>-204.8679244950823</v>
+        <v>-214.6629873865031</v>
       </c>
       <c r="O22">
-        <v>-49.16830187881975</v>
+        <v>-51.51911697276073</v>
       </c>
       <c r="P22">
-        <v>-155.6996226162626</v>
+        <v>-163.1438704137423</v>
       </c>
       <c r="Q22">
-        <v>-776.8996226162626</v>
+        <v>-784.3438704137424</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1466750428043992</v>
+        <v>0.1479519420804042</v>
       </c>
       <c r="T22">
-        <v>2.074097052880608</v>
+        <v>2.100351445955047</v>
       </c>
       <c r="U22">
         <v>0.2397577444416894</v>
       </c>
       <c r="V22">
-        <v>-0.01098512599589781</v>
+        <v>-0.01046202475799791</v>
       </c>
       <c r="W22">
-        <v>0.2423915134728736</v>
+        <v>0.2422660958999601</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3118,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>-0.04577135831624091</v>
+        <v>-0.04359176982499124</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3126,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1677579143825109</v>
+        <v>0.1696974918269278</v>
       </c>
       <c r="C23">
-        <v>2166.076814244539</v>
+        <v>2097.036366623664</v>
       </c>
       <c r="D23">
-        <v>1800.510814244538</v>
+        <v>1772.324366623664</v>
       </c>
       <c r="E23">
-        <v>-2580.566</v>
+        <v>-2539.712</v>
       </c>
       <c r="F23">
-        <v>857.934</v>
+        <v>898.788</v>
       </c>
       <c r="G23">
         <v>1223.5</v>
@@ -3162,37 +3173,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M23">
-        <v>205.6963207198363</v>
+        <v>215.4913836112571</v>
       </c>
       <c r="N23">
-        <v>-214.662987386503</v>
+        <v>-224.4580502779238</v>
       </c>
       <c r="O23">
-        <v>-51.51911697276073</v>
+        <v>-53.86993206670171</v>
       </c>
       <c r="P23">
-        <v>-163.1438704137423</v>
+        <v>-170.5881182112221</v>
       </c>
       <c r="Q23">
-        <v>-784.3438704137424</v>
+        <v>-791.7881182112221</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1479519420804042</v>
+        <v>0.1492615823634863</v>
       </c>
       <c r="T23">
-        <v>2.100351445955046</v>
+        <v>2.127279028595496</v>
       </c>
       <c r="U23">
         <v>0.2397577444416894</v>
       </c>
       <c r="V23">
-        <v>-0.01046202475799791</v>
+        <v>-0.009986478178088917</v>
       </c>
       <c r="W23">
-        <v>0.2422660958999601</v>
+        <v>0.2421520799245842</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3200,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>-0.04359176982499124</v>
+        <v>-0.04161032574203727</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3208,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1696974918269278</v>
+        <v>0.1716370692713447</v>
       </c>
       <c r="C24">
-        <v>2097.036366623664</v>
+        <v>2028.864817147991</v>
       </c>
       <c r="D24">
-        <v>1772.324366623664</v>
+        <v>1745.006817147991</v>
       </c>
       <c r="E24">
-        <v>-2539.712</v>
+        <v>-2498.858</v>
       </c>
       <c r="F24">
-        <v>898.788</v>
+        <v>939.6420000000001</v>
       </c>
       <c r="G24">
         <v>1223.5</v>
@@ -3244,37 +3255,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M24">
-        <v>215.4913836112571</v>
+        <v>225.2864465026779</v>
       </c>
       <c r="N24">
-        <v>-224.4580502779238</v>
+        <v>-234.2531131693446</v>
       </c>
       <c r="O24">
-        <v>-53.86993206670171</v>
+        <v>-56.22074716064271</v>
       </c>
       <c r="P24">
-        <v>-170.5881182112221</v>
+        <v>-178.0323660087019</v>
       </c>
       <c r="Q24">
-        <v>-791.7881182112221</v>
+        <v>-799.232366008702</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1492615823634863</v>
+        <v>0.1506052392772978</v>
       </c>
       <c r="T24">
-        <v>2.127279028595496</v>
+        <v>2.154906028966866</v>
       </c>
       <c r="U24">
         <v>0.2397577444416894</v>
       </c>
       <c r="V24">
-        <v>-0.009986478178088917</v>
+        <v>-0.009552283474693748</v>
       </c>
       <c r="W24">
-        <v>0.2421520799245842</v>
+        <v>0.2420479783818496</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3282,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>-0.04161032574203727</v>
+        <v>-0.03980118114455733</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3290,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1716370692713447</v>
+        <v>0.1735766467157616</v>
       </c>
       <c r="C25">
-        <v>2028.864817147991</v>
+        <v>1961.52259766589</v>
       </c>
       <c r="D25">
-        <v>1745.006817147991</v>
+        <v>1718.51859766589</v>
       </c>
       <c r="E25">
-        <v>-2498.858</v>
+        <v>-2458.004</v>
       </c>
       <c r="F25">
-        <v>939.6420000000001</v>
+        <v>980.4960000000001</v>
       </c>
       <c r="G25">
         <v>1223.5</v>
@@ -3326,37 +3337,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M25">
-        <v>225.2864465026779</v>
+        <v>235.0815093940987</v>
       </c>
       <c r="N25">
-        <v>-234.2531131693446</v>
+        <v>-244.0481760607654</v>
       </c>
       <c r="O25">
-        <v>-56.22074716064271</v>
+        <v>-58.5715622545837</v>
       </c>
       <c r="P25">
-        <v>-178.0323660087019</v>
+        <v>-185.4766138061817</v>
       </c>
       <c r="Q25">
-        <v>-799.232366008702</v>
+        <v>-806.6766138061818</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1506052392772978</v>
+        <v>0.1519842555835781</v>
       </c>
       <c r="T25">
-        <v>2.154906028966866</v>
+        <v>2.183260055663798</v>
       </c>
       <c r="U25">
         <v>0.2397577444416894</v>
       </c>
       <c r="V25">
-        <v>-0.009552283474693748</v>
+        <v>-0.009154271663248174</v>
       </c>
       <c r="W25">
-        <v>0.2420479783818496</v>
+        <v>0.2419525519676763</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3364,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>-0.03980118114455733</v>
+        <v>-0.03814279859686742</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3372,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1735766467157616</v>
+        <v>0.1755162241601785</v>
       </c>
       <c r="C26">
-        <v>1961.52259766589</v>
+        <v>1894.972506591517</v>
       </c>
       <c r="D26">
-        <v>1718.51859766589</v>
+        <v>1692.822506591517</v>
       </c>
       <c r="E26">
-        <v>-2458.004</v>
+        <v>-2417.15</v>
       </c>
       <c r="F26">
-        <v>980.496</v>
+        <v>1021.35</v>
       </c>
       <c r="G26">
         <v>1223.5</v>
@@ -3408,37 +3419,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M26">
-        <v>235.0815093940987</v>
+        <v>244.8765722855195</v>
       </c>
       <c r="N26">
-        <v>-244.0481760607654</v>
+        <v>-253.8432389521862</v>
       </c>
       <c r="O26">
-        <v>-58.57156225458369</v>
+        <v>-60.92237734852468</v>
       </c>
       <c r="P26">
-        <v>-185.4766138061817</v>
+        <v>-192.9208616036615</v>
       </c>
       <c r="Q26">
-        <v>-806.6766138061818</v>
+        <v>-814.1208616036615</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1519842555835781</v>
+        <v>0.1534000456580258</v>
       </c>
       <c r="T26">
-        <v>2.183260055663798</v>
+        <v>2.212370189739315</v>
       </c>
       <c r="U26">
         <v>0.2397577444416894</v>
       </c>
       <c r="V26">
-        <v>-0.009154271663248175</v>
+        <v>-0.008788100796718249</v>
       </c>
       <c r="W26">
-        <v>0.2419525519676763</v>
+        <v>0.2418647596666368</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3446,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>-0.03814279859686742</v>
+        <v>-0.03661708665299268</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3454,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1755162241601785</v>
+        <v>0.1774558016045954</v>
       </c>
       <c r="C27">
-        <v>1894.972506591517</v>
+        <v>1829.179534581402</v>
       </c>
       <c r="D27">
-        <v>1692.822506591517</v>
+        <v>1667.883534581402</v>
       </c>
       <c r="E27">
-        <v>-2417.15</v>
+        <v>-2376.296</v>
       </c>
       <c r="F27">
-        <v>1021.35</v>
+        <v>1062.204</v>
       </c>
       <c r="G27">
         <v>1223.5</v>
@@ -3490,37 +3501,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M27">
-        <v>244.8765722855195</v>
+        <v>254.6716351769402</v>
       </c>
       <c r="N27">
-        <v>-253.8432389521862</v>
+        <v>-263.6383018436069</v>
       </c>
       <c r="O27">
-        <v>-60.92237734852468</v>
+        <v>-63.27319244246566</v>
       </c>
       <c r="P27">
-        <v>-192.9208616036615</v>
+        <v>-200.3651094011413</v>
       </c>
       <c r="Q27">
-        <v>-814.1208616036615</v>
+        <v>-821.5651094011413</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1534000456580258</v>
+        <v>0.1548541003290802</v>
       </c>
       <c r="T27">
-        <v>2.212370189739315</v>
+        <v>2.242267084195252</v>
       </c>
       <c r="U27">
         <v>0.2397577444416894</v>
       </c>
       <c r="V27">
-        <v>-0.008788100796718249</v>
+        <v>-0.008450096919921391</v>
       </c>
       <c r="W27">
-        <v>0.2418647596666368</v>
+        <v>0.2417837206195234</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3528,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>-0.03661708665299268</v>
+        <v>-0.03520873716633921</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3536,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1774558016045954</v>
+        <v>0.1793953790490123</v>
       </c>
       <c r="C28">
-        <v>1829.179534581402</v>
+        <v>1764.110705396318</v>
       </c>
       <c r="D28">
-        <v>1667.883534581402</v>
+        <v>1643.668705396318</v>
       </c>
       <c r="E28">
-        <v>-2376.296</v>
+        <v>-2335.442</v>
       </c>
       <c r="F28">
-        <v>1062.204</v>
+        <v>1103.058</v>
       </c>
       <c r="G28">
         <v>1223.5</v>
@@ -3572,37 +3583,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M28">
-        <v>254.6716351769402</v>
+        <v>264.466698068361</v>
       </c>
       <c r="N28">
-        <v>-263.6383018436069</v>
+        <v>-273.4333647350277</v>
       </c>
       <c r="O28">
-        <v>-63.27319244246566</v>
+        <v>-65.62400753640665</v>
       </c>
       <c r="P28">
-        <v>-200.3651094011413</v>
+        <v>-207.8093571986211</v>
       </c>
       <c r="Q28">
-        <v>-821.5651094011413</v>
+        <v>-829.0093571986212</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1548541003290802</v>
+        <v>0.15634799211441</v>
       </c>
       <c r="T28">
-        <v>2.242267084195252</v>
+        <v>2.272983071649981</v>
       </c>
       <c r="U28">
         <v>0.2397577444416894</v>
       </c>
       <c r="V28">
-        <v>-0.008450096919921391</v>
+        <v>-0.008137130367331711</v>
       </c>
       <c r="W28">
-        <v>0.2417837206195234</v>
+        <v>0.2417086844647888</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3610,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>-0.03520873716633921</v>
+        <v>-0.03390470986388205</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3618,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1793953790490123</v>
+        <v>0.1813349564934292</v>
       </c>
       <c r="C29">
-        <v>1764.110705396318</v>
+        <v>1699.734930427252</v>
       </c>
       <c r="D29">
-        <v>1643.668705396318</v>
+        <v>1620.146930427252</v>
       </c>
       <c r="E29">
-        <v>-2335.442</v>
+        <v>-2294.588</v>
       </c>
       <c r="F29">
-        <v>1103.058</v>
+        <v>1143.912</v>
       </c>
       <c r="G29">
         <v>1223.5</v>
@@ -3654,37 +3665,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M29">
-        <v>264.466698068361</v>
+        <v>274.2617609597818</v>
       </c>
       <c r="N29">
-        <v>-273.4333647350277</v>
+        <v>-283.2284276264485</v>
       </c>
       <c r="O29">
-        <v>-65.62400753640665</v>
+        <v>-67.97482263034765</v>
       </c>
       <c r="P29">
-        <v>-207.8093571986211</v>
+        <v>-215.2536049961009</v>
       </c>
       <c r="Q29">
-        <v>-829.0093571986212</v>
+        <v>-836.4536049961009</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.15634799211441</v>
+        <v>0.1578833808937768</v>
       </c>
       <c r="T29">
-        <v>2.272983071649981</v>
+        <v>2.304552280978454</v>
       </c>
       <c r="U29">
         <v>0.2397577444416894</v>
       </c>
       <c r="V29">
-        <v>-0.008137130367331711</v>
+        <v>-0.007846518568498434</v>
       </c>
       <c r="W29">
-        <v>0.2417086844647888</v>
+        <v>0.2416390080353924</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3692,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>-0.03390470986388205</v>
+        <v>-0.03269382736874338</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3700,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1813349564934292</v>
+        <v>0.1832745339378461</v>
       </c>
       <c r="C30">
-        <v>1699.734930427252</v>
+        <v>1636.022875536019</v>
       </c>
       <c r="D30">
-        <v>1620.146930427252</v>
+        <v>1597.288875536019</v>
       </c>
       <c r="E30">
-        <v>-2294.588</v>
+        <v>-2253.734</v>
       </c>
       <c r="F30">
-        <v>1143.912</v>
+        <v>1184.766</v>
       </c>
       <c r="G30">
         <v>1223.5</v>
@@ -3736,37 +3747,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M30">
-        <v>274.2617609597818</v>
+        <v>284.0568238512026</v>
       </c>
       <c r="N30">
-        <v>-283.2284276264485</v>
+        <v>-293.0234905178693</v>
       </c>
       <c r="O30">
-        <v>-67.97482263034765</v>
+        <v>-70.32563772428863</v>
       </c>
       <c r="P30">
-        <v>-215.2536049961009</v>
+        <v>-222.6978527935806</v>
       </c>
       <c r="Q30">
-        <v>-836.4536049961009</v>
+        <v>-843.8978527935807</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1578833808937768</v>
+        <v>0.1594620200612948</v>
       </c>
       <c r="T30">
-        <v>2.304552280978454</v>
+        <v>2.337010763809136</v>
       </c>
       <c r="U30">
         <v>0.2397577444416894</v>
       </c>
       <c r="V30">
-        <v>-0.007846518568498434</v>
+        <v>-0.007575948962688144</v>
       </c>
       <c r="W30">
-        <v>0.2416390080353924</v>
+        <v>0.2415741368769889</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3774,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>-0.03269382736874338</v>
+        <v>-0.03156645401120062</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3782,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1832745339378461</v>
+        <v>0.185214111382263</v>
       </c>
       <c r="C31">
-        <v>1636.022875536019</v>
+        <v>1572.946839011231</v>
       </c>
       <c r="D31">
-        <v>1597.288875536019</v>
+        <v>1575.06683901123</v>
       </c>
       <c r="E31">
-        <v>-2253.734</v>
+        <v>-2212.88</v>
       </c>
       <c r="F31">
-        <v>1184.766</v>
+        <v>1225.62</v>
       </c>
       <c r="G31">
         <v>1223.5</v>
@@ -3818,37 +3829,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M31">
-        <v>284.0568238512025</v>
+        <v>293.8518867426233</v>
       </c>
       <c r="N31">
-        <v>-293.0234905178692</v>
+        <v>-302.81855340929</v>
       </c>
       <c r="O31">
-        <v>-70.32563772428861</v>
+        <v>-72.67645281822961</v>
       </c>
       <c r="P31">
-        <v>-222.6978527935806</v>
+        <v>-230.1421005910604</v>
       </c>
       <c r="Q31">
-        <v>-843.8978527935807</v>
+        <v>-851.3421005910604</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1594620200612948</v>
+        <v>0.1610857632050276</v>
       </c>
       <c r="T31">
-        <v>2.337010763809136</v>
+        <v>2.370396631863552</v>
       </c>
       <c r="U31">
         <v>0.2397577444416894</v>
       </c>
       <c r="V31">
-        <v>-0.007575948962688146</v>
+        <v>-0.00732341733059854</v>
       </c>
       <c r="W31">
-        <v>0.2415741368769889</v>
+        <v>0.2415135904624789</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3856,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>-0.03156645401120062</v>
+        <v>-0.03051423887749394</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3864,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.185214111382263</v>
+        <v>0.1871536888266799</v>
       </c>
       <c r="C32">
-        <v>1572.946839011231</v>
+        <v>1510.480639571985</v>
       </c>
       <c r="D32">
-        <v>1575.06683901123</v>
+        <v>1553.454639571985</v>
       </c>
       <c r="E32">
-        <v>-2212.88</v>
+        <v>-2172.026</v>
       </c>
       <c r="F32">
-        <v>1225.62</v>
+        <v>1266.474</v>
       </c>
       <c r="G32">
         <v>1223.5</v>
@@ -3900,37 +3911,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M32">
-        <v>293.8518867426233</v>
+        <v>303.6469496340441</v>
       </c>
       <c r="N32">
-        <v>-302.81855340929</v>
+        <v>-312.6136163007108</v>
       </c>
       <c r="O32">
-        <v>-72.67645281822961</v>
+        <v>-75.02726791217059</v>
       </c>
       <c r="P32">
-        <v>-230.1421005910604</v>
+        <v>-237.5863483885402</v>
       </c>
       <c r="Q32">
-        <v>-851.3421005910604</v>
+        <v>-858.7863483885403</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1610857632050276</v>
+        <v>0.1627565713674193</v>
       </c>
       <c r="T32">
-        <v>2.370396631863552</v>
+        <v>2.404750206238386</v>
       </c>
       <c r="U32">
         <v>0.2397577444416894</v>
       </c>
       <c r="V32">
-        <v>-0.00732341733059854</v>
+        <v>-0.007087178061869555</v>
       </c>
       <c r="W32">
-        <v>0.2415135904624789</v>
+        <v>0.2414569502682599</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3938,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>-0.03051423887749394</v>
+        <v>-0.02952990859112314</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3946,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1871536888266799</v>
+        <v>0.1890932662710968</v>
       </c>
       <c r="C33">
-        <v>1510.480639571985</v>
+        <v>1448.599513467272</v>
       </c>
       <c r="D33">
-        <v>1553.454639571985</v>
+        <v>1532.427513467271</v>
       </c>
       <c r="E33">
-        <v>-2172.026</v>
+        <v>-2131.172</v>
       </c>
       <c r="F33">
-        <v>1266.474</v>
+        <v>1307.328</v>
       </c>
       <c r="G33">
         <v>1223.5</v>
@@ -3982,37 +3993,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M33">
-        <v>303.6469496340441</v>
+        <v>313.4420125254649</v>
       </c>
       <c r="N33">
-        <v>-312.6136163007108</v>
+        <v>-322.4086791921316</v>
       </c>
       <c r="O33">
-        <v>-75.02726791217059</v>
+        <v>-77.37808300611158</v>
       </c>
       <c r="P33">
-        <v>-237.5863483885402</v>
+        <v>-245.03059618602</v>
       </c>
       <c r="Q33">
-        <v>-858.7863483885403</v>
+        <v>-866.2305961860201</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1627565713674193</v>
+        <v>0.164476520946352</v>
       </c>
       <c r="T33">
-        <v>2.404750206238386</v>
+        <v>2.440114179859539</v>
       </c>
       <c r="U33">
         <v>0.2397577444416894</v>
       </c>
       <c r="V33">
-        <v>-0.007087178061869555</v>
+        <v>-0.006865703747436131</v>
       </c>
       <c r="W33">
-        <v>0.2414569502682599</v>
+        <v>0.2414038500861796</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4020,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>-0.02952990859112314</v>
+        <v>-0.02860709894765057</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4028,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1890932662710968</v>
+        <v>0.1910328437155137</v>
       </c>
       <c r="C34">
-        <v>1448.599513467272</v>
+        <v>1387.280019820758</v>
       </c>
       <c r="D34">
-        <v>1532.427513467271</v>
+        <v>1511.962019820758</v>
       </c>
       <c r="E34">
-        <v>-2131.172</v>
+        <v>-2090.318</v>
       </c>
       <c r="F34">
-        <v>1307.328</v>
+        <v>1348.182</v>
       </c>
       <c r="G34">
         <v>1223.5</v>
@@ -4064,37 +4075,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M34">
-        <v>313.4420125254649</v>
+        <v>323.2370754168857</v>
       </c>
       <c r="N34">
-        <v>-322.4086791921316</v>
+        <v>-332.2037420835524</v>
       </c>
       <c r="O34">
-        <v>-77.37808300611158</v>
+        <v>-79.72889810005258</v>
       </c>
       <c r="P34">
-        <v>-245.03059618602</v>
+        <v>-252.4748439834999</v>
       </c>
       <c r="Q34">
-        <v>-866.2305961860201</v>
+        <v>-873.6748439834998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.164476520946352</v>
+        <v>0.1662478123037602</v>
       </c>
       <c r="T34">
-        <v>2.440114179859539</v>
+        <v>2.476533794484309</v>
       </c>
       <c r="U34">
         <v>0.2397577444416894</v>
       </c>
       <c r="V34">
-        <v>-0.006865703747436131</v>
+        <v>-0.006657652118725945</v>
       </c>
       <c r="W34">
-        <v>0.2414038500861796</v>
+        <v>0.2413539680969526</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4102,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>-0.02860709894765057</v>
+        <v>-0.02774021716135811</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4110,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1910328437155137</v>
+        <v>0.1929724211599306</v>
       </c>
       <c r="C35">
-        <v>1387.280019820758</v>
+        <v>1326.499953460318</v>
       </c>
       <c r="D35">
-        <v>1511.962019820758</v>
+        <v>1492.035953460318</v>
       </c>
       <c r="E35">
-        <v>-2090.318</v>
+        <v>-2049.464</v>
       </c>
       <c r="F35">
-        <v>1348.182</v>
+        <v>1389.036</v>
       </c>
       <c r="G35">
         <v>1223.5</v>
@@ -4146,37 +4157,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M35">
-        <v>323.2370754168857</v>
+        <v>333.0321383083065</v>
       </c>
       <c r="N35">
-        <v>-332.2037420835524</v>
+        <v>-341.9988049749732</v>
       </c>
       <c r="O35">
-        <v>-79.72889810005258</v>
+        <v>-82.07971319399357</v>
       </c>
       <c r="P35">
-        <v>-252.4748439834999</v>
+        <v>-259.9190917809797</v>
       </c>
       <c r="Q35">
-        <v>-873.6748439834998</v>
+        <v>-881.1190917809797</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1662478123037602</v>
+        <v>0.1680727791568475</v>
       </c>
       <c r="T35">
-        <v>2.476533794484309</v>
+        <v>2.514057033794677</v>
       </c>
       <c r="U35">
         <v>0.2397577444416894</v>
       </c>
       <c r="V35">
-        <v>-0.006657652118725945</v>
+        <v>-0.006461838821116357</v>
       </c>
       <c r="W35">
-        <v>0.2413539680969526</v>
+        <v>0.241307020342386</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4184,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>-0.02774021716135811</v>
+        <v>-0.02692432842131809</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4192,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1929724211599306</v>
+        <v>0.1949119986043474</v>
       </c>
       <c r="C36">
-        <v>1326.499953460318</v>
+        <v>1266.238264550793</v>
       </c>
       <c r="D36">
-        <v>1492.035953460318</v>
+        <v>1472.628264550793</v>
       </c>
       <c r="E36">
-        <v>-2049.464</v>
+        <v>-2008.61</v>
       </c>
       <c r="F36">
-        <v>1389.036</v>
+        <v>1429.89</v>
       </c>
       <c r="G36">
         <v>1223.5</v>
@@ -4228,37 +4239,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M36">
-        <v>333.0321383083065</v>
+        <v>342.8272011997273</v>
       </c>
       <c r="N36">
-        <v>-341.9988049749732</v>
+        <v>-351.793867866394</v>
       </c>
       <c r="O36">
-        <v>-82.07971319399357</v>
+        <v>-84.43052828793455</v>
       </c>
       <c r="P36">
-        <v>-259.9190917809797</v>
+        <v>-267.3633395784594</v>
       </c>
       <c r="Q36">
-        <v>-881.1190917809797</v>
+        <v>-888.5633395784595</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1680727791568475</v>
+        <v>0.1699538988361836</v>
       </c>
       <c r="T36">
-        <v>2.514057033794677</v>
+        <v>2.552734834314595</v>
       </c>
       <c r="U36">
         <v>0.2397577444416894</v>
       </c>
       <c r="V36">
-        <v>-0.006461838821116357</v>
+        <v>-0.006277214854798749</v>
       </c>
       <c r="W36">
-        <v>0.241307020342386</v>
+        <v>0.2412627553166518</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4266,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>-0.02692432842131809</v>
+        <v>-0.02615506189499484</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4274,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1949119986043474</v>
+        <v>0.1968515760487644</v>
       </c>
       <c r="C37">
-        <v>1266.238264550793</v>
+        <v>1206.474984418479</v>
       </c>
       <c r="D37">
-        <v>1472.628264550793</v>
+        <v>1453.71898441848</v>
       </c>
       <c r="E37">
-        <v>-2008.61</v>
+        <v>-1967.756</v>
       </c>
       <c r="F37">
-        <v>1429.89</v>
+        <v>1470.744</v>
       </c>
       <c r="G37">
         <v>1223.5</v>
@@ -4310,37 +4321,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M37">
-        <v>342.8272011997273</v>
+        <v>352.6222640911481</v>
       </c>
       <c r="N37">
-        <v>-351.793867866394</v>
+        <v>-361.5889307578148</v>
       </c>
       <c r="O37">
-        <v>-84.43052828793455</v>
+        <v>-86.78134338187553</v>
       </c>
       <c r="P37">
-        <v>-267.3633395784594</v>
+        <v>-274.8075873759392</v>
       </c>
       <c r="Q37">
-        <v>-888.5633395784595</v>
+        <v>-896.0075873759392</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1699538988361836</v>
+        <v>0.171893803505499</v>
       </c>
       <c r="T37">
-        <v>2.552734834314595</v>
+        <v>2.592621316100761</v>
       </c>
       <c r="U37">
         <v>0.2397577444416894</v>
       </c>
       <c r="V37">
-        <v>-0.006277214854798749</v>
+        <v>-0.006102847775498783</v>
       </c>
       <c r="W37">
-        <v>0.2412627553166518</v>
+        <v>0.241220949459014</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4348,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>-0.02615506189499484</v>
+        <v>-0.02542853239791154</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4356,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1968515760487644</v>
+        <v>0.1987911534931813</v>
       </c>
       <c r="C38">
-        <v>1206.47498441848</v>
+        <v>1147.191157017875</v>
       </c>
       <c r="D38">
-        <v>1453.71898441848</v>
+        <v>1435.289157017875</v>
       </c>
       <c r="E38">
-        <v>-1967.756</v>
+        <v>-1926.902</v>
       </c>
       <c r="F38">
-        <v>1470.744</v>
+        <v>1511.598</v>
       </c>
       <c r="G38">
         <v>1223.5</v>
@@ -4392,37 +4403,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M38">
-        <v>352.622264091148</v>
+        <v>362.4173269825688</v>
       </c>
       <c r="N38">
-        <v>-361.5889307578147</v>
+        <v>-371.3839936492355</v>
       </c>
       <c r="O38">
-        <v>-86.78134338187553</v>
+        <v>-89.13215847581651</v>
       </c>
       <c r="P38">
-        <v>-274.8075873759392</v>
+        <v>-282.251835173419</v>
       </c>
       <c r="Q38">
-        <v>-896.0075873759392</v>
+        <v>-903.451835173419</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.171893803505499</v>
+        <v>0.1738952924500307</v>
       </c>
       <c r="T38">
-        <v>2.59262131610076</v>
+        <v>2.633774035403947</v>
       </c>
       <c r="U38">
         <v>0.2397577444416894</v>
       </c>
       <c r="V38">
-        <v>-0.006102847775498784</v>
+        <v>-0.005937905943728545</v>
       </c>
       <c r="W38">
-        <v>0.241220949459014</v>
+        <v>0.2411814033774647</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4430,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>-0.02542853239791154</v>
+        <v>-0.02474127476553556</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4438,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1987911534931813</v>
+        <v>0.2007307309375982</v>
       </c>
       <c r="C39">
-        <v>1147.191157017875</v>
+        <v>1088.368775546227</v>
       </c>
       <c r="D39">
-        <v>1435.289157017875</v>
+        <v>1417.320775546227</v>
       </c>
       <c r="E39">
-        <v>-1926.902</v>
+        <v>-1886.048</v>
       </c>
       <c r="F39">
-        <v>1511.598</v>
+        <v>1552.452</v>
       </c>
       <c r="G39">
         <v>1223.5</v>
@@ -4474,37 +4485,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M39">
-        <v>362.4173269825688</v>
+        <v>372.2123898739896</v>
       </c>
       <c r="N39">
-        <v>-371.3839936492355</v>
+        <v>-381.1790565406563</v>
       </c>
       <c r="O39">
-        <v>-89.13215847581651</v>
+        <v>-91.4829735697575</v>
       </c>
       <c r="P39">
-        <v>-282.251835173419</v>
+        <v>-289.6960829708988</v>
       </c>
       <c r="Q39">
-        <v>-903.451835173419</v>
+        <v>-910.8960829708988</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1738952924500307</v>
+        <v>0.1759613455540635</v>
       </c>
       <c r="T39">
-        <v>2.633774035403947</v>
+        <v>2.67625426178143</v>
       </c>
       <c r="U39">
         <v>0.2397577444416894</v>
       </c>
       <c r="V39">
-        <v>-0.005937905943728545</v>
+        <v>-0.005781645260998847</v>
       </c>
       <c r="W39">
-        <v>0.2411814033774647</v>
+        <v>0.2411439386686285</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4512,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>-0.02474127476553556</v>
+        <v>-0.02409018858749512</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4520,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2007307309375982</v>
+        <v>0.2026703083820151</v>
       </c>
       <c r="C40">
-        <v>1088.368775546227</v>
+        <v>1029.99072376035</v>
       </c>
       <c r="D40">
-        <v>1417.320775546227</v>
+        <v>1399.79672376035</v>
       </c>
       <c r="E40">
-        <v>-1886.048</v>
+        <v>-1845.194</v>
       </c>
       <c r="F40">
-        <v>1552.452</v>
+        <v>1593.306</v>
       </c>
       <c r="G40">
         <v>1223.5</v>
@@ -4556,37 +4567,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M40">
-        <v>372.2123898739896</v>
+        <v>382.0074527654104</v>
       </c>
       <c r="N40">
-        <v>-381.1790565406563</v>
+        <v>-390.9741194320771</v>
       </c>
       <c r="O40">
-        <v>-91.4829735697575</v>
+        <v>-93.8337886636985</v>
       </c>
       <c r="P40">
-        <v>-289.6960829708988</v>
+        <v>-297.1403307683786</v>
       </c>
       <c r="Q40">
-        <v>-910.8960829708988</v>
+        <v>-918.3403307683786</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1759613455540635</v>
+        <v>0.1780951381041301</v>
       </c>
       <c r="T40">
-        <v>2.67625426178143</v>
+        <v>2.720127282466372</v>
       </c>
       <c r="U40">
         <v>0.2397577444416894</v>
       </c>
       <c r="V40">
-        <v>-0.005781645260998847</v>
+        <v>-0.005633397946614261</v>
       </c>
       <c r="W40">
-        <v>0.2411439386686285</v>
+        <v>0.2411083952269121</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4594,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>-0.02409018858749512</v>
+        <v>-0.02347249144422614</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4602,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2026703083820151</v>
+        <v>0.2046098858264319</v>
       </c>
       <c r="C41">
-        <v>1029.99072376035</v>
+        <v>972.0407215936996</v>
       </c>
       <c r="D41">
-        <v>1399.79672376035</v>
+        <v>1382.7007215937</v>
       </c>
       <c r="E41">
-        <v>-1845.194</v>
+        <v>-1804.34</v>
       </c>
       <c r="F41">
-        <v>1593.306</v>
+        <v>1634.16</v>
       </c>
       <c r="G41">
         <v>1223.5</v>
@@ -4638,37 +4649,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M41">
-        <v>382.0074527654104</v>
+        <v>391.8025156568312</v>
       </c>
       <c r="N41">
-        <v>-390.9741194320771</v>
+        <v>-400.7691823234979</v>
       </c>
       <c r="O41">
-        <v>-93.8337886636985</v>
+        <v>-96.18460375763949</v>
       </c>
       <c r="P41">
-        <v>-297.1403307683786</v>
+        <v>-304.5845785658584</v>
       </c>
       <c r="Q41">
-        <v>-918.3403307683786</v>
+        <v>-925.7845785658585</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1780951381041301</v>
+        <v>0.1803000570725322</v>
       </c>
       <c r="T41">
-        <v>2.720127282466372</v>
+        <v>2.765462737174144</v>
       </c>
       <c r="U41">
         <v>0.2397577444416894</v>
       </c>
       <c r="V41">
-        <v>-0.005633397946614261</v>
+        <v>-0.005492562997948904</v>
       </c>
       <c r="W41">
-        <v>0.2411083952269121</v>
+        <v>0.2410746289572815</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4676,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>-0.02347249144422614</v>
+        <v>-0.02288567915812045</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4684,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2046098858264319</v>
+        <v>0.2065494632708488</v>
       </c>
       <c r="C42">
-        <v>972.0407215936996</v>
+        <v>914.5032747104997</v>
       </c>
       <c r="D42">
-        <v>1382.7007215937</v>
+        <v>1366.0172747105</v>
       </c>
       <c r="E42">
-        <v>-1804.34</v>
+        <v>-1763.486</v>
       </c>
       <c r="F42">
-        <v>1634.16</v>
+        <v>1675.014</v>
       </c>
       <c r="G42">
         <v>1223.5</v>
@@ -4720,37 +4731,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M42">
-        <v>391.8025156568312</v>
+        <v>401.597578548252</v>
       </c>
       <c r="N42">
-        <v>-400.7691823234979</v>
+        <v>-410.5642452149187</v>
       </c>
       <c r="O42">
-        <v>-96.18460375763949</v>
+        <v>-98.53541885158049</v>
       </c>
       <c r="P42">
-        <v>-304.5845785658584</v>
+        <v>-312.0288263633382</v>
       </c>
       <c r="Q42">
-        <v>-925.7845785658585</v>
+        <v>-933.2288263633383</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1803000570725322</v>
+        <v>0.1825797190568124</v>
       </c>
       <c r="T42">
-        <v>2.765462737174144</v>
+        <v>2.812334986956757</v>
       </c>
       <c r="U42">
         <v>0.2397577444416894</v>
       </c>
       <c r="V42">
-        <v>-0.005492562997948904</v>
+        <v>-0.005358598046779419</v>
       </c>
       <c r="W42">
-        <v>0.2410746289572815</v>
+        <v>0.2410425098227549</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4758,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>-0.02288567915812045</v>
+        <v>-0.02232749186158101</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4766,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2065494632708488</v>
+        <v>0.2084890407152657</v>
       </c>
       <c r="C43">
-        <v>914.5032747104997</v>
+        <v>857.3636276683649</v>
       </c>
       <c r="D43">
-        <v>1366.0172747105</v>
+        <v>1349.731627668365</v>
       </c>
       <c r="E43">
-        <v>-1763.486</v>
+        <v>-1722.632</v>
       </c>
       <c r="F43">
-        <v>1675.014</v>
+        <v>1715.868</v>
       </c>
       <c r="G43">
         <v>1223.5</v>
@@ -4802,37 +4813,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M43">
-        <v>401.597578548252</v>
+        <v>411.3926414396727</v>
       </c>
       <c r="N43">
-        <v>-410.5642452149187</v>
+        <v>-420.3593081063394</v>
       </c>
       <c r="O43">
-        <v>-98.53541885158049</v>
+        <v>-100.8862339455215</v>
       </c>
       <c r="P43">
-        <v>-312.0288263633382</v>
+        <v>-319.473074160818</v>
       </c>
       <c r="Q43">
-        <v>-933.2288263633383</v>
+        <v>-940.673074160818</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1825797190568124</v>
+        <v>0.1849379900750333</v>
       </c>
       <c r="T43">
-        <v>2.812334986956757</v>
+        <v>2.860823521214632</v>
       </c>
       <c r="U43">
         <v>0.2397577444416894</v>
       </c>
       <c r="V43">
-        <v>-0.005358598046779419</v>
+        <v>-0.005231012378998957</v>
       </c>
       <c r="W43">
-        <v>0.2410425098227549</v>
+        <v>0.2410119201708247</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4840,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>-0.02232749186158101</v>
+        <v>-0.02179588491249573</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4848,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2084890407152657</v>
+        <v>0.2104286181596826</v>
       </c>
       <c r="C44">
-        <v>857.3636276683651</v>
+        <v>800.6077203918155</v>
       </c>
       <c r="D44">
-        <v>1349.731627668365</v>
+        <v>1333.829720391816</v>
       </c>
       <c r="E44">
-        <v>-1722.632</v>
+        <v>-1681.778</v>
       </c>
       <c r="F44">
-        <v>1715.868</v>
+        <v>1756.722</v>
       </c>
       <c r="G44">
         <v>1223.5</v>
@@ -4884,37 +4895,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M44">
-        <v>411.3926414396727</v>
+        <v>421.1877043310935</v>
       </c>
       <c r="N44">
-        <v>-420.3593081063394</v>
+        <v>-430.1543709977602</v>
       </c>
       <c r="O44">
-        <v>-100.8862339455214</v>
+        <v>-103.2370490394624</v>
       </c>
       <c r="P44">
-        <v>-319.4730741608179</v>
+        <v>-326.9173219582977</v>
       </c>
       <c r="Q44">
-        <v>-940.673074160818</v>
+        <v>-948.1173219582978</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1849379900750333</v>
+        <v>0.1873790074447708</v>
       </c>
       <c r="T44">
-        <v>2.860823521214632</v>
+        <v>2.911013407551731</v>
       </c>
       <c r="U44">
         <v>0.2397577444416894</v>
       </c>
       <c r="V44">
-        <v>-0.005231012378998957</v>
+        <v>-0.005109360928324562</v>
       </c>
       <c r="W44">
-        <v>0.2410119201708247</v>
+        <v>0.240982753293403</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4922,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>-0.02179588491249573</v>
+        <v>-0.02128900386801891</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4930,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2104286181596826</v>
+        <v>0.2123681956040995</v>
       </c>
       <c r="C45">
-        <v>800.6077203918155</v>
+        <v>744.2221476868212</v>
       </c>
       <c r="D45">
-        <v>1333.829720391816</v>
+        <v>1318.298147686821</v>
       </c>
       <c r="E45">
-        <v>-1681.778</v>
+        <v>-1640.924</v>
       </c>
       <c r="F45">
-        <v>1756.722</v>
+        <v>1797.576</v>
       </c>
       <c r="G45">
         <v>1223.5</v>
@@ -4966,37 +4977,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M45">
-        <v>421.1877043310935</v>
+        <v>430.9827672225143</v>
       </c>
       <c r="N45">
-        <v>-430.1543709977602</v>
+        <v>-439.949433889181</v>
       </c>
       <c r="O45">
-        <v>-103.2370490394624</v>
+        <v>-105.5878641334034</v>
       </c>
       <c r="P45">
-        <v>-326.9173219582977</v>
+        <v>-334.3615697557775</v>
       </c>
       <c r="Q45">
-        <v>-948.1173219582978</v>
+        <v>-955.5615697557776</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1873790074447708</v>
+        <v>0.1899072040062845</v>
       </c>
       <c r="T45">
-        <v>2.911013407551731</v>
+        <v>2.96299578982944</v>
       </c>
       <c r="U45">
         <v>0.2397577444416894</v>
       </c>
       <c r="V45">
-        <v>-0.005109360928324562</v>
+        <v>-0.004993239089044458</v>
       </c>
       <c r="W45">
-        <v>0.240982753293403</v>
+        <v>0.2409549121831367</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5004,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>-0.02128900386801891</v>
+        <v>-0.02080516287101863</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5012,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2123681956040995</v>
+        <v>0.2143077730485164</v>
       </c>
       <c r="C46">
-        <v>744.2221476868212</v>
+        <v>688.1941215513395</v>
       </c>
       <c r="D46">
-        <v>1318.298147686821</v>
+        <v>1303.12412155134</v>
       </c>
       <c r="E46">
-        <v>-1640.924</v>
+        <v>-1600.07</v>
       </c>
       <c r="F46">
-        <v>1797.576</v>
+        <v>1838.43</v>
       </c>
       <c r="G46">
         <v>1223.5</v>
@@ -5048,37 +5059,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M46">
-        <v>430.9827672225143</v>
+        <v>440.7778301139351</v>
       </c>
       <c r="N46">
-        <v>-439.949433889181</v>
+        <v>-449.7444967806018</v>
       </c>
       <c r="O46">
-        <v>-105.5878641334034</v>
+        <v>-107.9386792273444</v>
       </c>
       <c r="P46">
-        <v>-334.3615697557775</v>
+        <v>-341.8058175532573</v>
       </c>
       <c r="Q46">
-        <v>-955.5615697557776</v>
+        <v>-963.0058175532574</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1899072040062845</v>
+        <v>0.192527334988217</v>
       </c>
       <c r="T46">
-        <v>2.96299578982944</v>
+        <v>3.016868440553612</v>
       </c>
       <c r="U46">
         <v>0.2397577444416894</v>
       </c>
       <c r="V46">
-        <v>-0.004993239089044458</v>
+        <v>-0.004882278220399026</v>
       </c>
       <c r="W46">
-        <v>0.2409549121831367</v>
+        <v>0.2409283084555491</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5086,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>-0.02080516287101863</v>
+        <v>-0.02034282591832937</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5094,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2143077730485164</v>
+        <v>0.2162473504929333</v>
       </c>
       <c r="C47">
-        <v>688.1941215513395</v>
+        <v>632.511436059151</v>
       </c>
       <c r="D47">
-        <v>1303.12412155134</v>
+        <v>1288.295436059151</v>
       </c>
       <c r="E47">
-        <v>-1600.07</v>
+        <v>-1559.216</v>
       </c>
       <c r="F47">
-        <v>1838.43</v>
+        <v>1879.284</v>
       </c>
       <c r="G47">
         <v>1223.5</v>
@@ -5130,37 +5141,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M47">
-        <v>440.7778301139351</v>
+        <v>450.5728930053559</v>
       </c>
       <c r="N47">
-        <v>-449.7444967806018</v>
+        <v>-459.5395596720226</v>
       </c>
       <c r="O47">
-        <v>-107.9386792273444</v>
+        <v>-110.2894943212854</v>
       </c>
       <c r="P47">
-        <v>-341.8058175532573</v>
+        <v>-349.2500653507371</v>
       </c>
       <c r="Q47">
-        <v>-963.0058175532574</v>
+        <v>-970.4500653507372</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.192527334988217</v>
+        <v>0.1952445078583691</v>
       </c>
       <c r="T47">
-        <v>3.016868440553612</v>
+        <v>3.072736374637938</v>
       </c>
       <c r="U47">
         <v>0.2397577444416894</v>
       </c>
       <c r="V47">
-        <v>-0.004882278220399026</v>
+        <v>-0.004776141737346874</v>
       </c>
       <c r="W47">
-        <v>0.2409283084555491</v>
+        <v>0.2409028614117695</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5168,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>-0.02034282591832937</v>
+        <v>-0.01990059057227866</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5176,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2162473504929333</v>
+        <v>0.2181869279373502</v>
       </c>
       <c r="C48">
-        <v>632.511436059151</v>
+        <v>577.1624346142987</v>
       </c>
       <c r="D48">
-        <v>1288.295436059151</v>
+        <v>1273.800434614299</v>
       </c>
       <c r="E48">
-        <v>-1559.216</v>
+        <v>-1518.362</v>
       </c>
       <c r="F48">
-        <v>1879.284</v>
+        <v>1920.138</v>
       </c>
       <c r="G48">
         <v>1223.5</v>
@@ -5212,37 +5223,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M48">
-        <v>450.5728930053559</v>
+        <v>460.3679558967767</v>
       </c>
       <c r="N48">
-        <v>-459.5395596720226</v>
+        <v>-469.3346225634434</v>
       </c>
       <c r="O48">
-        <v>-110.2894943212854</v>
+        <v>-112.6403094152264</v>
       </c>
       <c r="P48">
-        <v>-349.2500653507371</v>
+        <v>-356.694313148217</v>
       </c>
       <c r="Q48">
-        <v>-970.4500653507372</v>
+        <v>-977.894313148217</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1952445078583691</v>
+        <v>0.1980642155538101</v>
       </c>
       <c r="T48">
-        <v>3.072736374637938</v>
+        <v>3.130712532649975</v>
       </c>
       <c r="U48">
         <v>0.2397577444416894</v>
       </c>
       <c r="V48">
-        <v>-0.004776141737346874</v>
+        <v>-0.004674521700382046</v>
       </c>
       <c r="W48">
-        <v>0.2409028614117695</v>
+        <v>0.2408784972209167</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5250,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>-0.01990059057227866</v>
+        <v>-0.01947717375159197</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5258,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2181869279373502</v>
+        <v>0.2201265053817671</v>
       </c>
       <c r="C49">
-        <v>577.1624346142987</v>
+        <v>522.1359793915212</v>
       </c>
       <c r="D49">
-        <v>1273.800434614299</v>
+        <v>1259.627979391521</v>
       </c>
       <c r="E49">
-        <v>-1518.362</v>
+        <v>-1477.508</v>
       </c>
       <c r="F49">
-        <v>1920.138</v>
+        <v>1960.992</v>
       </c>
       <c r="G49">
         <v>1223.5</v>
@@ -5294,37 +5305,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M49">
-        <v>460.3679558967767</v>
+        <v>470.1630187881974</v>
       </c>
       <c r="N49">
-        <v>-469.3346225634434</v>
+        <v>-479.1296854548641</v>
       </c>
       <c r="O49">
-        <v>-112.6403094152264</v>
+        <v>-114.9911245091674</v>
       </c>
       <c r="P49">
-        <v>-356.694313148217</v>
+        <v>-364.1385609456967</v>
       </c>
       <c r="Q49">
-        <v>-977.894313148217</v>
+        <v>-985.3385609456968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1980642155538101</v>
+        <v>0.2009923735452295</v>
       </c>
       <c r="T49">
-        <v>3.130712532649975</v>
+        <v>3.190918542893244</v>
       </c>
       <c r="U49">
         <v>0.2397577444416894</v>
       </c>
       <c r="V49">
-        <v>-0.004674521700382046</v>
+        <v>-0.004577135831624087</v>
       </c>
       <c r="W49">
-        <v>0.2408784972209167</v>
+        <v>0.2408551482046828</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5332,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>-0.01947717375159197</v>
+        <v>-0.01907139929843371</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5340,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.2201265053817671</v>
+        <v>0.222066082826184</v>
       </c>
       <c r="C50">
-        <v>522.1359793915215</v>
+        <v>467.4214227942925</v>
       </c>
       <c r="D50">
-        <v>1259.627979391521</v>
+        <v>1245.767422794293</v>
       </c>
       <c r="E50">
-        <v>-1477.508</v>
+        <v>-1436.654</v>
       </c>
       <c r="F50">
-        <v>1960.992</v>
+        <v>2001.846</v>
       </c>
       <c r="G50">
         <v>1223.5</v>
@@ -5376,37 +5387,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M50">
-        <v>470.1630187881973</v>
+        <v>479.9580816796181</v>
       </c>
       <c r="N50">
-        <v>-479.129685454864</v>
+        <v>-488.9247483462848</v>
       </c>
       <c r="O50">
-        <v>-114.9911245091674</v>
+        <v>-117.3419396031084</v>
       </c>
       <c r="P50">
-        <v>-364.1385609456967</v>
+        <v>-371.5828087431765</v>
       </c>
       <c r="Q50">
-        <v>-985.3385609456967</v>
+        <v>-992.7828087431765</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2009923735452295</v>
+        <v>0.2040353612618026</v>
       </c>
       <c r="T50">
-        <v>3.190918542893244</v>
+        <v>3.253485573146052</v>
       </c>
       <c r="U50">
         <v>0.2397577444416894</v>
       </c>
       <c r="V50">
-        <v>-0.004577135831624088</v>
+        <v>-0.00448372489628482</v>
       </c>
       <c r="W50">
-        <v>0.2408551482046828</v>
+        <v>0.2408327522095197</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5414,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>-0.01907139929843371</v>
+        <v>-0.01868218706785352</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5422,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.222066082826184</v>
+        <v>0.2240056602706009</v>
       </c>
       <c r="C51">
-        <v>467.4214227942925</v>
+        <v>413.0085807767484</v>
       </c>
       <c r="D51">
-        <v>1245.767422794293</v>
+        <v>1232.208580776748</v>
       </c>
       <c r="E51">
-        <v>-1436.654</v>
+        <v>-1395.8</v>
       </c>
       <c r="F51">
-        <v>2001.846</v>
+        <v>2042.7</v>
       </c>
       <c r="G51">
         <v>1223.5</v>
@@ -5458,37 +5469,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M51">
-        <v>479.9580816796181</v>
+        <v>489.7531445710389</v>
       </c>
       <c r="N51">
-        <v>-488.9247483462848</v>
+        <v>-498.7198112377056</v>
       </c>
       <c r="O51">
-        <v>-117.3419396031084</v>
+        <v>-119.6927546970494</v>
       </c>
       <c r="P51">
-        <v>-371.5828087431765</v>
+        <v>-379.0270565406563</v>
       </c>
       <c r="Q51">
-        <v>-992.7828087431765</v>
+        <v>-1000.227056540656</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2040353612618026</v>
+        <v>0.2072000684870386</v>
       </c>
       <c r="T51">
-        <v>3.253485573146052</v>
+        <v>3.318555284608973</v>
       </c>
       <c r="U51">
         <v>0.2397577444416894</v>
       </c>
       <c r="V51">
-        <v>-0.00448372489628482</v>
+        <v>-0.004394050398359124</v>
       </c>
       <c r="W51">
-        <v>0.2408327522095197</v>
+        <v>0.2408112520541631</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5496,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>-0.01868218706785352</v>
+        <v>-0.01830854332649645</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5504,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2240056602706009</v>
+        <v>0.2259452377150178</v>
       </c>
       <c r="C52">
-        <v>413.0085807767484</v>
+        <v>358.8877078890378</v>
       </c>
       <c r="D52">
-        <v>1232.208580776748</v>
+        <v>1218.941707889038</v>
       </c>
       <c r="E52">
-        <v>-1395.8</v>
+        <v>-1354.946</v>
       </c>
       <c r="F52">
-        <v>2042.7</v>
+        <v>2083.554</v>
       </c>
       <c r="G52">
         <v>1223.5</v>
@@ -5540,37 +5551,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M52">
-        <v>489.7531445710389</v>
+        <v>499.5482074624597</v>
       </c>
       <c r="N52">
-        <v>-498.7198112377056</v>
+        <v>-508.5148741291264</v>
       </c>
       <c r="O52">
-        <v>-119.6927546970494</v>
+        <v>-122.0435697909903</v>
       </c>
       <c r="P52">
-        <v>-379.0270565406563</v>
+        <v>-386.4713043381361</v>
       </c>
       <c r="Q52">
-        <v>-1000.227056540656</v>
+        <v>-1007.671304338136</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2072000684870386</v>
+        <v>0.2104939474357538</v>
       </c>
       <c r="T52">
-        <v>3.318555284608973</v>
+        <v>3.386280902662218</v>
       </c>
       <c r="U52">
         <v>0.2397577444416894</v>
       </c>
       <c r="V52">
-        <v>-0.004394050398359124</v>
+        <v>-0.004307892547410905</v>
       </c>
       <c r="W52">
-        <v>0.2408112520541631</v>
+        <v>0.2407905950421538</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5578,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>-0.01830854332649645</v>
+        <v>-0.0179495522808788</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5586,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2259452377150178</v>
+        <v>0.2278848151594347</v>
       </c>
       <c r="C53">
-        <v>358.8877078890378</v>
+        <v>305.0494739175756</v>
       </c>
       <c r="D53">
-        <v>1218.941707889038</v>
+        <v>1205.957473917575</v>
       </c>
       <c r="E53">
-        <v>-1354.946</v>
+        <v>-1314.092</v>
       </c>
       <c r="F53">
-        <v>2083.554</v>
+        <v>2124.408</v>
       </c>
       <c r="G53">
         <v>1223.5</v>
@@ -5622,37 +5633,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M53">
-        <v>499.5482074624597</v>
+        <v>509.3432703538805</v>
       </c>
       <c r="N53">
-        <v>-508.5148741291264</v>
+        <v>-518.3099370205472</v>
       </c>
       <c r="O53">
-        <v>-122.0435697909903</v>
+        <v>-124.3943848849313</v>
       </c>
       <c r="P53">
-        <v>-386.4713043381361</v>
+        <v>-393.9155521356159</v>
       </c>
       <c r="Q53">
-        <v>-1007.671304338136</v>
+        <v>-1015.115552135616</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2104939474357538</v>
+        <v>0.2139250713406653</v>
       </c>
       <c r="T53">
-        <v>3.386280902662218</v>
+        <v>3.456828421467681</v>
       </c>
       <c r="U53">
         <v>0.2397577444416894</v>
       </c>
       <c r="V53">
-        <v>-0.004307892547410905</v>
+        <v>-0.004225048459960696</v>
       </c>
       <c r="W53">
-        <v>0.2407905950421538</v>
+        <v>0.2407707325306064</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5660,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>-0.0179495522808788</v>
+        <v>-0.01760436858316949</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5668,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2278848151594347</v>
+        <v>0.2298243926038516</v>
       </c>
       <c r="C54">
-        <v>305.0494739175756</v>
+        <v>251.4849420025384</v>
       </c>
       <c r="D54">
-        <v>1205.957473917575</v>
+        <v>1193.246942002539</v>
       </c>
       <c r="E54">
-        <v>-1314.092</v>
+        <v>-1273.238</v>
       </c>
       <c r="F54">
-        <v>2124.408</v>
+        <v>2165.262</v>
       </c>
       <c r="G54">
         <v>1223.5</v>
@@ -5704,37 +5715,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M54">
-        <v>509.3432703538805</v>
+        <v>519.1383332453013</v>
       </c>
       <c r="N54">
-        <v>-518.3099370205472</v>
+        <v>-528.104999911968</v>
       </c>
       <c r="O54">
-        <v>-124.3943848849313</v>
+        <v>-126.7451999788723</v>
       </c>
       <c r="P54">
-        <v>-393.9155521356159</v>
+        <v>-401.3597999330957</v>
       </c>
       <c r="Q54">
-        <v>-1015.115552135616</v>
+        <v>-1022.559799933096</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2139250713406653</v>
+        <v>0.2175022005181262</v>
       </c>
       <c r="T54">
-        <v>3.456828421467681</v>
+        <v>3.530377962349971</v>
       </c>
       <c r="U54">
         <v>0.2397577444416894</v>
       </c>
       <c r="V54">
-        <v>-0.004225048459960696</v>
+        <v>-0.004145330564489739</v>
       </c>
       <c r="W54">
-        <v>0.2407707325306064</v>
+        <v>0.2407516195477967</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5742,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>-0.01760436858316949</v>
+        <v>-0.01727221068537399</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5750,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2298243926038516</v>
+        <v>0.2317639700482685</v>
       </c>
       <c r="C55">
-        <v>251.4849420025384</v>
+        <v>198.1855481247526</v>
       </c>
       <c r="D55">
-        <v>1193.246942002539</v>
+        <v>1180.801548124753</v>
       </c>
       <c r="E55">
-        <v>-1273.238</v>
+        <v>-1232.384</v>
       </c>
       <c r="F55">
-        <v>2165.262</v>
+        <v>2206.116</v>
       </c>
       <c r="G55">
         <v>1223.5</v>
@@ -5786,37 +5797,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M55">
-        <v>519.1383332453013</v>
+        <v>528.9333961367221</v>
       </c>
       <c r="N55">
-        <v>-528.104999911968</v>
+        <v>-537.9000628033888</v>
       </c>
       <c r="O55">
-        <v>-126.7451999788723</v>
+        <v>-129.0960150728133</v>
       </c>
       <c r="P55">
-        <v>-401.3597999330957</v>
+        <v>-408.8040477305755</v>
       </c>
       <c r="Q55">
-        <v>-1022.559799933096</v>
+        <v>-1030.004047730576</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2175022005181262</v>
+        <v>0.221234857051129</v>
       </c>
       <c r="T55">
-        <v>3.530377962349971</v>
+        <v>3.607125309357579</v>
       </c>
       <c r="U55">
         <v>0.2397577444416894</v>
       </c>
       <c r="V55">
-        <v>-0.004145330564489739</v>
+        <v>-0.004068565183665856</v>
       </c>
       <c r="W55">
-        <v>0.2407516195477967</v>
+        <v>0.2407332144532391</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5824,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>-0.01727221068537399</v>
+        <v>-0.01695235493194103</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5832,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2317639700482685</v>
+        <v>0.2337035474926853</v>
       </c>
       <c r="C56">
-        <v>198.1855481247526</v>
+        <v>145.1430818630151</v>
       </c>
       <c r="D56">
-        <v>1180.801548124753</v>
+        <v>1168.613081863015</v>
       </c>
       <c r="E56">
-        <v>-1232.384</v>
+        <v>-1191.53</v>
       </c>
       <c r="F56">
-        <v>2206.116</v>
+        <v>2246.97</v>
       </c>
       <c r="G56">
         <v>1223.5</v>
@@ -5868,37 +5879,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M56">
-        <v>528.9333961367221</v>
+        <v>538.7284590281429</v>
       </c>
       <c r="N56">
-        <v>-537.9000628033888</v>
+        <v>-547.6951256948096</v>
       </c>
       <c r="O56">
-        <v>-129.0960150728133</v>
+        <v>-131.4468301667543</v>
       </c>
       <c r="P56">
-        <v>-408.8040477305755</v>
+        <v>-416.2482955280553</v>
       </c>
       <c r="Q56">
-        <v>-1030.004047730576</v>
+        <v>-1037.448295528055</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.221234857051129</v>
+        <v>0.225133409430043</v>
       </c>
       <c r="T56">
-        <v>3.607125309357579</v>
+        <v>3.687283649565526</v>
       </c>
       <c r="U56">
         <v>0.2397577444416894</v>
       </c>
       <c r="V56">
-        <v>-0.004068565183665856</v>
+        <v>-0.003994591271235567</v>
       </c>
       <c r="W56">
-        <v>0.2407332144532391</v>
+        <v>0.2407154786348473</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5906,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>-0.01695235493194103</v>
+        <v>-0.01664413029681477</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5914,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2337035474926853</v>
+        <v>0.2356431249371023</v>
       </c>
       <c r="C57">
-        <v>145.1430818630151</v>
+        <v>92.34966833101089</v>
       </c>
       <c r="D57">
-        <v>1168.613081863015</v>
+        <v>1156.673668331011</v>
       </c>
       <c r="E57">
-        <v>-1191.53</v>
+        <v>-1150.676</v>
       </c>
       <c r="F57">
-        <v>2246.97</v>
+        <v>2287.824</v>
       </c>
       <c r="G57">
         <v>1223.5</v>
@@ -5950,37 +5961,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M57">
-        <v>538.7284590281429</v>
+        <v>548.5235219195637</v>
       </c>
       <c r="N57">
-        <v>-547.6951256948096</v>
+        <v>-557.4901885862304</v>
       </c>
       <c r="O57">
-        <v>-131.4468301667543</v>
+        <v>-133.7976452606953</v>
       </c>
       <c r="P57">
-        <v>-416.2482955280553</v>
+        <v>-423.6925433255351</v>
       </c>
       <c r="Q57">
-        <v>-1037.448295528055</v>
+        <v>-1044.892543325535</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.225133409430043</v>
+        <v>0.2292091687352713</v>
       </c>
       <c r="T57">
-        <v>3.687283649565526</v>
+        <v>3.771085550692016</v>
       </c>
       <c r="U57">
         <v>0.2397577444416894</v>
       </c>
       <c r="V57">
-        <v>-0.003994591271235567</v>
+        <v>-0.003923259284249217</v>
       </c>
       <c r="W57">
-        <v>0.2407154786348473</v>
+        <v>0.2406983762385409</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5988,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>-0.01664413029681477</v>
+        <v>-0.01634691368437169</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5996,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2356431249371023</v>
+        <v>0.2375827023815192</v>
       </c>
       <c r="C58">
-        <v>92.34966833101089</v>
+        <v>39.7977512102957</v>
       </c>
       <c r="D58">
-        <v>1156.673668331011</v>
+        <v>1144.975751210296</v>
       </c>
       <c r="E58">
-        <v>-1150.676</v>
+        <v>-1109.822</v>
       </c>
       <c r="F58">
-        <v>2287.824</v>
+        <v>2328.678</v>
       </c>
       <c r="G58">
         <v>1223.5</v>
@@ -6032,37 +6043,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M58">
-        <v>548.5235219195637</v>
+        <v>558.3185848109845</v>
       </c>
       <c r="N58">
-        <v>-557.4901885862304</v>
+        <v>-567.2852514776512</v>
       </c>
       <c r="O58">
-        <v>-133.7976452606953</v>
+        <v>-136.1484603546363</v>
       </c>
       <c r="P58">
-        <v>-423.6925433255351</v>
+        <v>-431.1367911230149</v>
       </c>
       <c r="Q58">
-        <v>-1044.892543325535</v>
+        <v>-1052.336791123015</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2292091687352713</v>
+        <v>0.2334744982407427</v>
       </c>
       <c r="T58">
-        <v>3.771085550692016</v>
+        <v>3.858785214661598</v>
       </c>
       <c r="U58">
         <v>0.2397577444416894</v>
       </c>
       <c r="V58">
-        <v>-0.003923259284249217</v>
+        <v>-0.003854430173999231</v>
       </c>
       <c r="W58">
-        <v>0.2406983762385409</v>
+        <v>0.2406818739263155</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6070,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>-0.01634691368437169</v>
+        <v>-0.01606012572499682</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6078,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2375827023815192</v>
+        <v>0.239522279825936</v>
       </c>
       <c r="C59">
-        <v>39.7977512102957</v>
+        <v>-12.51992319745568</v>
       </c>
       <c r="D59">
-        <v>1144.975751210296</v>
+        <v>1133.512076802545</v>
       </c>
       <c r="E59">
-        <v>-1109.822</v>
+        <v>-1068.968</v>
       </c>
       <c r="F59">
-        <v>2328.678</v>
+        <v>2369.532</v>
       </c>
       <c r="G59">
         <v>1223.5</v>
@@ -6114,37 +6125,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M59">
-        <v>558.3185848109845</v>
+        <v>568.1136477024052</v>
       </c>
       <c r="N59">
-        <v>-567.2852514776512</v>
+        <v>-577.0803143690719</v>
       </c>
       <c r="O59">
-        <v>-136.1484603546363</v>
+        <v>-138.4992754485772</v>
       </c>
       <c r="P59">
-        <v>-431.1367911230149</v>
+        <v>-438.5810389204946</v>
       </c>
       <c r="Q59">
-        <v>-1052.336791123015</v>
+        <v>-1059.781038920495</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2334744982407427</v>
+        <v>0.2379429386750461</v>
       </c>
       <c r="T59">
-        <v>3.858785214661598</v>
+        <v>3.950661053105921</v>
       </c>
       <c r="U59">
         <v>0.2397577444416894</v>
       </c>
       <c r="V59">
-        <v>-0.003854430173999231</v>
+        <v>-0.003787974481344072</v>
       </c>
       <c r="W59">
-        <v>0.2406818739263155</v>
+        <v>0.2406659406593391</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6152,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>-0.01606012572499682</v>
+        <v>-0.0157832270056002</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6160,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.239522279825936</v>
+        <v>0.2414618572703529</v>
       </c>
       <c r="C60">
-        <v>-12.51992319745523</v>
+        <v>-64.61032096967165</v>
       </c>
       <c r="D60">
-        <v>1133.512076802545</v>
+        <v>1122.275679030328</v>
       </c>
       <c r="E60">
-        <v>-1068.968</v>
+        <v>-1028.114</v>
       </c>
       <c r="F60">
-        <v>2369.532</v>
+        <v>2410.386</v>
       </c>
       <c r="G60">
         <v>1223.5</v>
@@ -6196,37 +6207,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M60">
-        <v>568.113647702405</v>
+        <v>577.908710593826</v>
       </c>
       <c r="N60">
-        <v>-577.0803143690717</v>
+        <v>-586.8753772604927</v>
       </c>
       <c r="O60">
-        <v>-138.4992754485772</v>
+        <v>-140.8500905425182</v>
       </c>
       <c r="P60">
-        <v>-438.5810389204945</v>
+        <v>-446.0252867179744</v>
       </c>
       <c r="Q60">
-        <v>-1059.781038920495</v>
+        <v>-1067.225286717975</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.237942938675046</v>
+        <v>0.2426293518134618</v>
       </c>
       <c r="T60">
-        <v>3.95066105310592</v>
+        <v>4.047018639767041</v>
       </c>
       <c r="U60">
         <v>0.2397577444416894</v>
       </c>
       <c r="V60">
-        <v>-0.003787974481344073</v>
+        <v>-0.003723771524033156</v>
       </c>
       <c r="W60">
-        <v>0.2406659406593391</v>
+        <v>0.2406505475031078</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6234,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>-0.0157832270056002</v>
+        <v>-0.01551571468347146</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6242,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2414618572703529</v>
+        <v>0.2434014347147698</v>
       </c>
       <c r="C61">
-        <v>-64.61032096967165</v>
+        <v>-116.4801346787517</v>
       </c>
       <c r="D61">
-        <v>1122.275679030328</v>
+        <v>1111.259865321248</v>
       </c>
       <c r="E61">
-        <v>-1028.114</v>
+        <v>-987.2600000000002</v>
       </c>
       <c r="F61">
-        <v>2410.386</v>
+        <v>2451.24</v>
       </c>
       <c r="G61">
         <v>1223.5</v>
@@ -6278,37 +6289,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M61">
-        <v>577.908710593826</v>
+        <v>587.7037734852466</v>
       </c>
       <c r="N61">
-        <v>-586.8753772604927</v>
+        <v>-596.6704401519133</v>
       </c>
       <c r="O61">
-        <v>-140.8500905425182</v>
+        <v>-143.2009056364592</v>
       </c>
       <c r="P61">
-        <v>-446.0252867179744</v>
+        <v>-453.4695345154541</v>
       </c>
       <c r="Q61">
-        <v>-1067.225286717975</v>
+        <v>-1074.669534515454</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2426293518134618</v>
+        <v>0.2475500856087983</v>
       </c>
       <c r="T61">
-        <v>4.047018639767041</v>
+        <v>4.148194105761216</v>
       </c>
       <c r="U61">
         <v>0.2397577444416894</v>
       </c>
       <c r="V61">
-        <v>-0.003723771524033156</v>
+        <v>-0.00366170866529927</v>
       </c>
       <c r="W61">
-        <v>0.2406505475031078</v>
+        <v>0.2406356674520841</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6316,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>-0.01551571468347146</v>
+        <v>-0.01525711943874697</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6324,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2434014347147698</v>
+        <v>0.2453410121591867</v>
       </c>
       <c r="C62">
-        <v>-116.4801346787517</v>
+        <v>-168.1357966846726</v>
       </c>
       <c r="D62">
-        <v>1111.259865321248</v>
+        <v>1100.458203315327</v>
       </c>
       <c r="E62">
-        <v>-987.2600000000002</v>
+        <v>-946.4059999999999</v>
       </c>
       <c r="F62">
-        <v>2451.24</v>
+        <v>2492.094</v>
       </c>
       <c r="G62">
         <v>1223.5</v>
@@ -6360,37 +6371,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M62">
-        <v>587.7037734852466</v>
+        <v>597.4988363766676</v>
       </c>
       <c r="N62">
-        <v>-596.6704401519133</v>
+        <v>-606.4655030433343</v>
       </c>
       <c r="O62">
-        <v>-143.2009056364592</v>
+        <v>-145.5517207304002</v>
       </c>
       <c r="P62">
-        <v>-453.4695345154541</v>
+        <v>-460.913782312934</v>
       </c>
       <c r="Q62">
-        <v>-1074.669534515454</v>
+        <v>-1082.113782312934</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2475500856087983</v>
+        <v>0.2527231647269726</v>
       </c>
       <c r="T62">
-        <v>4.148194105761216</v>
+        <v>4.254558057190992</v>
       </c>
       <c r="U62">
         <v>0.2397577444416894</v>
       </c>
       <c r="V62">
-        <v>-0.00366170866529927</v>
+        <v>-0.003601680654392724</v>
       </c>
       <c r="W62">
-        <v>0.2406356674520841</v>
+        <v>0.2406212752715859</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6398,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>-0.01525711943874697</v>
+        <v>-0.01500700272663624</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6406,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2453410121591867</v>
+        <v>0.2472805896036036</v>
       </c>
       <c r="C63">
-        <v>-168.1357966846726</v>
+        <v>-219.5834916598228</v>
       </c>
       <c r="D63">
-        <v>1100.458203315327</v>
+        <v>1089.864508340177</v>
       </c>
       <c r="E63">
-        <v>-946.4059999999999</v>
+        <v>-905.5520000000001</v>
       </c>
       <c r="F63">
-        <v>2492.094</v>
+        <v>2532.948</v>
       </c>
       <c r="G63">
         <v>1223.5</v>
@@ -6442,37 +6453,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M63">
-        <v>597.4988363766676</v>
+        <v>607.2938992680882</v>
       </c>
       <c r="N63">
-        <v>-606.4655030433343</v>
+        <v>-616.2605659347549</v>
       </c>
       <c r="O63">
-        <v>-145.5517207304002</v>
+        <v>-147.9025358243412</v>
       </c>
       <c r="P63">
-        <v>-460.913782312934</v>
+        <v>-468.3580301104138</v>
       </c>
       <c r="Q63">
-        <v>-1082.113782312934</v>
+        <v>-1089.558030110414</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2527231647269726</v>
+        <v>0.2581685111671561</v>
       </c>
       <c r="T63">
-        <v>4.254558057190992</v>
+        <v>4.366520111327596</v>
       </c>
       <c r="U63">
         <v>0.2397577444416894</v>
       </c>
       <c r="V63">
-        <v>-0.003601680654392724</v>
+        <v>-0.003543589030934778</v>
       </c>
       <c r="W63">
-        <v>0.2406212752715859</v>
+        <v>0.2406073473549746</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6480,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>-0.01500700272663624</v>
+        <v>-0.01476495429556168</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6488,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2472805896036036</v>
+        <v>0.2492201670480205</v>
       </c>
       <c r="C64">
-        <v>-219.5834916598228</v>
+        <v>-270.8291683973021</v>
       </c>
       <c r="D64">
-        <v>1089.864508340177</v>
+        <v>1079.472831602698</v>
       </c>
       <c r="E64">
-        <v>-905.5520000000001</v>
+        <v>-864.6979999999999</v>
       </c>
       <c r="F64">
-        <v>2532.948</v>
+        <v>2573.802</v>
       </c>
       <c r="G64">
         <v>1223.5</v>
@@ -6524,37 +6535,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M64">
-        <v>607.2938992680882</v>
+        <v>617.0889621595092</v>
       </c>
       <c r="N64">
-        <v>-616.2605659347549</v>
+        <v>-626.0556288261758</v>
       </c>
       <c r="O64">
-        <v>-147.9025358243412</v>
+        <v>-150.2533509182822</v>
       </c>
       <c r="P64">
-        <v>-468.3580301104138</v>
+        <v>-475.8022779078937</v>
       </c>
       <c r="Q64">
-        <v>-1089.558030110414</v>
+        <v>-1097.002277907894</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2581685111671561</v>
+        <v>0.2639082006581603</v>
       </c>
       <c r="T64">
-        <v>4.366520111327596</v>
+        <v>4.484534168390504</v>
       </c>
       <c r="U64">
         <v>0.2397577444416894</v>
       </c>
       <c r="V64">
-        <v>-0.003543589030934778</v>
+        <v>-0.003487341585999304</v>
       </c>
       <c r="W64">
-        <v>0.2406073473549746</v>
+        <v>0.2405938615944463</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6562,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>-0.01476495429556168</v>
+        <v>-0.01453058994166367</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6570,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2492201670480205</v>
+        <v>0.2511597444924374</v>
       </c>
       <c r="C65">
-        <v>-270.8291683973021</v>
+        <v>-321.8785509500622</v>
       </c>
       <c r="D65">
-        <v>1079.472831602698</v>
+        <v>1069.277449049938</v>
       </c>
       <c r="E65">
-        <v>-864.6979999999999</v>
+        <v>-823.8440000000001</v>
       </c>
       <c r="F65">
-        <v>2573.802</v>
+        <v>2614.656</v>
       </c>
       <c r="G65">
         <v>1223.5</v>
@@ -6606,37 +6617,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M65">
-        <v>617.0889621595092</v>
+        <v>626.8840250509298</v>
       </c>
       <c r="N65">
-        <v>-626.0556288261758</v>
+        <v>-635.8506917175965</v>
       </c>
       <c r="O65">
-        <v>-150.2533509182822</v>
+        <v>-152.6041660122232</v>
       </c>
       <c r="P65">
-        <v>-475.8022779078937</v>
+        <v>-483.2465257053734</v>
       </c>
       <c r="Q65">
-        <v>-1097.002277907894</v>
+        <v>-1104.446525705373</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2639082006581603</v>
+        <v>0.2699667617875537</v>
       </c>
       <c r="T65">
-        <v>4.484534168390504</v>
+        <v>4.609104561956907</v>
       </c>
       <c r="U65">
         <v>0.2397577444416894</v>
       </c>
       <c r="V65">
-        <v>-0.003487341585999304</v>
+        <v>-0.003432851873718066</v>
       </c>
       <c r="W65">
-        <v>0.2405938615944463</v>
+        <v>0.2405807972639345</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6644,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>-0.01453058994166367</v>
+        <v>-0.01430354947382528</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6652,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2511597444924374</v>
+        <v>0.2530993219368543</v>
       </c>
       <c r="C66">
-        <v>-321.8785509500622</v>
+        <v>-372.7371491447093</v>
       </c>
       <c r="D66">
-        <v>1069.277449049938</v>
+        <v>1059.272850855291</v>
       </c>
       <c r="E66">
-        <v>-823.8440000000001</v>
+        <v>-782.9899999999998</v>
       </c>
       <c r="F66">
-        <v>2614.656</v>
+        <v>2655.51</v>
       </c>
       <c r="G66">
         <v>1223.5</v>
@@ -6688,37 +6699,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M66">
-        <v>626.8840250509298</v>
+        <v>636.6790879423506</v>
       </c>
       <c r="N66">
-        <v>-635.8506917175965</v>
+        <v>-645.6457546090173</v>
       </c>
       <c r="O66">
-        <v>-152.6041660122232</v>
+        <v>-154.9549811061642</v>
       </c>
       <c r="P66">
-        <v>-483.2465257053734</v>
+        <v>-490.6907735028532</v>
       </c>
       <c r="Q66">
-        <v>-1104.446525705373</v>
+        <v>-1111.890773502853</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2699667617875537</v>
+        <v>0.2763715264100552</v>
       </c>
       <c r="T66">
-        <v>4.609104561956907</v>
+        <v>4.740793263727105</v>
       </c>
       <c r="U66">
         <v>0.2397577444416894</v>
       </c>
       <c r="V66">
-        <v>-0.003432851873718066</v>
+        <v>-0.003380038767968557</v>
       </c>
       <c r="W66">
-        <v>0.2405807972639345</v>
+        <v>0.240568134912823</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6726,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>-0.01430354947382528</v>
+        <v>-0.0140834948665356</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6734,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2530993219368543</v>
+        <v>0.2550388993812712</v>
       </c>
       <c r="C67">
-        <v>-372.7371491447093</v>
+        <v>-423.4102685105504</v>
       </c>
       <c r="D67">
-        <v>1059.272850855291</v>
+        <v>1049.45373148945</v>
       </c>
       <c r="E67">
-        <v>-782.9899999999998</v>
+        <v>-742.136</v>
       </c>
       <c r="F67">
-        <v>2655.51</v>
+        <v>2696.364</v>
       </c>
       <c r="G67">
         <v>1223.5</v>
@@ -6770,37 +6781,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M67">
-        <v>636.6790879423506</v>
+        <v>646.4741508337714</v>
       </c>
       <c r="N67">
-        <v>-645.6457546090173</v>
+        <v>-655.4408175004381</v>
       </c>
       <c r="O67">
-        <v>-154.9549811061642</v>
+        <v>-157.3057962001051</v>
       </c>
       <c r="P67">
-        <v>-490.6907735028532</v>
+        <v>-498.135021300333</v>
       </c>
       <c r="Q67">
-        <v>-1111.890773502853</v>
+        <v>-1119.335021300333</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2763715264100552</v>
+        <v>0.2831530418927039</v>
       </c>
       <c r="T67">
-        <v>4.740793263727105</v>
+        <v>4.880228359719078</v>
       </c>
       <c r="U67">
         <v>0.2397577444416894</v>
       </c>
       <c r="V67">
-        <v>-0.003380038767968557</v>
+        <v>-0.003328826059362972</v>
       </c>
       <c r="W67">
-        <v>0.240568134912823</v>
+        <v>0.240555856269321</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6808,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>-0.0140834948665356</v>
+        <v>-0.01387010858067894</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6816,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2550388993812712</v>
+        <v>0.2569784768256881</v>
       </c>
       <c r="C68">
-        <v>-423.4102685105504</v>
+        <v>-473.9030196614854</v>
       </c>
       <c r="D68">
-        <v>1049.45373148945</v>
+        <v>1039.814980338515</v>
       </c>
       <c r="E68">
-        <v>-742.136</v>
+        <v>-701.2819999999997</v>
       </c>
       <c r="F68">
-        <v>2696.364</v>
+        <v>2737.218</v>
       </c>
       <c r="G68">
         <v>1223.5</v>
@@ -6852,37 +6863,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M68">
-        <v>646.4741508337714</v>
+        <v>656.2692137251922</v>
       </c>
       <c r="N68">
-        <v>-655.4408175004381</v>
+        <v>-665.2358803918589</v>
       </c>
       <c r="O68">
-        <v>-157.3057962001051</v>
+        <v>-159.6566112940461</v>
       </c>
       <c r="P68">
-        <v>-498.135021300333</v>
+        <v>-505.5792690978128</v>
       </c>
       <c r="Q68">
-        <v>-1119.335021300333</v>
+        <v>-1126.779269097813</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2831530418927039</v>
+        <v>0.290345558313695</v>
       </c>
       <c r="T68">
-        <v>4.880228359719078</v>
+        <v>5.028114067589355</v>
       </c>
       <c r="U68">
         <v>0.2397577444416894</v>
       </c>
       <c r="V68">
-        <v>-0.003328826059362972</v>
+        <v>-0.003279142088327704</v>
       </c>
       <c r="W68">
-        <v>0.240555856269321</v>
+        <v>0.2405439441524907</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6890,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>-0.01387010858067894</v>
+        <v>-0.01366309203469873</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6898,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2569784768256881</v>
+        <v>0.258918054270105</v>
       </c>
       <c r="C69">
-        <v>-473.9030196614854</v>
+        <v>-524.2203271655749</v>
       </c>
       <c r="D69">
-        <v>1039.814980338515</v>
+        <v>1030.351672834425</v>
       </c>
       <c r="E69">
-        <v>-701.2819999999997</v>
+        <v>-660.4279999999999</v>
       </c>
       <c r="F69">
-        <v>2737.218</v>
+        <v>2778.072</v>
       </c>
       <c r="G69">
         <v>1223.5</v>
@@ -6934,37 +6945,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M69">
-        <v>656.2692137251922</v>
+        <v>666.064276616613</v>
       </c>
       <c r="N69">
-        <v>-665.2358803918589</v>
+        <v>-675.0309432832797</v>
       </c>
       <c r="O69">
-        <v>-159.6566112940461</v>
+        <v>-162.0074263879871</v>
       </c>
       <c r="P69">
-        <v>-505.5792690978128</v>
+        <v>-513.0235168952926</v>
       </c>
       <c r="Q69">
-        <v>-1126.779269097813</v>
+        <v>-1134.223516895293</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.290345558313695</v>
+        <v>0.297987607010998</v>
       </c>
       <c r="T69">
-        <v>5.028114067589355</v>
+        <v>5.185242632201522</v>
       </c>
       <c r="U69">
         <v>0.2397577444416894</v>
       </c>
       <c r="V69">
-        <v>-0.003279142088327704</v>
+        <v>-0.003230919410558179</v>
       </c>
       <c r="W69">
-        <v>0.2405439441524907</v>
+        <v>0.2405323823920377</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6972,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>-0.01366309203469873</v>
+        <v>-0.01346216421065916</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6980,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.258918054270105</v>
+        <v>0.2608576317145219</v>
       </c>
       <c r="C70">
-        <v>-524.2203271655749</v>
+        <v>-574.366937934672</v>
       </c>
       <c r="D70">
-        <v>1030.351672834425</v>
+        <v>1021.059062065328</v>
       </c>
       <c r="E70">
-        <v>-660.4279999999999</v>
+        <v>-619.5739999999996</v>
       </c>
       <c r="F70">
-        <v>2778.072</v>
+        <v>2818.926</v>
       </c>
       <c r="G70">
         <v>1223.5</v>
@@ -7016,37 +7027,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M70">
-        <v>666.064276616613</v>
+        <v>675.8593395080338</v>
       </c>
       <c r="N70">
-        <v>-675.0309432832797</v>
+        <v>-684.8260061747005</v>
       </c>
       <c r="O70">
-        <v>-162.0074263879871</v>
+        <v>-164.3582414819281</v>
       </c>
       <c r="P70">
-        <v>-513.0235168952926</v>
+        <v>-520.4677646927723</v>
       </c>
       <c r="Q70">
-        <v>-1134.223516895293</v>
+        <v>-1141.667764692772</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.297987607010998</v>
+        <v>0.3061226911081269</v>
       </c>
       <c r="T70">
-        <v>5.185242632201522</v>
+        <v>5.352508523562861</v>
       </c>
       <c r="U70">
         <v>0.2397577444416894</v>
       </c>
       <c r="V70">
-        <v>-0.003230919410558179</v>
+        <v>-0.003184094491564582</v>
       </c>
       <c r="W70">
-        <v>0.2405323823920377</v>
+        <v>0.2405211557550762</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7054,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>-0.01346216421065916</v>
+        <v>-0.01326706038151904</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7062,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2608576317145219</v>
+        <v>0.2627972091589388</v>
       </c>
       <c r="C71">
-        <v>-574.366937934672</v>
+        <v>-624.3474291641</v>
       </c>
       <c r="D71">
-        <v>1021.059062065328</v>
+        <v>1011.9325708359</v>
       </c>
       <c r="E71">
-        <v>-619.5739999999996</v>
+        <v>-578.7199999999998</v>
       </c>
       <c r="F71">
-        <v>2818.926</v>
+        <v>2859.78</v>
       </c>
       <c r="G71">
         <v>1223.5</v>
@@ -7098,37 +7109,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M71">
-        <v>675.8593395080338</v>
+        <v>685.6544023994545</v>
       </c>
       <c r="N71">
-        <v>-684.8260061747005</v>
+        <v>-694.6210690661212</v>
       </c>
       <c r="O71">
-        <v>-164.3582414819281</v>
+        <v>-166.7090565758691</v>
       </c>
       <c r="P71">
-        <v>-520.4677646927723</v>
+        <v>-527.9120124902521</v>
       </c>
       <c r="Q71">
-        <v>-1141.667764692772</v>
+        <v>-1149.112012490252</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3061226911081269</v>
+        <v>0.3148001141450645</v>
       </c>
       <c r="T71">
-        <v>5.352508523562861</v>
+        <v>5.530925474348289</v>
       </c>
       <c r="U71">
         <v>0.2397577444416894</v>
       </c>
       <c r="V71">
-        <v>-0.003184094491564582</v>
+        <v>-0.003138607427399374</v>
       </c>
       <c r="W71">
-        <v>0.2405211557550762</v>
+        <v>0.2405102498791706</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7136,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>-0.01326706038151904</v>
+        <v>-0.01307753094749731</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7144,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2627972091589388</v>
+        <v>0.2647367866033556</v>
       </c>
       <c r="C72">
-        <v>-624.3474291641</v>
+        <v>-674.1662158503136</v>
       </c>
       <c r="D72">
-        <v>1011.9325708359</v>
+        <v>1002.967784149687</v>
       </c>
       <c r="E72">
-        <v>-578.7199999999998</v>
+        <v>-537.8659999999995</v>
       </c>
       <c r="F72">
-        <v>2859.78</v>
+        <v>2900.634</v>
       </c>
       <c r="G72">
         <v>1223.5</v>
@@ -7180,37 +7191,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M72">
-        <v>685.6544023994545</v>
+        <v>695.4494652908754</v>
       </c>
       <c r="N72">
-        <v>-694.6210690661212</v>
+        <v>-704.4161319575421</v>
       </c>
       <c r="O72">
-        <v>-166.7090565758691</v>
+        <v>-169.0598716698101</v>
       </c>
       <c r="P72">
-        <v>-527.9120124902521</v>
+        <v>-535.3562602877321</v>
       </c>
       <c r="Q72">
-        <v>-1149.112012490252</v>
+        <v>-1156.556260287732</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3148001141450645</v>
+        <v>0.3240759801500668</v>
       </c>
       <c r="T72">
-        <v>5.530925474348289</v>
+        <v>5.721647042429266</v>
       </c>
       <c r="U72">
         <v>0.2397577444416894</v>
       </c>
       <c r="V72">
-        <v>-0.003138607427399374</v>
+        <v>-0.003094401688985298</v>
       </c>
       <c r="W72">
-        <v>0.2405102498791706</v>
+        <v>0.2404996512110371</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7218,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>-0.01307753094749731</v>
+        <v>-0.01289334037077206</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7226,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2647367866033556</v>
+        <v>0.2666763640477726</v>
       </c>
       <c r="C73">
-        <v>-674.1662158503132</v>
+        <v>-723.827557912467</v>
       </c>
       <c r="D73">
-        <v>1002.967784149687</v>
+        <v>994.1604420875331</v>
       </c>
       <c r="E73">
-        <v>-537.866</v>
+        <v>-497.0120000000002</v>
       </c>
       <c r="F73">
-        <v>2900.634</v>
+        <v>2941.488</v>
       </c>
       <c r="G73">
         <v>1223.5</v>
@@ -7262,37 +7273,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M73">
-        <v>695.4494652908753</v>
+        <v>705.244528182296</v>
       </c>
       <c r="N73">
-        <v>-704.416131957542</v>
+        <v>-714.2111948489627</v>
       </c>
       <c r="O73">
-        <v>-169.0598716698101</v>
+        <v>-171.410686763751</v>
       </c>
       <c r="P73">
-        <v>-535.356260287732</v>
+        <v>-542.8005080852116</v>
       </c>
       <c r="Q73">
-        <v>-1156.556260287732</v>
+        <v>-1164.000508085212</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3240759801500666</v>
+        <v>0.334014408012569</v>
       </c>
       <c r="T73">
-        <v>5.721647042429264</v>
+        <v>5.925991579658881</v>
       </c>
       <c r="U73">
         <v>0.2397577444416894</v>
       </c>
       <c r="V73">
-        <v>-0.003094401688985299</v>
+        <v>-0.003051423887749392</v>
       </c>
       <c r="W73">
-        <v>0.2404996512110371</v>
+        <v>0.2404893469503517</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7300,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>-0.01289334037077206</v>
+        <v>-0.01271426619895588</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7308,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2666763640477726</v>
+        <v>0.2686159414921894</v>
       </c>
       <c r="C74">
-        <v>-723.827557912467</v>
+        <v>-773.3355669420321</v>
       </c>
       <c r="D74">
-        <v>994.1604420875331</v>
+        <v>985.5064330579678</v>
       </c>
       <c r="E74">
-        <v>-497.0120000000002</v>
+        <v>-456.1579999999999</v>
       </c>
       <c r="F74">
-        <v>2941.488</v>
+        <v>2982.342</v>
       </c>
       <c r="G74">
         <v>1223.5</v>
@@ -7344,37 +7355,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M74">
-        <v>705.244528182296</v>
+        <v>715.0395910737169</v>
       </c>
       <c r="N74">
-        <v>-714.2111948489627</v>
+        <v>-724.0062577403836</v>
       </c>
       <c r="O74">
-        <v>-171.410686763751</v>
+        <v>-173.7615018576921</v>
       </c>
       <c r="P74">
-        <v>-542.8005080852116</v>
+        <v>-550.2447558826916</v>
       </c>
       <c r="Q74">
-        <v>-1164.000508085212</v>
+        <v>-1171.444755882692</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.334014408012569</v>
+        <v>0.3446890157167382</v>
       </c>
       <c r="T74">
-        <v>5.925991579658881</v>
+        <v>6.145472749275876</v>
       </c>
       <c r="U74">
         <v>0.2397577444416894</v>
       </c>
       <c r="V74">
-        <v>-0.003051423887749392</v>
+        <v>-0.003009623560519948</v>
       </c>
       <c r="W74">
-        <v>0.2404893469503517</v>
+        <v>0.2404793249981782</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7382,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>-0.01271426619895588</v>
+        <v>-0.01254009816883306</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7390,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2686159414921894</v>
+        <v>0.2705555189366063</v>
       </c>
       <c r="C75">
-        <v>-773.3355669420321</v>
+        <v>-822.6942126029298</v>
       </c>
       <c r="D75">
-        <v>985.5064330579678</v>
+        <v>977.0017873970703</v>
       </c>
       <c r="E75">
-        <v>-456.1579999999999</v>
+        <v>-415.3040000000001</v>
       </c>
       <c r="F75">
-        <v>2982.342</v>
+        <v>3023.196</v>
       </c>
       <c r="G75">
         <v>1223.5</v>
@@ -7426,37 +7437,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M75">
-        <v>715.0395910737169</v>
+        <v>724.8346539651376</v>
       </c>
       <c r="N75">
-        <v>-724.0062577403836</v>
+        <v>-733.8013206318043</v>
       </c>
       <c r="O75">
-        <v>-173.7615018576921</v>
+        <v>-176.112316951633</v>
       </c>
       <c r="P75">
-        <v>-550.2447558826916</v>
+        <v>-557.6890036801713</v>
       </c>
       <c r="Q75">
-        <v>-1171.444755882692</v>
+        <v>-1178.889003680171</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3446890157167382</v>
+        <v>0.3561847470904589</v>
       </c>
       <c r="T75">
-        <v>6.145472749275876</v>
+        <v>6.381837085786486</v>
       </c>
       <c r="U75">
         <v>0.2397577444416894</v>
       </c>
       <c r="V75">
-        <v>-0.003009623560519948</v>
+        <v>-0.002968952971864273</v>
       </c>
       <c r="W75">
-        <v>0.2404793249981782</v>
+        <v>0.240469573909577</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7464,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>-0.01254009816883306</v>
+        <v>-0.01237063738276789</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7472,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2705555189366063</v>
+        <v>0.2724950963810232</v>
       </c>
       <c r="C76">
-        <v>-822.6942126029298</v>
+        <v>-871.9073287031088</v>
       </c>
       <c r="D76">
-        <v>977.0017873970703</v>
+        <v>968.6426712968912</v>
       </c>
       <c r="E76">
-        <v>-415.3040000000001</v>
+        <v>-374.4499999999998</v>
       </c>
       <c r="F76">
-        <v>3023.196</v>
+        <v>3064.05</v>
       </c>
       <c r="G76">
         <v>1223.5</v>
@@ -7508,37 +7519,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M76">
-        <v>724.8346539651376</v>
+        <v>734.6297168565585</v>
       </c>
       <c r="N76">
-        <v>-733.8013206318043</v>
+        <v>-743.5963835232252</v>
       </c>
       <c r="O76">
-        <v>-176.112316951633</v>
+        <v>-178.463132045574</v>
       </c>
       <c r="P76">
-        <v>-557.6890036801713</v>
+        <v>-565.1332514776511</v>
       </c>
       <c r="Q76">
-        <v>-1178.889003680171</v>
+        <v>-1186.333251477651</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3561847470904589</v>
+        <v>0.3686001369740773</v>
       </c>
       <c r="T76">
-        <v>6.381837085786486</v>
+        <v>6.637110569217947</v>
       </c>
       <c r="U76">
         <v>0.2397577444416894</v>
       </c>
       <c r="V76">
-        <v>-0.002968952971864273</v>
+        <v>-0.002929366932239416</v>
       </c>
       <c r="W76">
-        <v>0.240469573909577</v>
+        <v>0.2404600828500052</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7546,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>-0.01237063738276789</v>
+        <v>-0.01220569555099749</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7554,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2724950963810232</v>
+        <v>0.2744346738254401</v>
       </c>
       <c r="C77">
-        <v>-871.9073287031088</v>
+        <v>-920.9786189570864</v>
       </c>
       <c r="D77">
-        <v>968.6426712968912</v>
+        <v>960.4253810429135</v>
       </c>
       <c r="E77">
-        <v>-374.4499999999998</v>
+        <v>-333.596</v>
       </c>
       <c r="F77">
-        <v>3064.05</v>
+        <v>3104.904</v>
       </c>
       <c r="G77">
         <v>1223.5</v>
@@ -7590,37 +7601,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M77">
-        <v>734.6297168565585</v>
+        <v>744.4247797479792</v>
       </c>
       <c r="N77">
-        <v>-743.5963835232252</v>
+        <v>-753.3914464146459</v>
       </c>
       <c r="O77">
-        <v>-178.463132045574</v>
+        <v>-180.813947139515</v>
       </c>
       <c r="P77">
-        <v>-565.1332514776511</v>
+        <v>-572.5774992751309</v>
       </c>
       <c r="Q77">
-        <v>-1186.333251477651</v>
+        <v>-1193.777499275131</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3686001369740773</v>
+        <v>0.3820501426813305</v>
       </c>
       <c r="T77">
-        <v>6.637110569217947</v>
+        <v>6.913656842935361</v>
       </c>
       <c r="U77">
         <v>0.2397577444416894</v>
       </c>
       <c r="V77">
-        <v>-0.002929366932239416</v>
+        <v>-0.002890822630499423</v>
       </c>
       <c r="W77">
-        <v>0.2404600828500052</v>
+        <v>0.2404508415551589</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7628,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>-0.01220569555099749</v>
+        <v>-0.01204509429374756</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7636,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2744346738254401</v>
+        <v>0.276374251269857</v>
       </c>
       <c r="C78">
-        <v>-920.9786189570864</v>
+        <v>-969.9116624576391</v>
       </c>
       <c r="D78">
-        <v>960.4253810429135</v>
+        <v>952.3463375423613</v>
       </c>
       <c r="E78">
-        <v>-333.596</v>
+        <v>-292.7419999999997</v>
       </c>
       <c r="F78">
-        <v>3104.904</v>
+        <v>3145.758</v>
       </c>
       <c r="G78">
         <v>1223.5</v>
@@ -7672,37 +7683,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M78">
-        <v>744.4247797479792</v>
+        <v>754.2198426394</v>
       </c>
       <c r="N78">
-        <v>-753.3914464146459</v>
+        <v>-763.1865093060667</v>
       </c>
       <c r="O78">
-        <v>-180.813947139515</v>
+        <v>-183.164762233456</v>
       </c>
       <c r="P78">
-        <v>-572.5774992751309</v>
+        <v>-580.0217470726107</v>
       </c>
       <c r="Q78">
-        <v>-1193.777499275131</v>
+        <v>-1201.221747072611</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3820501426813305</v>
+        <v>0.3966697141022579</v>
       </c>
       <c r="T78">
-        <v>6.913656842935361</v>
+        <v>7.214250618715159</v>
       </c>
       <c r="U78">
         <v>0.2397577444416894</v>
       </c>
       <c r="V78">
-        <v>-0.002890822630499423</v>
+        <v>-0.002853279479453976</v>
       </c>
       <c r="W78">
-        <v>0.2404508415551589</v>
+        <v>0.2404418402939451</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7710,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>-0.01204509429374756</v>
+        <v>-0.01188866449772497</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7718,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.276374251269857</v>
+        <v>0.2783138287142739</v>
       </c>
       <c r="C79">
-        <v>-969.9116624576391</v>
+        <v>-1018.709918873631</v>
       </c>
       <c r="D79">
-        <v>952.3463375423613</v>
+        <v>944.4020811263694</v>
       </c>
       <c r="E79">
-        <v>-292.7419999999997</v>
+        <v>-251.8879999999999</v>
       </c>
       <c r="F79">
-        <v>3145.758</v>
+        <v>3186.612</v>
       </c>
       <c r="G79">
         <v>1223.5</v>
@@ -7754,37 +7765,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M79">
-        <v>754.2198426394</v>
+        <v>764.0149055308208</v>
       </c>
       <c r="N79">
-        <v>-763.1865093060667</v>
+        <v>-772.9815721974875</v>
       </c>
       <c r="O79">
-        <v>-183.164762233456</v>
+        <v>-185.515577327397</v>
       </c>
       <c r="P79">
-        <v>-580.0217470726107</v>
+        <v>-587.4659948700905</v>
       </c>
       <c r="Q79">
-        <v>-1201.221747072611</v>
+        <v>-1208.665994870091</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3966697141022579</v>
+        <v>0.4126183374705425</v>
       </c>
       <c r="T79">
-        <v>7.214250618715159</v>
+        <v>7.542171101384032</v>
       </c>
       <c r="U79">
         <v>0.2397577444416894</v>
       </c>
       <c r="V79">
-        <v>-0.002853279479453976</v>
+        <v>-0.00281669897330713</v>
       </c>
       <c r="W79">
-        <v>0.2404418402939451</v>
+        <v>0.2404330698343007</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7792,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>-0.01188866449772497</v>
+        <v>-0.01173624572211307</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7800,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2783138287142739</v>
+        <v>0.2802534061586908</v>
       </c>
       <c r="C80">
-        <v>-1018.709918873631</v>
+        <v>-1067.376733389848</v>
       </c>
       <c r="D80">
-        <v>944.4020811263694</v>
+        <v>936.5892666101528</v>
       </c>
       <c r="E80">
-        <v>-251.8879999999999</v>
+        <v>-211.0339999999997</v>
       </c>
       <c r="F80">
-        <v>3186.612</v>
+        <v>3227.466</v>
       </c>
       <c r="G80">
         <v>1223.5</v>
@@ -7836,37 +7847,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M80">
-        <v>764.0149055308208</v>
+        <v>773.8099684222416</v>
       </c>
       <c r="N80">
-        <v>-772.9815721974875</v>
+        <v>-782.7766350889083</v>
       </c>
       <c r="O80">
-        <v>-185.515577327397</v>
+        <v>-187.866392421338</v>
       </c>
       <c r="P80">
-        <v>-587.4659948700905</v>
+        <v>-594.9102426675703</v>
       </c>
       <c r="Q80">
-        <v>-1208.665994870091</v>
+        <v>-1216.11024266757</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4126183374705425</v>
+        <v>0.4300858773500922</v>
       </c>
       <c r="T80">
-        <v>7.542171101384032</v>
+        <v>7.901322106211844</v>
       </c>
       <c r="U80">
         <v>0.2397577444416894</v>
       </c>
       <c r="V80">
-        <v>-0.00281669897330713</v>
+        <v>-0.002781044555923496</v>
       </c>
       <c r="W80">
-        <v>0.2404330698343007</v>
+        <v>0.2404245214116095</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7874,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>-0.01173624572211307</v>
+        <v>-0.01158768564968127</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7882,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2802534061586908</v>
+        <v>0.2821929836031077</v>
       </c>
       <c r="C81">
-        <v>-1067.376733389848</v>
+        <v>-1115.915341403637</v>
       </c>
       <c r="D81">
-        <v>936.5892666101528</v>
+        <v>928.9046585963631</v>
       </c>
       <c r="E81">
-        <v>-211.0339999999997</v>
+        <v>-170.1799999999998</v>
       </c>
       <c r="F81">
-        <v>3227.466</v>
+        <v>3268.32</v>
       </c>
       <c r="G81">
         <v>1223.5</v>
@@ -7918,37 +7929,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M81">
-        <v>773.8099684222416</v>
+        <v>783.6050313136624</v>
       </c>
       <c r="N81">
-        <v>-782.7766350889083</v>
+        <v>-792.5716979803291</v>
       </c>
       <c r="O81">
-        <v>-187.866392421338</v>
+        <v>-190.217207515279</v>
       </c>
       <c r="P81">
-        <v>-594.9102426675703</v>
+        <v>-602.35449046505</v>
       </c>
       <c r="Q81">
-        <v>-1216.11024266757</v>
+        <v>-1223.55449046505</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4300858773500922</v>
+        <v>0.4493001712175967</v>
       </c>
       <c r="T81">
-        <v>7.901322106211844</v>
+        <v>8.296388211522435</v>
       </c>
       <c r="U81">
         <v>0.2397577444416894</v>
       </c>
       <c r="V81">
-        <v>-0.002781044555923496</v>
+        <v>-0.002746281498974452</v>
       </c>
       <c r="W81">
-        <v>0.2404245214116095</v>
+        <v>0.2404161866994855</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7956,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>-0.01158768564968127</v>
+        <v>-0.01144283957906023</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7964,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2821929836031077</v>
+        <v>0.2841325610475246</v>
       </c>
       <c r="C82">
-        <v>-1115.915341403637</v>
+        <v>-1164.328872992223</v>
       </c>
       <c r="D82">
-        <v>928.9046585963631</v>
+        <v>921.3451270077776</v>
       </c>
       <c r="E82">
-        <v>-170.1799999999998</v>
+        <v>-129.3259999999996</v>
       </c>
       <c r="F82">
-        <v>3268.32</v>
+        <v>3309.174</v>
       </c>
       <c r="G82">
         <v>1223.5</v>
@@ -8000,37 +8011,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M82">
-        <v>783.6050313136624</v>
+        <v>793.4000942050832</v>
       </c>
       <c r="N82">
-        <v>-792.5716979803291</v>
+        <v>-802.3667608717499</v>
       </c>
       <c r="O82">
-        <v>-190.217207515279</v>
+        <v>-192.56802260922</v>
       </c>
       <c r="P82">
-        <v>-602.35449046505</v>
+        <v>-609.7987382625299</v>
       </c>
       <c r="Q82">
-        <v>-1223.55449046505</v>
+        <v>-1230.99873826253</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4493001712175967</v>
+        <v>0.4705370223343124</v>
       </c>
       <c r="T82">
-        <v>8.296388211522435</v>
+        <v>8.733040222655196</v>
       </c>
       <c r="U82">
         <v>0.2397577444416894</v>
       </c>
       <c r="V82">
-        <v>-0.002746281498974452</v>
+        <v>-0.00271237678911057</v>
       </c>
       <c r="W82">
-        <v>0.2404161866994855</v>
+        <v>0.2404080577827226</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8038,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>-0.01144283957906023</v>
+        <v>-0.01130156995462728</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8046,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2841325610475246</v>
+        <v>0.2860721384919415</v>
       </c>
       <c r="C83">
-        <v>-1164.328872992223</v>
+        <v>-1212.620357163645</v>
       </c>
       <c r="D83">
-        <v>921.3451270077776</v>
+        <v>913.9076428363552</v>
       </c>
       <c r="E83">
-        <v>-129.3259999999996</v>
+        <v>-88.47199999999975</v>
       </c>
       <c r="F83">
-        <v>3309.174</v>
+        <v>3350.028</v>
       </c>
       <c r="G83">
         <v>1223.5</v>
@@ -8082,37 +8093,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M83">
-        <v>793.4000942050832</v>
+        <v>803.195157096504</v>
       </c>
       <c r="N83">
-        <v>-802.3667608717499</v>
+        <v>-812.1618237631707</v>
       </c>
       <c r="O83">
-        <v>-192.56802260922</v>
+        <v>-194.918837703161</v>
       </c>
       <c r="P83">
-        <v>-609.7987382625299</v>
+        <v>-617.2429860600097</v>
       </c>
       <c r="Q83">
-        <v>-1230.99873826253</v>
+        <v>-1238.44298606001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4705370223343124</v>
+        <v>0.4941335235751075</v>
       </c>
       <c r="T83">
-        <v>8.733040222655196</v>
+        <v>9.218209123913818</v>
       </c>
       <c r="U83">
         <v>0.2397577444416894</v>
       </c>
       <c r="V83">
-        <v>-0.00271237678911057</v>
+        <v>-0.002679299023389709</v>
       </c>
       <c r="W83">
-        <v>0.2404080577827226</v>
+        <v>0.2404001271322221</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8120,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>-0.01130156995462728</v>
+        <v>-0.0111637459307905</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8128,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2860721384919415</v>
+        <v>0.2880117159363583</v>
       </c>
       <c r="C84">
-        <v>-1212.620357163645</v>
+        <v>-1260.79272590346</v>
       </c>
       <c r="D84">
-        <v>913.9076428363552</v>
+        <v>906.5892740965401</v>
       </c>
       <c r="E84">
-        <v>-88.47199999999975</v>
+        <v>-47.61799999999948</v>
       </c>
       <c r="F84">
-        <v>3350.028</v>
+        <v>3390.882000000001</v>
       </c>
       <c r="G84">
         <v>1223.5</v>
@@ -8164,37 +8175,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M84">
-        <v>803.195157096504</v>
+        <v>812.9902199879248</v>
       </c>
       <c r="N84">
-        <v>-812.1618237631707</v>
+        <v>-821.9568866545915</v>
       </c>
       <c r="O84">
-        <v>-194.918837703161</v>
+        <v>-197.2696527971019</v>
       </c>
       <c r="P84">
-        <v>-617.2429860600097</v>
+        <v>-624.6872338574896</v>
       </c>
       <c r="Q84">
-        <v>-1238.44298606001</v>
+        <v>-1245.88723385749</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4941335235751075</v>
+        <v>0.5205060837854079</v>
       </c>
       <c r="T84">
-        <v>9.218209123913818</v>
+        <v>9.760456719438158</v>
       </c>
       <c r="U84">
         <v>0.2397577444416894</v>
       </c>
       <c r="V84">
-        <v>-0.002679299023389709</v>
+        <v>-0.002647018312264532</v>
       </c>
       <c r="W84">
-        <v>0.2404001271322221</v>
+        <v>0.2403923875817338</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8202,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>-0.0111637459307905</v>
+        <v>-0.01102924296776897</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8210,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2880117159363583</v>
+        <v>0.2899512933807753</v>
       </c>
       <c r="C85">
-        <v>-1260.79272590346</v>
+        <v>-1308.848818028549</v>
       </c>
       <c r="D85">
-        <v>906.5892740965401</v>
+        <v>899.387181971451</v>
       </c>
       <c r="E85">
-        <v>-47.61799999999948</v>
+        <v>-6.763999999999669</v>
       </c>
       <c r="F85">
-        <v>3390.882000000001</v>
+        <v>3431.736</v>
       </c>
       <c r="G85">
         <v>1223.5</v>
@@ -8246,37 +8257,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M85">
-        <v>812.9902199879248</v>
+        <v>822.7852828793455</v>
       </c>
       <c r="N85">
-        <v>-821.9568866545915</v>
+        <v>-831.7519495460122</v>
       </c>
       <c r="O85">
-        <v>-197.2696527971019</v>
+        <v>-199.6204678910429</v>
       </c>
       <c r="P85">
-        <v>-624.6872338574896</v>
+        <v>-632.1314816549692</v>
       </c>
       <c r="Q85">
-        <v>-1245.88723385749</v>
+        <v>-1253.331481654969</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5205060837854079</v>
+        <v>0.5501752140219961</v>
       </c>
       <c r="T85">
-        <v>9.760456719438158</v>
+        <v>10.37048526440305</v>
       </c>
       <c r="U85">
         <v>0.2397577444416894</v>
       </c>
       <c r="V85">
-        <v>-0.002647018312264532</v>
+        <v>-0.002615506189499478</v>
       </c>
       <c r="W85">
-        <v>0.2403923875817338</v>
+        <v>0.2403848323062571</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8284,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>-0.01102924296776897</v>
+        <v>-0.01089794245624787</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8292,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2899512933807752</v>
+        <v>0.2918908708251922</v>
       </c>
       <c r="C86">
-        <v>-1308.848818028549</v>
+        <v>-1356.791382858687</v>
       </c>
       <c r="D86">
-        <v>899.3871819714512</v>
+        <v>892.298617141313</v>
       </c>
       <c r="E86">
-        <v>-6.764000000000124</v>
+        <v>34.09000000000015</v>
       </c>
       <c r="F86">
-        <v>3431.736</v>
+        <v>3472.59</v>
       </c>
       <c r="G86">
         <v>1223.5</v>
@@ -8328,37 +8339,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M86">
-        <v>822.7852828793453</v>
+        <v>832.5803457707663</v>
       </c>
       <c r="N86">
-        <v>-831.751949546012</v>
+        <v>-841.547012437433</v>
       </c>
       <c r="O86">
-        <v>-199.6204678910429</v>
+        <v>-201.9712829849839</v>
       </c>
       <c r="P86">
-        <v>-632.1314816549691</v>
+        <v>-639.5757294524491</v>
       </c>
       <c r="Q86">
-        <v>-1253.331481654969</v>
+        <v>-1260.775729452449</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5501752140219958</v>
+        <v>0.5838002282901288</v>
       </c>
       <c r="T86">
-        <v>10.37048526440304</v>
+        <v>11.06185094869658</v>
       </c>
       <c r="U86">
         <v>0.2397577444416894</v>
       </c>
       <c r="V86">
-        <v>-0.002615506189499479</v>
+        <v>-0.002584735528446543</v>
       </c>
       <c r="W86">
-        <v>0.2403848323062571</v>
+        <v>0.240377454801968</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8366,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>-0.01089794245624787</v>
+        <v>-0.01076973136852732</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8374,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2918908708251922</v>
+        <v>0.2938304482696091</v>
       </c>
       <c r="C87">
-        <v>-1356.791382858687</v>
+        <v>-1404.623083715843</v>
       </c>
       <c r="D87">
-        <v>892.298617141313</v>
+        <v>885.3209162841569</v>
       </c>
       <c r="E87">
-        <v>34.09000000000015</v>
+        <v>74.94399999999996</v>
       </c>
       <c r="F87">
-        <v>3472.59</v>
+        <v>3513.444</v>
       </c>
       <c r="G87">
         <v>1223.5</v>
@@ -8410,37 +8421,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M87">
-        <v>832.5803457707663</v>
+        <v>842.3754086621869</v>
       </c>
       <c r="N87">
-        <v>-841.547012437433</v>
+        <v>-851.3420753288536</v>
       </c>
       <c r="O87">
-        <v>-201.9712829849839</v>
+        <v>-204.3220980789249</v>
       </c>
       <c r="P87">
-        <v>-639.5757294524491</v>
+        <v>-647.0199772499288</v>
       </c>
       <c r="Q87">
-        <v>-1260.775729452449</v>
+        <v>-1268.219977249929</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5838002282901288</v>
+        <v>0.622228816025138</v>
       </c>
       <c r="T87">
-        <v>11.06185094869658</v>
+        <v>11.85198315931776</v>
       </c>
       <c r="U87">
         <v>0.2397577444416894</v>
       </c>
       <c r="V87">
-        <v>-0.002584735528446543</v>
+        <v>-0.002554680464162281</v>
       </c>
       <c r="W87">
-        <v>0.240377454801968</v>
+        <v>0.2403702488675462</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8448,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>-0.01076973136852732</v>
+        <v>-0.01064450193400956</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8456,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2938304482696091</v>
+        <v>0.2957700257140259</v>
       </c>
       <c r="C88">
-        <v>-1404.623083715843</v>
+        <v>-1452.346501260568</v>
       </c>
       <c r="D88">
-        <v>885.3209162841569</v>
+        <v>878.4514987394321</v>
       </c>
       <c r="E88">
-        <v>74.94399999999996</v>
+        <v>115.7980000000002</v>
       </c>
       <c r="F88">
-        <v>3513.444</v>
+        <v>3554.298</v>
       </c>
       <c r="G88">
         <v>1223.5</v>
@@ -8492,37 +8503,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M88">
-        <v>842.3754086621869</v>
+        <v>852.1704715536079</v>
       </c>
       <c r="N88">
-        <v>-851.3420753288536</v>
+        <v>-861.1371382202746</v>
       </c>
       <c r="O88">
-        <v>-204.3220980789249</v>
+        <v>-206.6729131728659</v>
       </c>
       <c r="P88">
-        <v>-647.0199772499288</v>
+        <v>-654.4642250474087</v>
       </c>
       <c r="Q88">
-        <v>-1268.219977249929</v>
+        <v>-1275.664225047409</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.622228816025138</v>
+        <v>0.6665694941809178</v>
       </c>
       <c r="T88">
-        <v>11.85198315931776</v>
+        <v>12.76367417157297</v>
       </c>
       <c r="U88">
         <v>0.2397577444416894</v>
       </c>
       <c r="V88">
-        <v>-0.002554680464162281</v>
+        <v>-0.002525316320896048</v>
       </c>
       <c r="W88">
-        <v>0.2403702488675462</v>
+        <v>0.2403632085867892</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8530,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>-0.01064450193400956</v>
+        <v>-0.0105221513370668</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8538,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2957700257140259</v>
+        <v>0.2977096031584429</v>
       </c>
       <c r="C89">
-        <v>-1452.346501260568</v>
+        <v>-1499.964136674251</v>
       </c>
       <c r="D89">
-        <v>878.4514987394321</v>
+        <v>871.6878633257493</v>
       </c>
       <c r="E89">
-        <v>115.7980000000002</v>
+        <v>156.652</v>
       </c>
       <c r="F89">
-        <v>3554.298</v>
+        <v>3595.152</v>
       </c>
       <c r="G89">
         <v>1223.5</v>
@@ -8574,37 +8585,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M89">
-        <v>852.1704715536079</v>
+        <v>861.9655344450285</v>
       </c>
       <c r="N89">
-        <v>-861.1371382202746</v>
+        <v>-870.9322011116952</v>
       </c>
       <c r="O89">
-        <v>-206.6729131728659</v>
+        <v>-209.0237282668068</v>
       </c>
       <c r="P89">
-        <v>-654.4642250474087</v>
+        <v>-661.9084728448884</v>
       </c>
       <c r="Q89">
-        <v>-1275.664225047409</v>
+        <v>-1283.108472844888</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6665694941809178</v>
+        <v>0.718300285362661</v>
       </c>
       <c r="T89">
-        <v>12.76367417157297</v>
+        <v>13.82731368587072</v>
       </c>
       <c r="U89">
         <v>0.2397577444416894</v>
       </c>
       <c r="V89">
-        <v>-0.002525316320896048</v>
+        <v>-0.002496619544522229</v>
       </c>
       <c r="W89">
-        <v>0.2403632085867892</v>
+        <v>0.2403563283124131</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8612,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>-0.0105221513370668</v>
+        <v>-0.01040258143550932</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8620,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2977096031584429</v>
+        <v>0.2996491806028597</v>
       </c>
       <c r="C90">
-        <v>-1499.964136674251</v>
+        <v>-1547.478414695489</v>
       </c>
       <c r="D90">
-        <v>871.6878633257493</v>
+        <v>865.0275853045111</v>
       </c>
       <c r="E90">
-        <v>156.652</v>
+        <v>197.5060000000003</v>
       </c>
       <c r="F90">
-        <v>3595.152</v>
+        <v>3636.006</v>
       </c>
       <c r="G90">
         <v>1223.5</v>
@@ -8656,37 +8667,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M90">
-        <v>861.9655344450285</v>
+        <v>871.7605973364493</v>
       </c>
       <c r="N90">
-        <v>-870.9322011116952</v>
+        <v>-880.727264003116</v>
       </c>
       <c r="O90">
-        <v>-209.0237282668068</v>
+        <v>-211.3745433607479</v>
       </c>
       <c r="P90">
-        <v>-661.9084728448884</v>
+        <v>-669.3527206423682</v>
       </c>
       <c r="Q90">
-        <v>-1283.108472844888</v>
+        <v>-1290.552720642368</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.718300285362661</v>
+        <v>0.7794366749410848</v>
       </c>
       <c r="T90">
-        <v>13.82731368587072</v>
+        <v>15.08434220276806</v>
       </c>
       <c r="U90">
         <v>0.2397577444416894</v>
       </c>
       <c r="V90">
-        <v>-0.002496619544522229</v>
+        <v>-0.002468567639527598</v>
       </c>
       <c r="W90">
-        <v>0.2403563283124131</v>
+        <v>0.2403496026509443</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8694,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>-0.01040258143550932</v>
+        <v>-0.01028569849803174</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8702,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2996491806028597</v>
+        <v>0.3015887580472766</v>
       </c>
       <c r="C91">
-        <v>-1547.478414695489</v>
+        <v>-1594.891686518314</v>
       </c>
       <c r="D91">
-        <v>865.0275853045111</v>
+        <v>858.4683134816858</v>
       </c>
       <c r="E91">
-        <v>197.5060000000003</v>
+        <v>238.3600000000001</v>
       </c>
       <c r="F91">
-        <v>3636.006</v>
+        <v>3676.86</v>
       </c>
       <c r="G91">
         <v>1223.5</v>
@@ -8738,37 +8749,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M91">
-        <v>871.7605973364493</v>
+        <v>881.5556602278701</v>
       </c>
       <c r="N91">
-        <v>-880.727264003116</v>
+        <v>-890.5223268945368</v>
       </c>
       <c r="O91">
-        <v>-211.3745433607479</v>
+        <v>-213.7253584546888</v>
       </c>
       <c r="P91">
-        <v>-669.3527206423682</v>
+        <v>-676.796968439848</v>
       </c>
       <c r="Q91">
-        <v>-1290.552720642368</v>
+        <v>-1297.996968439848</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7794366749410848</v>
+        <v>0.8528003424351934</v>
       </c>
       <c r="T91">
-        <v>15.08434220276806</v>
+        <v>16.59277642304487</v>
       </c>
       <c r="U91">
         <v>0.2397577444416894</v>
       </c>
       <c r="V91">
-        <v>-0.002468567639527598</v>
+        <v>-0.002441139110199513</v>
       </c>
       <c r="W91">
-        <v>0.2403496026509443</v>
+        <v>0.2403430264486192</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8776,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>-0.01028569849803174</v>
+        <v>-0.01017141295916457</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8784,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3015887580472766</v>
+        <v>0.3035283354916935</v>
       </c>
       <c r="C92">
-        <v>-1594.891686518314</v>
+        <v>-1642.206232559553</v>
       </c>
       <c r="D92">
-        <v>858.4683134816858</v>
+        <v>852.0077674404479</v>
       </c>
       <c r="E92">
-        <v>238.3600000000001</v>
+        <v>279.2140000000004</v>
       </c>
       <c r="F92">
-        <v>3676.86</v>
+        <v>3717.714</v>
       </c>
       <c r="G92">
         <v>1223.5</v>
@@ -8820,37 +8831,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M92">
-        <v>881.5556602278701</v>
+        <v>891.3507231192909</v>
       </c>
       <c r="N92">
-        <v>-890.5223268945368</v>
+        <v>-900.3173897859576</v>
       </c>
       <c r="O92">
-        <v>-213.7253584546888</v>
+        <v>-216.0761735486298</v>
       </c>
       <c r="P92">
-        <v>-676.796968439848</v>
+        <v>-684.2412162373278</v>
       </c>
       <c r="Q92">
-        <v>-1297.996968439848</v>
+        <v>-1305.441216237328</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.8528003424351934</v>
+        <v>0.9424670471502149</v>
       </c>
       <c r="T92">
-        <v>16.59277642304487</v>
+        <v>18.43641824782763</v>
       </c>
       <c r="U92">
         <v>0.2397577444416894</v>
       </c>
       <c r="V92">
-        <v>-0.002441139110199513</v>
+        <v>-0.002414313405691826</v>
       </c>
       <c r="W92">
-        <v>0.2403430264486192</v>
+        <v>0.2403365947782134</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8858,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>-0.01017141295916457</v>
+        <v>-0.01005963919038266</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8866,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3035283354916935</v>
+        <v>0.3054679129361104</v>
       </c>
       <c r="C93">
-        <v>-1642.206232559553</v>
+        <v>-1689.424265102156</v>
       </c>
       <c r="D93">
-        <v>852.0077674404479</v>
+        <v>845.6437348978437</v>
       </c>
       <c r="E93">
-        <v>279.2140000000004</v>
+        <v>320.0680000000002</v>
       </c>
       <c r="F93">
-        <v>3717.714</v>
+        <v>3758.568</v>
       </c>
       <c r="G93">
         <v>1223.5</v>
@@ -8902,37 +8913,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M93">
-        <v>891.3507231192909</v>
+        <v>901.1457860107117</v>
       </c>
       <c r="N93">
-        <v>-900.3173897859576</v>
+        <v>-910.1124526773784</v>
       </c>
       <c r="O93">
-        <v>-216.0761735486298</v>
+        <v>-218.4269886425708</v>
       </c>
       <c r="P93">
-        <v>-684.2412162373278</v>
+        <v>-691.6854640348076</v>
       </c>
       <c r="Q93">
-        <v>-1305.441216237328</v>
+        <v>-1312.885464034808</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9424670471502149</v>
+        <v>1.054550428043992</v>
       </c>
       <c r="T93">
-        <v>18.43641824782763</v>
+        <v>20.74097052880609</v>
       </c>
       <c r="U93">
         <v>0.2397577444416894</v>
       </c>
       <c r="V93">
-        <v>-0.002414313405691826</v>
+        <v>-0.002388070868673437</v>
       </c>
       <c r="W93">
-        <v>0.2403365947782134</v>
+        <v>0.2403303029267294</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8940,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>-0.01005963919038266</v>
+        <v>-0.009950295286139221</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8948,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3054679129361104</v>
+        <v>0.3074074903805273</v>
       </c>
       <c r="C94">
-        <v>-1689.424265102156</v>
+        <v>-1736.547930820958</v>
       </c>
       <c r="D94">
-        <v>845.6437348978437</v>
+        <v>839.3740691790426</v>
       </c>
       <c r="E94">
-        <v>320.0680000000002</v>
+        <v>360.9220000000005</v>
       </c>
       <c r="F94">
-        <v>3758.568</v>
+        <v>3799.422</v>
       </c>
       <c r="G94">
         <v>1223.5</v>
@@ -8984,37 +8995,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M94">
-        <v>901.1457860107117</v>
+        <v>910.9408489021325</v>
       </c>
       <c r="N94">
-        <v>-910.1124526773784</v>
+        <v>-919.9075155687992</v>
       </c>
       <c r="O94">
-        <v>-218.4269886425708</v>
+        <v>-220.7778037365118</v>
       </c>
       <c r="P94">
-        <v>-691.6854640348076</v>
+        <v>-699.1297118322874</v>
       </c>
       <c r="Q94">
-        <v>-1312.885464034808</v>
+        <v>-1320.329711832288</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.054550428043992</v>
+        <v>1.198657632050277</v>
       </c>
       <c r="T94">
-        <v>20.74097052880609</v>
+        <v>23.70396631863554</v>
       </c>
       <c r="U94">
         <v>0.2397577444416894</v>
       </c>
       <c r="V94">
-        <v>-0.002388070868673437</v>
+        <v>-0.002362392687289851</v>
       </c>
       <c r="W94">
-        <v>0.2403303029267294</v>
+        <v>0.2403241463838795</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9022,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>-0.009950295286139221</v>
+        <v>-0.009843302863707715</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9030,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3074074903805273</v>
+        <v>0.3093470678249443</v>
       </c>
       <c r="C95">
-        <v>-1736.547930820958</v>
+        <v>-1783.579313196881</v>
       </c>
       <c r="D95">
-        <v>839.3740691790426</v>
+        <v>833.1966868031191</v>
       </c>
       <c r="E95">
-        <v>360.9220000000005</v>
+        <v>401.7760000000003</v>
       </c>
       <c r="F95">
-        <v>3799.422</v>
+        <v>3840.276</v>
       </c>
       <c r="G95">
         <v>1223.5</v>
@@ -9066,37 +9077,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M95">
-        <v>910.9408489021325</v>
+        <v>920.7359117935533</v>
       </c>
       <c r="N95">
-        <v>-919.9075155687992</v>
+        <v>-929.70257846022</v>
       </c>
       <c r="O95">
-        <v>-220.7778037365118</v>
+        <v>-223.1286188304528</v>
       </c>
       <c r="P95">
-        <v>-699.1297118322874</v>
+        <v>-706.5739596297672</v>
       </c>
       <c r="Q95">
-        <v>-1320.329711832288</v>
+        <v>-1327.773959629767</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.198657632050277</v>
+        <v>1.390800570725323</v>
       </c>
       <c r="T95">
-        <v>23.70396631863554</v>
+        <v>27.65462737174147</v>
       </c>
       <c r="U95">
         <v>0.2397577444416894</v>
       </c>
       <c r="V95">
-        <v>-0.002362392687289851</v>
+        <v>-0.002337260850191023</v>
       </c>
       <c r="W95">
-        <v>0.2403241463838795</v>
+        <v>0.2403181208313031</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9104,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>-0.009843302863707715</v>
+        <v>-0.009738586875795985</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9112,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3093470678249443</v>
+        <v>0.3112866452693611</v>
       </c>
       <c r="C96">
-        <v>-1783.579313196881</v>
+        <v>-1830.520434825341</v>
       </c>
       <c r="D96">
-        <v>833.1966868031191</v>
+        <v>827.10956517466</v>
       </c>
       <c r="E96">
-        <v>401.7760000000003</v>
+        <v>442.6300000000006</v>
       </c>
       <c r="F96">
-        <v>3840.276</v>
+        <v>3881.130000000001</v>
       </c>
       <c r="G96">
         <v>1223.5</v>
@@ -9148,37 +9159,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M96">
-        <v>920.7359117935533</v>
+        <v>930.5309746849741</v>
       </c>
       <c r="N96">
-        <v>-929.70257846022</v>
+        <v>-939.4976413516408</v>
       </c>
       <c r="O96">
-        <v>-223.1286188304528</v>
+        <v>-225.4794339243938</v>
       </c>
       <c r="P96">
-        <v>-706.5739596297672</v>
+        <v>-714.018207427247</v>
       </c>
       <c r="Q96">
-        <v>-1327.773959629767</v>
+        <v>-1335.218207427247</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.390800570725323</v>
+        <v>1.659800684870389</v>
       </c>
       <c r="T96">
-        <v>27.65462737174147</v>
+        <v>33.18555284608978</v>
       </c>
       <c r="U96">
         <v>0.2397577444416894</v>
       </c>
       <c r="V96">
-        <v>-0.002337260850191023</v>
+        <v>-0.002312658104399538</v>
       </c>
       <c r="W96">
-        <v>0.2403181208313031</v>
+        <v>0.240312222132465</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9186,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>-0.009738586875795985</v>
+        <v>-0.009636075434998004</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9194,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3112866452693611</v>
+        <v>0.313226222713778</v>
       </c>
       <c r="C97">
-        <v>-1830.520434825341</v>
+        <v>-1877.373259624175</v>
       </c>
       <c r="D97">
-        <v>827.10956517466</v>
+        <v>821.1107403758249</v>
       </c>
       <c r="E97">
-        <v>442.6300000000006</v>
+        <v>483.4840000000004</v>
       </c>
       <c r="F97">
-        <v>3881.130000000001</v>
+        <v>3921.984</v>
       </c>
       <c r="G97">
         <v>1223.5</v>
@@ -9230,37 +9241,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M97">
-        <v>930.5309746849741</v>
+        <v>940.3260375763948</v>
       </c>
       <c r="N97">
-        <v>-939.4976413516408</v>
+        <v>-949.2927042430615</v>
       </c>
       <c r="O97">
-        <v>-225.4794339243938</v>
+        <v>-227.8302490183347</v>
       </c>
       <c r="P97">
-        <v>-714.018207427247</v>
+        <v>-721.4624552247268</v>
       </c>
       <c r="Q97">
-        <v>-1335.218207427247</v>
+        <v>-1342.662455224727</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.659800684870389</v>
+        <v>2.063300856087987</v>
       </c>
       <c r="T97">
-        <v>33.18555284608978</v>
+        <v>41.48194105761224</v>
       </c>
       <c r="U97">
         <v>0.2397577444416894</v>
       </c>
       <c r="V97">
-        <v>-0.002312658104399538</v>
+        <v>-0.002288567915812043</v>
       </c>
       <c r="W97">
-        <v>0.240312222132465</v>
+        <v>0.2403064463231861</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9268,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>-0.009636075434998004</v>
+        <v>-0.009535699649216856</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9276,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.313226222713778</v>
+        <v>0.3151658001581949</v>
       </c>
       <c r="C98">
-        <v>-1877.373259624175</v>
+        <v>-1924.139694946202</v>
       </c>
       <c r="D98">
-        <v>821.1107403758249</v>
+        <v>815.1983050537978</v>
       </c>
       <c r="E98">
-        <v>483.4839999999999</v>
+        <v>524.3380000000002</v>
       </c>
       <c r="F98">
-        <v>3921.984</v>
+        <v>3962.838</v>
       </c>
       <c r="G98">
         <v>1223.5</v>
@@ -9312,37 +9323,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M98">
-        <v>940.3260375763947</v>
+        <v>950.1211004678156</v>
       </c>
       <c r="N98">
-        <v>-949.2927042430614</v>
+        <v>-959.0877671344823</v>
       </c>
       <c r="O98">
-        <v>-227.8302490183347</v>
+        <v>-230.1810641122757</v>
       </c>
       <c r="P98">
-        <v>-721.4624552247267</v>
+        <v>-728.9067030222066</v>
       </c>
       <c r="Q98">
-        <v>-1342.662455224727</v>
+        <v>-1350.106703022207</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.063300856087981</v>
+        <v>2.735801141450642</v>
       </c>
       <c r="T98">
-        <v>41.48194105761213</v>
+        <v>55.30925474348284</v>
       </c>
       <c r="U98">
         <v>0.2397577444416894</v>
       </c>
       <c r="V98">
-        <v>-0.002288567915812044</v>
+        <v>-0.002264974432143878</v>
       </c>
       <c r="W98">
-        <v>0.2403064463231861</v>
+        <v>0.2403007896027583</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9350,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>-0.009535699649216856</v>
+        <v>-0.009437393467266242</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9358,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3151658001581949</v>
+        <v>0.3171053776026118</v>
       </c>
       <c r="C99">
-        <v>-1924.139694946202</v>
+        <v>-1970.821593601146</v>
       </c>
       <c r="D99">
-        <v>815.1983050537978</v>
+        <v>809.370406398854</v>
       </c>
       <c r="E99">
-        <v>524.3380000000002</v>
+        <v>565.192</v>
       </c>
       <c r="F99">
-        <v>3962.838</v>
+        <v>4003.692</v>
       </c>
       <c r="G99">
         <v>1223.5</v>
@@ -9394,37 +9405,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M99">
-        <v>950.1211004678156</v>
+        <v>959.9161633592363</v>
       </c>
       <c r="N99">
-        <v>-959.0877671344823</v>
+        <v>-968.882830025903</v>
       </c>
       <c r="O99">
-        <v>-230.1810641122757</v>
+        <v>-232.5318792062167</v>
       </c>
       <c r="P99">
-        <v>-728.9067030222066</v>
+        <v>-736.3509508196863</v>
       </c>
       <c r="Q99">
-        <v>-1350.106703022207</v>
+        <v>-1357.550950819686</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.735801141450642</v>
+        <v>4.080801712175963</v>
       </c>
       <c r="T99">
-        <v>55.30925474348284</v>
+        <v>82.96388211522427</v>
       </c>
       <c r="U99">
         <v>0.2397577444416894</v>
       </c>
       <c r="V99">
-        <v>-0.002264974432143878</v>
+        <v>-0.00224186244814241</v>
       </c>
       <c r="W99">
-        <v>0.2403007896027583</v>
+        <v>0.2402952483256046</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9432,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>-0.009437393467266242</v>
+        <v>-0.009341093533926648</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9440,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3171053776026118</v>
+        <v>0.3190449550470287</v>
       </c>
       <c r="C100">
-        <v>-1970.821593601146</v>
+        <v>-2017.420755791458</v>
       </c>
       <c r="D100">
-        <v>809.370406398854</v>
+        <v>803.6252442085419</v>
       </c>
       <c r="E100">
-        <v>565.192</v>
+        <v>606.0460000000003</v>
       </c>
       <c r="F100">
-        <v>4003.692</v>
+        <v>4044.546</v>
       </c>
       <c r="G100">
         <v>1223.5</v>
@@ -9476,37 +9487,37 @@
         <v>-8.966666666666697</v>
       </c>
       <c r="M100">
-        <v>959.9161633592363</v>
+        <v>969.7112262506572</v>
       </c>
       <c r="N100">
-        <v>-968.882830025903</v>
+        <v>-978.6778929173239</v>
       </c>
       <c r="O100">
-        <v>-232.5318792062167</v>
+        <v>-234.8826943001577</v>
       </c>
       <c r="P100">
-        <v>-736.3509508196863</v>
+        <v>-743.7951986171662</v>
       </c>
       <c r="Q100">
-        <v>-1357.550950819686</v>
+        <v>-1364.995198617166</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.080801712175963</v>
+        <v>8.115803424351927</v>
       </c>
       <c r="T100">
-        <v>82.96388211522427</v>
+        <v>165.9277642304486</v>
       </c>
       <c r="U100">
         <v>0.2397577444416894</v>
       </c>
       <c r="V100">
-        <v>-0.00224186244814241</v>
+        <v>-0.002219217372908648</v>
       </c>
       <c r="W100">
-        <v>0.2402952483256046</v>
+        <v>0.2402898189934438</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9514,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>-0.009341093533926648</v>
+        <v>-0.009246739053786035</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3190449550470287</v>
-      </c>
-      <c r="C101">
-        <v>-2017.420755791458</v>
-      </c>
-      <c r="D101">
-        <v>803.6252442085419</v>
-      </c>
-      <c r="E101">
-        <v>606.0460000000003</v>
-      </c>
-      <c r="F101">
-        <v>4044.546</v>
-      </c>
-      <c r="G101">
-        <v>1223.5</v>
-      </c>
-      <c r="H101">
-        <v>646.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>-630.1666666666667</v>
-      </c>
-      <c r="K101">
-        <v>-621.2</v>
-      </c>
-      <c r="L101">
-        <v>-8.966666666666697</v>
-      </c>
-      <c r="M101">
-        <v>969.7112262506572</v>
-      </c>
-      <c r="N101">
-        <v>-978.6778929173239</v>
-      </c>
-      <c r="O101">
-        <v>-234.8826943001577</v>
-      </c>
-      <c r="P101">
-        <v>-743.7951986171662</v>
-      </c>
-      <c r="Q101">
-        <v>-1364.995198617166</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.115803424351927</v>
-      </c>
-      <c r="T101">
-        <v>165.9277642304486</v>
-      </c>
-      <c r="U101">
-        <v>0.2397577444416894</v>
-      </c>
-      <c r="V101">
-        <v>-0.002219217372908648</v>
-      </c>
-      <c r="W101">
-        <v>0.2402898189934438</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>-0.009246739053786035</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
